--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -1964,7 +1964,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2480,7 +2480,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3352,7 +3352,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3787,7 +3787,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8717,7 +8717,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14960,10 +14960,10 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="54" customHeight="1">
+    <row r="187" ht="36" customHeight="1">
       <c r="D187" s="38" t="inlineStr">
         <is>
-          <t>追加レコード: `joho_henko_tekiyo_date`=読者情報変更適用日。販売店を変更した行は `hanbaiten_tekiyo_date = joho_henko_tekiyo_date`（同値）、変更しない行は `hanbaiten_tekiyo_date=NULL`。</t>
+          <t>追加レコード: `joho_henko_tekiyo_date`=読者情報変更適用日（販売店・支払方法を含む全変更の唯一の適用日。専用の販売店適用日列は持たない）。</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,6 @@
   zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id, zenkai_dokusya_busu, zenkai_yubin_no,
   zenkai_todofuken_code, zenkai_shikuchoson, zenkai_chome_banchi, zenkai_tatemono_mei,
-  hanbaiten_tekiyo_date,
   created_at, created_by
 )
 VALUES (
@@ -15029,9 +15028,6 @@
   :zougen_hokoku_flg, :shinki_flg, :kaiyaku_flg,
   :zenkai_hanbaiten_id, :zenkai_dokusya_busu, :zenkai_yubin_no,
   :zenkai_todofuken_code, :zenkai_shikuchoson, :zenkai_chome_banchi, :zenkai_tatemono_mei,
-  -- 販売店を変更した行のみ joho_henko_tekiyo_date と同値、変更しない行は NULL
-  -- （v1.3: 販売店適用日は入力列を廃止し joho から導出）
-  CASE WHEN :hanbaiten_changed THEN :joho_henko_tekiyo_date ELSE NULL END,
   NOW(), :user_account_id
 )</t>
         </is>

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1748,23 +1748,86 @@
       <c r="AF6" s="10" t="n"/>
       <c r="AG6" s="11" t="n"/>
     </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07：取込を**紙版/電子版の2モードに分離**。(1) 「購読種別」を Excel テンプレート列から**撤去**（49→48列）し、画面ラジオ（紙版/電子版）で選択して全取込行へ一律適用する **top-level パラメータ `dokusya_shubetsu`（1/2、必須・`@IsIn([1,2])`）** に変更（単一ソース。行データ・selected_columns からは除外）。(2) 3:併読はラジオに出さず取込不可（据え置き）。(3) UPDATE では既存購読者の購読種別が選択値と異なる行を `IMPORT_VALIDATION_ERROR`（field=dokusya_shubetsu）で弾く。(4) 電子版クレカ禁止・電子版メール必須/一意 等の種別依存ルールはラジオ値で判定。</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="49">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
@@ -1773,8 +1836,10 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
@@ -1784,6 +1849,7 @@
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
@@ -1964,7 +2030,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2480,7 +2546,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3352,7 +3418,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3497,7 +3563,7 @@
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータ取込用のテンプレートファイル（49列固定）を生成しダウンロードする。</t>
+          <t>購読者Excelデータ取込用のテンプレートファイル（48列固定）を生成しダウンロードする。</t>
         </is>
       </c>
       <c r="T6" s="10" t="n"/>
@@ -3787,7 +3853,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3911,7 +3977,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータ取込用のテンプレートファイル（49列固定）を生成しダウンロードする。</t>
+          <t>購読者Excelデータ取込用のテンプレートファイル（48列固定）を生成しダウンロードする。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -4819,12 +4885,14 @@
       <c r="AK31" s="11" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="31" t="n">
-        <v>2</v>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>購読種別</t>
+          <t>~~購読種別~~（**列から撤去** v1.5）</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -4838,7 +4906,7 @@
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>購読種別</t>
+          <t>~~購読種別~~</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
@@ -4846,14 +4914,14 @@
       <c r="P32" s="11" t="n"/>
       <c r="Q32" s="17" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu</t>
+          <t>~~dokusya_shubetsu~~</t>
         </is>
       </c>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="11" t="n"/>
       <c r="T32" s="17" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U32" s="10" t="n"/>
@@ -8033,17 +8101,17 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
+    <row r="111" ht="36" customHeight="1">
       <c r="C111" s="38" t="inlineStr">
         <is>
-          <t>1行目に49列のヘッダー文字列を以下の順序で書き込む。</t>
+          <t>1行目に48列のヘッダー文字列を以下の順序で書き込む（購読種別は画面ラジオの単一ソースのため列に含めない・v1.5）。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="162" customHeight="1">
       <c r="D112" s="38" t="inlineStr">
         <is>
-          <t>「ID」「購読種別」「手続種類」「管理支店」「支店」「組合員コード」「購読者苗字（漢字）」「購読者名前（漢字）」「購読者苗字（かな）」「購読者名前（かな）」「購読部数」「新聞単価」「メールアドレス」「メールマガジン」「生年（西暦）」「性別」「郵便番号」「都道府県」「市町村郡」「丁目番地」「マンション・アパート名」「連絡先１」「連絡先２」「郵便番号(配達先)」「都道府県(配達先)」「市町村郡(配達先)」「丁目番地(配達先)」「ﾏﾝｼｮﾝ・ｱﾊﾟｰﾄ名(配達先)」「連絡先１(配達先)」「連絡先２(配達先)」「配達先苗字（漢字）」「配達先名前（漢字）」「配達先苗字（かな）」「配達先名前（かな）」「販売店コード」「郵送区分」「支払方法」「購読料支払サイクル（月数）」「引落口座貯金種目」「引落口座支店コード」「引落口座支店名」「引落口座番号」「引落口座名義」「購読者層分類」「農業者分類」「購読開始日」「購読中止日」「備考」「読者情報変更適用日」</t>
+          <t>「ID」「管理支店」「支店」「組合員コード」「購読者苗字（漢字）」「購読者名前（漢字）」「購読者苗字（かな）」「購読者名前（かな）」「購読部数」「新聞単価」「メールアドレス」「メールマガジン」「生年（西暦）」「性別」「郵便番号」「都道府県」「市町村郡」「丁目番地」「マンション・アパート名」「連絡先１」「連絡先２」「郵便番号(配達先)」「都道府県(配達先)」「市町村郡(配達先)」「丁目番地(配達先)」「ﾏﾝｼｮﾝ・ｱﾊﾟｰﾄ名(配達先)」「連絡先１(配達先)」「連絡先２(配達先)」「配達先苗字（漢字）」「配達先名前（漢字）」「配達先苗字（かな）」「配達先名前（かな）」「販売店コード」「郵送区分」「支払方法」「購読料支払サイクル（月数）」「引落口座貯金種目」「引落口座支店コード」「引落口座支店名」「引落口座番号」「引落口座名義」「購読者層分類」「農業者分類」「購読開始日」「購読中止日」「備考」「読者情報変更適用日」</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK217"/>
+  <dimension ref="A1:AK218"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8717,7 +8785,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9459,7 +9527,7 @@
       <c r="AJ24" s="10" t="n"/>
       <c r="AK24" s="11" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="18" customHeight="1">
       <c r="B25" s="31" t="n">
         <v>1</v>
       </c>
@@ -9510,7 +9578,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>取込モード（`NEW`:新規登録, `UPDATE_ALL`:全項目更新, `UPDATE_PARTIAL`:入力箇所のみ更新）</t>
+          <t>取込モード（`NEW`:新規登録, `UPDATE`:更新）</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -9519,13 +9587,15 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="31" t="n">
-        <v>2</v>
+    <row r="26" ht="54" customHeight="1">
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>selected_columns</t>
+          <t>dokusya_shubetsu</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -9539,7 +9609,7 @@
       <c r="L26" s="11" t="n"/>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N26" s="10" t="n"/>
@@ -9547,7 +9617,7 @@
       <c r="P26" s="11" t="n"/>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="10" t="n"/>
@@ -9561,20 +9631,24 @@
       <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n"/>
-      <c r="Y26" s="17" t="n">
-        <v>1</v>
+      <c r="Y26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z26" s="10" t="n"/>
       <c r="AA26" s="10" t="n"/>
       <c r="AB26" s="11" t="n"/>
-      <c r="AC26" s="17" t="n">
-        <v>49</v>
+      <c r="AC26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>取込対象の列（物理カラム名）配列。新規登録モードでは必須列を必ず含むこと。</t>
+          <t>**購読種別（top-level・v1.5 顧客要件 2026-07）**。画面ラジオで選択し全取込行へ一律適用する単一ソース（Excel の列ではない）。**1:紙版 / 2:電子版 のみ**。3:併読は取込不可（`@IsIn([1,2])`）。</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -9583,13 +9657,13 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>rows</t>
+          <t>selected_columns</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -9632,13 +9706,13 @@
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="11" t="n"/>
       <c r="AC27" s="17" t="n">
-        <v>30000</v>
+        <v>48</v>
       </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>取込データ行の配列。30000件を超える場合は `ROW_LIMIT_EXCEEDED` を返却する。</t>
+          <t>取込対象の列（物理カラム名）配列。新規登録モードでは必須列を必ず含むこと。</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -9649,11 +9723,11 @@
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_id</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -9667,7 +9741,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -9675,38 +9749,34 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="11" t="n"/>
       <c r="T28" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y28" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
       <c r="AB28" s="11" t="n"/>
-      <c r="AC28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC28" s="17" t="n">
+        <v>30000</v>
       </c>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>購読者ID。`UPDATE_ALL` / `UPDATE_PARTIAL` モード（組合員コード未指定時）はキー項目として必須。`NEW` モードは無視する。</t>
+          <t>取込データ行の配列。30000件を超える場合は `ROW_LIMIT_EXCEEDED` を返却する。</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -9715,13 +9785,13 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="54" customHeight="1">
+    <row r="29" ht="36" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_shubetsu</t>
+          <t>→dokusya_id</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -9774,7 +9844,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）。Excel取込みは 1/2 のみ受付。3 はエラー。</t>
+          <t>購読者ID。`UPDATE` モード（組合員コード未指定時）はキー項目として必須。`NEW` モードは無視する。</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -9783,13 +9853,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="72" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>→tetsuzuki_shurui</t>
+          <t>~~→dokusya_shubetsu~~（**列から撤去** v1.5）</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -9803,7 +9873,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -9842,7 +9912,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）</t>
+          <t>購読種別は行データではなく top-level `dokusya_shubetsu`（#1a）で一律指定する（画面ラジオの単一ソース）。UPDATE では既存購読者の購読種別が選択値と異なる行を `IMPORT_VALIDATION_ERROR`（field=dokusya_shubetsu）で弾く。</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -9851,13 +9921,13 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="54" customHeight="1">
+    <row r="31" ht="36" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>→kanri_shiten_code</t>
+          <t>→tetsuzuki_shurui</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -9871,7 +9941,7 @@
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N31" s="10" t="n"/>
@@ -9893,20 +9963,24 @@
       <c r="V31" s="10" t="n"/>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="17" t="n">
-        <v>0</v>
+      <c r="Y31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z31" s="10" t="n"/>
       <c r="AA31" s="10" t="n"/>
       <c r="AB31" s="11" t="n"/>
-      <c r="AC31" s="17" t="n">
-        <v>20</v>
+      <c r="AC31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD31" s="10" t="n"/>
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>管理支店コード。自JA内の m_kanri_shiten.kanri_shiten_code を解決し t_dokusya.kanri_shiten_id へ保存。`NEW` モードは必須。</t>
+          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -9915,13 +9989,13 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="54" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>→shiten_code</t>
+          <t>→kanri_shiten_code</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -9970,7 +10044,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>支店コード。自JA内の m_shiten.shiten_code を解決し t_dokusya.shiten_id へ保存。</t>
+          <t>管理支店コード。自JA内の m_kanri_shiten.kanri_shiten_code を解決し t_dokusya.kanri_shiten_id へ保存。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -9979,13 +10053,13 @@
       <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="11" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="36" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>→kumiaiin_code</t>
+          <t>→shiten_code</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -10034,7 +10108,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>組合員コード。一括中止時にキー項目として必須。</t>
+          <t>支店コード。自JA内の m_shiten.shiten_code を解決し t_dokusya.shiten_id へ保存。</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -10045,11 +10119,11 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>→shimei_sei</t>
+          <t>→kumiaiin_code</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -10092,13 +10166,13 @@
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="11" t="n"/>
       <c r="AC34" s="17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>氏名（姓・漢字）</t>
+          <t>組合員コード。一括中止時にキー項目として必須。</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -10109,11 +10183,11 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>→shimei_mei</t>
+          <t>→shimei_sei</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
@@ -10162,7 +10236,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>氏名（名・漢字）</t>
+          <t>氏名（姓・漢字）</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -10173,11 +10247,11 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>→shimei_kana_sei</t>
+          <t>→shimei_mei</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -10220,13 +10294,13 @@
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="11" t="n"/>
       <c r="AC36" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>氏名かな（姓）</t>
+          <t>氏名（名・漢字）</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -10237,11 +10311,11 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>→shimei_kana_mei</t>
+          <t>→shimei_kana_sei</t>
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -10290,7 +10364,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>氏名かな（名）</t>
+          <t>氏名かな（姓）</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -10299,13 +10373,13 @@
       <c r="AJ37" s="10" t="n"/>
       <c r="AK37" s="11" t="n"/>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_busu</t>
+          <t>→shimei_kana_mei</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -10319,7 +10393,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -10341,24 +10415,20 @@
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n"/>
-      <c r="Y38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z38" s="10" t="n"/>
       <c r="AA38" s="10" t="n"/>
       <c r="AB38" s="11" t="n"/>
-      <c r="AC38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC38" s="17" t="n">
+        <v>100</v>
       </c>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>購読部数。`NEW`：&gt; 0、解約時：= 0。**電子版(2)は 1 固定**（v1.4・UI/一括置換と統一）。</t>
+          <t>氏名かな（名）</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -10369,11 +10439,11 @@
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>→tanka_code</t>
+          <t>→dokusya_busu</t>
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
@@ -10387,7 +10457,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -10409,20 +10479,24 @@
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="11" t="n"/>
-      <c r="Y39" s="17" t="n">
-        <v>0</v>
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z39" s="10" t="n"/>
       <c r="AA39" s="10" t="n"/>
       <c r="AB39" s="11" t="n"/>
-      <c r="AC39" s="17" t="n">
-        <v>10</v>
+      <c r="AC39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD39" s="10" t="n"/>
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>新聞単価コード（m_tanka の tanka_code・tanka_type=1 で解決）。`NEW` モードは必須。</t>
+          <t>購読部数。`NEW`：&gt; 0、解約時：= 0。**電子版(2)は 1 固定**（v1.4・UI/一括置換と統一）。</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -10431,13 +10505,13 @@
       <c r="AJ39" s="10" t="n"/>
       <c r="AK39" s="11" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="36" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>→email</t>
+          <t>→tanka_code</t>
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
@@ -10480,13 +10554,13 @@
       <c r="AA40" s="10" t="n"/>
       <c r="AB40" s="11" t="n"/>
       <c r="AC40" s="17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>メールアドレス。メール形式チェック。</t>
+          <t>新聞単価コード（m_tanka の tanka_code・tanka_type=1 で解決）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -10495,13 +10569,13 @@
       <c r="AJ40" s="10" t="n"/>
       <c r="AK40" s="11" t="n"/>
     </row>
-    <row r="41" ht="36" customHeight="1">
+    <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>→mail_magazine_flg</t>
+          <t>→email</t>
         </is>
       </c>
       <c r="D41" s="10" t="n"/>
@@ -10515,7 +10589,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -10537,24 +10611,20 @@
       <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
       <c r="X41" s="11" t="n"/>
-      <c r="Y41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z41" s="10" t="n"/>
       <c r="AA41" s="10" t="n"/>
       <c r="AB41" s="11" t="n"/>
-      <c r="AC41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC41" s="17" t="n">
+        <v>100</v>
       </c>
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>メールマガジン ※m_code.code_category='MAIL_MAGAZINE_FLG'を参照（0:配信しない, 1:配信する）</t>
+          <t>メールアドレス。メール形式チェック。</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -10563,13 +10633,13 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>→birth_year</t>
+          <t>→mail_magazine_flg</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -10622,7 +10692,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>生年（西暦、1900〜現在年）</t>
+          <t>メールマガジン ※m_code.code_category='MAIL_MAGAZINE_FLG'を参照（0:配信しない, 1:配信する）</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -10631,13 +10701,13 @@
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="43" ht="36" customHeight="1">
+    <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>→gender</t>
+          <t>→birth_year</t>
         </is>
       </c>
       <c r="D43" s="10" t="n"/>
@@ -10690,7 +10760,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>性別 ※m_code.code_category='GENDER'を参照（1:男性, 2:女性, 9:回答しない）。文言（「男性」「女性」「回答しない」）でも取込可。</t>
+          <t>生年（西暦、1900〜現在年）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -10699,13 +10769,13 @@
       <c r="AJ43" s="10" t="n"/>
       <c r="AK43" s="11" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="36" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>→yubin_no</t>
+          <t>→gender</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -10719,7 +10789,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N44" s="10" t="n"/>
@@ -10741,20 +10811,24 @@
       <c r="V44" s="10" t="n"/>
       <c r="W44" s="10" t="n"/>
       <c r="X44" s="11" t="n"/>
-      <c r="Y44" s="17" t="n">
-        <v>7</v>
+      <c r="Y44" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z44" s="10" t="n"/>
       <c r="AA44" s="10" t="n"/>
       <c r="AB44" s="11" t="n"/>
-      <c r="AC44" s="17" t="n">
-        <v>7</v>
+      <c r="AC44" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD44" s="10" t="n"/>
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>郵便番号（ハイフン除去、7桁固定）。`NEW` モードは必須。</t>
+          <t>性別 ※m_code.code_category='GENDER'を参照（1:男性, 2:女性, 9:回答しない）。文言（「男性」「女性」「回答しない」）でも取込可。</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -10765,11 +10839,11 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>→todofuken_code</t>
+          <t>→yubin_no</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -10806,19 +10880,19 @@
       <c r="W45" s="10" t="n"/>
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="11" t="n"/>
       <c r="AC45" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード（2桁）。`NEW` モードは必須。</t>
+          <t>郵便番号（ハイフン除去、7桁固定）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -10829,11 +10903,11 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>→shikuchoson</t>
+          <t>→todofuken_code</t>
         </is>
       </c>
       <c r="D46" s="10" t="n"/>
@@ -10870,19 +10944,19 @@
       <c r="W46" s="10" t="n"/>
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
       <c r="AB46" s="11" t="n"/>
       <c r="AC46" s="17" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AD46" s="10" t="n"/>
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>市町村郡。`NEW` モードは必須。</t>
+          <t>都道府県コード（2桁）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -10893,11 +10967,11 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>→chome_banchi</t>
+          <t>→shikuchoson</t>
         </is>
       </c>
       <c r="D47" s="10" t="n"/>
@@ -10946,7 +11020,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>丁目番地。`NEW` モードは必須。</t>
+          <t>市町村郡。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -10957,11 +11031,11 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>→tatemono_mei</t>
+          <t>→chome_banchi</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -11010,7 +11084,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>マンション・アパート名</t>
+          <t>丁目番地。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -11021,11 +11095,11 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>→renrakusaki_1</t>
+          <t>→tatemono_mei</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -11068,13 +11142,13 @@
       <c r="AA49" s="10" t="n"/>
       <c r="AB49" s="11" t="n"/>
       <c r="AC49" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD49" s="10" t="n"/>
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>連絡先１（数字のみ保存）。`NEW` モードは必須。</t>
+          <t>マンション・アパート名</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -11085,11 +11159,11 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>→renrakusaki_2</t>
+          <t>→renrakusaki_1</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -11138,7 +11212,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>連絡先２（数字のみ保存）</t>
+          <t>連絡先１（数字のみ保存）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -11149,11 +11223,11 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_yubin_no</t>
+          <t>→renrakusaki_2</t>
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
@@ -11196,13 +11270,13 @@
       <c r="AA51" s="10" t="n"/>
       <c r="AB51" s="11" t="n"/>
       <c r="AC51" s="17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>配達先郵便番号</t>
+          <t>連絡先２（数字のみ保存）</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -11213,11 +11287,11 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_todofuken_code</t>
+          <t>→haitatsu_yubin_no</t>
         </is>
       </c>
       <c r="D52" s="10" t="n"/>
@@ -11260,13 +11334,13 @@
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="11" t="n"/>
       <c r="AC52" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD52" s="10" t="n"/>
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>配達先都道府県コード</t>
+          <t>配達先郵便番号</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -11277,11 +11351,11 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shikuchoson</t>
+          <t>→haitatsu_todofuken_code</t>
         </is>
       </c>
       <c r="D53" s="10" t="n"/>
@@ -11324,13 +11398,13 @@
       <c r="AA53" s="10" t="n"/>
       <c r="AB53" s="11" t="n"/>
       <c r="AC53" s="17" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>配達先市町村郡</t>
+          <t>配達先都道府県コード</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -11341,11 +11415,11 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_chome_banchi</t>
+          <t>→haitatsu_shikuchoson</t>
         </is>
       </c>
       <c r="D54" s="10" t="n"/>
@@ -11394,7 +11468,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>配達先丁目番地</t>
+          <t>配達先市町村郡</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -11405,11 +11479,11 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_tatemono_mei</t>
+          <t>→haitatsu_chome_banchi</t>
         </is>
       </c>
       <c r="D55" s="10" t="n"/>
@@ -11458,7 +11532,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>配達先建物名</t>
+          <t>配達先丁目番地</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -11469,11 +11543,11 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_renrakusaki_1</t>
+          <t>→haitatsu_tatemono_mei</t>
         </is>
       </c>
       <c r="D56" s="10" t="n"/>
@@ -11516,13 +11590,13 @@
       <c r="AA56" s="10" t="n"/>
       <c r="AB56" s="11" t="n"/>
       <c r="AC56" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD56" s="10" t="n"/>
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>配達先連絡先１</t>
+          <t>配達先建物名</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -11533,11 +11607,11 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_renrakusaki_2</t>
+          <t>→haitatsu_renrakusaki_1</t>
         </is>
       </c>
       <c r="D57" s="10" t="n"/>
@@ -11586,7 +11660,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>配達先連絡先２</t>
+          <t>配達先連絡先１</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -11597,11 +11671,11 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_sei</t>
+          <t>→haitatsu_renrakusaki_2</t>
         </is>
       </c>
       <c r="D58" s="10" t="n"/>
@@ -11644,13 +11718,13 @@
       <c r="AA58" s="10" t="n"/>
       <c r="AB58" s="11" t="n"/>
       <c r="AC58" s="17" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AD58" s="10" t="n"/>
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名（姓・漢字）</t>
+          <t>配達先連絡先２</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -11661,11 +11735,11 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_mei</t>
+          <t>→haitatsu_shimei_sei</t>
         </is>
       </c>
       <c r="D59" s="10" t="n"/>
@@ -11714,7 +11788,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名（名・漢字）</t>
+          <t>配達先氏名（姓・漢字）</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -11725,11 +11799,11 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_kana_sei</t>
+          <t>→haitatsu_shimei_mei</t>
         </is>
       </c>
       <c r="D60" s="10" t="n"/>
@@ -11772,13 +11846,13 @@
       <c r="AA60" s="10" t="n"/>
       <c r="AB60" s="11" t="n"/>
       <c r="AC60" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD60" s="10" t="n"/>
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名かな（姓）</t>
+          <t>配達先氏名（名・漢字）</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -11789,11 +11863,11 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_kana_mei</t>
+          <t>→haitatsu_shimei_kana_sei</t>
         </is>
       </c>
       <c r="D61" s="10" t="n"/>
@@ -11842,7 +11916,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名かな（名）</t>
+          <t>配達先氏名かな（姓）</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -11851,13 +11925,13 @@
       <c r="AJ61" s="10" t="n"/>
       <c r="AK61" s="11" t="n"/>
     </row>
-    <row r="62" ht="36" customHeight="1">
+    <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>→hanbaiten_code</t>
+          <t>→haitatsu_shimei_kana_mei</t>
         </is>
       </c>
       <c r="D62" s="10" t="n"/>
@@ -11900,13 +11974,13 @@
       <c r="AA62" s="10" t="n"/>
       <c r="AB62" s="11" t="n"/>
       <c r="AC62" s="17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AD62" s="10" t="n"/>
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
         <is>
-          <t>販売店コード（m_hanbaiten の hanbaiten_code で解決）。`NEW` モードは必須。</t>
+          <t>配達先氏名かな（名）</t>
         </is>
       </c>
       <c r="AG62" s="10" t="n"/>
@@ -11917,11 +11991,11 @@
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="B63" s="31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>→yubin_kubun</t>
+          <t>→hanbaiten_code</t>
         </is>
       </c>
       <c r="D63" s="10" t="n"/>
@@ -11964,13 +12038,13 @@
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="11" t="n"/>
       <c r="AC63" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD63" s="10" t="n"/>
       <c r="AE63" s="11" t="n"/>
       <c r="AF63" s="19" t="inlineStr">
         <is>
-          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
+          <t>販売店コード（m_hanbaiten の hanbaiten_code で解決）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG63" s="10" t="n"/>
@@ -11979,13 +12053,13 @@
       <c r="AJ63" s="10" t="n"/>
       <c r="AK63" s="11" t="n"/>
     </row>
-    <row r="64" ht="54" customHeight="1">
+    <row r="64" ht="36" customHeight="1">
       <c r="B64" s="31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>→shiharai_hoho</t>
+          <t>→yubin_kubun</t>
         </is>
       </c>
       <c r="D64" s="10" t="n"/>
@@ -11999,7 +12073,7 @@
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N64" s="10" t="n"/>
@@ -12021,24 +12095,20 @@
       <c r="V64" s="10" t="n"/>
       <c r="W64" s="10" t="n"/>
       <c r="X64" s="11" t="n"/>
-      <c r="Y64" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y64" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z64" s="10" t="n"/>
       <c r="AA64" s="10" t="n"/>
       <c r="AB64" s="11" t="n"/>
-      <c r="AC64" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC64" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="AD64" s="10" t="n"/>
       <c r="AE64" s="11" t="n"/>
       <c r="AF64" s="19" t="inlineStr">
         <is>
-          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1:口座引落, 2:現金集金, 3:振込集金, 4:JA施設等, 5:給与天引き, 6:クレジットカード, 9:その他）。`NEW` モードは必須。</t>
+          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
         </is>
       </c>
       <c r="AG64" s="10" t="n"/>
@@ -12047,13 +12117,13 @@
       <c r="AJ64" s="10" t="n"/>
       <c r="AK64" s="11" t="n"/>
     </row>
-    <row r="65" ht="18" customHeight="1">
+    <row r="65" ht="54" customHeight="1">
       <c r="B65" s="31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>→dokusyaryo_shiharai_cycle</t>
+          <t>→shiharai_hoho</t>
         </is>
       </c>
       <c r="D65" s="10" t="n"/>
@@ -12106,7 +12176,7 @@
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>購読料支払サイクル（月数）</t>
+          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1:口座引落, 2:現金集金, 3:振込集金, 4:JA施設等, 5:給与天引き, 6:クレジットカード, 9:その他）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -12115,13 +12185,13 @@
       <c r="AJ65" s="10" t="n"/>
       <c r="AK65" s="11" t="n"/>
     </row>
-    <row r="66" ht="36" customHeight="1">
+    <row r="66" ht="18" customHeight="1">
       <c r="B66" s="31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>→hikiotoshi_yokin_shubetsu</t>
+          <t>→dokusyaryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="D66" s="10" t="n"/>
@@ -12174,7 +12244,7 @@
       <c r="AE66" s="11" t="n"/>
       <c r="AF66" s="19" t="inlineStr">
         <is>
-          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）。文言（「普通」「当座」）でも取込可。</t>
+          <t>購読料支払サイクル（月数）</t>
         </is>
       </c>
       <c r="AG66" s="10" t="n"/>
@@ -12183,13 +12253,13 @@
       <c r="AJ66" s="10" t="n"/>
       <c r="AK66" s="11" t="n"/>
     </row>
-    <row r="67" ht="18" customHeight="1">
+    <row r="67" ht="36" customHeight="1">
       <c r="B67" s="31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>→bank_branch_code</t>
+          <t>→hikiotoshi_yokin_shubetsu</t>
         </is>
       </c>
       <c r="D67" s="10" t="n"/>
@@ -12203,7 +12273,7 @@
       <c r="L67" s="11" t="n"/>
       <c r="M67" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N67" s="10" t="n"/>
@@ -12225,20 +12295,24 @@
       <c r="V67" s="10" t="n"/>
       <c r="W67" s="10" t="n"/>
       <c r="X67" s="11" t="n"/>
-      <c r="Y67" s="17" t="n">
-        <v>0</v>
+      <c r="Y67" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z67" s="10" t="n"/>
       <c r="AA67" s="10" t="n"/>
       <c r="AB67" s="11" t="n"/>
-      <c r="AC67" s="17" t="n">
-        <v>3</v>
+      <c r="AC67" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD67" s="10" t="n"/>
       <c r="AE67" s="11" t="n"/>
       <c r="AF67" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店コード</t>
+          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）。文言（「普通」「当座」）でも取込可。</t>
         </is>
       </c>
       <c r="AG67" s="10" t="n"/>
@@ -12249,11 +12323,11 @@
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>→bank_branch_name</t>
+          <t>→bank_branch_code</t>
         </is>
       </c>
       <c r="D68" s="10" t="n"/>
@@ -12296,13 +12370,13 @@
       <c r="AA68" s="10" t="n"/>
       <c r="AB68" s="11" t="n"/>
       <c r="AC68" s="17" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="AD68" s="10" t="n"/>
       <c r="AE68" s="11" t="n"/>
       <c r="AF68" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店名</t>
+          <t>引落口座支店コード</t>
         </is>
       </c>
       <c r="AG68" s="10" t="n"/>
@@ -12313,11 +12387,11 @@
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>→hikiotoshi_koza_no</t>
+          <t>→bank_branch_name</t>
         </is>
       </c>
       <c r="D69" s="10" t="n"/>
@@ -12360,13 +12434,13 @@
       <c r="AA69" s="10" t="n"/>
       <c r="AB69" s="11" t="n"/>
       <c r="AC69" s="17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AD69" s="10" t="n"/>
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>引落口座番号</t>
+          <t>引落口座支店名</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -12377,11 +12451,11 @@
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>→hikiotoshi_koza_meigi</t>
+          <t>→hikiotoshi_koza_no</t>
         </is>
       </c>
       <c r="D70" s="10" t="n"/>
@@ -12424,13 +12498,13 @@
       <c r="AA70" s="10" t="n"/>
       <c r="AB70" s="11" t="n"/>
       <c r="AC70" s="17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AD70" s="10" t="n"/>
       <c r="AE70" s="11" t="n"/>
       <c r="AF70" s="19" t="inlineStr">
         <is>
-          <t>引落口座名義（全角カナ→半角カナに変換して保存）</t>
+          <t>引落口座番号</t>
         </is>
       </c>
       <c r="AG70" s="10" t="n"/>
@@ -12441,11 +12515,11 @@
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>→dokusyaso_bunrui</t>
+          <t>→hikiotoshi_koza_meigi</t>
         </is>
       </c>
       <c r="D71" s="10" t="n"/>
@@ -12494,7 +12568,7 @@
       <c r="AE71" s="11" t="n"/>
       <c r="AF71" s="19" t="inlineStr">
         <is>
-          <t>購読者層分類（カンマ区切り）</t>
+          <t>引落口座名義（全角カナ→半角カナに変換して保存）</t>
         </is>
       </c>
       <c r="AG71" s="10" t="n"/>
@@ -12505,11 +12579,11 @@
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>→nogyosya_bunrui</t>
+          <t>→dokusyaso_bunrui</t>
         </is>
       </c>
       <c r="D72" s="10" t="n"/>
@@ -12558,7 +12632,7 @@
       <c r="AE72" s="11" t="n"/>
       <c r="AF72" s="19" t="inlineStr">
         <is>
-          <t>農業者分類（カンマ区切り）</t>
+          <t>購読者層分類（カンマ区切り）</t>
         </is>
       </c>
       <c r="AG72" s="10" t="n"/>
@@ -12569,11 +12643,11 @@
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_kaishi_date</t>
+          <t>→nogyosya_bunrui</t>
         </is>
       </c>
       <c r="D73" s="10" t="n"/>
@@ -12609,22 +12683,20 @@
       <c r="V73" s="10" t="n"/>
       <c r="W73" s="10" t="n"/>
       <c r="X73" s="11" t="n"/>
-      <c r="Y73" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y73" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z73" s="10" t="n"/>
       <c r="AA73" s="10" t="n"/>
       <c r="AB73" s="11" t="n"/>
       <c r="AC73" s="17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD73" s="10" t="n"/>
       <c r="AE73" s="11" t="n"/>
       <c r="AF73" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（YYYY-MM-DD）。`NEW` モードは必須。</t>
+          <t>農業者分類（カンマ区切り）</t>
         </is>
       </c>
       <c r="AG73" s="10" t="n"/>
@@ -12635,11 +12707,11 @@
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_chushi_date</t>
+          <t>→dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="D74" s="10" t="n"/>
@@ -12690,7 +12762,7 @@
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>購読中止日（YYYY-MM-DD）</t>
+          <t>購読開始日（YYYY-MM-DD）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -12701,11 +12773,11 @@
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>→biko</t>
+          <t>→dokusya_chushi_date</t>
         </is>
       </c>
       <c r="D75" s="10" t="n"/>
@@ -12749,16 +12821,14 @@
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="11" t="n"/>
-      <c r="AC75" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC75" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>購読中止日（YYYY-MM-DD）</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -12767,13 +12837,13 @@
       <c r="AJ75" s="10" t="n"/>
       <c r="AK75" s="11" t="n"/>
     </row>
-    <row r="76" ht="36" customHeight="1">
+    <row r="76" ht="18" customHeight="1">
       <c r="B76" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>→joho_henko_tekiyo_date</t>
+          <t>→biko</t>
         </is>
       </c>
       <c r="D76" s="10" t="n"/>
@@ -12817,14 +12887,16 @@
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
       <c r="AB76" s="11" t="n"/>
-      <c r="AC76" s="17" t="n">
-        <v>10</v>
+      <c r="AC76" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>読者情報変更適用日（YYYY-MM-DD）。UPDATE 必須。日付ルールは種別依存（v1.4）：紙版=当日/未来（帳票影響項目は未来のみ）、電子版=当日のみ。</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -12833,88 +12905,90 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1"/>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+    <row r="77" ht="36" customHeight="1">
+      <c r="B77" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>→joho_henko_tekiyo_date</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="11" t="n"/>
+      <c r="Y77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="11" t="n"/>
+      <c r="AC77" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="11" t="n"/>
+      <c r="AF77" s="19" t="inlineStr">
+        <is>
+          <t>読者情報変更適用日（YYYY-MM-DD）。UPDATE 必須。日付ルールは種別依存（v1.4）：紙版=当日/未来（帳票影響項目は未来のみ）、電子版=当日のみ。</t>
+        </is>
+      </c>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1"/>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="19.5" customHeight="1"/>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="B80" s="30" t="inlineStr">
+    <row r="80" ht="19.5" customHeight="1"/>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="B81" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="11" t="n"/>
-      <c r="M80" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="11" t="n"/>
-      <c r="Q80" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="11" t="n"/>
-      <c r="Y80" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="11" t="n"/>
-      <c r="AF80" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D81" s="10" t="n"/>
@@ -12926,29 +13000,33 @@
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="11" t="n"/>
-      <c r="M81" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
       <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q81" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R81" s="10" t="n"/>
       <c r="S81" s="11" t="n"/>
-      <c r="T81" s="17" t="inlineStr"/>
+      <c r="T81" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="11" t="n"/>
-      <c r="Y81" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y81" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z81" s="10" t="n"/>
@@ -12957,9 +13035,9 @@
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
-      <c r="AF81" s="19" t="inlineStr">
-        <is>
-          <t>取込結果サマリ</t>
+      <c r="AF81" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG81" s="10" t="n"/>
@@ -12968,16 +13046,16 @@
       <c r="AJ81" s="10" t="n"/>
       <c r="AK81" s="11" t="n"/>
     </row>
-    <row r="82" ht="36" customHeight="1">
+    <row r="82" ht="18" customHeight="1">
       <c r="B82" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C82" s="39" t="n"/>
-      <c r="D82" s="19" t="inlineStr">
-        <is>
-          <t>import_mode</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n"/>
       <c r="E82" s="10" t="n"/>
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="10" t="n"/>
@@ -12988,7 +13066,7 @@
       <c r="L82" s="11" t="n"/>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N82" s="10" t="n"/>
@@ -13019,7 +13097,7 @@
       <c r="AE82" s="11" t="n"/>
       <c r="AF82" s="19" t="inlineStr">
         <is>
-          <t>実行した取込モード（`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL`）</t>
+          <t>取込結果サマリ</t>
         </is>
       </c>
       <c r="AG82" s="10" t="n"/>
@@ -13028,14 +13106,14 @@
       <c r="AJ82" s="10" t="n"/>
       <c r="AK82" s="11" t="n"/>
     </row>
-    <row r="83" ht="18" customHeight="1">
+    <row r="83" ht="36" customHeight="1">
       <c r="B83" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C83" s="40" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C83" s="39" t="n"/>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t>total_rows</t>
+          <t>import_mode</t>
         </is>
       </c>
       <c r="E83" s="10" t="n"/>
@@ -13048,7 +13126,7 @@
       <c r="L83" s="11" t="n"/>
       <c r="M83" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N83" s="10" t="n"/>
@@ -13079,7 +13157,7 @@
       <c r="AE83" s="11" t="n"/>
       <c r="AF83" s="19" t="inlineStr">
         <is>
-          <t>取込対象行数</t>
+          <t>実行した取込モード（`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL`）</t>
         </is>
       </c>
       <c r="AG83" s="10" t="n"/>
@@ -13090,12 +13168,12 @@
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" s="40" t="n"/>
       <c r="D84" s="19" t="inlineStr">
         <is>
-          <t>created_count</t>
+          <t>total_rows</t>
         </is>
       </c>
       <c r="E84" s="10" t="n"/>
@@ -13139,7 +13217,7 @@
       <c r="AE84" s="11" t="n"/>
       <c r="AF84" s="19" t="inlineStr">
         <is>
-          <t>新規登録件数</t>
+          <t>取込対象行数</t>
         </is>
       </c>
       <c r="AG84" s="10" t="n"/>
@@ -13150,12 +13228,12 @@
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="40" t="n"/>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t>updated_count</t>
+          <t>created_count</t>
         </is>
       </c>
       <c r="E85" s="10" t="n"/>
@@ -13199,7 +13277,7 @@
       <c r="AE85" s="11" t="n"/>
       <c r="AF85" s="19" t="inlineStr">
         <is>
-          <t>更新件数</t>
+          <t>新規登録件数</t>
         </is>
       </c>
       <c r="AG85" s="10" t="n"/>
@@ -13210,12 +13288,12 @@
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="40" t="n"/>
       <c r="D86" s="19" t="inlineStr">
         <is>
-          <t>cancelled_count</t>
+          <t>updated_count</t>
         </is>
       </c>
       <c r="E86" s="10" t="n"/>
@@ -13259,7 +13337,7 @@
       <c r="AE86" s="11" t="n"/>
       <c r="AF86" s="19" t="inlineStr">
         <is>
-          <t>一括中止（解約）件数</t>
+          <t>更新件数</t>
         </is>
       </c>
       <c r="AG86" s="10" t="n"/>
@@ -13270,12 +13348,12 @@
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" s="40" t="n"/>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t>skipped_count</t>
+          <t>cancelled_count</t>
         </is>
       </c>
       <c r="E87" s="10" t="n"/>
@@ -13319,7 +13397,7 @@
       <c r="AE87" s="11" t="n"/>
       <c r="AF87" s="19" t="inlineStr">
         <is>
-          <t>スキップ件数</t>
+          <t>一括中止（解約）件数</t>
         </is>
       </c>
       <c r="AG87" s="10" t="n"/>
@@ -13330,12 +13408,12 @@
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="B88" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" s="40" t="n"/>
       <c r="D88" s="19" t="inlineStr">
         <is>
-          <t>rireki_count</t>
+          <t>skipped_count</t>
         </is>
       </c>
       <c r="E88" s="10" t="n"/>
@@ -13379,7 +13457,7 @@
       <c r="AE88" s="11" t="n"/>
       <c r="AF88" s="19" t="inlineStr">
         <is>
-          <t>履歴テーブル（t_dokusya_rireki）への追加件数</t>
+          <t>スキップ件数</t>
         </is>
       </c>
       <c r="AG88" s="10" t="n"/>
@@ -13390,12 +13468,12 @@
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="B89" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C89" s="41" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="C89" s="40" t="n"/>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t>imported_at</t>
+          <t>rireki_count</t>
         </is>
       </c>
       <c r="E89" s="10" t="n"/>
@@ -13408,7 +13486,7 @@
       <c r="L89" s="11" t="n"/>
       <c r="M89" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N89" s="10" t="n"/>
@@ -13421,11 +13499,7 @@
       </c>
       <c r="R89" s="10" t="n"/>
       <c r="S89" s="11" t="n"/>
-      <c r="T89" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T89" s="17" t="inlineStr"/>
       <c r="U89" s="10" t="n"/>
       <c r="V89" s="10" t="n"/>
       <c r="W89" s="10" t="n"/>
@@ -13443,7 +13517,7 @@
       <c r="AE89" s="11" t="n"/>
       <c r="AF89" s="19" t="inlineStr">
         <is>
-          <t>取込完了日時</t>
+          <t>履歴テーブル（t_dokusya_rireki）への追加件数</t>
         </is>
       </c>
       <c r="AG89" s="10" t="n"/>
@@ -13454,14 +13528,14 @@
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="B90" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="C90" s="41" t="n"/>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>imported_at</t>
+        </is>
+      </c>
       <c r="E90" s="10" t="n"/>
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="10" t="n"/>
@@ -13485,7 +13559,11 @@
       </c>
       <c r="R90" s="10" t="n"/>
       <c r="S90" s="11" t="n"/>
-      <c r="T90" s="17" t="inlineStr"/>
+      <c r="T90" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U90" s="10" t="n"/>
       <c r="V90" s="10" t="n"/>
       <c r="W90" s="10" t="n"/>
@@ -13503,7 +13581,7 @@
       <c r="AE90" s="11" t="n"/>
       <c r="AF90" s="19" t="inlineStr">
         <is>
-          <t>取り込みました。</t>
+          <t>取込完了日時</t>
         </is>
       </c>
       <c r="AG90" s="10" t="n"/>
@@ -13512,24 +13590,83 @@
       <c r="AJ90" s="10" t="n"/>
       <c r="AK90" s="11" t="n"/>
     </row>
-    <row r="91" ht="19.5" customHeight="1"/>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="B92" s="37" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="11" t="n"/>
+      <c r="Q91" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="11" t="n"/>
+      <c r="T91" s="17" t="inlineStr"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="11" t="n"/>
+      <c r="Y91" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="11" t="n"/>
+      <c r="AF91" s="19" t="inlineStr">
+        <is>
+          <t>取り込みました。</t>
+        </is>
+      </c>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1"/>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="B93" s="37" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="409" customHeight="1">
-      <c r="C93" s="19" t="inlineStr">
+    <row r="94" ht="409" customHeight="1">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/dokusya/import
 Content-Type: application/json
 {
   "import_mode": "NEW",
+  "dokusya_shubetsu": 1,
   "selected_columns": [
-    "dokusya_shubetsu",
-    "tetsuzuki_shurui",
     "kanri_shiten_code",
     "shiten_code",
     "shimei_sei",
@@ -13547,8 +13684,6 @@
   ],
   "rows": [
     {
-      "dokusya_shubetsu": 1,
-      "tetsuzuki_shurui": 1,
       "kanri_shiten_code": "KS001",
       "shiten_code": "SH001",
       "shimei_sei": "山田",
@@ -13565,8 +13700,6 @@
       "dokusya_kaishi_date": "2026-05-01"
     },
     {
-      "dokusya_shubetsu": 1,
-      "tetsuzuki_shurui": 1,
       "kanri_shiten_code": "KS001",
       "shiten_code": "SH001",
       "shimei_sei": "鈴木",
@@ -13586,50 +13719,50 @@
 }</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="10" t="n"/>
-      <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
-      <c r="T93" s="10" t="n"/>
-      <c r="U93" s="10" t="n"/>
-      <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
-      <c r="X93" s="10" t="n"/>
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-      <c r="AA93" s="10" t="n"/>
-      <c r="AB93" s="10" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="10" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="10" t="n"/>
-      <c r="AK93" s="11" t="n"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="B95" s="37" t="inlineStr">
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="B96" s="37" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="234" customHeight="1">
-      <c r="C96" s="19" t="inlineStr">
+    <row r="97" ht="234" customHeight="1">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -13646,50 +13779,50 @@
 }</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
-      <c r="P96" s="10" t="n"/>
-      <c r="Q96" s="10" t="n"/>
-      <c r="R96" s="10" t="n"/>
-      <c r="S96" s="10" t="n"/>
-      <c r="T96" s="10" t="n"/>
-      <c r="U96" s="10" t="n"/>
-      <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
-      <c r="X96" s="10" t="n"/>
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-      <c r="AA96" s="10" t="n"/>
-      <c r="AB96" s="10" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="10" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="10" t="n"/>
-      <c r="AK96" s="11" t="n"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="B98" s="37" t="inlineStr">
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="B99" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Validation Error)）</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="144" customHeight="1">
-      <c r="C99" s="19" t="inlineStr">
+    <row r="100" ht="144" customHeight="1">
+      <c r="C100" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -13701,56 +13834,56 @@
 }</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="10" t="n"/>
-      <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
-      <c r="T99" s="10" t="n"/>
-      <c r="U99" s="10" t="n"/>
-      <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
-      <c r="X99" s="10" t="n"/>
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-      <c r="AA99" s="10" t="n"/>
-      <c r="AB99" s="10" t="n"/>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="10" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="10" t="n"/>
-      <c r="AK99" s="11" t="n"/>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="B101" s="37" t="inlineStr">
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="10" t="n"/>
+      <c r="AK100" s="11" t="n"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="B102" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Import Validation Error — 行別エラー)）</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="198" customHeight="1">
-      <c r="C102" s="19" t="inlineStr">
+    <row r="103" ht="198" customHeight="1">
+      <c r="C103" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "IMPORT_VALIDATION_ERROR",
   "message": "Excel取込データにエラーがあります。詳細はerrorsフィールドを確認してください。",
   "errors": [
-    { "row": 2, "field": "dokusya_shubetsu", "message": "購読種別が3:併読のためExcel取込みできません。" },
+    { "row": 2, "field": "dokusya_shubetsu", "message": "選択した購読種別と異なる購読者が含まれています。" },
     { "row": 3, "field": "shiharai_hoho", "message": "電子版かつクレジットカード決済の組み合わせは取込みできません。" },
     { "row": 5, "field": "tanka_code", "message": "指定された新聞単価コードが見つかりません。" },
     { "row": 7, "field": "dokusya_busu", "message": "新規登録の場合、購読部数は0より大きい値を指定してください。" },
@@ -13759,50 +13892,50 @@
 }</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="B104" s="37" t="inlineStr">
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="10" t="n"/>
+      <c r="J103" s="10" t="n"/>
+      <c r="K103" s="10" t="n"/>
+      <c r="L103" s="10" t="n"/>
+      <c r="M103" s="10" t="n"/>
+      <c r="N103" s="10" t="n"/>
+      <c r="O103" s="10" t="n"/>
+      <c r="P103" s="10" t="n"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="10" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
+      <c r="U103" s="10" t="n"/>
+      <c r="V103" s="10" t="n"/>
+      <c r="W103" s="10" t="n"/>
+      <c r="X103" s="10" t="n"/>
+      <c r="Y103" s="10" t="n"/>
+      <c r="Z103" s="10" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="10" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="10" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="10" t="n"/>
+      <c r="AK103" s="11" t="n"/>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="B105" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Row Limit Exceeded)）</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="72" customHeight="1">
-      <c r="C105" s="19" t="inlineStr">
+    <row r="106" ht="72" customHeight="1">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "ROW_LIMIT_EXCEEDED",
@@ -13810,50 +13943,50 @@
 }</t>
         </is>
       </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
-      <c r="B107" s="37" t="inlineStr">
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="10" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="10" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="10" t="n"/>
+      <c r="AK106" s="11" t="n"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="B108" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (File Format Error)）</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="72" customHeight="1">
-      <c r="C108" s="19" t="inlineStr">
+    <row r="109" ht="72" customHeight="1">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FILE_FORMAT_ERROR",
@@ -13861,50 +13994,50 @@
 }</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
-      <c r="P108" s="10" t="n"/>
-      <c r="Q108" s="10" t="n"/>
-      <c r="R108" s="10" t="n"/>
-      <c r="S108" s="10" t="n"/>
-      <c r="T108" s="10" t="n"/>
-      <c r="U108" s="10" t="n"/>
-      <c r="V108" s="10" t="n"/>
-      <c r="W108" s="10" t="n"/>
-      <c r="X108" s="10" t="n"/>
-      <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="10" t="n"/>
-      <c r="AA108" s="10" t="n"/>
-      <c r="AB108" s="10" t="n"/>
-      <c r="AC108" s="10" t="n"/>
-      <c r="AD108" s="10" t="n"/>
-      <c r="AE108" s="10" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
-      <c r="AI108" s="10" t="n"/>
-      <c r="AJ108" s="10" t="n"/>
-      <c r="AK108" s="11" t="n"/>
-    </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="B110" s="37" t="inlineStr">
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="n"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="10" t="n"/>
+      <c r="Y109" s="10" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="10" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="B111" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="72" customHeight="1">
-      <c r="C111" s="19" t="inlineStr">
+    <row r="112" ht="72" customHeight="1">
+      <c r="C112" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -13912,50 +14045,50 @@
 }</t>
         </is>
       </c>
-      <c r="D111" s="10" t="n"/>
-      <c r="E111" s="10" t="n"/>
-      <c r="F111" s="10" t="n"/>
-      <c r="G111" s="10" t="n"/>
-      <c r="H111" s="10" t="n"/>
-      <c r="I111" s="10" t="n"/>
-      <c r="J111" s="10" t="n"/>
-      <c r="K111" s="10" t="n"/>
-      <c r="L111" s="10" t="n"/>
-      <c r="M111" s="10" t="n"/>
-      <c r="N111" s="10" t="n"/>
-      <c r="O111" s="10" t="n"/>
-      <c r="P111" s="10" t="n"/>
-      <c r="Q111" s="10" t="n"/>
-      <c r="R111" s="10" t="n"/>
-      <c r="S111" s="10" t="n"/>
-      <c r="T111" s="10" t="n"/>
-      <c r="U111" s="10" t="n"/>
-      <c r="V111" s="10" t="n"/>
-      <c r="W111" s="10" t="n"/>
-      <c r="X111" s="10" t="n"/>
-      <c r="Y111" s="10" t="n"/>
-      <c r="Z111" s="10" t="n"/>
-      <c r="AA111" s="10" t="n"/>
-      <c r="AB111" s="10" t="n"/>
-      <c r="AC111" s="10" t="n"/>
-      <c r="AD111" s="10" t="n"/>
-      <c r="AE111" s="10" t="n"/>
-      <c r="AF111" s="10" t="n"/>
-      <c r="AG111" s="10" t="n"/>
-      <c r="AH111" s="10" t="n"/>
-      <c r="AI111" s="10" t="n"/>
-      <c r="AJ111" s="10" t="n"/>
-      <c r="AK111" s="11" t="n"/>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="B113" s="37" t="inlineStr">
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="10" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="10" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
+      <c r="U112" s="10" t="n"/>
+      <c r="V112" s="10" t="n"/>
+      <c r="W112" s="10" t="n"/>
+      <c r="X112" s="10" t="n"/>
+      <c r="Y112" s="10" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="10" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="B114" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="72" customHeight="1">
-      <c r="C114" s="19" t="inlineStr">
+    <row r="115" ht="72" customHeight="1">
+      <c r="C115" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -13963,50 +14096,50 @@
 }</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
-      <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
-      <c r="J114" s="10" t="n"/>
-      <c r="K114" s="10" t="n"/>
-      <c r="L114" s="10" t="n"/>
-      <c r="M114" s="10" t="n"/>
-      <c r="N114" s="10" t="n"/>
-      <c r="O114" s="10" t="n"/>
-      <c r="P114" s="10" t="n"/>
-      <c r="Q114" s="10" t="n"/>
-      <c r="R114" s="10" t="n"/>
-      <c r="S114" s="10" t="n"/>
-      <c r="T114" s="10" t="n"/>
-      <c r="U114" s="10" t="n"/>
-      <c r="V114" s="10" t="n"/>
-      <c r="W114" s="10" t="n"/>
-      <c r="X114" s="10" t="n"/>
-      <c r="Y114" s="10" t="n"/>
-      <c r="Z114" s="10" t="n"/>
-      <c r="AA114" s="10" t="n"/>
-      <c r="AB114" s="10" t="n"/>
-      <c r="AC114" s="10" t="n"/>
-      <c r="AD114" s="10" t="n"/>
-      <c r="AE114" s="10" t="n"/>
-      <c r="AF114" s="10" t="n"/>
-      <c r="AG114" s="10" t="n"/>
-      <c r="AH114" s="10" t="n"/>
-      <c r="AI114" s="10" t="n"/>
-      <c r="AJ114" s="10" t="n"/>
-      <c r="AK114" s="11" t="n"/>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="B116" s="37" t="inlineStr">
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
+      <c r="V115" s="10" t="n"/>
+      <c r="W115" s="10" t="n"/>
+      <c r="X115" s="10" t="n"/>
+      <c r="Y115" s="10" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="B117" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden (DataScope Violation)）</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="72" customHeight="1">
-      <c r="C117" s="19" t="inlineStr">
+    <row r="118" ht="72" customHeight="1">
+      <c r="C118" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATA_SCOPE_VIOLATION",
@@ -14014,50 +14147,50 @@
 }</t>
         </is>
       </c>
-      <c r="D117" s="10" t="n"/>
-      <c r="E117" s="10" t="n"/>
-      <c r="F117" s="10" t="n"/>
-      <c r="G117" s="10" t="n"/>
-      <c r="H117" s="10" t="n"/>
-      <c r="I117" s="10" t="n"/>
-      <c r="J117" s="10" t="n"/>
-      <c r="K117" s="10" t="n"/>
-      <c r="L117" s="10" t="n"/>
-      <c r="M117" s="10" t="n"/>
-      <c r="N117" s="10" t="n"/>
-      <c r="O117" s="10" t="n"/>
-      <c r="P117" s="10" t="n"/>
-      <c r="Q117" s="10" t="n"/>
-      <c r="R117" s="10" t="n"/>
-      <c r="S117" s="10" t="n"/>
-      <c r="T117" s="10" t="n"/>
-      <c r="U117" s="10" t="n"/>
-      <c r="V117" s="10" t="n"/>
-      <c r="W117" s="10" t="n"/>
-      <c r="X117" s="10" t="n"/>
-      <c r="Y117" s="10" t="n"/>
-      <c r="Z117" s="10" t="n"/>
-      <c r="AA117" s="10" t="n"/>
-      <c r="AB117" s="10" t="n"/>
-      <c r="AC117" s="10" t="n"/>
-      <c r="AD117" s="10" t="n"/>
-      <c r="AE117" s="10" t="n"/>
-      <c r="AF117" s="10" t="n"/>
-      <c r="AG117" s="10" t="n"/>
-      <c r="AH117" s="10" t="n"/>
-      <c r="AI117" s="10" t="n"/>
-      <c r="AJ117" s="10" t="n"/>
-      <c r="AK117" s="11" t="n"/>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="B119" s="37" t="inlineStr">
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="10" t="n"/>
+      <c r="J118" s="10" t="n"/>
+      <c r="K118" s="10" t="n"/>
+      <c r="L118" s="10" t="n"/>
+      <c r="M118" s="10" t="n"/>
+      <c r="N118" s="10" t="n"/>
+      <c r="O118" s="10" t="n"/>
+      <c r="P118" s="10" t="n"/>
+      <c r="Q118" s="10" t="n"/>
+      <c r="R118" s="10" t="n"/>
+      <c r="S118" s="10" t="n"/>
+      <c r="T118" s="10" t="n"/>
+      <c r="U118" s="10" t="n"/>
+      <c r="V118" s="10" t="n"/>
+      <c r="W118" s="10" t="n"/>
+      <c r="X118" s="10" t="n"/>
+      <c r="Y118" s="10" t="n"/>
+      <c r="Z118" s="10" t="n"/>
+      <c r="AA118" s="10" t="n"/>
+      <c r="AB118" s="10" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="10" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="10" t="n"/>
+      <c r="AK118" s="11" t="n"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="B120" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="72" customHeight="1">
-      <c r="C120" s="19" t="inlineStr">
+    <row r="121" ht="72" customHeight="1">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -14065,284 +14198,284 @@
 }</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n"/>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="10" t="n"/>
-      <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
-      <c r="J120" s="10" t="n"/>
-      <c r="K120" s="10" t="n"/>
-      <c r="L120" s="10" t="n"/>
-      <c r="M120" s="10" t="n"/>
-      <c r="N120" s="10" t="n"/>
-      <c r="O120" s="10" t="n"/>
-      <c r="P120" s="10" t="n"/>
-      <c r="Q120" s="10" t="n"/>
-      <c r="R120" s="10" t="n"/>
-      <c r="S120" s="10" t="n"/>
-      <c r="T120" s="10" t="n"/>
-      <c r="U120" s="10" t="n"/>
-      <c r="V120" s="10" t="n"/>
-      <c r="W120" s="10" t="n"/>
-      <c r="X120" s="10" t="n"/>
-      <c r="Y120" s="10" t="n"/>
-      <c r="Z120" s="10" t="n"/>
-      <c r="AA120" s="10" t="n"/>
-      <c r="AB120" s="10" t="n"/>
-      <c r="AC120" s="10" t="n"/>
-      <c r="AD120" s="10" t="n"/>
-      <c r="AE120" s="10" t="n"/>
-      <c r="AF120" s="10" t="n"/>
-      <c r="AG120" s="10" t="n"/>
-      <c r="AH120" s="10" t="n"/>
-      <c r="AI120" s="10" t="n"/>
-      <c r="AJ120" s="10" t="n"/>
-      <c r="AK120" s="11" t="n"/>
-    </row>
-    <row r="122" ht="19.5" customHeight="1"/>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="27" t="inlineStr">
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="n"/>
+      <c r="J121" s="10" t="n"/>
+      <c r="K121" s="10" t="n"/>
+      <c r="L121" s="10" t="n"/>
+      <c r="M121" s="10" t="n"/>
+      <c r="N121" s="10" t="n"/>
+      <c r="O121" s="10" t="n"/>
+      <c r="P121" s="10" t="n"/>
+      <c r="Q121" s="10" t="n"/>
+      <c r="R121" s="10" t="n"/>
+      <c r="S121" s="10" t="n"/>
+      <c r="T121" s="10" t="n"/>
+      <c r="U121" s="10" t="n"/>
+      <c r="V121" s="10" t="n"/>
+      <c r="W121" s="10" t="n"/>
+      <c r="X121" s="10" t="n"/>
+      <c r="Y121" s="10" t="n"/>
+      <c r="Z121" s="10" t="n"/>
+      <c r="AA121" s="10" t="n"/>
+      <c r="AB121" s="10" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="10" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="10" t="n"/>
+      <c r="AK121" s="11" t="n"/>
+    </row>
+    <row r="123" ht="19.5" customHeight="1"/>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="54" customHeight="1">
-      <c r="B124" s="42" t="inlineStr">
+    <row r="125" ht="54" customHeight="1">
+      <c r="B125" s="42" t="inlineStr">
         <is>
           <t>※ 4.4 データ取込実行 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C124" s="10" t="n"/>
-      <c r="D124" s="10" t="n"/>
-      <c r="E124" s="10" t="n"/>
-      <c r="F124" s="10" t="n"/>
-      <c r="G124" s="10" t="n"/>
-      <c r="H124" s="10" t="n"/>
-      <c r="I124" s="10" t="n"/>
-      <c r="J124" s="10" t="n"/>
-      <c r="K124" s="10" t="n"/>
-      <c r="L124" s="10" t="n"/>
-      <c r="M124" s="10" t="n"/>
-      <c r="N124" s="10" t="n"/>
-      <c r="O124" s="10" t="n"/>
-      <c r="P124" s="10" t="n"/>
-      <c r="Q124" s="10" t="n"/>
-      <c r="R124" s="10" t="n"/>
-      <c r="S124" s="10" t="n"/>
-      <c r="T124" s="10" t="n"/>
-      <c r="U124" s="10" t="n"/>
-      <c r="V124" s="10" t="n"/>
-      <c r="W124" s="10" t="n"/>
-      <c r="X124" s="10" t="n"/>
-      <c r="Y124" s="10" t="n"/>
-      <c r="Z124" s="10" t="n"/>
-      <c r="AA124" s="10" t="n"/>
-      <c r="AB124" s="10" t="n"/>
-      <c r="AC124" s="10" t="n"/>
-      <c r="AD124" s="10" t="n"/>
-      <c r="AE124" s="10" t="n"/>
-      <c r="AF124" s="10" t="n"/>
-      <c r="AG124" s="10" t="n"/>
-      <c r="AH124" s="10" t="n"/>
-      <c r="AI124" s="10" t="n"/>
-      <c r="AJ124" s="10" t="n"/>
-      <c r="AK124" s="11" t="n"/>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="B125" s="27" t="inlineStr">
+      <c r="C125" s="10" t="n"/>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="10" t="n"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
+      <c r="H125" s="10" t="n"/>
+      <c r="I125" s="10" t="n"/>
+      <c r="J125" s="10" t="n"/>
+      <c r="K125" s="10" t="n"/>
+      <c r="L125" s="10" t="n"/>
+      <c r="M125" s="10" t="n"/>
+      <c r="N125" s="10" t="n"/>
+      <c r="O125" s="10" t="n"/>
+      <c r="P125" s="10" t="n"/>
+      <c r="Q125" s="10" t="n"/>
+      <c r="R125" s="10" t="n"/>
+      <c r="S125" s="10" t="n"/>
+      <c r="T125" s="10" t="n"/>
+      <c r="U125" s="10" t="n"/>
+      <c r="V125" s="10" t="n"/>
+      <c r="W125" s="10" t="n"/>
+      <c r="X125" s="10" t="n"/>
+      <c r="Y125" s="10" t="n"/>
+      <c r="Z125" s="10" t="n"/>
+      <c r="AA125" s="10" t="n"/>
+      <c r="AB125" s="10" t="n"/>
+      <c r="AC125" s="10" t="n"/>
+      <c r="AD125" s="10" t="n"/>
+      <c r="AE125" s="10" t="n"/>
+      <c r="AF125" s="10" t="n"/>
+      <c r="AG125" s="10" t="n"/>
+      <c r="AH125" s="10" t="n"/>
+      <c r="AI125" s="10" t="n"/>
+      <c r="AJ125" s="10" t="n"/>
+      <c r="AK125" s="11" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="B126" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="C126" s="38" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="C127" s="38" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="36" customHeight="1">
-      <c r="D127" s="38" t="inlineStr">
+    <row r="128" ht="36" customHeight="1">
+      <c r="D128" s="38" t="inlineStr">
         <is>
           <t>`import_mode`：必須、`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL` のいずれか</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="D128" s="38" t="inlineStr">
-        <is>
-          <t>`selected_columns`：必須、配列、1件以上</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="D129" s="38" t="inlineStr">
         <is>
-          <t>`rows`：必須、配列、1件以上、30000件以下</t>
+          <t>`selected_columns`：必須、配列、1件以上</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="D130" s="38" t="inlineStr">
         <is>
+          <t>`rows`：必須、配列、1件以上、30000件以下</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="D131" s="38" t="inlineStr">
+        <is>
           <t>各行 `rows[i]` の検証（`selected_columns` 対象列のみ）：</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="36" customHeight="1">
-      <c r="C131" s="38" t="inlineStr">
+    <row r="132" ht="36" customHeight="1">
+      <c r="C132" s="38" t="inlineStr">
         <is>
           <t>業務ルールチェック（v1.4 — 共通モジュール `dokusya-shubetsu.rules.ts` に集約し UI/取込/一括置換で統一）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="36" customHeight="1">
-      <c r="D132" s="38" t="inlineStr">
-        <is>
-          <t>併読（`dokusya_shubetsu`=3）は取込不可 → エラー「購読種別が3:併読のためExcel取込みできません。」（第3システム同期のため読取専用）</t>
         </is>
       </c>
     </row>
     <row r="133" ht="36" customHeight="1">
       <c r="D133" s="38" t="inlineStr">
         <is>
+          <t>併読（`dokusya_shubetsu`=3）は取込不可 → エラー「購読種別が3:併読のためExcel取込みできません。」（第3システム同期のため読取専用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="D134" s="38" t="inlineStr">
+        <is>
           <t>電子版（`dokusya_shubetsu`=2）かつクレジットカード決済（`shiharai_hoho`=6）の組み合わせは取込不可 → エラー（理由：電子版かつクレカ決済取込不可のため。読取専用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="D134" s="38" t="inlineStr">
-        <is>
-          <t>電子版の購読部数=1（上記 `dokusya_busu` 参照）</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="D135" s="38" t="inlineStr">
         <is>
+          <t>電子版の購読部数=1（上記 `dokusya_busu` 参照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="D136" s="38" t="inlineStr">
+        <is>
           <t>種別依存の適用日ルール（上記 `joho_henko_tekiyo_date` 参照）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="36" customHeight="1">
-      <c r="C136" s="38" t="inlineStr">
-        <is>
-          <t>トップレベルのバリデーションエラー：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
     <row r="137" ht="36" customHeight="1">
       <c r="C137" s="38" t="inlineStr">
         <is>
+          <t>トップレベルのバリデーションエラー：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="C138" s="38" t="inlineStr">
+        <is>
           <t>行レベルのバリデーションエラー：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（row番号含む。最大10件まで返却）</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="B138" s="27" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="B139" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="C139" s="38" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="C140" s="38" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="C141" s="38" t="inlineStr">
         <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="C142" s="38" t="inlineStr">
+        <is>
           <t>必要権限: `dokusya.import`</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="36" customHeight="1">
-      <c r="C142" s="38" t="inlineStr">
+    <row r="143" ht="36" customHeight="1">
+      <c r="C143" s="38" t="inlineStr">
         <is>
           <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="C143" s="38" t="inlineStr">
+    <row r="144" ht="18" customHeight="1">
+      <c r="C144" s="38" t="inlineStr">
         <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="36" customHeight="1">
-      <c r="C144" s="38" t="inlineStr">
+    <row r="145" ht="36" customHeight="1">
+      <c r="C145" s="38" t="inlineStr">
         <is>
           <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="D145" s="38" t="inlineStr">
-        <is>
-          <t>中央会：自中央会管轄JAのみ取込可能。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="D146" s="38" t="inlineStr">
         <is>
-          <t>JA本店：自JAのみ取込可能。</t>
+          <t>中央会：自中央会管轄JAのみ取込可能。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="D147" s="38" t="inlineStr">
         <is>
+          <t>JA本店：自JAのみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="D148" s="38" t="inlineStr">
+        <is>
           <t>JA管理支店：自管理支店配下のみ取込可能。</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="36" customHeight="1">
-      <c r="C148" s="38" t="inlineStr">
+    <row r="149" ht="36" customHeight="1">
+      <c r="C149" s="38" t="inlineStr">
         <is>
           <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="B149" s="27" t="inlineStr">
+    <row r="150" ht="18" customHeight="1">
+      <c r="B150" s="27" t="inlineStr">
         <is>
           <t>4.3 事前チェック（参照整合性・重複）</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="C150" s="38" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（`ja_id` / `kanri_shiten_id`）。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="C151" s="38" t="inlineStr">
         <is>
+          <t>ログインユーザーのスコープを取得する（`ja_id` / `kanri_shiten_id`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="C152" s="38" t="inlineStr">
+        <is>
           <t>DBとの整合性チェックをバッチで実行する。</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="108" customHeight="1">
-      <c r="C152" s="42" t="inlineStr">
+    <row r="153" ht="108" customHeight="1">
+      <c r="C153" s="42" t="inlineStr">
         <is>
           <t>SELECT tanka_id, tanka_code
 FROM m_tanka
@@ -14352,50 +14485,50 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D152" s="10" t="n"/>
-      <c r="E152" s="10" t="n"/>
-      <c r="F152" s="10" t="n"/>
-      <c r="G152" s="10" t="n"/>
-      <c r="H152" s="10" t="n"/>
-      <c r="I152" s="10" t="n"/>
-      <c r="J152" s="10" t="n"/>
-      <c r="K152" s="10" t="n"/>
-      <c r="L152" s="10" t="n"/>
-      <c r="M152" s="10" t="n"/>
-      <c r="N152" s="10" t="n"/>
-      <c r="O152" s="10" t="n"/>
-      <c r="P152" s="10" t="n"/>
-      <c r="Q152" s="10" t="n"/>
-      <c r="R152" s="10" t="n"/>
-      <c r="S152" s="10" t="n"/>
-      <c r="T152" s="10" t="n"/>
-      <c r="U152" s="10" t="n"/>
-      <c r="V152" s="10" t="n"/>
-      <c r="W152" s="10" t="n"/>
-      <c r="X152" s="10" t="n"/>
-      <c r="Y152" s="10" t="n"/>
-      <c r="Z152" s="10" t="n"/>
-      <c r="AA152" s="10" t="n"/>
-      <c r="AB152" s="10" t="n"/>
-      <c r="AC152" s="10" t="n"/>
-      <c r="AD152" s="10" t="n"/>
-      <c r="AE152" s="10" t="n"/>
-      <c r="AF152" s="10" t="n"/>
-      <c r="AG152" s="10" t="n"/>
-      <c r="AH152" s="10" t="n"/>
-      <c r="AI152" s="10" t="n"/>
-      <c r="AJ152" s="10" t="n"/>
-      <c r="AK152" s="11" t="n"/>
-    </row>
-    <row r="153" ht="36" customHeight="1">
-      <c r="C153" s="38" t="inlineStr">
+      <c r="D153" s="10" t="n"/>
+      <c r="E153" s="10" t="n"/>
+      <c r="F153" s="10" t="n"/>
+      <c r="G153" s="10" t="n"/>
+      <c r="H153" s="10" t="n"/>
+      <c r="I153" s="10" t="n"/>
+      <c r="J153" s="10" t="n"/>
+      <c r="K153" s="10" t="n"/>
+      <c r="L153" s="10" t="n"/>
+      <c r="M153" s="10" t="n"/>
+      <c r="N153" s="10" t="n"/>
+      <c r="O153" s="10" t="n"/>
+      <c r="P153" s="10" t="n"/>
+      <c r="Q153" s="10" t="n"/>
+      <c r="R153" s="10" t="n"/>
+      <c r="S153" s="10" t="n"/>
+      <c r="T153" s="10" t="n"/>
+      <c r="U153" s="10" t="n"/>
+      <c r="V153" s="10" t="n"/>
+      <c r="W153" s="10" t="n"/>
+      <c r="X153" s="10" t="n"/>
+      <c r="Y153" s="10" t="n"/>
+      <c r="Z153" s="10" t="n"/>
+      <c r="AA153" s="10" t="n"/>
+      <c r="AB153" s="10" t="n"/>
+      <c r="AC153" s="10" t="n"/>
+      <c r="AD153" s="10" t="n"/>
+      <c r="AE153" s="10" t="n"/>
+      <c r="AF153" s="10" t="n"/>
+      <c r="AG153" s="10" t="n"/>
+      <c r="AH153" s="10" t="n"/>
+      <c r="AI153" s="10" t="n"/>
+      <c r="AJ153" s="10" t="n"/>
+      <c r="AK153" s="11" t="n"/>
+    </row>
+    <row r="154" ht="36" customHeight="1">
+      <c r="C154" s="38" t="inlineStr">
         <is>
           <t>未ヒットの `tanka_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='tanka_code'）</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="90" customHeight="1">
-      <c r="C154" s="42" t="inlineStr">
+    <row r="155" ht="90" customHeight="1">
+      <c r="C155" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, hanbaiten_code
 FROM m_hanbaiten
@@ -14404,50 +14537,50 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D154" s="10" t="n"/>
-      <c r="E154" s="10" t="n"/>
-      <c r="F154" s="10" t="n"/>
-      <c r="G154" s="10" t="n"/>
-      <c r="H154" s="10" t="n"/>
-      <c r="I154" s="10" t="n"/>
-      <c r="J154" s="10" t="n"/>
-      <c r="K154" s="10" t="n"/>
-      <c r="L154" s="10" t="n"/>
-      <c r="M154" s="10" t="n"/>
-      <c r="N154" s="10" t="n"/>
-      <c r="O154" s="10" t="n"/>
-      <c r="P154" s="10" t="n"/>
-      <c r="Q154" s="10" t="n"/>
-      <c r="R154" s="10" t="n"/>
-      <c r="S154" s="10" t="n"/>
-      <c r="T154" s="10" t="n"/>
-      <c r="U154" s="10" t="n"/>
-      <c r="V154" s="10" t="n"/>
-      <c r="W154" s="10" t="n"/>
-      <c r="X154" s="10" t="n"/>
-      <c r="Y154" s="10" t="n"/>
-      <c r="Z154" s="10" t="n"/>
-      <c r="AA154" s="10" t="n"/>
-      <c r="AB154" s="10" t="n"/>
-      <c r="AC154" s="10" t="n"/>
-      <c r="AD154" s="10" t="n"/>
-      <c r="AE154" s="10" t="n"/>
-      <c r="AF154" s="10" t="n"/>
-      <c r="AG154" s="10" t="n"/>
-      <c r="AH154" s="10" t="n"/>
-      <c r="AI154" s="10" t="n"/>
-      <c r="AJ154" s="10" t="n"/>
-      <c r="AK154" s="11" t="n"/>
-    </row>
-    <row r="155" ht="36" customHeight="1">
-      <c r="C155" s="38" t="inlineStr">
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="10" t="n"/>
+      <c r="F155" s="10" t="n"/>
+      <c r="G155" s="10" t="n"/>
+      <c r="H155" s="10" t="n"/>
+      <c r="I155" s="10" t="n"/>
+      <c r="J155" s="10" t="n"/>
+      <c r="K155" s="10" t="n"/>
+      <c r="L155" s="10" t="n"/>
+      <c r="M155" s="10" t="n"/>
+      <c r="N155" s="10" t="n"/>
+      <c r="O155" s="10" t="n"/>
+      <c r="P155" s="10" t="n"/>
+      <c r="Q155" s="10" t="n"/>
+      <c r="R155" s="10" t="n"/>
+      <c r="S155" s="10" t="n"/>
+      <c r="T155" s="10" t="n"/>
+      <c r="U155" s="10" t="n"/>
+      <c r="V155" s="10" t="n"/>
+      <c r="W155" s="10" t="n"/>
+      <c r="X155" s="10" t="n"/>
+      <c r="Y155" s="10" t="n"/>
+      <c r="Z155" s="10" t="n"/>
+      <c r="AA155" s="10" t="n"/>
+      <c r="AB155" s="10" t="n"/>
+      <c r="AC155" s="10" t="n"/>
+      <c r="AD155" s="10" t="n"/>
+      <c r="AE155" s="10" t="n"/>
+      <c r="AF155" s="10" t="n"/>
+      <c r="AG155" s="10" t="n"/>
+      <c r="AH155" s="10" t="n"/>
+      <c r="AI155" s="10" t="n"/>
+      <c r="AJ155" s="10" t="n"/>
+      <c r="AK155" s="11" t="n"/>
+    </row>
+    <row r="156" ht="36" customHeight="1">
+      <c r="C156" s="38" t="inlineStr">
         <is>
           <t>未ヒットの `hanbaiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='hanbaiten_code'）</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="198" customHeight="1">
-      <c r="C156" s="42" t="inlineStr">
+    <row r="157" ht="198" customHeight="1">
+      <c r="C157" s="42" t="inlineStr">
         <is>
           <t>SELECT kanri_shiten_id, kanri_shiten_code
 FROM m_kanri_shiten
@@ -14461,71 +14594,71 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D156" s="10" t="n"/>
-      <c r="E156" s="10" t="n"/>
-      <c r="F156" s="10" t="n"/>
-      <c r="G156" s="10" t="n"/>
-      <c r="H156" s="10" t="n"/>
-      <c r="I156" s="10" t="n"/>
-      <c r="J156" s="10" t="n"/>
-      <c r="K156" s="10" t="n"/>
-      <c r="L156" s="10" t="n"/>
-      <c r="M156" s="10" t="n"/>
-      <c r="N156" s="10" t="n"/>
-      <c r="O156" s="10" t="n"/>
-      <c r="P156" s="10" t="n"/>
-      <c r="Q156" s="10" t="n"/>
-      <c r="R156" s="10" t="n"/>
-      <c r="S156" s="10" t="n"/>
-      <c r="T156" s="10" t="n"/>
-      <c r="U156" s="10" t="n"/>
-      <c r="V156" s="10" t="n"/>
-      <c r="W156" s="10" t="n"/>
-      <c r="X156" s="10" t="n"/>
-      <c r="Y156" s="10" t="n"/>
-      <c r="Z156" s="10" t="n"/>
-      <c r="AA156" s="10" t="n"/>
-      <c r="AB156" s="10" t="n"/>
-      <c r="AC156" s="10" t="n"/>
-      <c r="AD156" s="10" t="n"/>
-      <c r="AE156" s="10" t="n"/>
-      <c r="AF156" s="10" t="n"/>
-      <c r="AG156" s="10" t="n"/>
-      <c r="AH156" s="10" t="n"/>
-      <c r="AI156" s="10" t="n"/>
-      <c r="AJ156" s="10" t="n"/>
-      <c r="AK156" s="11" t="n"/>
-    </row>
-    <row r="157" ht="36" customHeight="1">
-      <c r="C157" s="38" t="inlineStr">
-        <is>
-          <t>未ヒットの `kanri_shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='kanri_shiten_code'）</t>
-        </is>
-      </c>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="10" t="n"/>
+      <c r="F157" s="10" t="n"/>
+      <c r="G157" s="10" t="n"/>
+      <c r="H157" s="10" t="n"/>
+      <c r="I157" s="10" t="n"/>
+      <c r="J157" s="10" t="n"/>
+      <c r="K157" s="10" t="n"/>
+      <c r="L157" s="10" t="n"/>
+      <c r="M157" s="10" t="n"/>
+      <c r="N157" s="10" t="n"/>
+      <c r="O157" s="10" t="n"/>
+      <c r="P157" s="10" t="n"/>
+      <c r="Q157" s="10" t="n"/>
+      <c r="R157" s="10" t="n"/>
+      <c r="S157" s="10" t="n"/>
+      <c r="T157" s="10" t="n"/>
+      <c r="U157" s="10" t="n"/>
+      <c r="V157" s="10" t="n"/>
+      <c r="W157" s="10" t="n"/>
+      <c r="X157" s="10" t="n"/>
+      <c r="Y157" s="10" t="n"/>
+      <c r="Z157" s="10" t="n"/>
+      <c r="AA157" s="10" t="n"/>
+      <c r="AB157" s="10" t="n"/>
+      <c r="AC157" s="10" t="n"/>
+      <c r="AD157" s="10" t="n"/>
+      <c r="AE157" s="10" t="n"/>
+      <c r="AF157" s="10" t="n"/>
+      <c r="AG157" s="10" t="n"/>
+      <c r="AH157" s="10" t="n"/>
+      <c r="AI157" s="10" t="n"/>
+      <c r="AJ157" s="10" t="n"/>
+      <c r="AK157" s="11" t="n"/>
     </row>
     <row r="158" ht="36" customHeight="1">
       <c r="C158" s="38" t="inlineStr">
         <is>
-          <t>未ヒットの `shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='shiten_code'）</t>
+          <t>未ヒットの `kanri_shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='kanri_shiten_code'）</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="C159" s="38" t="inlineStr">
         <is>
-          <t>未ヒット：`IMPORT_VALIDATION_ERROR` + errors（row, field）</t>
+          <t>未ヒットの `shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='shiten_code'）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="36" customHeight="1">
       <c r="C160" s="38" t="inlineStr">
         <is>
+          <t>未ヒット：`IMPORT_VALIDATION_ERROR` + errors（row, field）</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="36" customHeight="1">
+      <c r="C161" s="38" t="inlineStr">
+        <is>
           <t>JA_KANRI_SHITEN の場合、自管理支店 ID と一致しない `kanri_shiten_id` も DataScope 違反とする。</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="162" customHeight="1">
-      <c r="C161" s="42" t="inlineStr">
+    <row r="162" ht="162" customHeight="1">
+      <c r="C162" s="42" t="inlineStr">
         <is>
           <t>-- UPDATE_ALL / UPDATE_PARTIAL モード（dokusya_id をキー、または kumiaiin_code をキー）
 SELECT dokusya_id, kumiaiin_code, ja_id, kanri_shiten_id
@@ -14538,99 +14671,99 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D161" s="10" t="n"/>
-      <c r="E161" s="10" t="n"/>
-      <c r="F161" s="10" t="n"/>
-      <c r="G161" s="10" t="n"/>
-      <c r="H161" s="10" t="n"/>
-      <c r="I161" s="10" t="n"/>
-      <c r="J161" s="10" t="n"/>
-      <c r="K161" s="10" t="n"/>
-      <c r="L161" s="10" t="n"/>
-      <c r="M161" s="10" t="n"/>
-      <c r="N161" s="10" t="n"/>
-      <c r="O161" s="10" t="n"/>
-      <c r="P161" s="10" t="n"/>
-      <c r="Q161" s="10" t="n"/>
-      <c r="R161" s="10" t="n"/>
-      <c r="S161" s="10" t="n"/>
-      <c r="T161" s="10" t="n"/>
-      <c r="U161" s="10" t="n"/>
-      <c r="V161" s="10" t="n"/>
-      <c r="W161" s="10" t="n"/>
-      <c r="X161" s="10" t="n"/>
-      <c r="Y161" s="10" t="n"/>
-      <c r="Z161" s="10" t="n"/>
-      <c r="AA161" s="10" t="n"/>
-      <c r="AB161" s="10" t="n"/>
-      <c r="AC161" s="10" t="n"/>
-      <c r="AD161" s="10" t="n"/>
-      <c r="AE161" s="10" t="n"/>
-      <c r="AF161" s="10" t="n"/>
-      <c r="AG161" s="10" t="n"/>
-      <c r="AH161" s="10" t="n"/>
-      <c r="AI161" s="10" t="n"/>
-      <c r="AJ161" s="10" t="n"/>
-      <c r="AK161" s="11" t="n"/>
-    </row>
-    <row r="162" ht="54" customHeight="1">
-      <c r="C162" s="38" t="inlineStr">
+      <c r="D162" s="10" t="n"/>
+      <c r="E162" s="10" t="n"/>
+      <c r="F162" s="10" t="n"/>
+      <c r="G162" s="10" t="n"/>
+      <c r="H162" s="10" t="n"/>
+      <c r="I162" s="10" t="n"/>
+      <c r="J162" s="10" t="n"/>
+      <c r="K162" s="10" t="n"/>
+      <c r="L162" s="10" t="n"/>
+      <c r="M162" s="10" t="n"/>
+      <c r="N162" s="10" t="n"/>
+      <c r="O162" s="10" t="n"/>
+      <c r="P162" s="10" t="n"/>
+      <c r="Q162" s="10" t="n"/>
+      <c r="R162" s="10" t="n"/>
+      <c r="S162" s="10" t="n"/>
+      <c r="T162" s="10" t="n"/>
+      <c r="U162" s="10" t="n"/>
+      <c r="V162" s="10" t="n"/>
+      <c r="W162" s="10" t="n"/>
+      <c r="X162" s="10" t="n"/>
+      <c r="Y162" s="10" t="n"/>
+      <c r="Z162" s="10" t="n"/>
+      <c r="AA162" s="10" t="n"/>
+      <c r="AB162" s="10" t="n"/>
+      <c r="AC162" s="10" t="n"/>
+      <c r="AD162" s="10" t="n"/>
+      <c r="AE162" s="10" t="n"/>
+      <c r="AF162" s="10" t="n"/>
+      <c r="AG162" s="10" t="n"/>
+      <c r="AH162" s="10" t="n"/>
+      <c r="AI162" s="10" t="n"/>
+      <c r="AJ162" s="10" t="n"/>
+      <c r="AK162" s="11" t="n"/>
+    </row>
+    <row r="163" ht="54" customHeight="1">
+      <c r="C163" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_ALL` / `UPDATE_PARTIAL` モード：未ヒットの行は「存在しない」エラー → `IMPORT_VALIDATION_ERROR` + errors（row, field='dokusya_id' または 'kumiaiin_code'）</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="36" customHeight="1">
-      <c r="C163" s="38" t="inlineStr">
+    <row r="164" ht="36" customHeight="1">
+      <c r="C164" s="38" t="inlineStr">
         <is>
           <t>一括中止（`tetsuzuki_shurui`=0）：`kumiaiin_code` をキーに既存購読者を取得する。未ヒットはエラーとする。</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="54" customHeight="1">
-      <c r="C164" s="38" t="inlineStr">
+    <row r="165" ht="54" customHeight="1">
+      <c r="C165" s="38" t="inlineStr">
         <is>
           <t>取得した既存購読者の `kanri_shiten_id` が JA_KANRI_SHITEN の自管理支店と一致しない場合：DataScope 違反 → HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="36" customHeight="1">
-      <c r="C165" s="38" t="inlineStr">
+    <row r="166" ht="36" customHeight="1">
+      <c r="C166" s="38" t="inlineStr">
         <is>
           <t>事前チェックエラーが存在する場合：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（最大10件）を返却し、以降の処理を中断する。</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="B166" s="27" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="B167" s="27" t="inlineStr">
         <is>
           <t>4.4 データ取込実行（トランザクション）</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="C167" s="38" t="inlineStr">
-        <is>
-          <t>DBトランザクションを開始する。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="C168" s="38" t="inlineStr">
         <is>
-          <t>取込モードに応じて以下の SQL を行ごとに実行する。</t>
+          <t>DBトランザクションを開始する。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="C169" s="38" t="inlineStr">
         <is>
+          <t>取込モードに応じて以下の SQL を行ごとに実行する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="C170" s="38" t="inlineStr">
+        <is>
           <t>1件でもエラーが発生した場合はトランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="409" customHeight="1">
-      <c r="C170" s="42" t="inlineStr">
+    <row r="171" ht="409" customHeight="1">
+      <c r="C171" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya (
   ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -14669,78 +14802,78 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D170" s="10" t="n"/>
-      <c r="E170" s="10" t="n"/>
-      <c r="F170" s="10" t="n"/>
-      <c r="G170" s="10" t="n"/>
-      <c r="H170" s="10" t="n"/>
-      <c r="I170" s="10" t="n"/>
-      <c r="J170" s="10" t="n"/>
-      <c r="K170" s="10" t="n"/>
-      <c r="L170" s="10" t="n"/>
-      <c r="M170" s="10" t="n"/>
-      <c r="N170" s="10" t="n"/>
-      <c r="O170" s="10" t="n"/>
-      <c r="P170" s="10" t="n"/>
-      <c r="Q170" s="10" t="n"/>
-      <c r="R170" s="10" t="n"/>
-      <c r="S170" s="10" t="n"/>
-      <c r="T170" s="10" t="n"/>
-      <c r="U170" s="10" t="n"/>
-      <c r="V170" s="10" t="n"/>
-      <c r="W170" s="10" t="n"/>
-      <c r="X170" s="10" t="n"/>
-      <c r="Y170" s="10" t="n"/>
-      <c r="Z170" s="10" t="n"/>
-      <c r="AA170" s="10" t="n"/>
-      <c r="AB170" s="10" t="n"/>
-      <c r="AC170" s="10" t="n"/>
-      <c r="AD170" s="10" t="n"/>
-      <c r="AE170" s="10" t="n"/>
-      <c r="AF170" s="10" t="n"/>
-      <c r="AG170" s="10" t="n"/>
-      <c r="AH170" s="10" t="n"/>
-      <c r="AI170" s="10" t="n"/>
-      <c r="AJ170" s="10" t="n"/>
-      <c r="AK170" s="11" t="n"/>
-    </row>
-    <row r="171" ht="36" customHeight="1">
-      <c r="C171" s="38" t="inlineStr">
-        <is>
-          <t>`selected_columns` に含まれない列はデフォルト値（空文字 / NULL / 0 / false）を設定する。</t>
-        </is>
-      </c>
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="10" t="n"/>
+      <c r="F171" s="10" t="n"/>
+      <c r="G171" s="10" t="n"/>
+      <c r="H171" s="10" t="n"/>
+      <c r="I171" s="10" t="n"/>
+      <c r="J171" s="10" t="n"/>
+      <c r="K171" s="10" t="n"/>
+      <c r="L171" s="10" t="n"/>
+      <c r="M171" s="10" t="n"/>
+      <c r="N171" s="10" t="n"/>
+      <c r="O171" s="10" t="n"/>
+      <c r="P171" s="10" t="n"/>
+      <c r="Q171" s="10" t="n"/>
+      <c r="R171" s="10" t="n"/>
+      <c r="S171" s="10" t="n"/>
+      <c r="T171" s="10" t="n"/>
+      <c r="U171" s="10" t="n"/>
+      <c r="V171" s="10" t="n"/>
+      <c r="W171" s="10" t="n"/>
+      <c r="X171" s="10" t="n"/>
+      <c r="Y171" s="10" t="n"/>
+      <c r="Z171" s="10" t="n"/>
+      <c r="AA171" s="10" t="n"/>
+      <c r="AB171" s="10" t="n"/>
+      <c r="AC171" s="10" t="n"/>
+      <c r="AD171" s="10" t="n"/>
+      <c r="AE171" s="10" t="n"/>
+      <c r="AF171" s="10" t="n"/>
+      <c r="AG171" s="10" t="n"/>
+      <c r="AH171" s="10" t="n"/>
+      <c r="AI171" s="10" t="n"/>
+      <c r="AJ171" s="10" t="n"/>
+      <c r="AK171" s="11" t="n"/>
     </row>
     <row r="172" ht="36" customHeight="1">
       <c r="C172" s="38" t="inlineStr">
         <is>
+          <t>`selected_columns` に含まれない列はデフォルト値（空文字 / NULL / 0 / false）を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="36" customHeight="1">
+      <c r="C173" s="38" t="inlineStr">
+        <is>
           <t>`shoki_dokusya_kaishi_date` には `dokusya_kaishi_date` と同じ値を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="72" customHeight="1">
-      <c r="C173" s="38" t="inlineStr">
+    <row r="174" ht="72" customHeight="1">
+      <c r="C174" s="38" t="inlineStr">
         <is>
           <t>`haitatsu_same_flg`（v1.2 顧客要件 2026-06）：**取込列「購読者情報と同じ」で明示指定された値を採用する**（BE は推論しない）。TRUE のとき配達先項目は未入力でよく、配達先住所は購読者住所を使用する。列が未指定（空欄）の行のみ、従来どおり「配達先項目が全て未入力→TRUE / いずれか入力あり→FALSE」で導出する。</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="54" customHeight="1">
-      <c r="C174" s="38" t="inlineStr">
+    <row r="175" ht="54" customHeight="1">
+      <c r="C175" s="38" t="inlineStr">
         <is>
           <t>既存購読者を `dokusya_id` または `kumiaiin_code` で検索し、`selected_columns` 対象外の項目も含めて全項目を更新する（未選択列は NULL / 空文字 / 0 で上書き）。</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="162" customHeight="1">
-      <c r="C175" s="38" t="inlineStr">
+    <row r="176" ht="162" customHeight="1">
+      <c r="C176" s="38" t="inlineStr">
         <is>
           <t>ただし NOT NULL の FK・参照列（kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id / dokusya_shubetsu / tetsuzuki_shurui / shiharai_hoho）は空欄上書きで制約違反になるため `COALESCE(:値, 既存値)` で既存値を維持する（UPDATE モードでは FK コードは任意入力＝存在時のみ検証）。`dokusya_kaishi_date` も空欄時は既存値を維持。`shoki_dokusya_kaishi_date`（初回購読開始日）は不変のため SET から除外する。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="409" customHeight="1">
-      <c r="C176" s="42" t="inlineStr">
+    <row r="177" ht="409" customHeight="1">
+      <c r="C177" s="42" t="inlineStr">
         <is>
           <t>-- 更新前データ取得（操作ログ用）
 SELECT * FROM t_dokusya
@@ -14807,64 +14940,64 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D176" s="10" t="n"/>
-      <c r="E176" s="10" t="n"/>
-      <c r="F176" s="10" t="n"/>
-      <c r="G176" s="10" t="n"/>
-      <c r="H176" s="10" t="n"/>
-      <c r="I176" s="10" t="n"/>
-      <c r="J176" s="10" t="n"/>
-      <c r="K176" s="10" t="n"/>
-      <c r="L176" s="10" t="n"/>
-      <c r="M176" s="10" t="n"/>
-      <c r="N176" s="10" t="n"/>
-      <c r="O176" s="10" t="n"/>
-      <c r="P176" s="10" t="n"/>
-      <c r="Q176" s="10" t="n"/>
-      <c r="R176" s="10" t="n"/>
-      <c r="S176" s="10" t="n"/>
-      <c r="T176" s="10" t="n"/>
-      <c r="U176" s="10" t="n"/>
-      <c r="V176" s="10" t="n"/>
-      <c r="W176" s="10" t="n"/>
-      <c r="X176" s="10" t="n"/>
-      <c r="Y176" s="10" t="n"/>
-      <c r="Z176" s="10" t="n"/>
-      <c r="AA176" s="10" t="n"/>
-      <c r="AB176" s="10" t="n"/>
-      <c r="AC176" s="10" t="n"/>
-      <c r="AD176" s="10" t="n"/>
-      <c r="AE176" s="10" t="n"/>
-      <c r="AF176" s="10" t="n"/>
-      <c r="AG176" s="10" t="n"/>
-      <c r="AH176" s="10" t="n"/>
-      <c r="AI176" s="10" t="n"/>
-      <c r="AJ176" s="10" t="n"/>
-      <c r="AK176" s="11" t="n"/>
-    </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="C177" s="38" t="inlineStr">
+      <c r="D177" s="10" t="n"/>
+      <c r="E177" s="10" t="n"/>
+      <c r="F177" s="10" t="n"/>
+      <c r="G177" s="10" t="n"/>
+      <c r="H177" s="10" t="n"/>
+      <c r="I177" s="10" t="n"/>
+      <c r="J177" s="10" t="n"/>
+      <c r="K177" s="10" t="n"/>
+      <c r="L177" s="10" t="n"/>
+      <c r="M177" s="10" t="n"/>
+      <c r="N177" s="10" t="n"/>
+      <c r="O177" s="10" t="n"/>
+      <c r="P177" s="10" t="n"/>
+      <c r="Q177" s="10" t="n"/>
+      <c r="R177" s="10" t="n"/>
+      <c r="S177" s="10" t="n"/>
+      <c r="T177" s="10" t="n"/>
+      <c r="U177" s="10" t="n"/>
+      <c r="V177" s="10" t="n"/>
+      <c r="W177" s="10" t="n"/>
+      <c r="X177" s="10" t="n"/>
+      <c r="Y177" s="10" t="n"/>
+      <c r="Z177" s="10" t="n"/>
+      <c r="AA177" s="10" t="n"/>
+      <c r="AB177" s="10" t="n"/>
+      <c r="AC177" s="10" t="n"/>
+      <c r="AD177" s="10" t="n"/>
+      <c r="AE177" s="10" t="n"/>
+      <c r="AF177" s="10" t="n"/>
+      <c r="AG177" s="10" t="n"/>
+      <c r="AH177" s="10" t="n"/>
+      <c r="AI177" s="10" t="n"/>
+      <c r="AJ177" s="10" t="n"/>
+      <c r="AK177" s="11" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="C178" s="38" t="inlineStr">
         <is>
           <t>`selected_columns` に含まれる列のみ更新する。未選択列は既存値を維持する。</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="108" customHeight="1">
-      <c r="C178" s="38" t="inlineStr">
+    <row r="179" ht="108" customHeight="1">
+      <c r="C179" s="38" t="inlineStr">
         <is>
           <t>更新可能カラムは取込テンプレートの全項目（email / 住所 / 配達先 / 口座 / 単価・販売店 等を含む）。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。NOT NULL の FK・参照列は `COALESCE(:値, 既存値)` で既存値を維持する。`dokusya_id` はキーのため更新しない。</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="C179" s="38" t="inlineStr">
+    <row r="180" ht="18" customHeight="1">
+      <c r="C180" s="38" t="inlineStr">
         <is>
           <t>動的に SET 句を構築する（擬似コード）。</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="288" customHeight="1">
-      <c r="C180" s="42" t="inlineStr">
+    <row r="181" ht="288" customHeight="1">
+      <c r="C181" s="42" t="inlineStr">
         <is>
           <t>-- 更新前データ取得（操作ログ用）
 SELECT * FROM t_dokusya
@@ -14883,106 +15016,106 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D180" s="10" t="n"/>
-      <c r="E180" s="10" t="n"/>
-      <c r="F180" s="10" t="n"/>
-      <c r="G180" s="10" t="n"/>
-      <c r="H180" s="10" t="n"/>
-      <c r="I180" s="10" t="n"/>
-      <c r="J180" s="10" t="n"/>
-      <c r="K180" s="10" t="n"/>
-      <c r="L180" s="10" t="n"/>
-      <c r="M180" s="10" t="n"/>
-      <c r="N180" s="10" t="n"/>
-      <c r="O180" s="10" t="n"/>
-      <c r="P180" s="10" t="n"/>
-      <c r="Q180" s="10" t="n"/>
-      <c r="R180" s="10" t="n"/>
-      <c r="S180" s="10" t="n"/>
-      <c r="T180" s="10" t="n"/>
-      <c r="U180" s="10" t="n"/>
-      <c r="V180" s="10" t="n"/>
-      <c r="W180" s="10" t="n"/>
-      <c r="X180" s="10" t="n"/>
-      <c r="Y180" s="10" t="n"/>
-      <c r="Z180" s="10" t="n"/>
-      <c r="AA180" s="10" t="n"/>
-      <c r="AB180" s="10" t="n"/>
-      <c r="AC180" s="10" t="n"/>
-      <c r="AD180" s="10" t="n"/>
-      <c r="AE180" s="10" t="n"/>
-      <c r="AF180" s="10" t="n"/>
-      <c r="AG180" s="10" t="n"/>
-      <c r="AH180" s="10" t="n"/>
-      <c r="AI180" s="10" t="n"/>
-      <c r="AJ180" s="10" t="n"/>
-      <c r="AK180" s="11" t="n"/>
-    </row>
-    <row r="181" ht="54" customHeight="1">
-      <c r="C181" s="38" t="inlineStr">
+      <c r="D181" s="10" t="n"/>
+      <c r="E181" s="10" t="n"/>
+      <c r="F181" s="10" t="n"/>
+      <c r="G181" s="10" t="n"/>
+      <c r="H181" s="10" t="n"/>
+      <c r="I181" s="10" t="n"/>
+      <c r="J181" s="10" t="n"/>
+      <c r="K181" s="10" t="n"/>
+      <c r="L181" s="10" t="n"/>
+      <c r="M181" s="10" t="n"/>
+      <c r="N181" s="10" t="n"/>
+      <c r="O181" s="10" t="n"/>
+      <c r="P181" s="10" t="n"/>
+      <c r="Q181" s="10" t="n"/>
+      <c r="R181" s="10" t="n"/>
+      <c r="S181" s="10" t="n"/>
+      <c r="T181" s="10" t="n"/>
+      <c r="U181" s="10" t="n"/>
+      <c r="V181" s="10" t="n"/>
+      <c r="W181" s="10" t="n"/>
+      <c r="X181" s="10" t="n"/>
+      <c r="Y181" s="10" t="n"/>
+      <c r="Z181" s="10" t="n"/>
+      <c r="AA181" s="10" t="n"/>
+      <c r="AB181" s="10" t="n"/>
+      <c r="AC181" s="10" t="n"/>
+      <c r="AD181" s="10" t="n"/>
+      <c r="AE181" s="10" t="n"/>
+      <c r="AF181" s="10" t="n"/>
+      <c r="AG181" s="10" t="n"/>
+      <c r="AH181" s="10" t="n"/>
+      <c r="AI181" s="10" t="n"/>
+      <c r="AJ181" s="10" t="n"/>
+      <c r="AK181" s="11" t="n"/>
+    </row>
+    <row r="182" ht="54" customHeight="1">
+      <c r="C182" s="38" t="inlineStr">
         <is>
           <t>**本処理は廃止**。手続種類カラムを取込テンプレートから削除し、取込で解約は扱わない。NEW は `tetsuzuki_shurui=1`（新規）固定、UPDATE は手続種類を変更しない（既存値を維持）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="36" customHeight="1">
-      <c r="C182" s="38" t="inlineStr">
-        <is>
-          <t>解約は SCR-011/013 の編集運用と同じく「解約予定日（購読中止日）」の登録のみとし、実際の解約処理（購読部数=0・解約状態）は日次バッチが担う（バッチ未実装）。</t>
         </is>
       </c>
     </row>
     <row r="183" ht="36" customHeight="1">
       <c r="C183" s="38" t="inlineStr">
         <is>
+          <t>解約は SCR-011/013 の編集運用と同じく「解約予定日（購読中止日）」の登録のみとし、実際の解約処理（購読部数=0・解約状態）は日次バッチが担う（バッチ未実装）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="36" customHeight="1">
+      <c r="C184" s="38" t="inlineStr">
+        <is>
           <t>取込モードに関わらず、取り込んだデータ件数分のレコードを `t_dokusya_rireki` に追加する。</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="C184" s="38" t="inlineStr">
+    <row r="185" ht="18" customHeight="1">
+      <c r="C185" s="38" t="inlineStr">
         <is>
           <t>履歴No（`rireki_no`）は `t_dokusya.rireki_no` の値を引き継ぐ。</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="36" customHeight="1">
-      <c r="C185" s="38" t="inlineStr">
+    <row r="186" ht="36" customHeight="1">
+      <c r="C186" s="38" t="inlineStr">
         <is>
           <t>`saishin_data_flg` は新規追加レコードのみ TRUE、既存履歴は FALSE に更新する。</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="90" customHeight="1">
-      <c r="C186" s="38" t="inlineStr">
+    <row r="187" ht="90" customHeight="1">
+      <c r="C187" s="38" t="inlineStr">
         <is>
           <t>**v1.3（顧客要件 2026-07）— UPDATE は1更新1レコード**: 販売店適用日を廃止し、適用日は `joho_henko_tekiyo_date` に統一。情報変更（購読部数/住所等）と販売店変更が同一行で同時に起きても履歴は **1件**にまとめる（UI編集 SCR-011/013・一括置換 SCR-015 と同一ロジック・共通実装）。旧 v1.2 の「適用日順に2件分割」は廃止。</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="36" customHeight="1">
-      <c r="D187" s="38" t="inlineStr">
-        <is>
-          <t>追加レコード: `joho_henko_tekiyo_date`=読者情報変更適用日（販売店・支払方法を含む全変更の唯一の適用日。専用の販売店適用日列は持たない）。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="36" customHeight="1">
       <c r="D188" s="38" t="inlineStr">
         <is>
-          <t>`saishin_data_flg` は当日基準の再計算（recomputeMaster）で確定。`zenkai_*` / `zougen_hokoku_flg` は直前状態との差分で算出。</t>
+          <t>追加レコード: `joho_henko_tekiyo_date`=読者情報変更適用日（販売店・支払方法を含む全変更の唯一の適用日。専用の販売店適用日列は持たない）。</t>
         </is>
       </c>
     </row>
     <row r="189" ht="36" customHeight="1">
       <c r="D189" s="38" t="inlineStr">
         <is>
+          <t>`saishin_data_flg` は当日基準の再計算（recomputeMaster）で確定。`zenkai_*` / `zougen_hokoku_flg` は直前状態との差分で算出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="36" customHeight="1">
+      <c r="D190" s="38" t="inlineStr">
+        <is>
           <t>取込で解約は扱わないため `kaiyaku_flg` は常に FALSE。`shinki_flg` は NEW かつ手続種類=新規(1) のときのみ TRUE。</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="409" customHeight="1">
-      <c r="C190" s="42" t="inlineStr">
+    <row r="191" ht="409" customHeight="1">
+      <c r="C191" s="42" t="inlineStr">
         <is>
           <t>-- 既存履歴の saishin_data_flg を FALSE に更新
 UPDATE t_dokusya_rireki
@@ -15032,92 +15165,92 @@
 )</t>
         </is>
       </c>
-      <c r="D190" s="10" t="n"/>
-      <c r="E190" s="10" t="n"/>
-      <c r="F190" s="10" t="n"/>
-      <c r="G190" s="10" t="n"/>
-      <c r="H190" s="10" t="n"/>
-      <c r="I190" s="10" t="n"/>
-      <c r="J190" s="10" t="n"/>
-      <c r="K190" s="10" t="n"/>
-      <c r="L190" s="10" t="n"/>
-      <c r="M190" s="10" t="n"/>
-      <c r="N190" s="10" t="n"/>
-      <c r="O190" s="10" t="n"/>
-      <c r="P190" s="10" t="n"/>
-      <c r="Q190" s="10" t="n"/>
-      <c r="R190" s="10" t="n"/>
-      <c r="S190" s="10" t="n"/>
-      <c r="T190" s="10" t="n"/>
-      <c r="U190" s="10" t="n"/>
-      <c r="V190" s="10" t="n"/>
-      <c r="W190" s="10" t="n"/>
-      <c r="X190" s="10" t="n"/>
-      <c r="Y190" s="10" t="n"/>
-      <c r="Z190" s="10" t="n"/>
-      <c r="AA190" s="10" t="n"/>
-      <c r="AB190" s="10" t="n"/>
-      <c r="AC190" s="10" t="n"/>
-      <c r="AD190" s="10" t="n"/>
-      <c r="AE190" s="10" t="n"/>
-      <c r="AF190" s="10" t="n"/>
-      <c r="AG190" s="10" t="n"/>
-      <c r="AH190" s="10" t="n"/>
-      <c r="AI190" s="10" t="n"/>
-      <c r="AJ190" s="10" t="n"/>
-      <c r="AK190" s="11" t="n"/>
-    </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="C191" s="38" t="inlineStr">
-        <is>
-          <t>`shinki_flg`：新規購読 / 解約→再購読 の場合 TRUE</t>
-        </is>
-      </c>
+      <c r="D191" s="10" t="n"/>
+      <c r="E191" s="10" t="n"/>
+      <c r="F191" s="10" t="n"/>
+      <c r="G191" s="10" t="n"/>
+      <c r="H191" s="10" t="n"/>
+      <c r="I191" s="10" t="n"/>
+      <c r="J191" s="10" t="n"/>
+      <c r="K191" s="10" t="n"/>
+      <c r="L191" s="10" t="n"/>
+      <c r="M191" s="10" t="n"/>
+      <c r="N191" s="10" t="n"/>
+      <c r="O191" s="10" t="n"/>
+      <c r="P191" s="10" t="n"/>
+      <c r="Q191" s="10" t="n"/>
+      <c r="R191" s="10" t="n"/>
+      <c r="S191" s="10" t="n"/>
+      <c r="T191" s="10" t="n"/>
+      <c r="U191" s="10" t="n"/>
+      <c r="V191" s="10" t="n"/>
+      <c r="W191" s="10" t="n"/>
+      <c r="X191" s="10" t="n"/>
+      <c r="Y191" s="10" t="n"/>
+      <c r="Z191" s="10" t="n"/>
+      <c r="AA191" s="10" t="n"/>
+      <c r="AB191" s="10" t="n"/>
+      <c r="AC191" s="10" t="n"/>
+      <c r="AD191" s="10" t="n"/>
+      <c r="AE191" s="10" t="n"/>
+      <c r="AF191" s="10" t="n"/>
+      <c r="AG191" s="10" t="n"/>
+      <c r="AH191" s="10" t="n"/>
+      <c r="AI191" s="10" t="n"/>
+      <c r="AJ191" s="10" t="n"/>
+      <c r="AK191" s="11" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="C192" s="38" t="inlineStr">
         <is>
-          <t>`kaiyaku_flg`：購読中→解約 の場合 TRUE</t>
+          <t>`shinki_flg`：新規購読 / 解約→再購読 の場合 TRUE</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="C193" s="38" t="inlineStr">
         <is>
+          <t>`kaiyaku_flg`：購読中→解約 の場合 TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="C194" s="38" t="inlineStr">
+        <is>
           <t>`zougen_hokoku_flg`：購読部数や販売店等の増減報告対象項目が変化した場合 TRUE</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="36" customHeight="1">
-      <c r="C194" s="38" t="inlineStr">
+    <row r="195" ht="36" customHeight="1">
+      <c r="C195" s="38" t="inlineStr">
         <is>
           <t>`zenkai_*` 項目：UPDATE系の場合、更新前の値を格納する（初回履歴・NEWモードは NULL）。</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="54" customHeight="1">
-      <c r="C195" s="38" t="inlineStr">
+    <row r="196" ht="54" customHeight="1">
+      <c r="C196" s="38" t="inlineStr">
         <is>
           <t>実行中に DB 制約違反等が発生した場合：トランザクションを即時ロールバックし、HTTP 400 (`IMPORT_VALIDATION_ERROR`) または HTTP 500 (`INTERNAL_SERVER_ERROR`) を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="B196" s="27" t="inlineStr">
+    <row r="197" ht="18" customHeight="1">
+      <c r="B197" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="C197" s="38" t="inlineStr">
+    <row r="198" ht="18" customHeight="1">
+      <c r="C198" s="38" t="inlineStr">
         <is>
           <t>全行の処理が完了した後、一括取込操作の操作ログを取込バッチ単位で1件記録する（行単位ではない）。</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="144" customHeight="1">
-      <c r="C198" s="42" t="inlineStr">
+    <row r="199" ht="144" customHeight="1">
+      <c r="C199" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -15129,106 +15262,106 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D198" s="10" t="n"/>
-      <c r="E198" s="10" t="n"/>
-      <c r="F198" s="10" t="n"/>
-      <c r="G198" s="10" t="n"/>
-      <c r="H198" s="10" t="n"/>
-      <c r="I198" s="10" t="n"/>
-      <c r="J198" s="10" t="n"/>
-      <c r="K198" s="10" t="n"/>
-      <c r="L198" s="10" t="n"/>
-      <c r="M198" s="10" t="n"/>
-      <c r="N198" s="10" t="n"/>
-      <c r="O198" s="10" t="n"/>
-      <c r="P198" s="10" t="n"/>
-      <c r="Q198" s="10" t="n"/>
-      <c r="R198" s="10" t="n"/>
-      <c r="S198" s="10" t="n"/>
-      <c r="T198" s="10" t="n"/>
-      <c r="U198" s="10" t="n"/>
-      <c r="V198" s="10" t="n"/>
-      <c r="W198" s="10" t="n"/>
-      <c r="X198" s="10" t="n"/>
-      <c r="Y198" s="10" t="n"/>
-      <c r="Z198" s="10" t="n"/>
-      <c r="AA198" s="10" t="n"/>
-      <c r="AB198" s="10" t="n"/>
-      <c r="AC198" s="10" t="n"/>
-      <c r="AD198" s="10" t="n"/>
-      <c r="AE198" s="10" t="n"/>
-      <c r="AF198" s="10" t="n"/>
-      <c r="AG198" s="10" t="n"/>
-      <c r="AH198" s="10" t="n"/>
-      <c r="AI198" s="10" t="n"/>
-      <c r="AJ198" s="10" t="n"/>
-      <c r="AK198" s="11" t="n"/>
-    </row>
-    <row r="199" ht="36" customHeight="1">
-      <c r="C199" s="38" t="inlineStr">
+      <c r="D199" s="10" t="n"/>
+      <c r="E199" s="10" t="n"/>
+      <c r="F199" s="10" t="n"/>
+      <c r="G199" s="10" t="n"/>
+      <c r="H199" s="10" t="n"/>
+      <c r="I199" s="10" t="n"/>
+      <c r="J199" s="10" t="n"/>
+      <c r="K199" s="10" t="n"/>
+      <c r="L199" s="10" t="n"/>
+      <c r="M199" s="10" t="n"/>
+      <c r="N199" s="10" t="n"/>
+      <c r="O199" s="10" t="n"/>
+      <c r="P199" s="10" t="n"/>
+      <c r="Q199" s="10" t="n"/>
+      <c r="R199" s="10" t="n"/>
+      <c r="S199" s="10" t="n"/>
+      <c r="T199" s="10" t="n"/>
+      <c r="U199" s="10" t="n"/>
+      <c r="V199" s="10" t="n"/>
+      <c r="W199" s="10" t="n"/>
+      <c r="X199" s="10" t="n"/>
+      <c r="Y199" s="10" t="n"/>
+      <c r="Z199" s="10" t="n"/>
+      <c r="AA199" s="10" t="n"/>
+      <c r="AB199" s="10" t="n"/>
+      <c r="AC199" s="10" t="n"/>
+      <c r="AD199" s="10" t="n"/>
+      <c r="AE199" s="10" t="n"/>
+      <c r="AF199" s="10" t="n"/>
+      <c r="AG199" s="10" t="n"/>
+      <c r="AH199" s="10" t="n"/>
+      <c r="AI199" s="10" t="n"/>
+      <c r="AJ199" s="10" t="n"/>
+      <c r="AK199" s="11" t="n"/>
+    </row>
+    <row r="200" ht="36" customHeight="1">
+      <c r="C200" s="38" t="inlineStr">
         <is>
           <t>`operation`：取込モード別の prefixed ラベル（販売店取込 SCR-019 と統一・bare-verb ルールの例外）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="18" customHeight="1">
-      <c r="D200" s="38" t="inlineStr">
-        <is>
-          <t>`NEW` → `'IMPORT_NEW'`</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="D201" s="38" t="inlineStr">
         <is>
-          <t>`UPDATE_ALL` → `'IMPORT_UPDATE_ALL'`</t>
+          <t>`NEW` → `'IMPORT_NEW'`</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="D202" s="38" t="inlineStr">
         <is>
+          <t>`UPDATE_ALL` → `'IMPORT_UPDATE_ALL'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="D203" s="38" t="inlineStr">
+        <is>
           <t>`UPDATE_PARTIAL` → `'IMPORT_UPDATE_PARTIAL'`</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="C203" s="38" t="inlineStr">
+    <row r="204" ht="18" customHeight="1">
+      <c r="C204" s="38" t="inlineStr">
         <is>
           <t>`before_value`：</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="D204" s="38" t="inlineStr">
+    <row r="205" ht="18" customHeight="1">
+      <c r="D205" s="38" t="inlineStr">
         <is>
           <t>`NEW` モード：空文字列</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="54" customHeight="1">
-      <c r="D205" s="38" t="inlineStr">
+    <row r="206" ht="54" customHeight="1">
+      <c r="D206" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_ALL` / `UPDATE_PARTIAL` / 一括中止：更新前データのサマリJSON `{ "rows": [{...}, ...] }`（各行の更新前状態を格納、最大100件まで）</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="72" customHeight="1">
-      <c r="C206" s="38" t="inlineStr">
+    <row r="207" ht="72" customHeight="1">
+      <c r="C207" s="38" t="inlineStr">
         <is>
           <t>`after_value`：取込結果サマリJSON `{ "import_mode", "total_rows", "created_count", "updated_count", "cancelled_count", "created_ids": [...], "updated_ids": [...] }`</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="18" customHeight="1">
-      <c r="C207" s="38" t="inlineStr">
+    <row r="208" ht="18" customHeight="1">
+      <c r="C208" s="38" t="inlineStr">
         <is>
           <t>パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="180" customHeight="1">
-      <c r="C208" s="42" t="inlineStr">
+    <row r="209" ht="180" customHeight="1">
+      <c r="C209" s="42" t="inlineStr">
         <is>
           <t>{
   "import_mode": "NEW",
@@ -15242,99 +15375,99 @@
 }</t>
         </is>
       </c>
-      <c r="D208" s="10" t="n"/>
-      <c r="E208" s="10" t="n"/>
-      <c r="F208" s="10" t="n"/>
-      <c r="G208" s="10" t="n"/>
-      <c r="H208" s="10" t="n"/>
-      <c r="I208" s="10" t="n"/>
-      <c r="J208" s="10" t="n"/>
-      <c r="K208" s="10" t="n"/>
-      <c r="L208" s="10" t="n"/>
-      <c r="M208" s="10" t="n"/>
-      <c r="N208" s="10" t="n"/>
-      <c r="O208" s="10" t="n"/>
-      <c r="P208" s="10" t="n"/>
-      <c r="Q208" s="10" t="n"/>
-      <c r="R208" s="10" t="n"/>
-      <c r="S208" s="10" t="n"/>
-      <c r="T208" s="10" t="n"/>
-      <c r="U208" s="10" t="n"/>
-      <c r="V208" s="10" t="n"/>
-      <c r="W208" s="10" t="n"/>
-      <c r="X208" s="10" t="n"/>
-      <c r="Y208" s="10" t="n"/>
-      <c r="Z208" s="10" t="n"/>
-      <c r="AA208" s="10" t="n"/>
-      <c r="AB208" s="10" t="n"/>
-      <c r="AC208" s="10" t="n"/>
-      <c r="AD208" s="10" t="n"/>
-      <c r="AE208" s="10" t="n"/>
-      <c r="AF208" s="10" t="n"/>
-      <c r="AG208" s="10" t="n"/>
-      <c r="AH208" s="10" t="n"/>
-      <c r="AI208" s="10" t="n"/>
-      <c r="AJ208" s="10" t="n"/>
-      <c r="AK208" s="11" t="n"/>
-    </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="B209" s="27" t="inlineStr">
+      <c r="D209" s="10" t="n"/>
+      <c r="E209" s="10" t="n"/>
+      <c r="F209" s="10" t="n"/>
+      <c r="G209" s="10" t="n"/>
+      <c r="H209" s="10" t="n"/>
+      <c r="I209" s="10" t="n"/>
+      <c r="J209" s="10" t="n"/>
+      <c r="K209" s="10" t="n"/>
+      <c r="L209" s="10" t="n"/>
+      <c r="M209" s="10" t="n"/>
+      <c r="N209" s="10" t="n"/>
+      <c r="O209" s="10" t="n"/>
+      <c r="P209" s="10" t="n"/>
+      <c r="Q209" s="10" t="n"/>
+      <c r="R209" s="10" t="n"/>
+      <c r="S209" s="10" t="n"/>
+      <c r="T209" s="10" t="n"/>
+      <c r="U209" s="10" t="n"/>
+      <c r="V209" s="10" t="n"/>
+      <c r="W209" s="10" t="n"/>
+      <c r="X209" s="10" t="n"/>
+      <c r="Y209" s="10" t="n"/>
+      <c r="Z209" s="10" t="n"/>
+      <c r="AA209" s="10" t="n"/>
+      <c r="AB209" s="10" t="n"/>
+      <c r="AC209" s="10" t="n"/>
+      <c r="AD209" s="10" t="n"/>
+      <c r="AE209" s="10" t="n"/>
+      <c r="AF209" s="10" t="n"/>
+      <c r="AG209" s="10" t="n"/>
+      <c r="AH209" s="10" t="n"/>
+      <c r="AI209" s="10" t="n"/>
+      <c r="AJ209" s="10" t="n"/>
+      <c r="AK209" s="11" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="B210" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="18" customHeight="1">
-      <c r="C210" s="38" t="inlineStr">
-        <is>
-          <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="C211" s="38" t="inlineStr">
         <is>
-          <t>取込結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
+          <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="C212" s="38" t="inlineStr">
         <is>
+          <t>取込結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="C213" s="38" t="inlineStr">
+        <is>
           <t>`message`：`取り込みました。`（ACSMS-MSG-016-004）</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="B213" s="27" t="inlineStr">
+    <row r="214" ht="18" customHeight="1">
+      <c r="B214" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="18" customHeight="1">
-      <c r="C214" s="38" t="inlineStr">
-        <is>
-          <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="C215" s="38" t="inlineStr">
         <is>
+          <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="C216" s="38" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="36" customHeight="1">
-      <c r="C216" s="38" t="inlineStr">
+    <row r="217" ht="36" customHeight="1">
+      <c r="C217" s="38" t="inlineStr">
         <is>
           <t>エラー発生時もエラーログを記録する（`log_type = 3`）。**トランザクション外で別途記録する**。</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="144" customHeight="1">
-      <c r="C217" s="42" t="inlineStr">
+    <row r="218" ht="144" customHeight="1">
+      <c r="C218" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -15346,47 +15479,46 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D217" s="10" t="n"/>
-      <c r="E217" s="10" t="n"/>
-      <c r="F217" s="10" t="n"/>
-      <c r="G217" s="10" t="n"/>
-      <c r="H217" s="10" t="n"/>
-      <c r="I217" s="10" t="n"/>
-      <c r="J217" s="10" t="n"/>
-      <c r="K217" s="10" t="n"/>
-      <c r="L217" s="10" t="n"/>
-      <c r="M217" s="10" t="n"/>
-      <c r="N217" s="10" t="n"/>
-      <c r="O217" s="10" t="n"/>
-      <c r="P217" s="10" t="n"/>
-      <c r="Q217" s="10" t="n"/>
-      <c r="R217" s="10" t="n"/>
-      <c r="S217" s="10" t="n"/>
-      <c r="T217" s="10" t="n"/>
-      <c r="U217" s="10" t="n"/>
-      <c r="V217" s="10" t="n"/>
-      <c r="W217" s="10" t="n"/>
-      <c r="X217" s="10" t="n"/>
-      <c r="Y217" s="10" t="n"/>
-      <c r="Z217" s="10" t="n"/>
-      <c r="AA217" s="10" t="n"/>
-      <c r="AB217" s="10" t="n"/>
-      <c r="AC217" s="10" t="n"/>
-      <c r="AD217" s="10" t="n"/>
-      <c r="AE217" s="10" t="n"/>
-      <c r="AF217" s="10" t="n"/>
-      <c r="AG217" s="10" t="n"/>
-      <c r="AH217" s="10" t="n"/>
-      <c r="AI217" s="10" t="n"/>
-      <c r="AJ217" s="10" t="n"/>
-      <c r="AK217" s="11" t="n"/>
+      <c r="D218" s="10" t="n"/>
+      <c r="E218" s="10" t="n"/>
+      <c r="F218" s="10" t="n"/>
+      <c r="G218" s="10" t="n"/>
+      <c r="H218" s="10" t="n"/>
+      <c r="I218" s="10" t="n"/>
+      <c r="J218" s="10" t="n"/>
+      <c r="K218" s="10" t="n"/>
+      <c r="L218" s="10" t="n"/>
+      <c r="M218" s="10" t="n"/>
+      <c r="N218" s="10" t="n"/>
+      <c r="O218" s="10" t="n"/>
+      <c r="P218" s="10" t="n"/>
+      <c r="Q218" s="10" t="n"/>
+      <c r="R218" s="10" t="n"/>
+      <c r="S218" s="10" t="n"/>
+      <c r="T218" s="10" t="n"/>
+      <c r="U218" s="10" t="n"/>
+      <c r="V218" s="10" t="n"/>
+      <c r="W218" s="10" t="n"/>
+      <c r="X218" s="10" t="n"/>
+      <c r="Y218" s="10" t="n"/>
+      <c r="Z218" s="10" t="n"/>
+      <c r="AA218" s="10" t="n"/>
+      <c r="AB218" s="10" t="n"/>
+      <c r="AC218" s="10" t="n"/>
+      <c r="AD218" s="10" t="n"/>
+      <c r="AE218" s="10" t="n"/>
+      <c r="AF218" s="10" t="n"/>
+      <c r="AG218" s="10" t="n"/>
+      <c r="AH218" s="10" t="n"/>
+      <c r="AI218" s="10" t="n"/>
+      <c r="AJ218" s="10" t="n"/>
+      <c r="AK218" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="599">
+  <mergeCells count="606">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="C174:AK174"/>
     <mergeCell ref="AF65:AK65"/>
-    <mergeCell ref="D200:AK200"/>
     <mergeCell ref="D134:AK134"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y61:AB61"/>
@@ -15395,35 +15527,37 @@
     <mergeCell ref="D202:AK202"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="Y41:AB41"/>
-    <mergeCell ref="Q80:S80"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="Y56:AB56"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="Y43:AB43"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="AF91:AK91"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="M88:P88"/>
     <mergeCell ref="M82:P82"/>
     <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF84:AK84"/>
+    <mergeCell ref="Q91:S91"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="M90:P90"/>
     <mergeCell ref="AF86:AK86"/>
+    <mergeCell ref="Q77:S77"/>
     <mergeCell ref="AC57:AE57"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y59:AB59"/>
-    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M85:P85"/>
     <mergeCell ref="Y36:AB36"/>
     <mergeCell ref="AC58:AE58"/>
-    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="AC39:AE39"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
@@ -15431,9 +15565,7 @@
     <mergeCell ref="C195:AK195"/>
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="D129:AK129"/>
-    <mergeCell ref="C197:AK197"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="Q86:S86"/>
@@ -15443,7 +15575,6 @@
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y62:AB62"/>
     <mergeCell ref="AF81:AK81"/>
-    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="C73:L73"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D89:L89"/>
@@ -15452,14 +15583,18 @@
     <mergeCell ref="T76:X76"/>
     <mergeCell ref="Y64:AB64"/>
     <mergeCell ref="Y51:AB51"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="T69:X69"/>
+    <mergeCell ref="C213:AK213"/>
+    <mergeCell ref="B197:AK197"/>
     <mergeCell ref="AC71:AE71"/>
-    <mergeCell ref="C150:AK150"/>
     <mergeCell ref="C144:AK144"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="C208:AK208"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="M91:P91"/>
+    <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Y33:AB33"/>
@@ -15467,13 +15602,11 @@
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C72:L72"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C210:AK210"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="T87:X87"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Y75:AB75"/>
-    <mergeCell ref="B166:AK166"/>
     <mergeCell ref="AC60:AE60"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T59:X59"/>
@@ -15496,18 +15629,18 @@
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="B95:I95"/>
     <mergeCell ref="C56:L56"/>
-    <mergeCell ref="D145:AK145"/>
     <mergeCell ref="C43:L43"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="C158:AK158"/>
     <mergeCell ref="Q64:S64"/>
+    <mergeCell ref="T77:X77"/>
     <mergeCell ref="D147:AK147"/>
     <mergeCell ref="Y65:AB65"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B167:AK167"/>
     <mergeCell ref="Y57:AB57"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="AC73:AE73"/>
@@ -15517,23 +15650,23 @@
     <mergeCell ref="C216:AK216"/>
     <mergeCell ref="Y87:AE87"/>
     <mergeCell ref="AF75:AK75"/>
+    <mergeCell ref="C218:AK218"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="C211:AK211"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
+    <mergeCell ref="B108:I108"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="C65:L65"/>
-    <mergeCell ref="B124:AK124"/>
     <mergeCell ref="Y82:AE82"/>
-    <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C80:L80"/>
     <mergeCell ref="Y60:AB60"/>
     <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="B126:AK126"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="D84:L84"/>
     <mergeCell ref="T90:X90"/>
@@ -15547,20 +15680,23 @@
     <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC67:AE67"/>
-    <mergeCell ref="C102:AK102"/>
+    <mergeCell ref="C91:L91"/>
     <mergeCell ref="AC69:AE69"/>
     <mergeCell ref="C179:AK179"/>
     <mergeCell ref="J18:M18"/>
+    <mergeCell ref="B96:I96"/>
     <mergeCell ref="C57:L57"/>
+    <mergeCell ref="C166:AK166"/>
     <mergeCell ref="C160:AK160"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="C141:AK141"/>
+    <mergeCell ref="B111:I111"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
-    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="D148:AK148"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="Y71:AB71"/>
@@ -15568,6 +15704,7 @@
     <mergeCell ref="Y58:AB58"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Y73:AB73"/>
+    <mergeCell ref="B139:AK139"/>
     <mergeCell ref="T84:X84"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
@@ -15590,7 +15727,6 @@
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC42:AE42"/>
-    <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="C81:L81"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
@@ -15598,14 +15734,15 @@
     <mergeCell ref="AC44:AE44"/>
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="B196:AK196"/>
+    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="C168:AK168"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="C180:AK180"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
-    <mergeCell ref="C167:AK167"/>
     <mergeCell ref="C63:L63"/>
+    <mergeCell ref="D131:AK131"/>
     <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
@@ -15619,27 +15756,28 @@
     <mergeCell ref="D189:AK189"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
-    <mergeCell ref="B209:AK209"/>
+    <mergeCell ref="B114:I114"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
-    <mergeCell ref="Y80:AE80"/>
     <mergeCell ref="Y49:AB49"/>
+    <mergeCell ref="B214:AK214"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
-    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="Y76:AB76"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
+    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="C187:AK187"/>
+    <mergeCell ref="Y91:AE91"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="M83:P83"/>
     <mergeCell ref="C162:AK162"/>
     <mergeCell ref="M49:P49"/>
-    <mergeCell ref="B119:I119"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="C164:AK164"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="AC52:AE52"/>
+    <mergeCell ref="D190:AK190"/>
     <mergeCell ref="Y54:AB54"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="V1:Y1"/>
@@ -15653,10 +15791,8 @@
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="T36:X36"/>
-    <mergeCell ref="C190:AK190"/>
     <mergeCell ref="AC76:AE76"/>
     <mergeCell ref="AF63:AK63"/>
-    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="C66:L66"/>
     <mergeCell ref="Q81:S81"/>
@@ -15672,23 +15808,19 @@
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="D188:AK188"/>
     <mergeCell ref="Q74:S74"/>
-    <mergeCell ref="B107:I107"/>
     <mergeCell ref="C68:L68"/>
     <mergeCell ref="T62:X62"/>
-    <mergeCell ref="D132:AK132"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="Y44:AB44"/>
-    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
-    <mergeCell ref="C203:AK203"/>
-    <mergeCell ref="C82:C89"/>
+    <mergeCell ref="C138:AK138"/>
+    <mergeCell ref="C132:AK132"/>
     <mergeCell ref="M86:P86"/>
     <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M80:P80"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="AF87:AK87"/>
     <mergeCell ref="J11:AK11"/>
@@ -15703,23 +15835,24 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
-    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="AC46:AE46"/>
     <mergeCell ref="Q89:S89"/>
     <mergeCell ref="Y47:AB47"/>
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="C183:AK183"/>
     <mergeCell ref="M70:P70"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="C193:AK193"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="C176:AK176"/>
-    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="J2:P3"/>
-    <mergeCell ref="A78:AK78"/>
+    <mergeCell ref="AF77:AK77"/>
     <mergeCell ref="Y50:AB50"/>
     <mergeCell ref="C178:AK178"/>
     <mergeCell ref="N20:AK20"/>
@@ -15729,15 +15862,15 @@
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T72:X72"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="D204:AK204"/>
-    <mergeCell ref="B110:I110"/>
     <mergeCell ref="Y52:AB52"/>
+    <mergeCell ref="AC77:AE77"/>
     <mergeCell ref="AC74:AE74"/>
     <mergeCell ref="D135:AK135"/>
+    <mergeCell ref="C209:AK209"/>
     <mergeCell ref="AC68:AE68"/>
+    <mergeCell ref="D206:AK206"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
-    <mergeCell ref="B149:AK149"/>
     <mergeCell ref="AC43:AE43"/>
     <mergeCell ref="Y45:AB45"/>
     <mergeCell ref="C140:AK140"/>
@@ -15745,13 +15878,14 @@
     <mergeCell ref="AC72:AE72"/>
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C204:AK204"/>
     <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="C83:C90"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y42:AB42"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="AF88:AK88"/>
-    <mergeCell ref="C206:AK206"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -15759,7 +15893,6 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="T83:X83"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="AF90:AK90"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
@@ -15782,9 +15915,9 @@
     <mergeCell ref="C161:AK161"/>
     <mergeCell ref="C217:AK217"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="B93:I93"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="Y66:AB66"/>
     <mergeCell ref="T65:X65"/>
@@ -15793,27 +15926,21 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Y53:AB53"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="Y68:AB68"/>
-    <mergeCell ref="B101:I101"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="Y55:AB55"/>
     <mergeCell ref="C212:AK212"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y83:AE83"/>
-    <mergeCell ref="C105:AK105"/>
-    <mergeCell ref="C214:AK214"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
-    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="C207:AK207"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="B104:I104"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="B125:AK125"/>
     <mergeCell ref="M89:P89"/>
+    <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="Y37:AB37"/>
     <mergeCell ref="C27:L27"/>
@@ -15826,16 +15953,17 @@
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="D87:L87"/>
     <mergeCell ref="AC65:AE65"/>
+    <mergeCell ref="C200:AK200"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="Y63:AB63"/>
     <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="D82:L82"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="Y74:AB74"/>
     <mergeCell ref="C177:AK177"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
+    <mergeCell ref="B99:I99"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="C47:L47"/>
@@ -15843,7 +15971,6 @@
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
-    <mergeCell ref="B92:I92"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="AC75:AE75"/>
@@ -15863,10 +15990,13 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="C157:AK157"/>
     <mergeCell ref="C151:AK151"/>
+    <mergeCell ref="B105:I105"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="Y38:AB38"/>
+    <mergeCell ref="C77:L77"/>
+    <mergeCell ref="B120:I120"/>
     <mergeCell ref="C215:AK215"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
@@ -15881,11 +16011,12 @@
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="D90:L90"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="C59:L59"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="C46:L46"/>
     <mergeCell ref="Y81:AE81"/>
-    <mergeCell ref="B113:I113"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
@@ -15893,18 +16024,20 @@
     <mergeCell ref="C170:AK170"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="AF62:AK62"/>
+    <mergeCell ref="Y77:AB77"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
+    <mergeCell ref="B102:I102"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D127:AK127"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="Y72:AB72"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="C196:AK196"/>
     <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="M73:P73"/>
-    <mergeCell ref="A123:AK123"/>
+    <mergeCell ref="D203:AK203"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="C198:AK198"/>
@@ -15940,7 +16073,7 @@
     <mergeCell ref="C171:AK171"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="AC59:AE59"/>
-    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="AF72:AK72"/>
     <mergeCell ref="C64:L64"/>
@@ -15950,17 +16083,20 @@
     <mergeCell ref="D128:AK128"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="AC61:AE61"/>
-    <mergeCell ref="B213:AK213"/>
+    <mergeCell ref="A124:AK124"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="Y40:AB40"/>
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="AF54:AK54"/>
+    <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q88:S88"/>
     <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="C82:L82"/>
     <mergeCell ref="T49:X49"/>
+    <mergeCell ref="B210:AK210"/>
     <mergeCell ref="D146:AK146"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
@@ -15969,18 +16105,22 @@
     <mergeCell ref="Q90:S90"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="AC56:AE56"/>
     <mergeCell ref="AF60:AK60"/>
     <mergeCell ref="C58:L58"/>
     <mergeCell ref="AC49:AE49"/>
-    <mergeCell ref="D187:AK187"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="C192:AK192"/>
+    <mergeCell ref="A79:AK79"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="C194:AK194"/>
     <mergeCell ref="C181:AK181"/>
+    <mergeCell ref="D136:AK136"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="B150:AK150"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -2030,7 +2030,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2546,7 +2546,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3418,7 +3418,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3853,7 +3853,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8785,7 +8785,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15137,7 +15137,7 @@
   bank_branch_code, bank_branch_name, hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi,
   dokusyaso_bunrui, nogyosya_bunrui,
   shoki_dokusya_kaishi_date, dokusya_kaishi_date, dokusya_chushi_date, joho_henko_tekiyo_date,
-  seikyu_kaishi_month, biko, henko_riyu, saishin_data_flg,
+  seikyu_kaishi_month, biko, saishin_data_flg,
   zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id, zenkai_dokusya_busu, zenkai_yubin_no,
   zenkai_todofuken_code, zenkai_shikuchoson, zenkai_chome_banchi, zenkai_tatemono_mei,
@@ -15157,7 +15157,7 @@
   :bank_branch_code, :bank_branch_name, :hikiotoshi_yokin_shubetsu, :hikiotoshi_koza_no, :hikiotoshi_koza_meigi,
   :dokusyaso_bunrui, :nogyosya_bunrui,
   :shoki_dokusya_kaishi_date, :dokusya_kaishi_date, :dokusya_chushi_date, :joho_henko_tekiyo_date,
-  :seikyu_kaishi_month, :biko, '', TRUE,
+  :seikyu_kaishi_month, :biko, TRUE,
   :zougen_hokoku_flg, :shinki_flg, :kaiyaku_flg,
   :zenkai_hanbaiten_id, :zenkai_dokusya_busu, :zenkai_yubin_no,
   :zenkai_todofuken_code, :zenkai_shikuchoson, :zenkai_chome_banchi, :zenkai_tatemono_mei,

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1807,9 +1807,69 @@
       <c r="AF7" s="10" t="n"/>
       <c r="AG7" s="11" t="n"/>
     </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：**適用日・中止日を Excel 列から top-level パラメータへ**。(1) `joho_henko_tekiyo_date` / `dokusya_chushi_date` を行データ・テンプレート列から**撤去**し、画面の入力欄で1ファイル1つ指定する top-level パラメータに変更（48→46列）。両者は**排他**で、`NEW` では指定不可、`UPDATE` はどちらか必須（電子版は当日固定のため適用日を省略可）。違反は `VALIDATION_ERROR`（行エラーではなくフォームエラー）。(2) **`dokusya_chushi_date` 指定＝一括中止**（§4.8 新設）。解約予約を1件 append し、`selected_columns` の他列は書かない。確定は到来日バッチ。(3) 電子版の一括中止は同一処理内で `cancel` を push し、1件でも失敗したら全件ロールバック＋送信済み分へ打ち消し（`cancel_ym` 空）。打ち消し失敗分は会員IDをエラーログへ。紙版は連携なし。(4) 電子版の一括中止は500行まで。(5) 旧「一括中止」（組合員コードをキーに手続種類=解約）の記述を概要から削除（v1.2 で廃止済みだが残存していた）。</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="11" t="n"/>
+      <c r="W8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="56">
     <mergeCell ref="R1:V1"/>
+    <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
@@ -1835,6 +1895,7 @@
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
@@ -1843,17 +1904,22 @@
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
+    <mergeCell ref="K8:Q8"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
@@ -2030,7 +2096,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2546,7 +2612,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3418,7 +3484,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3563,7 +3629,7 @@
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータ取込用のテンプレートファイル（48列固定）を生成しダウンロードする。</t>
+          <t>購読者Excelデータ取込用のテンプレートファイル（46列固定）を生成しダウンロードする。</t>
         </is>
       </c>
       <c r="T6" s="10" t="n"/>
@@ -3620,7 +3686,7 @@
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータを一括取込する（新規登録 / 全項目更新 / 入力箇所のみ更新）。1トランザクションで処理し、エラー時は全件ロールバック。一括中止の場合は組合員コードをキーに手続種類＝解約・購読中止日を設定して更新する。取り込みと同件数分のレコードを `t_dokusya_rireki` テーブルに追加する。</t>
+          <t>購読者Excelデータを一括取込する（新規登録 / 更新）。1トランザクションで処理し、エラー時は全件ロールバック。`dokusya_chushi_date` を指定した取込は**一括中止**（解約予約の作成）となる（→ §4.8）。取り込みと同件数分のレコードを `t_dokusya_rireki` テーブルに追加する。</t>
         </is>
       </c>
       <c r="T7" s="10" t="n"/>
@@ -3692,7 +3758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3853,7 +3919,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3977,7 +4043,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータ取込用のテンプレートファイル（48列固定）を生成しダウンロードする。</t>
+          <t>購読者Excelデータ取込用のテンプレートファイル（46列固定）を生成しダウンロードする。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -7582,7 +7648,7 @@
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>購読中止日</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="D78" s="10" t="n"/>
@@ -7596,7 +7662,7 @@
       <c r="L78" s="11" t="n"/>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>購読中止日</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="N78" s="10" t="n"/>
@@ -7604,14 +7670,14 @@
       <c r="P78" s="11" t="n"/>
       <c r="Q78" s="17" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="R78" s="10" t="n"/>
       <c r="S78" s="11" t="n"/>
       <c r="T78" s="17" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="U78" s="10" t="n"/>
@@ -7636,184 +7702,64 @@
       <c r="AJ78" s="10" t="n"/>
       <c r="AK78" s="11" t="n"/>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="31" t="n">
-        <v>48</v>
-      </c>
-      <c r="C79" s="19" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="17" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="11" t="n"/>
-      <c r="Q79" s="17" t="inlineStr">
-        <is>
-          <t>biko</t>
-        </is>
-      </c>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="11" t="n"/>
-      <c r="T79" s="17" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="U79" s="10" t="n"/>
-      <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
-      <c r="X79" s="11" t="n"/>
-      <c r="Y79" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z79" s="10" t="n"/>
-      <c r="AA79" s="10" t="n"/>
-      <c r="AB79" s="10" t="n"/>
-      <c r="AC79" s="10" t="n"/>
-      <c r="AD79" s="10" t="n"/>
-      <c r="AE79" s="11" t="n"/>
-      <c r="AF79" s="19" t="inlineStr"/>
-      <c r="AG79" s="10" t="n"/>
-      <c r="AH79" s="10" t="n"/>
-      <c r="AI79" s="10" t="n"/>
-      <c r="AJ79" s="10" t="n"/>
-      <c r="AK79" s="11" t="n"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="31" t="n">
-        <v>49</v>
-      </c>
-      <c r="C80" s="19" t="inlineStr">
-        <is>
-          <t>読者情報変更適用日</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="11" t="n"/>
-      <c r="M80" s="17" t="inlineStr">
-        <is>
-          <t>読者情報変更適用日</t>
-        </is>
-      </c>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="11" t="n"/>
-      <c r="Q80" s="17" t="inlineStr">
-        <is>
-          <t>joho_henko_tekiyo_date</t>
-        </is>
-      </c>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="17" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="11" t="n"/>
-      <c r="Y80" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="11" t="n"/>
-      <c r="AF80" s="19" t="inlineStr"/>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1"/>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="B82" s="37" t="inlineStr">
+    <row r="79" ht="19.5" customHeight="1"/>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="B80" s="37" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="19" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/dokusya/import/template</t>
         </is>
       </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
-      <c r="B85" s="37" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="B83" s="37" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="90" customHeight="1">
-      <c r="C86" s="19" t="inlineStr">
+    <row r="84" ht="90" customHeight="1">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>HTTP/1.1 200 OK
 Content-Type: application/vnd.openxmlformats-officedocument.spreadsheetml.sheet
@@ -7821,50 +7767,50 @@
 (バイナリデータ)</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="10" t="n"/>
-      <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="n"/>
-      <c r="L86" s="10" t="n"/>
-      <c r="M86" s="10" t="n"/>
-      <c r="N86" s="10" t="n"/>
-      <c r="O86" s="10" t="n"/>
-      <c r="P86" s="10" t="n"/>
-      <c r="Q86" s="10" t="n"/>
-      <c r="R86" s="10" t="n"/>
-      <c r="S86" s="10" t="n"/>
-      <c r="T86" s="10" t="n"/>
-      <c r="U86" s="10" t="n"/>
-      <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n"/>
-      <c r="X86" s="10" t="n"/>
-      <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="10" t="n"/>
-      <c r="AA86" s="10" t="n"/>
-      <c r="AB86" s="10" t="n"/>
-      <c r="AC86" s="10" t="n"/>
-      <c r="AD86" s="10" t="n"/>
-      <c r="AE86" s="10" t="n"/>
-      <c r="AF86" s="10" t="n"/>
-      <c r="AG86" s="10" t="n"/>
-      <c r="AH86" s="10" t="n"/>
-      <c r="AI86" s="10" t="n"/>
-      <c r="AJ86" s="10" t="n"/>
-      <c r="AK86" s="11" t="n"/>
-    </row>
-    <row r="88" ht="19.5" customHeight="1">
-      <c r="B88" s="37" t="inlineStr">
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="B86" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="72" customHeight="1">
-      <c r="C89" s="19" t="inlineStr">
+    <row r="87" ht="72" customHeight="1">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -7872,50 +7818,50 @@
 }</t>
         </is>
       </c>
-      <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="n"/>
-      <c r="F89" s="10" t="n"/>
-      <c r="G89" s="10" t="n"/>
-      <c r="H89" s="10" t="n"/>
-      <c r="I89" s="10" t="n"/>
-      <c r="J89" s="10" t="n"/>
-      <c r="K89" s="10" t="n"/>
-      <c r="L89" s="10" t="n"/>
-      <c r="M89" s="10" t="n"/>
-      <c r="N89" s="10" t="n"/>
-      <c r="O89" s="10" t="n"/>
-      <c r="P89" s="10" t="n"/>
-      <c r="Q89" s="10" t="n"/>
-      <c r="R89" s="10" t="n"/>
-      <c r="S89" s="10" t="n"/>
-      <c r="T89" s="10" t="n"/>
-      <c r="U89" s="10" t="n"/>
-      <c r="V89" s="10" t="n"/>
-      <c r="W89" s="10" t="n"/>
-      <c r="X89" s="10" t="n"/>
-      <c r="Y89" s="10" t="n"/>
-      <c r="Z89" s="10" t="n"/>
-      <c r="AA89" s="10" t="n"/>
-      <c r="AB89" s="10" t="n"/>
-      <c r="AC89" s="10" t="n"/>
-      <c r="AD89" s="10" t="n"/>
-      <c r="AE89" s="10" t="n"/>
-      <c r="AF89" s="10" t="n"/>
-      <c r="AG89" s="10" t="n"/>
-      <c r="AH89" s="10" t="n"/>
-      <c r="AI89" s="10" t="n"/>
-      <c r="AJ89" s="10" t="n"/>
-      <c r="AK89" s="11" t="n"/>
-    </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="B91" s="37" t="inlineStr">
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="B89" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="72" customHeight="1">
-      <c r="C92" s="19" t="inlineStr">
+    <row r="90" ht="72" customHeight="1">
+      <c r="C90" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -7923,50 +7869,50 @@
 }</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="10" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="10" t="n"/>
-      <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
-      <c r="J92" s="10" t="n"/>
-      <c r="K92" s="10" t="n"/>
-      <c r="L92" s="10" t="n"/>
-      <c r="M92" s="10" t="n"/>
-      <c r="N92" s="10" t="n"/>
-      <c r="O92" s="10" t="n"/>
-      <c r="P92" s="10" t="n"/>
-      <c r="Q92" s="10" t="n"/>
-      <c r="R92" s="10" t="n"/>
-      <c r="S92" s="10" t="n"/>
-      <c r="T92" s="10" t="n"/>
-      <c r="U92" s="10" t="n"/>
-      <c r="V92" s="10" t="n"/>
-      <c r="W92" s="10" t="n"/>
-      <c r="X92" s="10" t="n"/>
-      <c r="Y92" s="10" t="n"/>
-      <c r="Z92" s="10" t="n"/>
-      <c r="AA92" s="10" t="n"/>
-      <c r="AB92" s="10" t="n"/>
-      <c r="AC92" s="10" t="n"/>
-      <c r="AD92" s="10" t="n"/>
-      <c r="AE92" s="10" t="n"/>
-      <c r="AF92" s="10" t="n"/>
-      <c r="AG92" s="10" t="n"/>
-      <c r="AH92" s="10" t="n"/>
-      <c r="AI92" s="10" t="n"/>
-      <c r="AJ92" s="10" t="n"/>
-      <c r="AK92" s="11" t="n"/>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="B94" s="37" t="inlineStr">
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="B92" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="72" customHeight="1">
-      <c r="C95" s="19" t="inlineStr">
+    <row r="93" ht="72" customHeight="1">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -7974,233 +7920,232 @@
 }</t>
         </is>
       </c>
-      <c r="D95" s="10" t="n"/>
-      <c r="E95" s="10" t="n"/>
-      <c r="F95" s="10" t="n"/>
-      <c r="G95" s="10" t="n"/>
-      <c r="H95" s="10" t="n"/>
-      <c r="I95" s="10" t="n"/>
-      <c r="J95" s="10" t="n"/>
-      <c r="K95" s="10" t="n"/>
-      <c r="L95" s="10" t="n"/>
-      <c r="M95" s="10" t="n"/>
-      <c r="N95" s="10" t="n"/>
-      <c r="O95" s="10" t="n"/>
-      <c r="P95" s="10" t="n"/>
-      <c r="Q95" s="10" t="n"/>
-      <c r="R95" s="10" t="n"/>
-      <c r="S95" s="10" t="n"/>
-      <c r="T95" s="10" t="n"/>
-      <c r="U95" s="10" t="n"/>
-      <c r="V95" s="10" t="n"/>
-      <c r="W95" s="10" t="n"/>
-      <c r="X95" s="10" t="n"/>
-      <c r="Y95" s="10" t="n"/>
-      <c r="Z95" s="10" t="n"/>
-      <c r="AA95" s="10" t="n"/>
-      <c r="AB95" s="10" t="n"/>
-      <c r="AC95" s="10" t="n"/>
-      <c r="AD95" s="10" t="n"/>
-      <c r="AE95" s="10" t="n"/>
-      <c r="AF95" s="10" t="n"/>
-      <c r="AG95" s="10" t="n"/>
-      <c r="AH95" s="10" t="n"/>
-      <c r="AI95" s="10" t="n"/>
-      <c r="AJ95" s="10" t="n"/>
-      <c r="AK95" s="11" t="n"/>
-    </row>
-    <row r="97" ht="19.5" customHeight="1"/>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="10" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="11" t="n"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1"/>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="38" t="inlineStr">
+        <is>
+          <t>リクエストパラメータなし。特に検証なし。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>4.1 リクエストのバリデーション</t>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="C100" s="38" t="inlineStr">
         <is>
-          <t>リクエストパラメータなし。特に検証なし。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="B101" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C101" s="38" t="inlineStr">
+        <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="38" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
+          <t>必要権限: `dokusya.import`</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
       <c r="C103" s="38" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="C104" s="38" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.import`</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="36" customHeight="1">
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
       <c r="C105" s="38" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>DataScope: 本APIはマスターデータを返さないため、DataScope違反は発生しない。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="38" t="inlineStr">
-        <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>4.3 テンプレート生成</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="C107" s="38" t="inlineStr">
         <is>
-          <t>DataScope: 本APIはマスターデータを返さないため、DataScope違反は発生しない。</t>
+          <t>ExcelJSライブラリを使用して新規ワークブックを生成する。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="B108" s="27" t="inlineStr">
-        <is>
-          <t>4.3 テンプレート生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
+      <c r="C108" s="38" t="inlineStr">
+        <is>
+          <t>シート名：`購読者`</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
       <c r="C109" s="38" t="inlineStr">
         <is>
-          <t>ExcelJSライブラリを使用して新規ワークブックを生成する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="C110" s="38" t="inlineStr">
-        <is>
-          <t>シート名：`購読者`</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="36" customHeight="1">
+          <t>1行目に46列のヘッダー文字列を以下の順序で書き込む（購読種別・読者情報変更適用日・購読中止日は画面で指定する単一ソースのため列に含めない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="162" customHeight="1">
+      <c r="D110" s="38" t="inlineStr">
+        <is>
+          <t>「ID」「管理支店」「支店」「組合員コード」「購読者苗字（漢字）」「購読者名前（漢字）」「購読者苗字（かな）」「購読者名前（かな）」「購読部数」「新聞単価」「メールアドレス」「メールマガジン」「生年（西暦）」「性別」「郵便番号」「都道府県」「市町村郡」「丁目番地」「マンション・アパート名」「連絡先１」「連絡先２」「郵便番号(配達先)」「都道府県(配達先)」「市町村郡(配達先)」「丁目番地(配達先)」「ﾏﾝｼｮﾝ・ｱﾊﾟｰﾄ名(配達先)」「連絡先１(配達先)」「連絡先２(配達先)」「配達先苗字（漢字）」「配達先名前（漢字）」「配達先苗字（かな）」「配達先名前（かな）」「販売店コード」「郵送区分」「支払方法」「購読料支払サイクル（月数）」「引落口座貯金種目」「引落口座支店コード」「引落口座支店名」「引落口座番号」「引落口座名義」「購読者層分類」「農業者分類」「購読開始日」「購読中止日」「備考」「読者情報変更適用日」</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
       <c r="C111" s="38" t="inlineStr">
         <is>
-          <t>1行目に48列のヘッダー文字列を以下の順序で書き込む（購読種別は画面ラジオの単一ソースのため列に含めない・v1.5）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="162" customHeight="1">
-      <c r="D112" s="38" t="inlineStr">
-        <is>
-          <t>「ID」「管理支店」「支店」「組合員コード」「購読者苗字（漢字）」「購読者名前（漢字）」「購読者苗字（かな）」「購読者名前（かな）」「購読部数」「新聞単価」「メールアドレス」「メールマガジン」「生年（西暦）」「性別」「郵便番号」「都道府県」「市町村郡」「丁目番地」「マンション・アパート名」「連絡先１」「連絡先２」「郵便番号(配達先)」「都道府県(配達先)」「市町村郡(配達先)」「丁目番地(配達先)」「ﾏﾝｼｮﾝ・ｱﾊﾟｰﾄ名(配達先)」「連絡先１(配達先)」「連絡先２(配達先)」「配達先苗字（漢字）」「配達先名前（漢字）」「配達先苗字（かな）」「配達先名前（かな）」「販売店コード」「郵送区分」「支払方法」「購読料支払サイクル（月数）」「引落口座貯金種目」「引落口座支店コード」「引落口座支店名」「引落口座番号」「引落口座名義」「購読者層分類」「農業者分類」「購読開始日」「購読中止日」「備考」「読者情報変更適用日」</t>
+          <t>ヘッダー行はボールドスタイル、背景色を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="72" customHeight="1">
+      <c r="C112" s="38" t="inlineStr">
+        <is>
+          <t>2行目に書式見本となるサンプルデータ行を1行書き込む（紙版(1)/新規(1)、購読部数&gt;0、性別1、かなはひらがな、郵便番号7桁、連絡先は半角数字、支払方法は現金集金(2)で引落口座不要、購読開始日は YYYY-MM-DD）。管理支店・支店・新聞単価・販売店コード等のFKコード列は自組織固有のため空欄とし、備考欄に「インポート前に書き換えてください。」と明記する。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="C113" s="38" t="inlineStr">
         <is>
-          <t>ヘッダー行はボールドスタイル、背景色を設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="72" customHeight="1">
+          <t>各列の幅を項目内容に合わせて自動調整する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="36" customHeight="1">
       <c r="C114" s="38" t="inlineStr">
         <is>
-          <t>2行目に書式見本となるサンプルデータ行を1行書き込む（紙版(1)/新規(1)、購読部数&gt;0、性別1、かなはひらがな、郵便番号7桁、連絡先は半角数字、支払方法は現金集金(2)で引落口座不要、購読開始日は YYYY-MM-DD）。管理支店・支店・新聞単価・販売店コード等のFKコード列は自組織固有のため空欄とし、備考欄に「インポート前に書き換えてください。」と明記する。</t>
+          <t>数字コードと文言の両方での取込みに対応するため、コードまたは文言のいずれかを入力可能とする旨を備考欄や説明シートで案内してもよい（例: 性別は「1」「男性」のいずれも可）。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="C115" s="38" t="inlineStr">
-        <is>
-          <t>各列の幅を項目内容に合わせて自動調整する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="36" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>4.4 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
       <c r="C116" s="38" t="inlineStr">
         <is>
-          <t>数字コードと文言の両方での取込みに対応するため、コードまたは文言のいずれかを入力可能とする旨を備考欄や説明シートで案内してもよい（例: 性別は「1」「男性」のいずれも可）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="B117" s="27" t="inlineStr">
-        <is>
-          <t>4.4 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
+          <t>生成したExcelファイルをバイナリデータとしてレスポンスに設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="C117" s="38" t="inlineStr">
+        <is>
+          <t>Content-Type: `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="36" customHeight="1">
       <c r="C118" s="38" t="inlineStr">
         <is>
-          <t>生成したExcelファイルをバイナリデータとしてレスポンスに設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="36" customHeight="1">
+          <t>Content-Disposition: `attachment; filename="購読者Excelデータ取込_テンプレート.xlsx"`</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
       <c r="C119" s="38" t="inlineStr">
         <is>
-          <t>Content-Type: `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="36" customHeight="1">
-      <c r="C120" s="38" t="inlineStr">
-        <is>
-          <t>Content-Disposition: `attachment; filename="購読者Excelデータ取込_テンプレート.xlsx"`</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
+          <t>HTTP 200 で返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>4.5 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
       <c r="C121" s="38" t="inlineStr">
         <is>
-          <t>HTTP 200 で返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="B122" s="27" t="inlineStr">
-        <is>
-          <t>4.5 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="36" customHeight="1">
-      <c r="C123" s="38" t="inlineStr">
-        <is>
           <t>ファイル生成エラー、DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="419">
+  <mergeCells count="407">
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="T53:X53"/>
-    <mergeCell ref="Q80:S80"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
@@ -8212,11 +8157,11 @@
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
-    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="Q77:S77"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="B115:AK115"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
@@ -8232,15 +8177,16 @@
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="C79:L79"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="C73:L73"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="T76:X76"/>
-    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="T69:X69"/>
+    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="T45:X45"/>
@@ -8259,7 +8205,6 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="B108:AK108"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="Y74:AE74"/>
@@ -8274,6 +8219,7 @@
     <mergeCell ref="Q62:S62"/>
     <mergeCell ref="C119:AK119"/>
     <mergeCell ref="C56:L56"/>
+    <mergeCell ref="B89:I89"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="Y25:AE25"/>
     <mergeCell ref="C43:L43"/>
@@ -8290,7 +8236,6 @@
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
-    <mergeCell ref="A98:AK98"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="C65:L65"/>
@@ -8298,7 +8243,6 @@
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C80:L80"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
@@ -8333,11 +8277,10 @@
     <mergeCell ref="C70:L70"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="B117:AK117"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
-    <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="C103:AK103"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="C118:AK118"/>
@@ -8356,18 +8299,17 @@
     <mergeCell ref="AF66:AK66"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
-    <mergeCell ref="B122:AK122"/>
-    <mergeCell ref="Y80:AE80"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
-    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="C116:AK116"/>
     <mergeCell ref="C78:L78"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
@@ -8379,10 +8321,8 @@
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="AF63:AK63"/>
-    <mergeCell ref="Q79:S79"/>
     <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Y61:AE61"/>
-    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="C66:L66"/>
@@ -8395,12 +8335,12 @@
     <mergeCell ref="T62:X62"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="T64:X64"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M80:P80"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
@@ -8408,13 +8348,14 @@
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="C74:L74"/>
-    <mergeCell ref="B88:I88"/>
     <mergeCell ref="C109:AK109"/>
-    <mergeCell ref="B82:I82"/>
     <mergeCell ref="Y62:AE62"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="M70:P70"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="Y21:AB21"/>
@@ -8423,19 +8364,18 @@
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T72:X72"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B85:I85"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
@@ -8456,10 +8396,10 @@
     <mergeCell ref="Q47:S47"/>
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="C55:L55"/>
+    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M36:P36"/>
-    <mergeCell ref="B91:I91"/>
     <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
@@ -8474,15 +8414,12 @@
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF40:AK40"/>
-    <mergeCell ref="T79:X79"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="Q55:S55"/>
@@ -8492,6 +8429,7 @@
     <mergeCell ref="C76:L76"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
@@ -8508,10 +8446,10 @@
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
+    <mergeCell ref="B92:I92"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="C40:L40"/>
-    <mergeCell ref="B94:I94"/>
     <mergeCell ref="C51:L51"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="C71:L71"/>
@@ -8519,7 +8457,6 @@
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
@@ -8534,10 +8471,8 @@
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="C59:L59"/>
-    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="C46:L46"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
@@ -8545,18 +8480,18 @@
     <mergeCell ref="C61:L61"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="AF62:AK62"/>
-    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="A23:AK23"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
     <mergeCell ref="AF64:AK64"/>
+    <mergeCell ref="A96:AK96"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="M79:P79"/>
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="M73:P73"/>
     <mergeCell ref="M60:P60"/>
@@ -8598,19 +8533,18 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="AF60:AK60"/>
+    <mergeCell ref="D110:AK110"/>
     <mergeCell ref="C58:L58"/>
     <mergeCell ref="B99:AK99"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="C110:AK110"/>
+    <mergeCell ref="B80:I80"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -8624,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK218"/>
+  <dimension ref="A1:AK222"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8785,7 +8719,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8909,7 +8843,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータを一括取込する（新規登録 / 全項目更新 / 入力箇所のみ更新）。1トランザクションで処理し、エラー時は全件ロールバック。一括中止の場合は組合員コードをキーに手続種類＝解約・購読中止日を設定して更新する。取り込みと同件数分のレコードを `t_dokusya_rireki` テーブルに追加する。</t>
+          <t>購読者Excelデータを一括取込する（新規登録 / 更新）。1トランザクションで処理し、エラー時は全件ロールバック。`dokusya_chushi_date` を指定した取込は**一括中止**（解約予約の作成）となる（→ §4.8）。取り込みと同件数分のレコードを `t_dokusya_rireki` テーブルに追加する。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -9657,13 +9591,15 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="31" t="n">
-        <v>2</v>
+    <row r="27" ht="72" customHeight="1">
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>selected_columns</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -9677,7 +9613,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
@@ -9685,34 +9621,36 @@
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="11" t="n"/>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="17" t="n">
-        <v>1</v>
+      <c r="Y27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="11" t="n"/>
       <c r="AC27" s="17" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>取込対象の列（物理カラム名）配列。新規登録モードでは必須列を必ず含むこと。</t>
+          <t>**読者情報変更適用日（top-level・v1.6 顧客要件 2026-08）**。画面の入力欄で指定し全取込行へ一律適用（Excel の列ではない）。`YYYY-MM-DD`。`UPDATE` で必須（電子版は当日固定のため省略可・BE が当日を補う）。`dokusya_chushi_date` とは**排他**。`NEW` では指定不可。</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -9721,13 +9659,15 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="B28" s="31" t="n">
-        <v>3</v>
+    <row r="28" ht="72" customHeight="1">
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>rows</t>
+          <t>dokusya_chushi_date</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -9741,7 +9681,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -9749,34 +9689,36 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="11" t="n"/>
       <c r="T28" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="n">
-        <v>1</v>
+      <c r="Y28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
       <c r="AB28" s="11" t="n"/>
       <c r="AC28" s="17" t="n">
-        <v>30000</v>
+        <v>10</v>
       </c>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>取込データ行の配列。30000件を超える場合は `ROW_LIMIT_EXCEEDED` を返却する。</t>
+          <t>**購読中止日（top-level・v1.6 顧客要件 2026-08）**。指定すると**一括中止**（解約予約の作成）になる（→ §4.8）。`YYYY-MM-DD`。`joho_henko_tekiyo_date` とは**排他**。`NEW` では指定不可。空文字による一括取消は受け付けない。</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -9787,11 +9729,11 @@
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_id</t>
+          <t>selected_columns</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -9805,7 +9747,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N29" s="10" t="n"/>
@@ -9813,38 +9755,34 @@
       <c r="P29" s="11" t="n"/>
       <c r="Q29" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R29" s="10" t="n"/>
       <c r="S29" s="11" t="n"/>
       <c r="T29" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U29" s="10" t="n"/>
       <c r="V29" s="10" t="n"/>
       <c r="W29" s="10" t="n"/>
       <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y29" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z29" s="10" t="n"/>
       <c r="AA29" s="10" t="n"/>
       <c r="AB29" s="11" t="n"/>
-      <c r="AC29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC29" s="17" t="n">
+        <v>46</v>
       </c>
       <c r="AD29" s="10" t="n"/>
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>購読者ID。`UPDATE` モード（組合員コード未指定時）はキー項目として必須。`NEW` モードは無視する。</t>
+          <t>取込対象の列（物理カラム名）配列。新規登録モードでは必須列を必ず含むこと。一括中止ではキー列（`dokusya_id`）以外は無視される。</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -9853,13 +9791,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="72" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>~~→dokusya_shubetsu~~（**列から撤去** v1.5）</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -9873,7 +9811,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -9881,38 +9819,34 @@
       <c r="P30" s="11" t="n"/>
       <c r="Q30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="11" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y30" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z30" s="10" t="n"/>
       <c r="AA30" s="10" t="n"/>
       <c r="AB30" s="11" t="n"/>
-      <c r="AC30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC30" s="17" t="n">
+        <v>30000</v>
       </c>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>購読種別は行データではなく top-level `dokusya_shubetsu`（#1a）で一律指定する（画面ラジオの単一ソース）。UPDATE では既存購読者の購読種別が選択値と異なる行を `IMPORT_VALIDATION_ERROR`（field=dokusya_shubetsu）で弾く。</t>
+          <t>取込データ行の配列。30000件を超える場合は `ROW_LIMIT_EXCEEDED` を返却する。</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -9923,11 +9857,11 @@
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>→tetsuzuki_shurui</t>
+          <t>→dokusya_id</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -9980,7 +9914,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）</t>
+          <t>購読者ID。`UPDATE` モード（組合員コード未指定時）はキー項目として必須。`NEW` モードは無視する。</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -9989,13 +9923,13 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="54" customHeight="1">
+    <row r="32" ht="72" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>→kanri_shiten_code</t>
+          <t>~~→dokusya_shubetsu~~（**列から撤去** v1.5）</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -10009,7 +9943,7 @@
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
@@ -10031,20 +9965,24 @@
       <c r="V32" s="10" t="n"/>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="n">
-        <v>0</v>
+      <c r="Y32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="11" t="n"/>
-      <c r="AC32" s="17" t="n">
-        <v>20</v>
+      <c r="AC32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>管理支店コード。自JA内の m_kanri_shiten.kanri_shiten_code を解決し t_dokusya.kanri_shiten_id へ保存。`NEW` モードは必須。</t>
+          <t>購読種別は行データではなく top-level `dokusya_shubetsu`（#1a）で一律指定する（画面ラジオの単一ソース）。UPDATE では既存購読者の購読種別が選択値と異なる行を `IMPORT_VALIDATION_ERROR`（field=dokusya_shubetsu）で弾く。</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -10055,11 +9993,11 @@
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>→shiten_code</t>
+          <t>→tetsuzuki_shurui</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -10073,7 +10011,7 @@
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N33" s="10" t="n"/>
@@ -10095,20 +10033,24 @@
       <c r="V33" s="10" t="n"/>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="17" t="n">
-        <v>0</v>
+      <c r="Y33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="11" t="n"/>
-      <c r="AC33" s="17" t="n">
-        <v>20</v>
+      <c r="AC33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>支店コード。自JA内の m_shiten.shiten_code を解決し t_dokusya.shiten_id へ保存。</t>
+          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -10117,13 +10059,13 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="54" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>→kumiaiin_code</t>
+          <t>→kanri_shiten_code</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -10172,7 +10114,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>組合員コード。一括中止時にキー項目として必須。</t>
+          <t>管理支店コード。自JA内の m_kanri_shiten.kanri_shiten_code を解決し t_dokusya.kanri_shiten_id へ保存。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -10181,13 +10123,13 @@
       <c r="AJ34" s="10" t="n"/>
       <c r="AK34" s="11" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1">
+    <row r="35" ht="36" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>→shimei_sei</t>
+          <t>→shiten_code</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
@@ -10230,13 +10172,13 @@
       <c r="AA35" s="10" t="n"/>
       <c r="AB35" s="11" t="n"/>
       <c r="AC35" s="17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>氏名（姓・漢字）</t>
+          <t>支店コード。自JA内の m_shiten.shiten_code を解決し t_dokusya.shiten_id へ保存。</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -10247,11 +10189,11 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>→shimei_mei</t>
+          <t>→kumiaiin_code</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -10294,13 +10236,13 @@
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="11" t="n"/>
       <c r="AC36" s="17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>氏名（名・漢字）</t>
+          <t>組合員コード。UPDATE で ID が空のときの代替キー。</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -10311,11 +10253,11 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>→shimei_kana_sei</t>
+          <t>→shimei_sei</t>
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -10358,13 +10300,13 @@
       <c r="AA37" s="10" t="n"/>
       <c r="AB37" s="11" t="n"/>
       <c r="AC37" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>氏名かな（姓）</t>
+          <t>氏名（姓・漢字）</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -10375,11 +10317,11 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>→shimei_kana_mei</t>
+          <t>→shimei_mei</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -10422,13 +10364,13 @@
       <c r="AA38" s="10" t="n"/>
       <c r="AB38" s="11" t="n"/>
       <c r="AC38" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>氏名かな（名）</t>
+          <t>氏名（名・漢字）</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -10437,13 +10379,13 @@
       <c r="AJ38" s="10" t="n"/>
       <c r="AK38" s="11" t="n"/>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_busu</t>
+          <t>→shimei_kana_sei</t>
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
@@ -10457,7 +10399,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -10479,24 +10421,20 @@
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="11" t="n"/>
-      <c r="Y39" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z39" s="10" t="n"/>
       <c r="AA39" s="10" t="n"/>
       <c r="AB39" s="11" t="n"/>
-      <c r="AC39" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC39" s="17" t="n">
+        <v>100</v>
       </c>
       <c r="AD39" s="10" t="n"/>
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>購読部数。`NEW`：&gt; 0、解約時：= 0。**電子版(2)は 1 固定**（v1.4・UI/一括置換と統一）。</t>
+          <t>氏名かな（姓）</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -10505,13 +10443,13 @@
       <c r="AJ39" s="10" t="n"/>
       <c r="AK39" s="11" t="n"/>
     </row>
-    <row r="40" ht="36" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>→tanka_code</t>
+          <t>→shimei_kana_mei</t>
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
@@ -10554,13 +10492,13 @@
       <c r="AA40" s="10" t="n"/>
       <c r="AB40" s="11" t="n"/>
       <c r="AC40" s="17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>新聞単価コード（m_tanka の tanka_code・tanka_type=1 で解決）。`NEW` モードは必須。</t>
+          <t>氏名かな（名）</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -10569,13 +10507,13 @@
       <c r="AJ40" s="10" t="n"/>
       <c r="AK40" s="11" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1">
+    <row r="41" ht="36" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>→email</t>
+          <t>→dokusya_busu</t>
         </is>
       </c>
       <c r="D41" s="10" t="n"/>
@@ -10589,7 +10527,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -10611,20 +10549,24 @@
       <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
       <c r="X41" s="11" t="n"/>
-      <c r="Y41" s="17" t="n">
-        <v>0</v>
+      <c r="Y41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z41" s="10" t="n"/>
       <c r="AA41" s="10" t="n"/>
       <c r="AB41" s="11" t="n"/>
-      <c r="AC41" s="17" t="n">
-        <v>100</v>
+      <c r="AC41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>メールアドレス。メール形式チェック。</t>
+          <t>購読部数。`NEW`：&gt; 0、解約時：= 0。**電子版(2)は 1 固定**（v1.4・UI/一括置換と統一）。</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -10635,11 +10577,11 @@
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>→mail_magazine_flg</t>
+          <t>→tanka_code</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -10653,7 +10595,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -10675,24 +10617,20 @@
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n"/>
-      <c r="Y42" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y42" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z42" s="10" t="n"/>
       <c r="AA42" s="10" t="n"/>
       <c r="AB42" s="11" t="n"/>
-      <c r="AC42" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC42" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="AD42" s="10" t="n"/>
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>メールマガジン ※m_code.code_category='MAIL_MAGAZINE_FLG'を参照（0:配信しない, 1:配信する）</t>
+          <t>新聞単価コード（m_tanka の tanka_code・tanka_type=1 で解決）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -10703,11 +10641,11 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>→birth_year</t>
+          <t>→email</t>
         </is>
       </c>
       <c r="D43" s="10" t="n"/>
@@ -10721,7 +10659,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -10743,24 +10681,20 @@
       <c r="V43" s="10" t="n"/>
       <c r="W43" s="10" t="n"/>
       <c r="X43" s="11" t="n"/>
-      <c r="Y43" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y43" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z43" s="10" t="n"/>
       <c r="AA43" s="10" t="n"/>
       <c r="AB43" s="11" t="n"/>
-      <c r="AC43" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC43" s="17" t="n">
+        <v>100</v>
       </c>
       <c r="AD43" s="10" t="n"/>
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>生年（西暦、1900〜現在年）</t>
+          <t>メールアドレス。メール形式チェック。</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -10771,11 +10705,11 @@
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>→gender</t>
+          <t>→mail_magazine_flg</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -10828,7 +10762,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>性別 ※m_code.code_category='GENDER'を参照（1:男性, 2:女性, 9:回答しない）。文言（「男性」「女性」「回答しない」）でも取込可。</t>
+          <t>メールマガジン ※m_code.code_category='MAIL_MAGAZINE_FLG'を参照（0:配信しない, 1:配信する）</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -10839,11 +10773,11 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>→yubin_no</t>
+          <t>→birth_year</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -10857,7 +10791,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -10879,20 +10813,24 @@
       <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
       <c r="X45" s="11" t="n"/>
-      <c r="Y45" s="17" t="n">
-        <v>7</v>
+      <c r="Y45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="11" t="n"/>
-      <c r="AC45" s="17" t="n">
-        <v>7</v>
+      <c r="AC45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>郵便番号（ハイフン除去、7桁固定）。`NEW` モードは必須。</t>
+          <t>生年（西暦、1900〜現在年）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -10901,13 +10839,13 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>→todofuken_code</t>
+          <t>→gender</t>
         </is>
       </c>
       <c r="D46" s="10" t="n"/>
@@ -10921,7 +10859,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -10943,20 +10881,24 @@
       <c r="V46" s="10" t="n"/>
       <c r="W46" s="10" t="n"/>
       <c r="X46" s="11" t="n"/>
-      <c r="Y46" s="17" t="n">
-        <v>2</v>
+      <c r="Y46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
       <c r="AB46" s="11" t="n"/>
-      <c r="AC46" s="17" t="n">
-        <v>2</v>
+      <c r="AC46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD46" s="10" t="n"/>
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード（2桁）。`NEW` モードは必須。</t>
+          <t>性別 ※m_code.code_category='GENDER'を参照（1:男性, 2:女性, 9:回答しない）。文言（「男性」「女性」「回答しない」）でも取込可。</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -10967,11 +10909,11 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>→shikuchoson</t>
+          <t>→yubin_no</t>
         </is>
       </c>
       <c r="D47" s="10" t="n"/>
@@ -11008,19 +10950,19 @@
       <c r="W47" s="10" t="n"/>
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z47" s="10" t="n"/>
       <c r="AA47" s="10" t="n"/>
       <c r="AB47" s="11" t="n"/>
       <c r="AC47" s="17" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="AD47" s="10" t="n"/>
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>市町村郡。`NEW` モードは必須。</t>
+          <t>郵便番号（ハイフン除去、7桁固定）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -11031,11 +10973,11 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>→chome_banchi</t>
+          <t>→todofuken_code</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -11072,19 +11014,19 @@
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z48" s="10" t="n"/>
       <c r="AA48" s="10" t="n"/>
       <c r="AB48" s="11" t="n"/>
       <c r="AC48" s="17" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AD48" s="10" t="n"/>
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>丁目番地。`NEW` モードは必須。</t>
+          <t>都道府県コード（2桁）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -11095,11 +11037,11 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>→tatemono_mei</t>
+          <t>→shikuchoson</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -11148,7 +11090,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>マンション・アパート名</t>
+          <t>市町村郡。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -11159,11 +11101,11 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>→renrakusaki_1</t>
+          <t>→chome_banchi</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -11206,13 +11148,13 @@
       <c r="AA50" s="10" t="n"/>
       <c r="AB50" s="11" t="n"/>
       <c r="AC50" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD50" s="10" t="n"/>
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>連絡先１（数字のみ保存）。`NEW` モードは必須。</t>
+          <t>丁目番地。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -11223,11 +11165,11 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>→renrakusaki_2</t>
+          <t>→tatemono_mei</t>
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
@@ -11270,13 +11212,13 @@
       <c r="AA51" s="10" t="n"/>
       <c r="AB51" s="11" t="n"/>
       <c r="AC51" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>連絡先２（数字のみ保存）</t>
+          <t>マンション・アパート名</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -11287,11 +11229,11 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_yubin_no</t>
+          <t>→renrakusaki_1</t>
         </is>
       </c>
       <c r="D52" s="10" t="n"/>
@@ -11334,13 +11276,13 @@
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="11" t="n"/>
       <c r="AC52" s="17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AD52" s="10" t="n"/>
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>配達先郵便番号</t>
+          <t>連絡先１（数字のみ保存）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -11351,11 +11293,11 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_todofuken_code</t>
+          <t>→renrakusaki_2</t>
         </is>
       </c>
       <c r="D53" s="10" t="n"/>
@@ -11398,13 +11340,13 @@
       <c r="AA53" s="10" t="n"/>
       <c r="AB53" s="11" t="n"/>
       <c r="AC53" s="17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>配達先都道府県コード</t>
+          <t>連絡先２（数字のみ保存）</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -11415,11 +11357,11 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shikuchoson</t>
+          <t>→haitatsu_yubin_no</t>
         </is>
       </c>
       <c r="D54" s="10" t="n"/>
@@ -11462,13 +11404,13 @@
       <c r="AA54" s="10" t="n"/>
       <c r="AB54" s="11" t="n"/>
       <c r="AC54" s="17" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="AD54" s="10" t="n"/>
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>配達先市町村郡</t>
+          <t>配達先郵便番号</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -11479,11 +11421,11 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_chome_banchi</t>
+          <t>→haitatsu_todofuken_code</t>
         </is>
       </c>
       <c r="D55" s="10" t="n"/>
@@ -11526,13 +11468,13 @@
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="11" t="n"/>
       <c r="AC55" s="17" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AD55" s="10" t="n"/>
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>配達先丁目番地</t>
+          <t>配達先都道府県コード</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -11543,11 +11485,11 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_tatemono_mei</t>
+          <t>→haitatsu_shikuchoson</t>
         </is>
       </c>
       <c r="D56" s="10" t="n"/>
@@ -11596,7 +11538,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>配達先建物名</t>
+          <t>配達先市町村郡</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -11607,11 +11549,11 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_renrakusaki_1</t>
+          <t>→haitatsu_chome_banchi</t>
         </is>
       </c>
       <c r="D57" s="10" t="n"/>
@@ -11654,13 +11596,13 @@
       <c r="AA57" s="10" t="n"/>
       <c r="AB57" s="11" t="n"/>
       <c r="AC57" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD57" s="10" t="n"/>
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>配達先連絡先１</t>
+          <t>配達先丁目番地</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -11671,11 +11613,11 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_renrakusaki_2</t>
+          <t>→haitatsu_tatemono_mei</t>
         </is>
       </c>
       <c r="D58" s="10" t="n"/>
@@ -11718,13 +11660,13 @@
       <c r="AA58" s="10" t="n"/>
       <c r="AB58" s="11" t="n"/>
       <c r="AC58" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD58" s="10" t="n"/>
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>配達先連絡先２</t>
+          <t>配達先建物名</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -11735,11 +11677,11 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_sei</t>
+          <t>→haitatsu_renrakusaki_1</t>
         </is>
       </c>
       <c r="D59" s="10" t="n"/>
@@ -11782,13 +11724,13 @@
       <c r="AA59" s="10" t="n"/>
       <c r="AB59" s="11" t="n"/>
       <c r="AC59" s="17" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AD59" s="10" t="n"/>
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名（姓・漢字）</t>
+          <t>配達先連絡先１</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -11799,11 +11741,11 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_mei</t>
+          <t>→haitatsu_renrakusaki_2</t>
         </is>
       </c>
       <c r="D60" s="10" t="n"/>
@@ -11846,13 +11788,13 @@
       <c r="AA60" s="10" t="n"/>
       <c r="AB60" s="11" t="n"/>
       <c r="AC60" s="17" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AD60" s="10" t="n"/>
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名（名・漢字）</t>
+          <t>配達先連絡先２</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -11863,11 +11805,11 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_kana_sei</t>
+          <t>→haitatsu_shimei_sei</t>
         </is>
       </c>
       <c r="D61" s="10" t="n"/>
@@ -11910,13 +11852,13 @@
       <c r="AA61" s="10" t="n"/>
       <c r="AB61" s="11" t="n"/>
       <c r="AC61" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD61" s="10" t="n"/>
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名かな（姓）</t>
+          <t>配達先氏名（姓・漢字）</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -11927,11 +11869,11 @@
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>→haitatsu_shimei_kana_mei</t>
+          <t>→haitatsu_shimei_mei</t>
         </is>
       </c>
       <c r="D62" s="10" t="n"/>
@@ -11974,13 +11916,13 @@
       <c r="AA62" s="10" t="n"/>
       <c r="AB62" s="11" t="n"/>
       <c r="AC62" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD62" s="10" t="n"/>
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名かな（名）</t>
+          <t>配達先氏名（名・漢字）</t>
         </is>
       </c>
       <c r="AG62" s="10" t="n"/>
@@ -11989,13 +11931,13 @@
       <c r="AJ62" s="10" t="n"/>
       <c r="AK62" s="11" t="n"/>
     </row>
-    <row r="63" ht="36" customHeight="1">
+    <row r="63" ht="18" customHeight="1">
       <c r="B63" s="31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>→hanbaiten_code</t>
+          <t>→haitatsu_shimei_kana_sei</t>
         </is>
       </c>
       <c r="D63" s="10" t="n"/>
@@ -12038,13 +11980,13 @@
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="11" t="n"/>
       <c r="AC63" s="17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AD63" s="10" t="n"/>
       <c r="AE63" s="11" t="n"/>
       <c r="AF63" s="19" t="inlineStr">
         <is>
-          <t>販売店コード（m_hanbaiten の hanbaiten_code で解決）。`NEW` モードは必須。</t>
+          <t>配達先氏名かな（姓）</t>
         </is>
       </c>
       <c r="AG63" s="10" t="n"/>
@@ -12053,13 +11995,13 @@
       <c r="AJ63" s="10" t="n"/>
       <c r="AK63" s="11" t="n"/>
     </row>
-    <row r="64" ht="36" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="B64" s="31" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>→yubin_kubun</t>
+          <t>→haitatsu_shimei_kana_mei</t>
         </is>
       </c>
       <c r="D64" s="10" t="n"/>
@@ -12102,13 +12044,13 @@
       <c r="AA64" s="10" t="n"/>
       <c r="AB64" s="11" t="n"/>
       <c r="AC64" s="17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AD64" s="10" t="n"/>
       <c r="AE64" s="11" t="n"/>
       <c r="AF64" s="19" t="inlineStr">
         <is>
-          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
+          <t>配達先氏名かな（名）</t>
         </is>
       </c>
       <c r="AG64" s="10" t="n"/>
@@ -12117,13 +12059,13 @@
       <c r="AJ64" s="10" t="n"/>
       <c r="AK64" s="11" t="n"/>
     </row>
-    <row r="65" ht="54" customHeight="1">
+    <row r="65" ht="36" customHeight="1">
       <c r="B65" s="31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>→shiharai_hoho</t>
+          <t>→hanbaiten_code</t>
         </is>
       </c>
       <c r="D65" s="10" t="n"/>
@@ -12137,7 +12079,7 @@
       <c r="L65" s="11" t="n"/>
       <c r="M65" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N65" s="10" t="n"/>
@@ -12159,24 +12101,20 @@
       <c r="V65" s="10" t="n"/>
       <c r="W65" s="10" t="n"/>
       <c r="X65" s="11" t="n"/>
-      <c r="Y65" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z65" s="10" t="n"/>
       <c r="AA65" s="10" t="n"/>
       <c r="AB65" s="11" t="n"/>
-      <c r="AC65" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC65" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="AD65" s="10" t="n"/>
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1:口座引落, 2:現金集金, 3:振込集金, 4:JA施設等, 5:給与天引き, 6:クレジットカード, 9:その他）。`NEW` モードは必須。</t>
+          <t>販売店コード（m_hanbaiten の hanbaiten_code で解決）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -12185,13 +12123,13 @@
       <c r="AJ65" s="10" t="n"/>
       <c r="AK65" s="11" t="n"/>
     </row>
-    <row r="66" ht="18" customHeight="1">
+    <row r="66" ht="36" customHeight="1">
       <c r="B66" s="31" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>→dokusyaryo_shiharai_cycle</t>
+          <t>→yubin_kubun</t>
         </is>
       </c>
       <c r="D66" s="10" t="n"/>
@@ -12205,7 +12143,7 @@
       <c r="L66" s="11" t="n"/>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N66" s="10" t="n"/>
@@ -12227,24 +12165,20 @@
       <c r="V66" s="10" t="n"/>
       <c r="W66" s="10" t="n"/>
       <c r="X66" s="11" t="n"/>
-      <c r="Y66" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y66" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z66" s="10" t="n"/>
       <c r="AA66" s="10" t="n"/>
       <c r="AB66" s="11" t="n"/>
-      <c r="AC66" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC66" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="AD66" s="10" t="n"/>
       <c r="AE66" s="11" t="n"/>
       <c r="AF66" s="19" t="inlineStr">
         <is>
-          <t>購読料支払サイクル（月数）</t>
+          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
         </is>
       </c>
       <c r="AG66" s="10" t="n"/>
@@ -12253,13 +12187,13 @@
       <c r="AJ66" s="10" t="n"/>
       <c r="AK66" s="11" t="n"/>
     </row>
-    <row r="67" ht="36" customHeight="1">
+    <row r="67" ht="54" customHeight="1">
       <c r="B67" s="31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>→hikiotoshi_yokin_shubetsu</t>
+          <t>→shiharai_hoho</t>
         </is>
       </c>
       <c r="D67" s="10" t="n"/>
@@ -12312,7 +12246,7 @@
       <c r="AE67" s="11" t="n"/>
       <c r="AF67" s="19" t="inlineStr">
         <is>
-          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）。文言（「普通」「当座」）でも取込可。</t>
+          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1:口座引落, 2:現金集金, 3:振込集金, 4:JA施設等, 5:給与天引き, 6:クレジットカード, 9:その他）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG67" s="10" t="n"/>
@@ -12323,11 +12257,11 @@
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="31" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>→bank_branch_code</t>
+          <t>→dokusyaryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="D68" s="10" t="n"/>
@@ -12341,7 +12275,7 @@
       <c r="L68" s="11" t="n"/>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N68" s="10" t="n"/>
@@ -12363,20 +12297,24 @@
       <c r="V68" s="10" t="n"/>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="11" t="n"/>
-      <c r="Y68" s="17" t="n">
-        <v>0</v>
+      <c r="Y68" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z68" s="10" t="n"/>
       <c r="AA68" s="10" t="n"/>
       <c r="AB68" s="11" t="n"/>
-      <c r="AC68" s="17" t="n">
-        <v>3</v>
+      <c r="AC68" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD68" s="10" t="n"/>
       <c r="AE68" s="11" t="n"/>
       <c r="AF68" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店コード</t>
+          <t>購読料支払サイクル（月数）</t>
         </is>
       </c>
       <c r="AG68" s="10" t="n"/>
@@ -12385,13 +12323,13 @@
       <c r="AJ68" s="10" t="n"/>
       <c r="AK68" s="11" t="n"/>
     </row>
-    <row r="69" ht="18" customHeight="1">
+    <row r="69" ht="36" customHeight="1">
       <c r="B69" s="31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>→bank_branch_name</t>
+          <t>→hikiotoshi_yokin_shubetsu</t>
         </is>
       </c>
       <c r="D69" s="10" t="n"/>
@@ -12405,7 +12343,7 @@
       <c r="L69" s="11" t="n"/>
       <c r="M69" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N69" s="10" t="n"/>
@@ -12427,20 +12365,24 @@
       <c r="V69" s="10" t="n"/>
       <c r="W69" s="10" t="n"/>
       <c r="X69" s="11" t="n"/>
-      <c r="Y69" s="17" t="n">
-        <v>0</v>
+      <c r="Y69" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z69" s="10" t="n"/>
       <c r="AA69" s="10" t="n"/>
       <c r="AB69" s="11" t="n"/>
-      <c r="AC69" s="17" t="n">
-        <v>100</v>
+      <c r="AC69" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD69" s="10" t="n"/>
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店名</t>
+          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）。文言（「普通」「当座」）でも取込可。</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -12451,11 +12393,11 @@
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="31" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>→hikiotoshi_koza_no</t>
+          <t>→bank_branch_code</t>
         </is>
       </c>
       <c r="D70" s="10" t="n"/>
@@ -12498,13 +12440,13 @@
       <c r="AA70" s="10" t="n"/>
       <c r="AB70" s="11" t="n"/>
       <c r="AC70" s="17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AD70" s="10" t="n"/>
       <c r="AE70" s="11" t="n"/>
       <c r="AF70" s="19" t="inlineStr">
         <is>
-          <t>引落口座番号</t>
+          <t>引落口座支店コード</t>
         </is>
       </c>
       <c r="AG70" s="10" t="n"/>
@@ -12515,11 +12457,11 @@
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>→hikiotoshi_koza_meigi</t>
+          <t>→bank_branch_name</t>
         </is>
       </c>
       <c r="D71" s="10" t="n"/>
@@ -12562,13 +12504,13 @@
       <c r="AA71" s="10" t="n"/>
       <c r="AB71" s="11" t="n"/>
       <c r="AC71" s="17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AD71" s="10" t="n"/>
       <c r="AE71" s="11" t="n"/>
       <c r="AF71" s="19" t="inlineStr">
         <is>
-          <t>引落口座名義（全角カナ→半角カナに変換して保存）</t>
+          <t>引落口座支店名</t>
         </is>
       </c>
       <c r="AG71" s="10" t="n"/>
@@ -12579,11 +12521,11 @@
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="31" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>→dokusyaso_bunrui</t>
+          <t>→hikiotoshi_koza_no</t>
         </is>
       </c>
       <c r="D72" s="10" t="n"/>
@@ -12626,13 +12568,13 @@
       <c r="AA72" s="10" t="n"/>
       <c r="AB72" s="11" t="n"/>
       <c r="AC72" s="17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AD72" s="10" t="n"/>
       <c r="AE72" s="11" t="n"/>
       <c r="AF72" s="19" t="inlineStr">
         <is>
-          <t>購読者層分類（カンマ区切り）</t>
+          <t>引落口座番号</t>
         </is>
       </c>
       <c r="AG72" s="10" t="n"/>
@@ -12643,11 +12585,11 @@
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="31" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>→nogyosya_bunrui</t>
+          <t>→hikiotoshi_koza_meigi</t>
         </is>
       </c>
       <c r="D73" s="10" t="n"/>
@@ -12696,7 +12638,7 @@
       <c r="AE73" s="11" t="n"/>
       <c r="AF73" s="19" t="inlineStr">
         <is>
-          <t>農業者分類（カンマ区切り）</t>
+          <t>引落口座名義（全角カナ→半角カナに変換して保存）</t>
         </is>
       </c>
       <c r="AG73" s="10" t="n"/>
@@ -12707,11 +12649,11 @@
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="31" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_kaishi_date</t>
+          <t>→dokusyaso_bunrui</t>
         </is>
       </c>
       <c r="D74" s="10" t="n"/>
@@ -12747,22 +12689,20 @@
       <c r="V74" s="10" t="n"/>
       <c r="W74" s="10" t="n"/>
       <c r="X74" s="11" t="n"/>
-      <c r="Y74" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y74" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z74" s="10" t="n"/>
       <c r="AA74" s="10" t="n"/>
       <c r="AB74" s="11" t="n"/>
       <c r="AC74" s="17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD74" s="10" t="n"/>
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（YYYY-MM-DD）。`NEW` モードは必須。</t>
+          <t>購読者層分類（カンマ区切り）</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -12773,11 +12713,11 @@
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_chushi_date</t>
+          <t>→nogyosya_bunrui</t>
         </is>
       </c>
       <c r="D75" s="10" t="n"/>
@@ -12813,22 +12753,20 @@
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="11" t="n"/>
-      <c r="Y75" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="11" t="n"/>
       <c r="AC75" s="17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>購読中止日（YYYY-MM-DD）</t>
+          <t>農業者分類（カンマ区切り）</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -12839,11 +12777,11 @@
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="31" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>→biko</t>
+          <t>→dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="D76" s="10" t="n"/>
@@ -12887,16 +12825,14 @@
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
       <c r="AB76" s="11" t="n"/>
-      <c r="AC76" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC76" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>購読開始日（YYYY-MM-DD）。`NEW` モードは必須。</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -12905,13 +12841,13 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="36" customHeight="1">
+    <row r="77" ht="18" customHeight="1">
       <c r="B77" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>→joho_henko_tekiyo_date</t>
+          <t>→biko</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -12955,14 +12891,16 @@
       <c r="Z77" s="10" t="n"/>
       <c r="AA77" s="10" t="n"/>
       <c r="AB77" s="11" t="n"/>
-      <c r="AC77" s="17" t="n">
-        <v>10</v>
+      <c r="AC77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD77" s="10" t="n"/>
       <c r="AE77" s="11" t="n"/>
       <c r="AF77" s="19" t="inlineStr">
         <is>
-          <t>読者情報変更適用日（YYYY-MM-DD）。UPDATE 必須。日付ルールは種別依存（v1.4）：紙版=当日/未来（帳票影響項目は未来のみ）、電子版=当日のみ。</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG77" s="10" t="n"/>
@@ -15514,8 +15452,36 @@
       <c r="AJ218" s="10" t="n"/>
       <c r="AK218" s="11" t="n"/>
     </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="B219" s="27" t="inlineStr">
+        <is>
+          <t>4.8 一括中止（`dokusya_chushi_date` 指定時・v1.6 顧客要件 2026-08）</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="36" customHeight="1">
+      <c r="C220" s="38" t="inlineStr">
+        <is>
+          <t>対象は `dokusya_id`（無い行は `kumiaiin_code`）で特定し、行ロックのうえ**解約予約の履歴を1件 append** する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="36" customHeight="1">
+      <c r="C221" s="38" t="inlineStr">
+        <is>
+          <t>**`selected_columns` に他の列が入っていても書き込まない**（画面も列グリッドをキー列へ縮退させるが、直接呼ばれても同じ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="36" customHeight="1">
+      <c r="C222" s="38" t="inlineStr">
+        <is>
+          <t>中止日は予約時点で `t_dokusya.dokusya_chushi_date` へ反映し、一覧（SCR-014）・詳細（SCR-011）に即時表示する。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="606">
+  <mergeCells count="610">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="C174:AK174"/>
     <mergeCell ref="AF65:AK65"/>
@@ -15560,6 +15526,7 @@
     <mergeCell ref="AC58:AE58"/>
     <mergeCell ref="AC39:AE39"/>
     <mergeCell ref="T38:X38"/>
+    <mergeCell ref="C220:AK220"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="C195:AK195"/>
@@ -15783,6 +15750,7 @@
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="C222:AK222"/>
     <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="AC32:AE32"/>
@@ -16033,6 +16001,7 @@
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="Y72:AB72"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="C221:AK221"/>
     <mergeCell ref="C196:AK196"/>
     <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
@@ -16092,6 +16061,7 @@
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B219:AK219"/>
     <mergeCell ref="Q88:S88"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="C82:L82"/>

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1866,14 +1866,67 @@
       <c r="AF8" s="10" t="n"/>
       <c r="AG8" s="11" t="n"/>
     </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08（#56568）：電子版・併読レコードのメールアドレス重複チェックを **JA 横断** に変更。取込前の既存メール事前ロードから `ja_id` 条件を外し、他 JA の電子版・併読レコードとも突き合わせる（電子版ではメールが会員の同定キー＝ログインIDのため）。同一取込バッチ内の重複検知は従来どおり。紙版は対象外、論理削除済みは再利用可。SCR-011 画面登録と同一ルール。</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="17" t="inlineStr"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="17" t="inlineStr"/>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="63">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="R5:V5"/>
     <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
@@ -1897,6 +1950,8 @@
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K9:Q9"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
@@ -1913,15 +1968,18 @@
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W9:AA9"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
+    <mergeCell ref="H9:J9"/>
     <mergeCell ref="K8:Q8"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="R9:V9"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
@@ -2096,7 +2154,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2612,7 +2670,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3484,7 +3542,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3758,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3919,7 +3977,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7530,7 +7588,7 @@
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>農業者分類</t>
+          <t>かつJAグループ役職員</t>
         </is>
       </c>
       <c r="D76" s="10" t="n"/>
@@ -7544,7 +7602,7 @@
       <c r="L76" s="11" t="n"/>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>農業者分類</t>
+          <t>かつJAグループ役職員</t>
         </is>
       </c>
       <c r="N76" s="10" t="n"/>
@@ -7552,22 +7610,24 @@
       <c r="P76" s="11" t="n"/>
       <c r="Q76" s="17" t="inlineStr">
         <is>
-          <t>nogyosya_bunrui</t>
+          <t>ja_yakushokuin_flg</t>
         </is>
       </c>
       <c r="R76" s="10" t="n"/>
       <c r="S76" s="11" t="n"/>
       <c r="T76" s="17" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="11" t="n"/>
-      <c r="Y76" s="17" t="n">
-        <v>50</v>
+      <c r="Y76" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
@@ -7588,7 +7648,7 @@
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>購読開始日</t>
+          <t>農業関係</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -7602,7 +7662,7 @@
       <c r="L77" s="11" t="n"/>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>購読開始日</t>
+          <t>農業関係</t>
         </is>
       </c>
       <c r="N77" s="10" t="n"/>
@@ -7610,14 +7670,14 @@
       <c r="P77" s="11" t="n"/>
       <c r="Q77" s="17" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date</t>
+          <t>nogyo_kankei_flg</t>
         </is>
       </c>
       <c r="R77" s="10" t="n"/>
       <c r="S77" s="11" t="n"/>
       <c r="T77" s="17" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="U77" s="10" t="n"/>
@@ -7648,7 +7708,7 @@
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>読者属性（その他の内容）</t>
         </is>
       </c>
       <c r="D78" s="10" t="n"/>
@@ -7662,7 +7722,7 @@
       <c r="L78" s="11" t="n"/>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>購読者層分類その他</t>
         </is>
       </c>
       <c r="N78" s="10" t="n"/>
@@ -7670,24 +7730,22 @@
       <c r="P78" s="11" t="n"/>
       <c r="Q78" s="17" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>dokusyaso_bunrui_sonota</t>
         </is>
       </c>
       <c r="R78" s="10" t="n"/>
       <c r="S78" s="11" t="n"/>
       <c r="T78" s="17" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR</t>
         </is>
       </c>
       <c r="U78" s="10" t="n"/>
       <c r="V78" s="10" t="n"/>
       <c r="W78" s="10" t="n"/>
       <c r="X78" s="11" t="n"/>
-      <c r="Y78" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y78" s="17" t="n">
+        <v>255</v>
       </c>
       <c r="Z78" s="10" t="n"/>
       <c r="AA78" s="10" t="n"/>
@@ -7702,18 +7760,129 @@
       <c r="AJ78" s="10" t="n"/>
       <c r="AK78" s="11" t="n"/>
     </row>
-    <row r="79" ht="19.5" customHeight="1"/>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="B80" s="37" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="31" t="n">
+        <v>48</v>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>農業者分類</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="11" t="n"/>
+      <c r="M79" s="17" t="inlineStr">
+        <is>
+          <t>農業者分類</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="17" t="inlineStr">
+        <is>
+          <t>nogyosya_bunrui</t>
+        </is>
+      </c>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="17" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="11" t="n"/>
+      <c r="Y79" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="11" t="n"/>
+      <c r="AF79" s="19" t="inlineStr"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="31" t="n">
+        <v>49</v>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>主な生産物（その他の内容）</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="17" t="inlineStr">
+        <is>
+          <t>農業者分類その他</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="11" t="n"/>
+      <c r="Q80" s="17" t="inlineStr">
+        <is>
+          <t>nogyosya_bunrui_sonota</t>
+        </is>
+      </c>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="11" t="n"/>
+      <c r="T80" s="17" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="11" t="n"/>
+      <c r="Y80" s="17" t="n">
+        <v>255</v>
+      </c>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="11" t="n"/>
+      <c r="AF80" s="19" t="inlineStr"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="31" t="n">
+        <v>50</v>
+      </c>
       <c r="C81" s="19" t="inlineStr">
         <is>
-          <t>GET /api/v1/dokusya/import/template</t>
+          <t>購読開始日</t>
         </is>
       </c>
       <c r="D81" s="10" t="n"/>
@@ -7724,42 +7893,167 @@
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="17" t="inlineStr">
+        <is>
+          <t>購読開始日</t>
+        </is>
+      </c>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
+      <c r="P81" s="11" t="n"/>
+      <c r="Q81" s="17" t="inlineStr">
+        <is>
+          <t>dokusya_kaishi_date</t>
+        </is>
+      </c>
       <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="10" t="n"/>
+      <c r="S81" s="11" t="n"/>
+      <c r="T81" s="17" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
       <c r="W81" s="10" t="n"/>
-      <c r="X81" s="10" t="n"/>
-      <c r="Y81" s="10" t="n"/>
+      <c r="X81" s="11" t="n"/>
+      <c r="Y81" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z81" s="10" t="n"/>
       <c r="AA81" s="10" t="n"/>
       <c r="AB81" s="10" t="n"/>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
-      <c r="AE81" s="10" t="n"/>
-      <c r="AF81" s="10" t="n"/>
+      <c r="AE81" s="11" t="n"/>
+      <c r="AF81" s="19" t="inlineStr"/>
       <c r="AG81" s="10" t="n"/>
       <c r="AH81" s="10" t="n"/>
       <c r="AI81" s="10" t="n"/>
       <c r="AJ81" s="10" t="n"/>
       <c r="AK81" s="11" t="n"/>
     </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="B83" s="37" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="10" t="n"/>
+      <c r="J82" s="10" t="n"/>
+      <c r="K82" s="10" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="17" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="11" t="n"/>
+      <c r="Q82" s="17" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="R82" s="10" t="n"/>
+      <c r="S82" s="11" t="n"/>
+      <c r="T82" s="17" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="U82" s="10" t="n"/>
+      <c r="V82" s="10" t="n"/>
+      <c r="W82" s="10" t="n"/>
+      <c r="X82" s="11" t="n"/>
+      <c r="Y82" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z82" s="10" t="n"/>
+      <c r="AA82" s="10" t="n"/>
+      <c r="AB82" s="10" t="n"/>
+      <c r="AC82" s="10" t="n"/>
+      <c r="AD82" s="10" t="n"/>
+      <c r="AE82" s="11" t="n"/>
+      <c r="AF82" s="19" t="inlineStr"/>
+      <c r="AG82" s="10" t="n"/>
+      <c r="AH82" s="10" t="n"/>
+      <c r="AI82" s="10" t="n"/>
+      <c r="AJ82" s="10" t="n"/>
+      <c r="AK82" s="11" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1"/>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="B84" s="37" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/dokusya/import/template</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="B87" s="37" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="90" customHeight="1">
-      <c r="C84" s="19" t="inlineStr">
+    <row r="88" ht="90" customHeight="1">
+      <c r="C88" s="19" t="inlineStr">
         <is>
           <t>HTTP/1.1 200 OK
 Content-Type: application/vnd.openxmlformats-officedocument.spreadsheetml.sheet
@@ -7767,50 +8061,50 @@
 (バイナリデータ)</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n"/>
-      <c r="E84" s="10" t="n"/>
-      <c r="F84" s="10" t="n"/>
-      <c r="G84" s="10" t="n"/>
-      <c r="H84" s="10" t="n"/>
-      <c r="I84" s="10" t="n"/>
-      <c r="J84" s="10" t="n"/>
-      <c r="K84" s="10" t="n"/>
-      <c r="L84" s="10" t="n"/>
-      <c r="M84" s="10" t="n"/>
-      <c r="N84" s="10" t="n"/>
-      <c r="O84" s="10" t="n"/>
-      <c r="P84" s="10" t="n"/>
-      <c r="Q84" s="10" t="n"/>
-      <c r="R84" s="10" t="n"/>
-      <c r="S84" s="10" t="n"/>
-      <c r="T84" s="10" t="n"/>
-      <c r="U84" s="10" t="n"/>
-      <c r="V84" s="10" t="n"/>
-      <c r="W84" s="10" t="n"/>
-      <c r="X84" s="10" t="n"/>
-      <c r="Y84" s="10" t="n"/>
-      <c r="Z84" s="10" t="n"/>
-      <c r="AA84" s="10" t="n"/>
-      <c r="AB84" s="10" t="n"/>
-      <c r="AC84" s="10" t="n"/>
-      <c r="AD84" s="10" t="n"/>
-      <c r="AE84" s="10" t="n"/>
-      <c r="AF84" s="10" t="n"/>
-      <c r="AG84" s="10" t="n"/>
-      <c r="AH84" s="10" t="n"/>
-      <c r="AI84" s="10" t="n"/>
-      <c r="AJ84" s="10" t="n"/>
-      <c r="AK84" s="11" t="n"/>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="B86" s="37" t="inlineStr">
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="10" t="n"/>
+      <c r="J88" s="10" t="n"/>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="10" t="n"/>
+      <c r="M88" s="10" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="10" t="n"/>
+      <c r="X88" s="10" t="n"/>
+      <c r="Y88" s="10" t="n"/>
+      <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="10" t="n"/>
+      <c r="AD88" s="10" t="n"/>
+      <c r="AE88" s="10" t="n"/>
+      <c r="AF88" s="10" t="n"/>
+      <c r="AG88" s="10" t="n"/>
+      <c r="AH88" s="10" t="n"/>
+      <c r="AI88" s="10" t="n"/>
+      <c r="AJ88" s="10" t="n"/>
+      <c r="AK88" s="11" t="n"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="B90" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="72" customHeight="1">
-      <c r="C87" s="19" t="inlineStr">
+    <row r="91" ht="72" customHeight="1">
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -7818,50 +8112,50 @@
 }</t>
         </is>
       </c>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="10" t="n"/>
-      <c r="G87" s="10" t="n"/>
-      <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="10" t="n"/>
-      <c r="M87" s="10" t="n"/>
-      <c r="N87" s="10" t="n"/>
-      <c r="O87" s="10" t="n"/>
-      <c r="P87" s="10" t="n"/>
-      <c r="Q87" s="10" t="n"/>
-      <c r="R87" s="10" t="n"/>
-      <c r="S87" s="10" t="n"/>
-      <c r="T87" s="10" t="n"/>
-      <c r="U87" s="10" t="n"/>
-      <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n"/>
-      <c r="X87" s="10" t="n"/>
-      <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="10" t="n"/>
-      <c r="AA87" s="10" t="n"/>
-      <c r="AB87" s="10" t="n"/>
-      <c r="AC87" s="10" t="n"/>
-      <c r="AD87" s="10" t="n"/>
-      <c r="AE87" s="10" t="n"/>
-      <c r="AF87" s="10" t="n"/>
-      <c r="AG87" s="10" t="n"/>
-      <c r="AH87" s="10" t="n"/>
-      <c r="AI87" s="10" t="n"/>
-      <c r="AJ87" s="10" t="n"/>
-      <c r="AK87" s="11" t="n"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="B89" s="37" t="inlineStr">
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="B93" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="72" customHeight="1">
-      <c r="C90" s="19" t="inlineStr">
+    <row r="94" ht="72" customHeight="1">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -7869,50 +8163,50 @@
 }</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
-      <c r="P90" s="10" t="n"/>
-      <c r="Q90" s="10" t="n"/>
-      <c r="R90" s="10" t="n"/>
-      <c r="S90" s="10" t="n"/>
-      <c r="T90" s="10" t="n"/>
-      <c r="U90" s="10" t="n"/>
-      <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
-      <c r="X90" s="10" t="n"/>
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-      <c r="AA90" s="10" t="n"/>
-      <c r="AB90" s="10" t="n"/>
-      <c r="AC90" s="10" t="n"/>
-      <c r="AD90" s="10" t="n"/>
-      <c r="AE90" s="10" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
-      <c r="AI90" s="10" t="n"/>
-      <c r="AJ90" s="10" t="n"/>
-      <c r="AK90" s="11" t="n"/>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="B92" s="37" t="inlineStr">
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="B96" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="72" customHeight="1">
-      <c r="C93" s="19" t="inlineStr">
+    <row r="97" ht="72" customHeight="1">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -7920,240 +8214,242 @@
 }</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="10" t="n"/>
-      <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
-      <c r="T93" s="10" t="n"/>
-      <c r="U93" s="10" t="n"/>
-      <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
-      <c r="X93" s="10" t="n"/>
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-      <c r="AA93" s="10" t="n"/>
-      <c r="AB93" s="10" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="10" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="10" t="n"/>
-      <c r="AK93" s="11" t="n"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1"/>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="27" t="inlineStr">
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1"/>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="38" t="inlineStr">
-        <is>
-          <t>リクエストパラメータなし。特に検証なし。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="38" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="38" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="38" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.import`</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="36" customHeight="1">
-      <c r="C103" s="38" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>リクエストパラメータなし。特に検証なし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="C104" s="38" t="inlineStr">
         <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="C105" s="38" t="inlineStr">
         <is>
-          <t>DataScope: 本APIはマスターデータを返さないため、DataScope違反は発生しない。</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
-        <is>
-          <t>4.3 テンプレート生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
+      <c r="C106" s="38" t="inlineStr">
+        <is>
+          <t>必要権限: `dokusya.import`</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1">
       <c r="C107" s="38" t="inlineStr">
         <is>
-          <t>ExcelJSライブラリを使用して新規ワークブックを生成する。</t>
+          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="C108" s="38" t="inlineStr">
         <is>
-          <t>シート名：`購読者`</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="36" customHeight="1">
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
       <c r="C109" s="38" t="inlineStr">
         <is>
-          <t>1行目に46列のヘッダー文字列を以下の順序で書き込む（購読種別・読者情報変更適用日・購読中止日は画面で指定する単一ソースのため列に含めない）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="162" customHeight="1">
-      <c r="D110" s="38" t="inlineStr">
-        <is>
-          <t>「ID」「管理支店」「支店」「組合員コード」「購読者苗字（漢字）」「購読者名前（漢字）」「購読者苗字（かな）」「購読者名前（かな）」「購読部数」「新聞単価」「メールアドレス」「メールマガジン」「生年（西暦）」「性別」「郵便番号」「都道府県」「市町村郡」「丁目番地」「マンション・アパート名」「連絡先１」「連絡先２」「郵便番号(配達先)」「都道府県(配達先)」「市町村郡(配達先)」「丁目番地(配達先)」「ﾏﾝｼｮﾝ・ｱﾊﾟｰﾄ名(配達先)」「連絡先１(配達先)」「連絡先２(配達先)」「配達先苗字（漢字）」「配達先名前（漢字）」「配達先苗字（かな）」「配達先名前（かな）」「販売店コード」「郵送区分」「支払方法」「購読料支払サイクル（月数）」「引落口座貯金種目」「引落口座支店コード」「引落口座支店名」「引落口座番号」「引落口座名義」「購読者層分類」「農業者分類」「購読開始日」「購読中止日」「備考」「読者情報変更適用日」</t>
+          <t>DataScope: 本APIはマスターデータを返さないため、DataScope違反は発生しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>4.3 テンプレート生成</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="C111" s="38" t="inlineStr">
         <is>
+          <t>ExcelJSライブラリを使用して新規ワークブックを生成する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="C112" s="38" t="inlineStr">
+        <is>
+          <t>シート名：`購読者`</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="C113" s="38" t="inlineStr">
+        <is>
+          <t>1行目に46列のヘッダー文字列を以下の順序で書き込む（購読種別・読者情報変更適用日・購読中止日は画面で指定する単一ソースのため列に含めない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="180" customHeight="1">
+      <c r="D114" s="38" t="inlineStr">
+        <is>
+          <t>「ID」「管理支店」「支店」「組合員コード」「購読者苗字（漢字）」「購読者名前（漢字）」「購読者苗字（かな）」「購読者名前（かな）」「購読部数」「新聞単価」「メールアドレス」「メールマガジン」「生年（西暦）」「性別」「郵便番号」「都道府県」「市町村郡」「丁目番地」「マンション・アパート名」「連絡先１」「連絡先２」「郵便番号(配達先)」「都道府県(配達先)」「市町村郡(配達先)」「丁目番地(配達先)」「ﾏﾝｼｮﾝ・ｱﾊﾟｰﾄ名(配達先)」「連絡先１(配達先)」「連絡先２(配達先)」「配達先苗字（漢字）」「配達先名前（漢字）」「配達先苗字（かな）」「配達先名前（かな）」「販売店コード」「郵送区分」「支払方法」「購読料支払サイクル（月数）」「引落口座貯金種目」「引落口座支店コード」「引落口座支店名」「引落口座番号」「引落口座名義」「購読者層分類」「かつJAグループ役職員」「農業関係」「読者属性（その他の内容）」「農業者分類」「主な生産物（その他の内容）」「購読開始日」「備考」&lt;br&gt;※「購読中止日」「読者情報変更適用日」は画面の入力欄へ移したため列には無い（v1.7）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="C115" s="38" t="inlineStr">
+        <is>
           <t>ヘッダー行はボールドスタイル、背景色を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="72" customHeight="1">
-      <c r="C112" s="38" t="inlineStr">
+    <row r="116" ht="72" customHeight="1">
+      <c r="C116" s="38" t="inlineStr">
         <is>
           <t>2行目に書式見本となるサンプルデータ行を1行書き込む（紙版(1)/新規(1)、購読部数&gt;0、性別1、かなはひらがな、郵便番号7桁、連絡先は半角数字、支払方法は現金集金(2)で引落口座不要、購読開始日は YYYY-MM-DD）。管理支店・支店・新聞単価・販売店コード等のFKコード列は自組織固有のため空欄とし、備考欄に「インポート前に書き換えてください。」と明記する。</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="C113" s="38" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="C117" s="38" t="inlineStr">
         <is>
           <t>各列の幅を項目内容に合わせて自動調整する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="36" customHeight="1">
-      <c r="C114" s="38" t="inlineStr">
-        <is>
-          <t>数字コードと文言の両方での取込みに対応するため、コードまたは文言のいずれかを入力可能とする旨を備考欄や説明シートで案内してもよい（例: 性別は「1」「男性」のいずれも可）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="B115" s="27" t="inlineStr">
-        <is>
-          <t>4.4 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="C116" s="38" t="inlineStr">
-        <is>
-          <t>生成したExcelファイルをバイナリデータとしてレスポンスに設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="36" customHeight="1">
-      <c r="C117" s="38" t="inlineStr">
-        <is>
-          <t>Content-Type: `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`</t>
         </is>
       </c>
     </row>
     <row r="118" ht="36" customHeight="1">
       <c r="C118" s="38" t="inlineStr">
         <is>
-          <t>Content-Disposition: `attachment; filename="購読者Excelデータ取込_テンプレート.xlsx"`</t>
+          <t>数字コードと文言の両方での取込みに対応するため、コードまたは文言のいずれかを入力可能とする旨を備考欄や説明シートで案内してもよい（例: 性別は「1」「男性」のいずれも可）。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="38" t="inlineStr">
-        <is>
-          <t>HTTP 200 で返却する。</t>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="B120" s="27" t="inlineStr">
-        <is>
-          <t>4.5 例外処理</t>
+      <c r="C120" s="38" t="inlineStr">
+        <is>
+          <t>生成したExcelファイルをバイナリデータとしてレスポンスに設定する。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="36" customHeight="1">
       <c r="C121" s="38" t="inlineStr">
         <is>
+          <t>Content-Type: `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="C122" s="38" t="inlineStr">
+        <is>
+          <t>Content-Disposition: `attachment; filename="購読者Excelデータ取込_テンプレート.xlsx"`</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="38" t="inlineStr">
+        <is>
+          <t>HTTP 200 で返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>4.5 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="C125" s="38" t="inlineStr">
+        <is>
           <t>ファイル生成エラー、DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="407">
+  <mergeCells count="431">
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="T53:X53"/>
+    <mergeCell ref="Q80:S80"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="M82:P82"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
@@ -8161,13 +8457,13 @@
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="B115:AK115"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y66:AE66"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
@@ -8177,16 +8473,18 @@
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="AF81:AK81"/>
     <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="C79:L79"/>
     <mergeCell ref="C73:L73"/>
     <mergeCell ref="T40:X40"/>
+    <mergeCell ref="B87:I87"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="T76:X76"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="T69:X69"/>
-    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y37:AE37"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="T45:X45"/>
@@ -8217,9 +8515,7 @@
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="C56:L56"/>
-    <mergeCell ref="B89:I89"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="Y25:AE25"/>
     <mergeCell ref="C43:L43"/>
@@ -8229,6 +8525,7 @@
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="Y38:AE38"/>
@@ -8239,10 +8536,13 @@
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="C65:L65"/>
+    <mergeCell ref="Y82:AE82"/>
+    <mergeCell ref="B124:AK124"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C80:L80"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
@@ -8253,6 +8553,7 @@
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="B96:I96"/>
     <mergeCell ref="C57:L57"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
@@ -8279,9 +8580,10 @@
     <mergeCell ref="Q60:S60"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
+    <mergeCell ref="AF80:AK80"/>
+    <mergeCell ref="C81:L81"/>
     <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="B119:AK119"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
@@ -8299,17 +8601,16 @@
     <mergeCell ref="AF66:AK66"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
+    <mergeCell ref="Y80:AE80"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
-    <mergeCell ref="C87:AK87"/>
-    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="C116:AK116"/>
     <mergeCell ref="C78:L78"/>
     <mergeCell ref="M34:P34"/>
+    <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
@@ -8321,11 +8622,13 @@
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="AF63:AK63"/>
+    <mergeCell ref="Q79:S79"/>
     <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Y61:AE61"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="C66:L66"/>
+    <mergeCell ref="Q81:S81"/>
     <mergeCell ref="C53:L53"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
@@ -8335,36 +8638,36 @@
     <mergeCell ref="T62:X62"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="T64:X64"/>
-    <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M80:P80"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T33:X33"/>
+    <mergeCell ref="T82:X82"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="C112:AK112"/>
     <mergeCell ref="C74:L74"/>
     <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Y62:AE62"/>
-    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="M70:P70"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
-    <mergeCell ref="B83:I83"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -8376,6 +8679,7 @@
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
@@ -8396,10 +8700,11 @@
     <mergeCell ref="Q47:S47"/>
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="C55:L55"/>
-    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M36:P36"/>
+    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
@@ -8407,6 +8712,7 @@
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="B93:I93"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T78:X78"/>
     <mergeCell ref="T65:X65"/>
@@ -8414,12 +8720,15 @@
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
+    <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="T79:X79"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="Q55:S55"/>
@@ -8429,7 +8738,6 @@
     <mergeCell ref="C76:L76"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
@@ -8446,17 +8754,19 @@
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
-    <mergeCell ref="B92:I92"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="C40:L40"/>
+    <mergeCell ref="T81:X81"/>
     <mergeCell ref="C51:L51"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="C71:L71"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="M29:P29"/>
+    <mergeCell ref="A100:AK100"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
@@ -8471,9 +8781,12 @@
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="C59:L59"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="C46:L46"/>
+    <mergeCell ref="Y81:AE81"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
@@ -8482,25 +8795,28 @@
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="A23:AK23"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
     <mergeCell ref="AF64:AK64"/>
-    <mergeCell ref="A96:AK96"/>
+    <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="M79:P79"/>
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="M73:P73"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="AF82:AK82"/>
     <mergeCell ref="Y31:AE31"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
+    <mergeCell ref="Q82:S82"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="T32:X32"/>
@@ -8525,26 +8841,28 @@
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="Y44:AE44"/>
     <mergeCell ref="T52:X52"/>
+    <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="C82:L82"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="AF60:AK60"/>
-    <mergeCell ref="D110:AK110"/>
     <mergeCell ref="C58:L58"/>
-    <mergeCell ref="B99:AK99"/>
+    <mergeCell ref="B84:I84"/>
     <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="B80:I80"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -8558,7 +8876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK222"/>
+  <dimension ref="A1:AK226"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8719,7 +9037,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12711,13 +13029,13 @@
       <c r="AJ74" s="10" t="n"/>
       <c r="AK74" s="11" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1">
+    <row r="75" ht="72" customHeight="1">
       <c r="B75" s="31" t="n">
         <v>48</v>
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>→nogyosya_bunrui</t>
+          <t>→ja_yakushokuin_flg</t>
         </is>
       </c>
       <c r="D75" s="10" t="n"/>
@@ -12731,7 +13049,7 @@
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N75" s="10" t="n"/>
@@ -12753,20 +13071,24 @@
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="11" t="n"/>
-      <c r="Y75" s="17" t="n">
-        <v>0</v>
+      <c r="Y75" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="11" t="n"/>
-      <c r="AC75" s="17" t="n">
-        <v>50</v>
+      <c r="AC75" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>農業者分類（カンマ区切り）</t>
+          <t>かつJAグループ役職員。購読者層分類=0:農業者 のときのみ有効。従属項目。購読者層分類が該当コードを含むときのみ有効で、外れる場合はサーバ側で false / 空文字へ落とす（画面 SCR-011 と同じ buildBunruiPayload を通す）。電子版 users.profession_and_* / others_* との連携用</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -12775,13 +13097,13 @@
       <c r="AJ75" s="10" t="n"/>
       <c r="AK75" s="11" t="n"/>
     </row>
-    <row r="76" ht="18" customHeight="1">
+    <row r="76" ht="72" customHeight="1">
       <c r="B76" s="31" t="n">
         <v>49</v>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>→dokusya_kaishi_date</t>
+          <t>→nogyo_kankei_flg</t>
         </is>
       </c>
       <c r="D76" s="10" t="n"/>
@@ -12795,7 +13117,7 @@
       <c r="L76" s="11" t="n"/>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N76" s="10" t="n"/>
@@ -12825,14 +13147,16 @@
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
       <c r="AB76" s="11" t="n"/>
-      <c r="AC76" s="17" t="n">
-        <v>10</v>
+      <c r="AC76" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（YYYY-MM-DD）。`NEW` モードは必須。</t>
+          <t>農業関係。購読者層分類=2:企業・団体 のときのみ有効。従属項目。購読者層分類が該当コードを含むときのみ有効で、外れる場合はサーバ側で false / 空文字へ落とす（画面 SCR-011 と同じ buildBunruiPayload を通す）。電子版 users.profession_and_* / others_* との連携用</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -12841,13 +13165,13 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="18" customHeight="1">
+    <row r="77" ht="72" customHeight="1">
       <c r="B77" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>→biko</t>
+          <t>→dokusyaso_bunrui_sonota</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -12883,24 +13207,20 @@
       <c r="V77" s="10" t="n"/>
       <c r="W77" s="10" t="n"/>
       <c r="X77" s="11" t="n"/>
-      <c r="Y77" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y77" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="Z77" s="10" t="n"/>
       <c r="AA77" s="10" t="n"/>
       <c r="AB77" s="11" t="n"/>
-      <c r="AC77" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AC77" s="17" t="n">
+        <v>255</v>
       </c>
       <c r="AD77" s="10" t="n"/>
       <c r="AE77" s="11" t="n"/>
       <c r="AF77" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>読者属性（その他の内容）。購読者層分類=999:その他 のときのみ有効。従属項目。購読者層分類が該当コードを含むときのみ有効で、外れる場合はサーバ側で false / 空文字へ落とす（画面 SCR-011 と同じ buildBunruiPayload を通す）。電子版 users.profession_and_* / others_* との連携用</t>
         </is>
       </c>
       <c r="AG77" s="10" t="n"/>
@@ -12909,24 +13229,207 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="19.5" customHeight="1"/>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1"/>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="B81" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>→nogyosya_bunrui</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="11" t="n"/>
+      <c r="T78" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="11" t="n"/>
+      <c r="Y78" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="11" t="n"/>
+      <c r="AC78" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="11" t="n"/>
+      <c r="AF78" s="19" t="inlineStr">
+        <is>
+          <t>農業者分類（カンマ区切り）</t>
+        </is>
+      </c>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="72" customHeight="1">
+      <c r="B79" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>→nogyosya_bunrui_sonota</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="11" t="n"/>
+      <c r="M79" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="11" t="n"/>
+      <c r="Y79" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="11" t="n"/>
+      <c r="AC79" s="17" t="n">
+        <v>255</v>
+      </c>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="11" t="n"/>
+      <c r="AF79" s="19" t="inlineStr">
+        <is>
+          <t>主な生産物（その他の内容）。農業者分類に 999:その他 を含むときのみ有効。従属項目。購読者層分類が該当コードを含むときのみ有効で、外れる場合はサーバ側で false / 空文字へ落とす（画面 SCR-011 と同じ buildBunruiPayload を通す）。電子版 users.profession_and_* / others_* との連携用</t>
+        </is>
+      </c>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="31" t="n">
+        <v>53</v>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>→dokusya_kaishi_date</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="11" t="n"/>
+      <c r="Q80" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="11" t="n"/>
+      <c r="T80" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="11" t="n"/>
+      <c r="Y80" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="11" t="n"/>
+      <c r="AC80" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="11" t="n"/>
+      <c r="AF80" s="19" t="inlineStr">
+        <is>
+          <t>購読開始日（YYYY-MM-DD）。`NEW` モードは必須。</t>
+        </is>
+      </c>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>→biko</t>
         </is>
       </c>
       <c r="D81" s="10" t="n"/>
@@ -12938,44 +13441,48 @@
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="11" t="n"/>
-      <c r="M81" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M81" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
       <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q81" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R81" s="10" t="n"/>
       <c r="S81" s="11" t="n"/>
-      <c r="T81" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T81" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="11" t="n"/>
-      <c r="Y81" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
+      <c r="Y81" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="Z81" s="10" t="n"/>
       <c r="AA81" s="10" t="n"/>
-      <c r="AB81" s="10" t="n"/>
-      <c r="AC81" s="10" t="n"/>
+      <c r="AB81" s="11" t="n"/>
+      <c r="AC81" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
-      <c r="AF81" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF81" s="19" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG81" s="10" t="n"/>
@@ -12984,196 +13491,27 @@
       <c r="AJ81" s="10" t="n"/>
       <c r="AK81" s="11" t="n"/>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="11" t="n"/>
-      <c r="M82" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="11" t="n"/>
-      <c r="Q82" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="11" t="n"/>
-      <c r="T82" s="17" t="inlineStr"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="11" t="n"/>
-      <c r="Y82" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="11" t="n"/>
-      <c r="AF82" s="19" t="inlineStr">
-        <is>
-          <t>取込結果サマリ</t>
-        </is>
-      </c>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="B83" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C83" s="39" t="n"/>
-      <c r="D83" s="19" t="inlineStr">
-        <is>
-          <t>import_mode</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="11" t="n"/>
-      <c r="Q83" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="11" t="n"/>
-      <c r="T83" s="17" t="inlineStr"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="11" t="n"/>
-      <c r="Y83" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="11" t="n"/>
-      <c r="AF83" s="19" t="inlineStr">
-        <is>
-          <t>実行した取込モード（`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL`）</t>
-        </is>
-      </c>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C84" s="40" t="n"/>
-      <c r="D84" s="19" t="inlineStr">
-        <is>
-          <t>total_rows</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="n"/>
-      <c r="F84" s="10" t="n"/>
-      <c r="G84" s="10" t="n"/>
-      <c r="H84" s="10" t="n"/>
-      <c r="I84" s="10" t="n"/>
-      <c r="J84" s="10" t="n"/>
-      <c r="K84" s="10" t="n"/>
-      <c r="L84" s="11" t="n"/>
-      <c r="M84" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N84" s="10" t="n"/>
-      <c r="O84" s="10" t="n"/>
-      <c r="P84" s="11" t="n"/>
-      <c r="Q84" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R84" s="10" t="n"/>
-      <c r="S84" s="11" t="n"/>
-      <c r="T84" s="17" t="inlineStr"/>
-      <c r="U84" s="10" t="n"/>
-      <c r="V84" s="10" t="n"/>
-      <c r="W84" s="10" t="n"/>
-      <c r="X84" s="11" t="n"/>
-      <c r="Y84" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z84" s="10" t="n"/>
-      <c r="AA84" s="10" t="n"/>
-      <c r="AB84" s="10" t="n"/>
-      <c r="AC84" s="10" t="n"/>
-      <c r="AD84" s="10" t="n"/>
-      <c r="AE84" s="11" t="n"/>
-      <c r="AF84" s="19" t="inlineStr">
-        <is>
-          <t>取込対象行数</t>
-        </is>
-      </c>
-      <c r="AG84" s="10" t="n"/>
-      <c r="AH84" s="10" t="n"/>
-      <c r="AI84" s="10" t="n"/>
-      <c r="AJ84" s="10" t="n"/>
-      <c r="AK84" s="11" t="n"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C85" s="40" t="n"/>
-      <c r="D85" s="19" t="inlineStr">
-        <is>
-          <t>created_count</t>
-        </is>
-      </c>
+    <row r="82" ht="19.5" customHeight="1"/>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1"/>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="B85" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n"/>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
@@ -13182,29 +13520,33 @@
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="11" t="n"/>
-      <c r="M85" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
       <c r="P85" s="11" t="n"/>
-      <c r="Q85" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q85" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R85" s="10" t="n"/>
       <c r="S85" s="11" t="n"/>
-      <c r="T85" s="17" t="inlineStr"/>
+      <c r="T85" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U85" s="10" t="n"/>
       <c r="V85" s="10" t="n"/>
       <c r="W85" s="10" t="n"/>
       <c r="X85" s="11" t="n"/>
-      <c r="Y85" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y85" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z85" s="10" t="n"/>
@@ -13213,9 +13555,9 @@
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="11" t="n"/>
-      <c r="AF85" s="19" t="inlineStr">
-        <is>
-          <t>新規登録件数</t>
+      <c r="AF85" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG85" s="10" t="n"/>
@@ -13226,14 +13568,14 @@
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C86" s="40" t="n"/>
-      <c r="D86" s="19" t="inlineStr">
-        <is>
-          <t>updated_count</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n"/>
       <c r="E86" s="10" t="n"/>
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="10" t="n"/>
@@ -13244,7 +13586,7 @@
       <c r="L86" s="11" t="n"/>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N86" s="10" t="n"/>
@@ -13275,7 +13617,7 @@
       <c r="AE86" s="11" t="n"/>
       <c r="AF86" s="19" t="inlineStr">
         <is>
-          <t>更新件数</t>
+          <t>取込結果サマリ</t>
         </is>
       </c>
       <c r="AG86" s="10" t="n"/>
@@ -13284,14 +13626,14 @@
       <c r="AJ86" s="10" t="n"/>
       <c r="AK86" s="11" t="n"/>
     </row>
-    <row r="87" ht="18" customHeight="1">
+    <row r="87" ht="36" customHeight="1">
       <c r="B87" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C87" s="40" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C87" s="39" t="n"/>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t>cancelled_count</t>
+          <t>import_mode</t>
         </is>
       </c>
       <c r="E87" s="10" t="n"/>
@@ -13304,7 +13646,7 @@
       <c r="L87" s="11" t="n"/>
       <c r="M87" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N87" s="10" t="n"/>
@@ -13335,7 +13677,7 @@
       <c r="AE87" s="11" t="n"/>
       <c r="AF87" s="19" t="inlineStr">
         <is>
-          <t>一括中止（解約）件数</t>
+          <t>実行した取込モード（`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL`）</t>
         </is>
       </c>
       <c r="AG87" s="10" t="n"/>
@@ -13346,12 +13688,12 @@
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="B88" s="31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C88" s="40" t="n"/>
       <c r="D88" s="19" t="inlineStr">
         <is>
-          <t>skipped_count</t>
+          <t>total_rows</t>
         </is>
       </c>
       <c r="E88" s="10" t="n"/>
@@ -13395,7 +13737,7 @@
       <c r="AE88" s="11" t="n"/>
       <c r="AF88" s="19" t="inlineStr">
         <is>
-          <t>スキップ件数</t>
+          <t>取込対象行数</t>
         </is>
       </c>
       <c r="AG88" s="10" t="n"/>
@@ -13406,12 +13748,12 @@
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="B89" s="31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t>rireki_count</t>
+          <t>created_count</t>
         </is>
       </c>
       <c r="E89" s="10" t="n"/>
@@ -13455,7 +13797,7 @@
       <c r="AE89" s="11" t="n"/>
       <c r="AF89" s="19" t="inlineStr">
         <is>
-          <t>履歴テーブル（t_dokusya_rireki）への追加件数</t>
+          <t>新規登録件数</t>
         </is>
       </c>
       <c r="AG89" s="10" t="n"/>
@@ -13466,12 +13808,12 @@
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="B90" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C90" s="41" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="C90" s="40" t="n"/>
       <c r="D90" s="19" t="inlineStr">
         <is>
-          <t>imported_at</t>
+          <t>updated_count</t>
         </is>
       </c>
       <c r="E90" s="10" t="n"/>
@@ -13484,7 +13826,7 @@
       <c r="L90" s="11" t="n"/>
       <c r="M90" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N90" s="10" t="n"/>
@@ -13497,11 +13839,7 @@
       </c>
       <c r="R90" s="10" t="n"/>
       <c r="S90" s="11" t="n"/>
-      <c r="T90" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T90" s="17" t="inlineStr"/>
       <c r="U90" s="10" t="n"/>
       <c r="V90" s="10" t="n"/>
       <c r="W90" s="10" t="n"/>
@@ -13519,7 +13857,7 @@
       <c r="AE90" s="11" t="n"/>
       <c r="AF90" s="19" t="inlineStr">
         <is>
-          <t>取込完了日時</t>
+          <t>更新件数</t>
         </is>
       </c>
       <c r="AG90" s="10" t="n"/>
@@ -13530,14 +13868,14 @@
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="B91" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="C91" s="19" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="C91" s="40" t="n"/>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>cancelled_count</t>
+        </is>
+      </c>
       <c r="E91" s="10" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
@@ -13548,7 +13886,7 @@
       <c r="L91" s="11" t="n"/>
       <c r="M91" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N91" s="10" t="n"/>
@@ -13579,7 +13917,7 @@
       <c r="AE91" s="11" t="n"/>
       <c r="AF91" s="19" t="inlineStr">
         <is>
-          <t>取り込みました。</t>
+          <t>一括中止（解約）件数</t>
         </is>
       </c>
       <c r="AG91" s="10" t="n"/>
@@ -13588,16 +13926,260 @@
       <c r="AJ91" s="10" t="n"/>
       <c r="AK91" s="11" t="n"/>
     </row>
-    <row r="92" ht="19.5" customHeight="1"/>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="B93" s="37" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C92" s="40" t="n"/>
+      <c r="D92" s="19" t="inlineStr">
+        <is>
+          <t>skipped_count</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="10" t="n"/>
+      <c r="I92" s="10" t="n"/>
+      <c r="J92" s="10" t="n"/>
+      <c r="K92" s="10" t="n"/>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="n"/>
+      <c r="O92" s="10" t="n"/>
+      <c r="P92" s="11" t="n"/>
+      <c r="Q92" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R92" s="10" t="n"/>
+      <c r="S92" s="11" t="n"/>
+      <c r="T92" s="17" t="inlineStr"/>
+      <c r="U92" s="10" t="n"/>
+      <c r="V92" s="10" t="n"/>
+      <c r="W92" s="10" t="n"/>
+      <c r="X92" s="11" t="n"/>
+      <c r="Y92" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z92" s="10" t="n"/>
+      <c r="AA92" s="10" t="n"/>
+      <c r="AB92" s="10" t="n"/>
+      <c r="AC92" s="10" t="n"/>
+      <c r="AD92" s="10" t="n"/>
+      <c r="AE92" s="11" t="n"/>
+      <c r="AF92" s="19" t="inlineStr">
+        <is>
+          <t>スキップ件数</t>
+        </is>
+      </c>
+      <c r="AG92" s="10" t="n"/>
+      <c r="AH92" s="10" t="n"/>
+      <c r="AI92" s="10" t="n"/>
+      <c r="AJ92" s="10" t="n"/>
+      <c r="AK92" s="11" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" s="40" t="n"/>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>rireki_count</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="11" t="n"/>
+      <c r="M93" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="11" t="n"/>
+      <c r="Q93" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="11" t="n"/>
+      <c r="T93" s="17" t="inlineStr"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="11" t="n"/>
+      <c r="Y93" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="19" t="inlineStr">
+        <is>
+          <t>履歴テーブル（t_dokusya_rireki）への追加件数</t>
+        </is>
+      </c>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="11" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C94" s="41" t="n"/>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>imported_at</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="11" t="n"/>
+      <c r="Q94" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="11" t="n"/>
+      <c r="T94" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="11" t="n"/>
+      <c r="Y94" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="19" t="inlineStr">
+        <is>
+          <t>取込完了日時</t>
+        </is>
+      </c>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="10" t="n"/>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="11" t="n"/>
+      <c r="Q95" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="11" t="n"/>
+      <c r="T95" s="17" t="inlineStr"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="10" t="n"/>
+      <c r="W95" s="10" t="n"/>
+      <c r="X95" s="11" t="n"/>
+      <c r="Y95" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="10" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="19" t="inlineStr">
+        <is>
+          <t>取り込みました。</t>
+        </is>
+      </c>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="11" t="n"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1"/>
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="B97" s="37" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="409" customHeight="1">
-      <c r="C94" s="19" t="inlineStr">
+    <row r="98" ht="409" customHeight="1">
+      <c r="C98" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/dokusya/import
 Content-Type: application/json
@@ -13657,50 +14239,50 @@
 }</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="B96" s="37" t="inlineStr">
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="10" t="n"/>
+      <c r="J98" s="10" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="10" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="10" t="n"/>
+      <c r="T98" s="10" t="n"/>
+      <c r="U98" s="10" t="n"/>
+      <c r="V98" s="10" t="n"/>
+      <c r="W98" s="10" t="n"/>
+      <c r="X98" s="10" t="n"/>
+      <c r="Y98" s="10" t="n"/>
+      <c r="Z98" s="10" t="n"/>
+      <c r="AA98" s="10" t="n"/>
+      <c r="AB98" s="10" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="10" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="10" t="n"/>
+      <c r="AK98" s="11" t="n"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="B100" s="37" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="234" customHeight="1">
-      <c r="C97" s="19" t="inlineStr">
+    <row r="101" ht="234" customHeight="1">
+      <c r="C101" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -13717,50 +14299,50 @@
 }</t>
         </is>
       </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="B99" s="37" t="inlineStr">
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="10" t="n"/>
+      <c r="F101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="10" t="n"/>
+      <c r="J101" s="10" t="n"/>
+      <c r="K101" s="10" t="n"/>
+      <c r="L101" s="10" t="n"/>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n"/>
+      <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="10" t="n"/>
+      <c r="U101" s="10" t="n"/>
+      <c r="V101" s="10" t="n"/>
+      <c r="W101" s="10" t="n"/>
+      <c r="X101" s="10" t="n"/>
+      <c r="Y101" s="10" t="n"/>
+      <c r="Z101" s="10" t="n"/>
+      <c r="AA101" s="10" t="n"/>
+      <c r="AB101" s="10" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="10" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="10" t="n"/>
+      <c r="AK101" s="11" t="n"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="B103" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Validation Error)）</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="144" customHeight="1">
-      <c r="C100" s="19" t="inlineStr">
+    <row r="104" ht="144" customHeight="1">
+      <c r="C104" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -13772,50 +14354,50 @@
 }</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
-      <c r="P100" s="10" t="n"/>
-      <c r="Q100" s="10" t="n"/>
-      <c r="R100" s="10" t="n"/>
-      <c r="S100" s="10" t="n"/>
-      <c r="T100" s="10" t="n"/>
-      <c r="U100" s="10" t="n"/>
-      <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
-      <c r="X100" s="10" t="n"/>
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AA100" s="10" t="n"/>
-      <c r="AB100" s="10" t="n"/>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="10" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="10" t="n"/>
-      <c r="AK100" s="11" t="n"/>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
-      <c r="B102" s="37" t="inlineStr">
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="10" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="10" t="n"/>
+      <c r="I104" s="10" t="n"/>
+      <c r="J104" s="10" t="n"/>
+      <c r="K104" s="10" t="n"/>
+      <c r="L104" s="10" t="n"/>
+      <c r="M104" s="10" t="n"/>
+      <c r="N104" s="10" t="n"/>
+      <c r="O104" s="10" t="n"/>
+      <c r="P104" s="10" t="n"/>
+      <c r="Q104" s="10" t="n"/>
+      <c r="R104" s="10" t="n"/>
+      <c r="S104" s="10" t="n"/>
+      <c r="T104" s="10" t="n"/>
+      <c r="U104" s="10" t="n"/>
+      <c r="V104" s="10" t="n"/>
+      <c r="W104" s="10" t="n"/>
+      <c r="X104" s="10" t="n"/>
+      <c r="Y104" s="10" t="n"/>
+      <c r="Z104" s="10" t="n"/>
+      <c r="AA104" s="10" t="n"/>
+      <c r="AB104" s="10" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="10" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="10" t="n"/>
+      <c r="AK104" s="11" t="n"/>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="B106" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Import Validation Error — 行別エラー)）</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="198" customHeight="1">
-      <c r="C103" s="19" t="inlineStr">
+    <row r="107" ht="198" customHeight="1">
+      <c r="C107" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "IMPORT_VALIDATION_ERROR",
@@ -13830,50 +14412,50 @@
 }</t>
         </is>
       </c>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="10" t="n"/>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="n"/>
-      <c r="O103" s="10" t="n"/>
-      <c r="P103" s="10" t="n"/>
-      <c r="Q103" s="10" t="n"/>
-      <c r="R103" s="10" t="n"/>
-      <c r="S103" s="10" t="n"/>
-      <c r="T103" s="10" t="n"/>
-      <c r="U103" s="10" t="n"/>
-      <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n"/>
-      <c r="X103" s="10" t="n"/>
-      <c r="Y103" s="10" t="n"/>
-      <c r="Z103" s="10" t="n"/>
-      <c r="AA103" s="10" t="n"/>
-      <c r="AB103" s="10" t="n"/>
-      <c r="AC103" s="10" t="n"/>
-      <c r="AD103" s="10" t="n"/>
-      <c r="AE103" s="10" t="n"/>
-      <c r="AF103" s="10" t="n"/>
-      <c r="AG103" s="10" t="n"/>
-      <c r="AH103" s="10" t="n"/>
-      <c r="AI103" s="10" t="n"/>
-      <c r="AJ103" s="10" t="n"/>
-      <c r="AK103" s="11" t="n"/>
-    </row>
-    <row r="105" ht="19.5" customHeight="1">
-      <c r="B105" s="37" t="inlineStr">
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="10" t="n"/>
+      <c r="J107" s="10" t="n"/>
+      <c r="K107" s="10" t="n"/>
+      <c r="L107" s="10" t="n"/>
+      <c r="M107" s="10" t="n"/>
+      <c r="N107" s="10" t="n"/>
+      <c r="O107" s="10" t="n"/>
+      <c r="P107" s="10" t="n"/>
+      <c r="Q107" s="10" t="n"/>
+      <c r="R107" s="10" t="n"/>
+      <c r="S107" s="10" t="n"/>
+      <c r="T107" s="10" t="n"/>
+      <c r="U107" s="10" t="n"/>
+      <c r="V107" s="10" t="n"/>
+      <c r="W107" s="10" t="n"/>
+      <c r="X107" s="10" t="n"/>
+      <c r="Y107" s="10" t="n"/>
+      <c r="Z107" s="10" t="n"/>
+      <c r="AA107" s="10" t="n"/>
+      <c r="AB107" s="10" t="n"/>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="10" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="10" t="n"/>
+      <c r="AK107" s="11" t="n"/>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="B109" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Row Limit Exceeded)）</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="72" customHeight="1">
-      <c r="C106" s="19" t="inlineStr">
+    <row r="110" ht="72" customHeight="1">
+      <c r="C110" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "ROW_LIMIT_EXCEEDED",
@@ -13881,50 +14463,50 @@
 }</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n"/>
-      <c r="E106" s="10" t="n"/>
-      <c r="F106" s="10" t="n"/>
-      <c r="G106" s="10" t="n"/>
-      <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
-      <c r="J106" s="10" t="n"/>
-      <c r="K106" s="10" t="n"/>
-      <c r="L106" s="10" t="n"/>
-      <c r="M106" s="10" t="n"/>
-      <c r="N106" s="10" t="n"/>
-      <c r="O106" s="10" t="n"/>
-      <c r="P106" s="10" t="n"/>
-      <c r="Q106" s="10" t="n"/>
-      <c r="R106" s="10" t="n"/>
-      <c r="S106" s="10" t="n"/>
-      <c r="T106" s="10" t="n"/>
-      <c r="U106" s="10" t="n"/>
-      <c r="V106" s="10" t="n"/>
-      <c r="W106" s="10" t="n"/>
-      <c r="X106" s="10" t="n"/>
-      <c r="Y106" s="10" t="n"/>
-      <c r="Z106" s="10" t="n"/>
-      <c r="AA106" s="10" t="n"/>
-      <c r="AB106" s="10" t="n"/>
-      <c r="AC106" s="10" t="n"/>
-      <c r="AD106" s="10" t="n"/>
-      <c r="AE106" s="10" t="n"/>
-      <c r="AF106" s="10" t="n"/>
-      <c r="AG106" s="10" t="n"/>
-      <c r="AH106" s="10" t="n"/>
-      <c r="AI106" s="10" t="n"/>
-      <c r="AJ106" s="10" t="n"/>
-      <c r="AK106" s="11" t="n"/>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="B108" s="37" t="inlineStr">
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="10" t="n"/>
+      <c r="M110" s="10" t="n"/>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="10" t="n"/>
+      <c r="T110" s="10" t="n"/>
+      <c r="U110" s="10" t="n"/>
+      <c r="V110" s="10" t="n"/>
+      <c r="W110" s="10" t="n"/>
+      <c r="X110" s="10" t="n"/>
+      <c r="Y110" s="10" t="n"/>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="10" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="10" t="n"/>
+      <c r="AK110" s="11" t="n"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="B112" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (File Format Error)）</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="72" customHeight="1">
-      <c r="C109" s="19" t="inlineStr">
+    <row r="113" ht="72" customHeight="1">
+      <c r="C113" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FILE_FORMAT_ERROR",
@@ -13932,50 +14514,50 @@
 }</t>
         </is>
       </c>
-      <c r="D109" s="10" t="n"/>
-      <c r="E109" s="10" t="n"/>
-      <c r="F109" s="10" t="n"/>
-      <c r="G109" s="10" t="n"/>
-      <c r="H109" s="10" t="n"/>
-      <c r="I109" s="10" t="n"/>
-      <c r="J109" s="10" t="n"/>
-      <c r="K109" s="10" t="n"/>
-      <c r="L109" s="10" t="n"/>
-      <c r="M109" s="10" t="n"/>
-      <c r="N109" s="10" t="n"/>
-      <c r="O109" s="10" t="n"/>
-      <c r="P109" s="10" t="n"/>
-      <c r="Q109" s="10" t="n"/>
-      <c r="R109" s="10" t="n"/>
-      <c r="S109" s="10" t="n"/>
-      <c r="T109" s="10" t="n"/>
-      <c r="U109" s="10" t="n"/>
-      <c r="V109" s="10" t="n"/>
-      <c r="W109" s="10" t="n"/>
-      <c r="X109" s="10" t="n"/>
-      <c r="Y109" s="10" t="n"/>
-      <c r="Z109" s="10" t="n"/>
-      <c r="AA109" s="10" t="n"/>
-      <c r="AB109" s="10" t="n"/>
-      <c r="AC109" s="10" t="n"/>
-      <c r="AD109" s="10" t="n"/>
-      <c r="AE109" s="10" t="n"/>
-      <c r="AF109" s="10" t="n"/>
-      <c r="AG109" s="10" t="n"/>
-      <c r="AH109" s="10" t="n"/>
-      <c r="AI109" s="10" t="n"/>
-      <c r="AJ109" s="10" t="n"/>
-      <c r="AK109" s="11" t="n"/>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="B111" s="37" t="inlineStr">
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="10" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="10" t="n"/>
+      <c r="J113" s="10" t="n"/>
+      <c r="K113" s="10" t="n"/>
+      <c r="L113" s="10" t="n"/>
+      <c r="M113" s="10" t="n"/>
+      <c r="N113" s="10" t="n"/>
+      <c r="O113" s="10" t="n"/>
+      <c r="P113" s="10" t="n"/>
+      <c r="Q113" s="10" t="n"/>
+      <c r="R113" s="10" t="n"/>
+      <c r="S113" s="10" t="n"/>
+      <c r="T113" s="10" t="n"/>
+      <c r="U113" s="10" t="n"/>
+      <c r="V113" s="10" t="n"/>
+      <c r="W113" s="10" t="n"/>
+      <c r="X113" s="10" t="n"/>
+      <c r="Y113" s="10" t="n"/>
+      <c r="Z113" s="10" t="n"/>
+      <c r="AA113" s="10" t="n"/>
+      <c r="AB113" s="10" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="10" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="10" t="n"/>
+      <c r="AK113" s="11" t="n"/>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="B115" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="72" customHeight="1">
-      <c r="C112" s="19" t="inlineStr">
+    <row r="116" ht="72" customHeight="1">
+      <c r="C116" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -13983,50 +14565,50 @@
 }</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
-      <c r="P112" s="10" t="n"/>
-      <c r="Q112" s="10" t="n"/>
-      <c r="R112" s="10" t="n"/>
-      <c r="S112" s="10" t="n"/>
-      <c r="T112" s="10" t="n"/>
-      <c r="U112" s="10" t="n"/>
-      <c r="V112" s="10" t="n"/>
-      <c r="W112" s="10" t="n"/>
-      <c r="X112" s="10" t="n"/>
-      <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AA112" s="10" t="n"/>
-      <c r="AB112" s="10" t="n"/>
-      <c r="AC112" s="10" t="n"/>
-      <c r="AD112" s="10" t="n"/>
-      <c r="AE112" s="10" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
-      <c r="AI112" s="10" t="n"/>
-      <c r="AJ112" s="10" t="n"/>
-      <c r="AK112" s="11" t="n"/>
-    </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="B114" s="37" t="inlineStr">
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="10" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
+      <c r="H116" s="10" t="n"/>
+      <c r="I116" s="10" t="n"/>
+      <c r="J116" s="10" t="n"/>
+      <c r="K116" s="10" t="n"/>
+      <c r="L116" s="10" t="n"/>
+      <c r="M116" s="10" t="n"/>
+      <c r="N116" s="10" t="n"/>
+      <c r="O116" s="10" t="n"/>
+      <c r="P116" s="10" t="n"/>
+      <c r="Q116" s="10" t="n"/>
+      <c r="R116" s="10" t="n"/>
+      <c r="S116" s="10" t="n"/>
+      <c r="T116" s="10" t="n"/>
+      <c r="U116" s="10" t="n"/>
+      <c r="V116" s="10" t="n"/>
+      <c r="W116" s="10" t="n"/>
+      <c r="X116" s="10" t="n"/>
+      <c r="Y116" s="10" t="n"/>
+      <c r="Z116" s="10" t="n"/>
+      <c r="AA116" s="10" t="n"/>
+      <c r="AB116" s="10" t="n"/>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="10" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="10" t="n"/>
+      <c r="AK116" s="11" t="n"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="B118" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="72" customHeight="1">
-      <c r="C115" s="19" t="inlineStr">
+    <row r="119" ht="72" customHeight="1">
+      <c r="C119" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -14034,50 +14616,50 @@
 }</t>
         </is>
       </c>
-      <c r="D115" s="10" t="n"/>
-      <c r="E115" s="10" t="n"/>
-      <c r="F115" s="10" t="n"/>
-      <c r="G115" s="10" t="n"/>
-      <c r="H115" s="10" t="n"/>
-      <c r="I115" s="10" t="n"/>
-      <c r="J115" s="10" t="n"/>
-      <c r="K115" s="10" t="n"/>
-      <c r="L115" s="10" t="n"/>
-      <c r="M115" s="10" t="n"/>
-      <c r="N115" s="10" t="n"/>
-      <c r="O115" s="10" t="n"/>
-      <c r="P115" s="10" t="n"/>
-      <c r="Q115" s="10" t="n"/>
-      <c r="R115" s="10" t="n"/>
-      <c r="S115" s="10" t="n"/>
-      <c r="T115" s="10" t="n"/>
-      <c r="U115" s="10" t="n"/>
-      <c r="V115" s="10" t="n"/>
-      <c r="W115" s="10" t="n"/>
-      <c r="X115" s="10" t="n"/>
-      <c r="Y115" s="10" t="n"/>
-      <c r="Z115" s="10" t="n"/>
-      <c r="AA115" s="10" t="n"/>
-      <c r="AB115" s="10" t="n"/>
-      <c r="AC115" s="10" t="n"/>
-      <c r="AD115" s="10" t="n"/>
-      <c r="AE115" s="10" t="n"/>
-      <c r="AF115" s="10" t="n"/>
-      <c r="AG115" s="10" t="n"/>
-      <c r="AH115" s="10" t="n"/>
-      <c r="AI115" s="10" t="n"/>
-      <c r="AJ115" s="10" t="n"/>
-      <c r="AK115" s="11" t="n"/>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="B117" s="37" t="inlineStr">
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="10" t="n"/>
+      <c r="J119" s="10" t="n"/>
+      <c r="K119" s="10" t="n"/>
+      <c r="L119" s="10" t="n"/>
+      <c r="M119" s="10" t="n"/>
+      <c r="N119" s="10" t="n"/>
+      <c r="O119" s="10" t="n"/>
+      <c r="P119" s="10" t="n"/>
+      <c r="Q119" s="10" t="n"/>
+      <c r="R119" s="10" t="n"/>
+      <c r="S119" s="10" t="n"/>
+      <c r="T119" s="10" t="n"/>
+      <c r="U119" s="10" t="n"/>
+      <c r="V119" s="10" t="n"/>
+      <c r="W119" s="10" t="n"/>
+      <c r="X119" s="10" t="n"/>
+      <c r="Y119" s="10" t="n"/>
+      <c r="Z119" s="10" t="n"/>
+      <c r="AA119" s="10" t="n"/>
+      <c r="AB119" s="10" t="n"/>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="10" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="10" t="n"/>
+      <c r="AK119" s="11" t="n"/>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="B121" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden (DataScope Violation)）</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="72" customHeight="1">
-      <c r="C118" s="19" t="inlineStr">
+    <row r="122" ht="72" customHeight="1">
+      <c r="C122" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATA_SCOPE_VIOLATION",
@@ -14085,50 +14667,50 @@
 }</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n"/>
-      <c r="E118" s="10" t="n"/>
-      <c r="F118" s="10" t="n"/>
-      <c r="G118" s="10" t="n"/>
-      <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="n"/>
-      <c r="J118" s="10" t="n"/>
-      <c r="K118" s="10" t="n"/>
-      <c r="L118" s="10" t="n"/>
-      <c r="M118" s="10" t="n"/>
-      <c r="N118" s="10" t="n"/>
-      <c r="O118" s="10" t="n"/>
-      <c r="P118" s="10" t="n"/>
-      <c r="Q118" s="10" t="n"/>
-      <c r="R118" s="10" t="n"/>
-      <c r="S118" s="10" t="n"/>
-      <c r="T118" s="10" t="n"/>
-      <c r="U118" s="10" t="n"/>
-      <c r="V118" s="10" t="n"/>
-      <c r="W118" s="10" t="n"/>
-      <c r="X118" s="10" t="n"/>
-      <c r="Y118" s="10" t="n"/>
-      <c r="Z118" s="10" t="n"/>
-      <c r="AA118" s="10" t="n"/>
-      <c r="AB118" s="10" t="n"/>
-      <c r="AC118" s="10" t="n"/>
-      <c r="AD118" s="10" t="n"/>
-      <c r="AE118" s="10" t="n"/>
-      <c r="AF118" s="10" t="n"/>
-      <c r="AG118" s="10" t="n"/>
-      <c r="AH118" s="10" t="n"/>
-      <c r="AI118" s="10" t="n"/>
-      <c r="AJ118" s="10" t="n"/>
-      <c r="AK118" s="11" t="n"/>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="B120" s="37" t="inlineStr">
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="10" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="10" t="n"/>
+      <c r="J122" s="10" t="n"/>
+      <c r="K122" s="10" t="n"/>
+      <c r="L122" s="10" t="n"/>
+      <c r="M122" s="10" t="n"/>
+      <c r="N122" s="10" t="n"/>
+      <c r="O122" s="10" t="n"/>
+      <c r="P122" s="10" t="n"/>
+      <c r="Q122" s="10" t="n"/>
+      <c r="R122" s="10" t="n"/>
+      <c r="S122" s="10" t="n"/>
+      <c r="T122" s="10" t="n"/>
+      <c r="U122" s="10" t="n"/>
+      <c r="V122" s="10" t="n"/>
+      <c r="W122" s="10" t="n"/>
+      <c r="X122" s="10" t="n"/>
+      <c r="Y122" s="10" t="n"/>
+      <c r="Z122" s="10" t="n"/>
+      <c r="AA122" s="10" t="n"/>
+      <c r="AB122" s="10" t="n"/>
+      <c r="AC122" s="10" t="n"/>
+      <c r="AD122" s="10" t="n"/>
+      <c r="AE122" s="10" t="n"/>
+      <c r="AF122" s="10" t="n"/>
+      <c r="AG122" s="10" t="n"/>
+      <c r="AH122" s="10" t="n"/>
+      <c r="AI122" s="10" t="n"/>
+      <c r="AJ122" s="10" t="n"/>
+      <c r="AK122" s="11" t="n"/>
+    </row>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="B124" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="72" customHeight="1">
-      <c r="C121" s="19" t="inlineStr">
+    <row r="125" ht="72" customHeight="1">
+      <c r="C125" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -14136,58 +14718,6 @@
 }</t>
         </is>
       </c>
-      <c r="D121" s="10" t="n"/>
-      <c r="E121" s="10" t="n"/>
-      <c r="F121" s="10" t="n"/>
-      <c r="G121" s="10" t="n"/>
-      <c r="H121" s="10" t="n"/>
-      <c r="I121" s="10" t="n"/>
-      <c r="J121" s="10" t="n"/>
-      <c r="K121" s="10" t="n"/>
-      <c r="L121" s="10" t="n"/>
-      <c r="M121" s="10" t="n"/>
-      <c r="N121" s="10" t="n"/>
-      <c r="O121" s="10" t="n"/>
-      <c r="P121" s="10" t="n"/>
-      <c r="Q121" s="10" t="n"/>
-      <c r="R121" s="10" t="n"/>
-      <c r="S121" s="10" t="n"/>
-      <c r="T121" s="10" t="n"/>
-      <c r="U121" s="10" t="n"/>
-      <c r="V121" s="10" t="n"/>
-      <c r="W121" s="10" t="n"/>
-      <c r="X121" s="10" t="n"/>
-      <c r="Y121" s="10" t="n"/>
-      <c r="Z121" s="10" t="n"/>
-      <c r="AA121" s="10" t="n"/>
-      <c r="AB121" s="10" t="n"/>
-      <c r="AC121" s="10" t="n"/>
-      <c r="AD121" s="10" t="n"/>
-      <c r="AE121" s="10" t="n"/>
-      <c r="AF121" s="10" t="n"/>
-      <c r="AG121" s="10" t="n"/>
-      <c r="AH121" s="10" t="n"/>
-      <c r="AI121" s="10" t="n"/>
-      <c r="AJ121" s="10" t="n"/>
-      <c r="AK121" s="11" t="n"/>
-    </row>
-    <row r="123" ht="19.5" customHeight="1"/>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="27" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="54" customHeight="1">
-      <c r="B125" s="42" t="inlineStr">
-        <is>
-          <t>※ 4.4 データ取込実行 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
-いずれかが失敗した場合は全てロールバックすること。
-例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="n"/>
       <c r="D125" s="10" t="n"/>
       <c r="E125" s="10" t="n"/>
       <c r="F125" s="10" t="n"/>
@@ -14223,312 +14753,255 @@
       <c r="AJ125" s="10" t="n"/>
       <c r="AK125" s="11" t="n"/>
     </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="B126" s="27" t="inlineStr">
+    <row r="127" ht="19.5" customHeight="1"/>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="54" customHeight="1">
+      <c r="B129" s="42" t="inlineStr">
+        <is>
+          <t>※ 4.4 データ取込実行 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="10" t="n"/>
+      <c r="I129" s="10" t="n"/>
+      <c r="J129" s="10" t="n"/>
+      <c r="K129" s="10" t="n"/>
+      <c r="L129" s="10" t="n"/>
+      <c r="M129" s="10" t="n"/>
+      <c r="N129" s="10" t="n"/>
+      <c r="O129" s="10" t="n"/>
+      <c r="P129" s="10" t="n"/>
+      <c r="Q129" s="10" t="n"/>
+      <c r="R129" s="10" t="n"/>
+      <c r="S129" s="10" t="n"/>
+      <c r="T129" s="10" t="n"/>
+      <c r="U129" s="10" t="n"/>
+      <c r="V129" s="10" t="n"/>
+      <c r="W129" s="10" t="n"/>
+      <c r="X129" s="10" t="n"/>
+      <c r="Y129" s="10" t="n"/>
+      <c r="Z129" s="10" t="n"/>
+      <c r="AA129" s="10" t="n"/>
+      <c r="AB129" s="10" t="n"/>
+      <c r="AC129" s="10" t="n"/>
+      <c r="AD129" s="10" t="n"/>
+      <c r="AE129" s="10" t="n"/>
+      <c r="AF129" s="10" t="n"/>
+      <c r="AG129" s="10" t="n"/>
+      <c r="AH129" s="10" t="n"/>
+      <c r="AI129" s="10" t="n"/>
+      <c r="AJ129" s="10" t="n"/>
+      <c r="AK129" s="11" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="B130" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="C127" s="38" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="C131" s="38" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="36" customHeight="1">
-      <c r="D128" s="38" t="inlineStr">
+    <row r="132" ht="36" customHeight="1">
+      <c r="D132" s="38" t="inlineStr">
         <is>
           <t>`import_mode`：必須、`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL` のいずれか</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="D129" s="38" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="D133" s="38" t="inlineStr">
         <is>
           <t>`selected_columns`：必須、配列、1件以上</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="D130" s="38" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="D134" s="38" t="inlineStr">
         <is>
           <t>`rows`：必須、配列、1件以上、30000件以下</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="D131" s="38" t="inlineStr">
-        <is>
-          <t>各行 `rows[i]` の検証（`selected_columns` 対象列のみ）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="36" customHeight="1">
-      <c r="C132" s="38" t="inlineStr">
-        <is>
-          <t>業務ルールチェック（v1.4 — 共通モジュール `dokusya-shubetsu.rules.ts` に集約し UI/取込/一括置換で統一）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="36" customHeight="1">
-      <c r="D133" s="38" t="inlineStr">
-        <is>
-          <t>併読（`dokusya_shubetsu`=3）は取込不可 → エラー「購読種別が3:併読のためExcel取込みできません。」（第3システム同期のため読取専用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="36" customHeight="1">
-      <c r="D134" s="38" t="inlineStr">
-        <is>
-          <t>電子版（`dokusya_shubetsu`=2）かつクレジットカード決済（`shiharai_hoho`=6）の組み合わせは取込不可 → エラー（理由：電子版かつクレカ決済取込不可のため。読取専用）</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="D135" s="38" t="inlineStr">
         <is>
+          <t>各行 `rows[i]` の検証（`selected_columns` 対象列のみ）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="C136" s="38" t="inlineStr">
+        <is>
+          <t>業務ルールチェック（v1.4 — 共通モジュール `dokusya-shubetsu.rules.ts` に集約し UI/取込/一括置換で統一）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="D137" s="38" t="inlineStr">
+        <is>
+          <t>併読（`dokusya_shubetsu`=3）は取込不可 → エラー「購読種別が3:併読のためExcel取込みできません。」（第3システム同期のため読取専用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="D138" s="38" t="inlineStr">
+        <is>
+          <t>電子版（`dokusya_shubetsu`=2）かつクレジットカード決済（`shiharai_hoho`=6）の組み合わせは取込不可 → エラー（理由：電子版かつクレカ決済取込不可のため。読取専用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="D139" s="38" t="inlineStr">
+        <is>
           <t>電子版の購読部数=1（上記 `dokusya_busu` 参照）</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="D136" s="38" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="D140" s="38" t="inlineStr">
         <is>
           <t>種別依存の適用日ルール（上記 `joho_henko_tekiyo_date` 参照）</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="36" customHeight="1">
-      <c r="C137" s="38" t="inlineStr">
+    <row r="141" ht="36" customHeight="1">
+      <c r="C141" s="38" t="inlineStr">
         <is>
           <t>トップレベルのバリデーションエラー：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="36" customHeight="1">
-      <c r="C138" s="38" t="inlineStr">
+    <row r="142" ht="36" customHeight="1">
+      <c r="C142" s="38" t="inlineStr">
         <is>
           <t>行レベルのバリデーションエラー：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（row番号含む。最大10件まで返却）</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="B139" s="27" t="inlineStr">
+    <row r="143" ht="18" customHeight="1">
+      <c r="B143" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="C140" s="38" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="C141" s="38" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="C142" s="38" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.import`</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="36" customHeight="1">
-      <c r="C143" s="38" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="C144" s="38" t="inlineStr">
         <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="C145" s="38" t="inlineStr">
+        <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="C146" s="38" t="inlineStr">
+        <is>
+          <t>必要権限: `dokusya.import`</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="C147" s="38" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="C148" s="38" t="inlineStr">
+        <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="36" customHeight="1">
-      <c r="C145" s="38" t="inlineStr">
-        <is>
-          <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="D146" s="38" t="inlineStr">
-        <is>
-          <t>中央会：自中央会管轄JAのみ取込可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="D147" s="38" t="inlineStr">
-        <is>
-          <t>JA本店：自JAのみ取込可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="D148" s="38" t="inlineStr">
-        <is>
-          <t>JA管理支店：自管理支店配下のみ取込可能。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="C149" s="38" t="inlineStr">
         <is>
+          <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="D150" s="38" t="inlineStr">
+        <is>
+          <t>中央会：自中央会管轄JAのみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="D151" s="38" t="inlineStr">
+        <is>
+          <t>JA本店：自JAのみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="D152" s="38" t="inlineStr">
+        <is>
+          <t>JA管理支店：自管理支店配下のみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="36" customHeight="1">
+      <c r="C153" s="38" t="inlineStr">
+        <is>
           <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="B150" s="27" t="inlineStr">
+    <row r="154" ht="18" customHeight="1">
+      <c r="B154" s="27" t="inlineStr">
         <is>
           <t>4.3 事前チェック（参照整合性・重複）</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="C151" s="38" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="C155" s="38" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープを取得する（`ja_id` / `kanri_shiten_id`）。</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="C152" s="38" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="C156" s="38" t="inlineStr">
         <is>
           <t>DBとの整合性チェックをバッチで実行する。</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="108" customHeight="1">
-      <c r="C153" s="42" t="inlineStr">
+    <row r="157" ht="108" customHeight="1">
+      <c r="C157" s="42" t="inlineStr">
         <is>
           <t>SELECT tanka_id, tanka_code
 FROM m_tanka
 WHERE ja_id = :ja_id
   AND tanka_code = ANY(:tanka_codes)
   AND tanka_type = 1  -- 購読料
-  AND deleted_at IS NULL</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="n"/>
-      <c r="E153" s="10" t="n"/>
-      <c r="F153" s="10" t="n"/>
-      <c r="G153" s="10" t="n"/>
-      <c r="H153" s="10" t="n"/>
-      <c r="I153" s="10" t="n"/>
-      <c r="J153" s="10" t="n"/>
-      <c r="K153" s="10" t="n"/>
-      <c r="L153" s="10" t="n"/>
-      <c r="M153" s="10" t="n"/>
-      <c r="N153" s="10" t="n"/>
-      <c r="O153" s="10" t="n"/>
-      <c r="P153" s="10" t="n"/>
-      <c r="Q153" s="10" t="n"/>
-      <c r="R153" s="10" t="n"/>
-      <c r="S153" s="10" t="n"/>
-      <c r="T153" s="10" t="n"/>
-      <c r="U153" s="10" t="n"/>
-      <c r="V153" s="10" t="n"/>
-      <c r="W153" s="10" t="n"/>
-      <c r="X153" s="10" t="n"/>
-      <c r="Y153" s="10" t="n"/>
-      <c r="Z153" s="10" t="n"/>
-      <c r="AA153" s="10" t="n"/>
-      <c r="AB153" s="10" t="n"/>
-      <c r="AC153" s="10" t="n"/>
-      <c r="AD153" s="10" t="n"/>
-      <c r="AE153" s="10" t="n"/>
-      <c r="AF153" s="10" t="n"/>
-      <c r="AG153" s="10" t="n"/>
-      <c r="AH153" s="10" t="n"/>
-      <c r="AI153" s="10" t="n"/>
-      <c r="AJ153" s="10" t="n"/>
-      <c r="AK153" s="11" t="n"/>
-    </row>
-    <row r="154" ht="36" customHeight="1">
-      <c r="C154" s="38" t="inlineStr">
-        <is>
-          <t>未ヒットの `tanka_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='tanka_code'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="90" customHeight="1">
-      <c r="C155" s="42" t="inlineStr">
-        <is>
-          <t>SELECT hanbaiten_id, hanbaiten_code
-FROM m_hanbaiten
-WHERE ja_id = :ja_id
-  AND hanbaiten_code = ANY(:hanbaiten_codes)
-  AND deleted_at IS NULL</t>
-        </is>
-      </c>
-      <c r="D155" s="10" t="n"/>
-      <c r="E155" s="10" t="n"/>
-      <c r="F155" s="10" t="n"/>
-      <c r="G155" s="10" t="n"/>
-      <c r="H155" s="10" t="n"/>
-      <c r="I155" s="10" t="n"/>
-      <c r="J155" s="10" t="n"/>
-      <c r="K155" s="10" t="n"/>
-      <c r="L155" s="10" t="n"/>
-      <c r="M155" s="10" t="n"/>
-      <c r="N155" s="10" t="n"/>
-      <c r="O155" s="10" t="n"/>
-      <c r="P155" s="10" t="n"/>
-      <c r="Q155" s="10" t="n"/>
-      <c r="R155" s="10" t="n"/>
-      <c r="S155" s="10" t="n"/>
-      <c r="T155" s="10" t="n"/>
-      <c r="U155" s="10" t="n"/>
-      <c r="V155" s="10" t="n"/>
-      <c r="W155" s="10" t="n"/>
-      <c r="X155" s="10" t="n"/>
-      <c r="Y155" s="10" t="n"/>
-      <c r="Z155" s="10" t="n"/>
-      <c r="AA155" s="10" t="n"/>
-      <c r="AB155" s="10" t="n"/>
-      <c r="AC155" s="10" t="n"/>
-      <c r="AD155" s="10" t="n"/>
-      <c r="AE155" s="10" t="n"/>
-      <c r="AF155" s="10" t="n"/>
-      <c r="AG155" s="10" t="n"/>
-      <c r="AH155" s="10" t="n"/>
-      <c r="AI155" s="10" t="n"/>
-      <c r="AJ155" s="10" t="n"/>
-      <c r="AK155" s="11" t="n"/>
-    </row>
-    <row r="156" ht="36" customHeight="1">
-      <c r="C156" s="38" t="inlineStr">
-        <is>
-          <t>未ヒットの `hanbaiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='hanbaiten_code'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="198" customHeight="1">
-      <c r="C157" s="42" t="inlineStr">
-        <is>
-          <t>SELECT kanri_shiten_id, kanri_shiten_code
-FROM m_kanri_shiten
-WHERE ja_id = :ja_id
-  AND kanri_shiten_code = ANY(:kanri_shiten_codes)
-  AND deleted_at IS NULL
-SELECT shiten_id, shiten_code
-FROM m_shiten
-WHERE ja_id = :ja_id
-  AND shiten_code = ANY(:shiten_codes)
   AND deleted_at IS NULL</t>
         </is>
       </c>
@@ -14570,33 +15043,142 @@
     <row r="158" ht="36" customHeight="1">
       <c r="C158" s="38" t="inlineStr">
         <is>
-          <t>未ヒットの `kanri_shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='kanri_shiten_code'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="36" customHeight="1">
-      <c r="C159" s="38" t="inlineStr">
-        <is>
-          <t>未ヒットの `shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='shiten_code'）</t>
-        </is>
-      </c>
+          <t>未ヒットの `tanka_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='tanka_code'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="90" customHeight="1">
+      <c r="C159" s="42" t="inlineStr">
+        <is>
+          <t>SELECT hanbaiten_id, hanbaiten_code
+FROM m_hanbaiten
+WHERE ja_id = :ja_id
+  AND hanbaiten_code = ANY(:hanbaiten_codes)
+  AND deleted_at IS NULL</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="n"/>
+      <c r="E159" s="10" t="n"/>
+      <c r="F159" s="10" t="n"/>
+      <c r="G159" s="10" t="n"/>
+      <c r="H159" s="10" t="n"/>
+      <c r="I159" s="10" t="n"/>
+      <c r="J159" s="10" t="n"/>
+      <c r="K159" s="10" t="n"/>
+      <c r="L159" s="10" t="n"/>
+      <c r="M159" s="10" t="n"/>
+      <c r="N159" s="10" t="n"/>
+      <c r="O159" s="10" t="n"/>
+      <c r="P159" s="10" t="n"/>
+      <c r="Q159" s="10" t="n"/>
+      <c r="R159" s="10" t="n"/>
+      <c r="S159" s="10" t="n"/>
+      <c r="T159" s="10" t="n"/>
+      <c r="U159" s="10" t="n"/>
+      <c r="V159" s="10" t="n"/>
+      <c r="W159" s="10" t="n"/>
+      <c r="X159" s="10" t="n"/>
+      <c r="Y159" s="10" t="n"/>
+      <c r="Z159" s="10" t="n"/>
+      <c r="AA159" s="10" t="n"/>
+      <c r="AB159" s="10" t="n"/>
+      <c r="AC159" s="10" t="n"/>
+      <c r="AD159" s="10" t="n"/>
+      <c r="AE159" s="10" t="n"/>
+      <c r="AF159" s="10" t="n"/>
+      <c r="AG159" s="10" t="n"/>
+      <c r="AH159" s="10" t="n"/>
+      <c r="AI159" s="10" t="n"/>
+      <c r="AJ159" s="10" t="n"/>
+      <c r="AK159" s="11" t="n"/>
     </row>
     <row r="160" ht="36" customHeight="1">
       <c r="C160" s="38" t="inlineStr">
         <is>
+          <t>未ヒットの `hanbaiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='hanbaiten_code'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="198" customHeight="1">
+      <c r="C161" s="42" t="inlineStr">
+        <is>
+          <t>SELECT kanri_shiten_id, kanri_shiten_code
+FROM m_kanri_shiten
+WHERE ja_id = :ja_id
+  AND kanri_shiten_code = ANY(:kanri_shiten_codes)
+  AND deleted_at IS NULL
+SELECT shiten_id, shiten_code
+FROM m_shiten
+WHERE ja_id = :ja_id
+  AND shiten_code = ANY(:shiten_codes)
+  AND deleted_at IS NULL</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="n"/>
+      <c r="E161" s="10" t="n"/>
+      <c r="F161" s="10" t="n"/>
+      <c r="G161" s="10" t="n"/>
+      <c r="H161" s="10" t="n"/>
+      <c r="I161" s="10" t="n"/>
+      <c r="J161" s="10" t="n"/>
+      <c r="K161" s="10" t="n"/>
+      <c r="L161" s="10" t="n"/>
+      <c r="M161" s="10" t="n"/>
+      <c r="N161" s="10" t="n"/>
+      <c r="O161" s="10" t="n"/>
+      <c r="P161" s="10" t="n"/>
+      <c r="Q161" s="10" t="n"/>
+      <c r="R161" s="10" t="n"/>
+      <c r="S161" s="10" t="n"/>
+      <c r="T161" s="10" t="n"/>
+      <c r="U161" s="10" t="n"/>
+      <c r="V161" s="10" t="n"/>
+      <c r="W161" s="10" t="n"/>
+      <c r="X161" s="10" t="n"/>
+      <c r="Y161" s="10" t="n"/>
+      <c r="Z161" s="10" t="n"/>
+      <c r="AA161" s="10" t="n"/>
+      <c r="AB161" s="10" t="n"/>
+      <c r="AC161" s="10" t="n"/>
+      <c r="AD161" s="10" t="n"/>
+      <c r="AE161" s="10" t="n"/>
+      <c r="AF161" s="10" t="n"/>
+      <c r="AG161" s="10" t="n"/>
+      <c r="AH161" s="10" t="n"/>
+      <c r="AI161" s="10" t="n"/>
+      <c r="AJ161" s="10" t="n"/>
+      <c r="AK161" s="11" t="n"/>
+    </row>
+    <row r="162" ht="36" customHeight="1">
+      <c r="C162" s="38" t="inlineStr">
+        <is>
+          <t>未ヒットの `kanri_shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='kanri_shiten_code'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="36" customHeight="1">
+      <c r="C163" s="38" t="inlineStr">
+        <is>
+          <t>未ヒットの `shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='shiten_code'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="36" customHeight="1">
+      <c r="C164" s="38" t="inlineStr">
+        <is>
           <t>未ヒット：`IMPORT_VALIDATION_ERROR` + errors（row, field）</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="36" customHeight="1">
-      <c r="C161" s="38" t="inlineStr">
+    <row r="165" ht="36" customHeight="1">
+      <c r="C165" s="38" t="inlineStr">
         <is>
           <t>JA_KANRI_SHITEN の場合、自管理支店 ID と一致しない `kanri_shiten_id` も DataScope 違反とする。</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="162" customHeight="1">
-      <c r="C162" s="42" t="inlineStr">
+    <row r="166" ht="162" customHeight="1">
+      <c r="C166" s="42" t="inlineStr">
         <is>
           <t>-- UPDATE_ALL / UPDATE_PARTIAL モード（dokusya_id をキー、または kumiaiin_code をキー）
 SELECT dokusya_id, kumiaiin_code, ja_id, kanri_shiten_id
@@ -14609,99 +15191,99 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D162" s="10" t="n"/>
-      <c r="E162" s="10" t="n"/>
-      <c r="F162" s="10" t="n"/>
-      <c r="G162" s="10" t="n"/>
-      <c r="H162" s="10" t="n"/>
-      <c r="I162" s="10" t="n"/>
-      <c r="J162" s="10" t="n"/>
-      <c r="K162" s="10" t="n"/>
-      <c r="L162" s="10" t="n"/>
-      <c r="M162" s="10" t="n"/>
-      <c r="N162" s="10" t="n"/>
-      <c r="O162" s="10" t="n"/>
-      <c r="P162" s="10" t="n"/>
-      <c r="Q162" s="10" t="n"/>
-      <c r="R162" s="10" t="n"/>
-      <c r="S162" s="10" t="n"/>
-      <c r="T162" s="10" t="n"/>
-      <c r="U162" s="10" t="n"/>
-      <c r="V162" s="10" t="n"/>
-      <c r="W162" s="10" t="n"/>
-      <c r="X162" s="10" t="n"/>
-      <c r="Y162" s="10" t="n"/>
-      <c r="Z162" s="10" t="n"/>
-      <c r="AA162" s="10" t="n"/>
-      <c r="AB162" s="10" t="n"/>
-      <c r="AC162" s="10" t="n"/>
-      <c r="AD162" s="10" t="n"/>
-      <c r="AE162" s="10" t="n"/>
-      <c r="AF162" s="10" t="n"/>
-      <c r="AG162" s="10" t="n"/>
-      <c r="AH162" s="10" t="n"/>
-      <c r="AI162" s="10" t="n"/>
-      <c r="AJ162" s="10" t="n"/>
-      <c r="AK162" s="11" t="n"/>
-    </row>
-    <row r="163" ht="54" customHeight="1">
-      <c r="C163" s="38" t="inlineStr">
+      <c r="D166" s="10" t="n"/>
+      <c r="E166" s="10" t="n"/>
+      <c r="F166" s="10" t="n"/>
+      <c r="G166" s="10" t="n"/>
+      <c r="H166" s="10" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="10" t="n"/>
+      <c r="K166" s="10" t="n"/>
+      <c r="L166" s="10" t="n"/>
+      <c r="M166" s="10" t="n"/>
+      <c r="N166" s="10" t="n"/>
+      <c r="O166" s="10" t="n"/>
+      <c r="P166" s="10" t="n"/>
+      <c r="Q166" s="10" t="n"/>
+      <c r="R166" s="10" t="n"/>
+      <c r="S166" s="10" t="n"/>
+      <c r="T166" s="10" t="n"/>
+      <c r="U166" s="10" t="n"/>
+      <c r="V166" s="10" t="n"/>
+      <c r="W166" s="10" t="n"/>
+      <c r="X166" s="10" t="n"/>
+      <c r="Y166" s="10" t="n"/>
+      <c r="Z166" s="10" t="n"/>
+      <c r="AA166" s="10" t="n"/>
+      <c r="AB166" s="10" t="n"/>
+      <c r="AC166" s="10" t="n"/>
+      <c r="AD166" s="10" t="n"/>
+      <c r="AE166" s="10" t="n"/>
+      <c r="AF166" s="10" t="n"/>
+      <c r="AG166" s="10" t="n"/>
+      <c r="AH166" s="10" t="n"/>
+      <c r="AI166" s="10" t="n"/>
+      <c r="AJ166" s="10" t="n"/>
+      <c r="AK166" s="11" t="n"/>
+    </row>
+    <row r="167" ht="54" customHeight="1">
+      <c r="C167" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_ALL` / `UPDATE_PARTIAL` モード：未ヒットの行は「存在しない」エラー → `IMPORT_VALIDATION_ERROR` + errors（row, field='dokusya_id' または 'kumiaiin_code'）</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="36" customHeight="1">
-      <c r="C164" s="38" t="inlineStr">
+    <row r="168" ht="36" customHeight="1">
+      <c r="C168" s="38" t="inlineStr">
         <is>
           <t>一括中止（`tetsuzuki_shurui`=0）：`kumiaiin_code` をキーに既存購読者を取得する。未ヒットはエラーとする。</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="54" customHeight="1">
-      <c r="C165" s="38" t="inlineStr">
+    <row r="169" ht="54" customHeight="1">
+      <c r="C169" s="38" t="inlineStr">
         <is>
           <t>取得した既存購読者の `kanri_shiten_id` が JA_KANRI_SHITEN の自管理支店と一致しない場合：DataScope 違反 → HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="36" customHeight="1">
-      <c r="C166" s="38" t="inlineStr">
+    <row r="170" ht="36" customHeight="1">
+      <c r="C170" s="38" t="inlineStr">
         <is>
           <t>事前チェックエラーが存在する場合：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（最大10件）を返却し、以降の処理を中断する。</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="B167" s="27" t="inlineStr">
+    <row r="171" ht="18" customHeight="1">
+      <c r="B171" s="27" t="inlineStr">
         <is>
           <t>4.4 データ取込実行（トランザクション）</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="C168" s="38" t="inlineStr">
+    <row r="172" ht="18" customHeight="1">
+      <c r="C172" s="38" t="inlineStr">
         <is>
           <t>DBトランザクションを開始する。</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="C169" s="38" t="inlineStr">
+    <row r="173" ht="18" customHeight="1">
+      <c r="C173" s="38" t="inlineStr">
         <is>
           <t>取込モードに応じて以下の SQL を行ごとに実行する。</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="C170" s="38" t="inlineStr">
+    <row r="174" ht="18" customHeight="1">
+      <c r="C174" s="38" t="inlineStr">
         <is>
           <t>1件でもエラーが発生した場合はトランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="409" customHeight="1">
-      <c r="C171" s="42" t="inlineStr">
+    <row r="175" ht="409" customHeight="1">
+      <c r="C175" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya (
   ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -14740,78 +15322,78 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D171" s="10" t="n"/>
-      <c r="E171" s="10" t="n"/>
-      <c r="F171" s="10" t="n"/>
-      <c r="G171" s="10" t="n"/>
-      <c r="H171" s="10" t="n"/>
-      <c r="I171" s="10" t="n"/>
-      <c r="J171" s="10" t="n"/>
-      <c r="K171" s="10" t="n"/>
-      <c r="L171" s="10" t="n"/>
-      <c r="M171" s="10" t="n"/>
-      <c r="N171" s="10" t="n"/>
-      <c r="O171" s="10" t="n"/>
-      <c r="P171" s="10" t="n"/>
-      <c r="Q171" s="10" t="n"/>
-      <c r="R171" s="10" t="n"/>
-      <c r="S171" s="10" t="n"/>
-      <c r="T171" s="10" t="n"/>
-      <c r="U171" s="10" t="n"/>
-      <c r="V171" s="10" t="n"/>
-      <c r="W171" s="10" t="n"/>
-      <c r="X171" s="10" t="n"/>
-      <c r="Y171" s="10" t="n"/>
-      <c r="Z171" s="10" t="n"/>
-      <c r="AA171" s="10" t="n"/>
-      <c r="AB171" s="10" t="n"/>
-      <c r="AC171" s="10" t="n"/>
-      <c r="AD171" s="10" t="n"/>
-      <c r="AE171" s="10" t="n"/>
-      <c r="AF171" s="10" t="n"/>
-      <c r="AG171" s="10" t="n"/>
-      <c r="AH171" s="10" t="n"/>
-      <c r="AI171" s="10" t="n"/>
-      <c r="AJ171" s="10" t="n"/>
-      <c r="AK171" s="11" t="n"/>
-    </row>
-    <row r="172" ht="36" customHeight="1">
-      <c r="C172" s="38" t="inlineStr">
+      <c r="D175" s="10" t="n"/>
+      <c r="E175" s="10" t="n"/>
+      <c r="F175" s="10" t="n"/>
+      <c r="G175" s="10" t="n"/>
+      <c r="H175" s="10" t="n"/>
+      <c r="I175" s="10" t="n"/>
+      <c r="J175" s="10" t="n"/>
+      <c r="K175" s="10" t="n"/>
+      <c r="L175" s="10" t="n"/>
+      <c r="M175" s="10" t="n"/>
+      <c r="N175" s="10" t="n"/>
+      <c r="O175" s="10" t="n"/>
+      <c r="P175" s="10" t="n"/>
+      <c r="Q175" s="10" t="n"/>
+      <c r="R175" s="10" t="n"/>
+      <c r="S175" s="10" t="n"/>
+      <c r="T175" s="10" t="n"/>
+      <c r="U175" s="10" t="n"/>
+      <c r="V175" s="10" t="n"/>
+      <c r="W175" s="10" t="n"/>
+      <c r="X175" s="10" t="n"/>
+      <c r="Y175" s="10" t="n"/>
+      <c r="Z175" s="10" t="n"/>
+      <c r="AA175" s="10" t="n"/>
+      <c r="AB175" s="10" t="n"/>
+      <c r="AC175" s="10" t="n"/>
+      <c r="AD175" s="10" t="n"/>
+      <c r="AE175" s="10" t="n"/>
+      <c r="AF175" s="10" t="n"/>
+      <c r="AG175" s="10" t="n"/>
+      <c r="AH175" s="10" t="n"/>
+      <c r="AI175" s="10" t="n"/>
+      <c r="AJ175" s="10" t="n"/>
+      <c r="AK175" s="11" t="n"/>
+    </row>
+    <row r="176" ht="36" customHeight="1">
+      <c r="C176" s="38" t="inlineStr">
         <is>
           <t>`selected_columns` に含まれない列はデフォルト値（空文字 / NULL / 0 / false）を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="36" customHeight="1">
-      <c r="C173" s="38" t="inlineStr">
+    <row r="177" ht="36" customHeight="1">
+      <c r="C177" s="38" t="inlineStr">
         <is>
           <t>`shoki_dokusya_kaishi_date` には `dokusya_kaishi_date` と同じ値を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="72" customHeight="1">
-      <c r="C174" s="38" t="inlineStr">
+    <row r="178" ht="72" customHeight="1">
+      <c r="C178" s="38" t="inlineStr">
         <is>
           <t>`haitatsu_same_flg`（v1.2 顧客要件 2026-06）：**取込列「購読者情報と同じ」で明示指定された値を採用する**（BE は推論しない）。TRUE のとき配達先項目は未入力でよく、配達先住所は購読者住所を使用する。列が未指定（空欄）の行のみ、従来どおり「配達先項目が全て未入力→TRUE / いずれか入力あり→FALSE」で導出する。</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="54" customHeight="1">
-      <c r="C175" s="38" t="inlineStr">
+    <row r="179" ht="54" customHeight="1">
+      <c r="C179" s="38" t="inlineStr">
         <is>
           <t>既存購読者を `dokusya_id` または `kumiaiin_code` で検索し、`selected_columns` 対象外の項目も含めて全項目を更新する（未選択列は NULL / 空文字 / 0 で上書き）。</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="162" customHeight="1">
-      <c r="C176" s="38" t="inlineStr">
+    <row r="180" ht="162" customHeight="1">
+      <c r="C180" s="38" t="inlineStr">
         <is>
           <t>ただし NOT NULL の FK・参照列（kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id / dokusya_shubetsu / tetsuzuki_shurui / shiharai_hoho）は空欄上書きで制約違反になるため `COALESCE(:値, 既存値)` で既存値を維持する（UPDATE モードでは FK コードは任意入力＝存在時のみ検証）。`dokusya_kaishi_date` も空欄時は既存値を維持。`shoki_dokusya_kaishi_date`（初回購読開始日）は不変のため SET から除外する。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="409" customHeight="1">
-      <c r="C177" s="42" t="inlineStr">
+    <row r="181" ht="409" customHeight="1">
+      <c r="C181" s="42" t="inlineStr">
         <is>
           <t>-- 更新前データ取得（操作ログ用）
 SELECT * FROM t_dokusya
@@ -14878,82 +15460,6 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D177" s="10" t="n"/>
-      <c r="E177" s="10" t="n"/>
-      <c r="F177" s="10" t="n"/>
-      <c r="G177" s="10" t="n"/>
-      <c r="H177" s="10" t="n"/>
-      <c r="I177" s="10" t="n"/>
-      <c r="J177" s="10" t="n"/>
-      <c r="K177" s="10" t="n"/>
-      <c r="L177" s="10" t="n"/>
-      <c r="M177" s="10" t="n"/>
-      <c r="N177" s="10" t="n"/>
-      <c r="O177" s="10" t="n"/>
-      <c r="P177" s="10" t="n"/>
-      <c r="Q177" s="10" t="n"/>
-      <c r="R177" s="10" t="n"/>
-      <c r="S177" s="10" t="n"/>
-      <c r="T177" s="10" t="n"/>
-      <c r="U177" s="10" t="n"/>
-      <c r="V177" s="10" t="n"/>
-      <c r="W177" s="10" t="n"/>
-      <c r="X177" s="10" t="n"/>
-      <c r="Y177" s="10" t="n"/>
-      <c r="Z177" s="10" t="n"/>
-      <c r="AA177" s="10" t="n"/>
-      <c r="AB177" s="10" t="n"/>
-      <c r="AC177" s="10" t="n"/>
-      <c r="AD177" s="10" t="n"/>
-      <c r="AE177" s="10" t="n"/>
-      <c r="AF177" s="10" t="n"/>
-      <c r="AG177" s="10" t="n"/>
-      <c r="AH177" s="10" t="n"/>
-      <c r="AI177" s="10" t="n"/>
-      <c r="AJ177" s="10" t="n"/>
-      <c r="AK177" s="11" t="n"/>
-    </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="C178" s="38" t="inlineStr">
-        <is>
-          <t>`selected_columns` に含まれる列のみ更新する。未選択列は既存値を維持する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="108" customHeight="1">
-      <c r="C179" s="38" t="inlineStr">
-        <is>
-          <t>更新可能カラムは取込テンプレートの全項目（email / 住所 / 配達先 / 口座 / 単価・販売店 等を含む）。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。NOT NULL の FK・参照列は `COALESCE(:値, 既存値)` で既存値を維持する。`dokusya_id` はキーのため更新しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="C180" s="38" t="inlineStr">
-        <is>
-          <t>動的に SET 句を構築する（擬似コード）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="288" customHeight="1">
-      <c r="C181" s="42" t="inlineStr">
-        <is>
-          <t>-- 更新前データ取得（操作ログ用）
-SELECT * FROM t_dokusya
-WHERE ja_id = :ja_id
-  AND dokusya_id = :dokusya_id
-  AND deleted_at IS NULL
--- 動的 UPDATE（selected_columns に含まれる項目のみ SET）
-UPDATE t_dokusya
-SET {dynamic_set_clause},
-    rireki_no = rireki_no + 1,
-    updated_at = NOW(),
-    updated_by = :user_account_id
-WHERE ja_id = :ja_id
-  AND dokusya_id = :dokusya_id
-  AND deleted_at IS NULL
-RETURNING *</t>
-        </is>
-      </c>
       <c r="D181" s="10" t="n"/>
       <c r="E181" s="10" t="n"/>
       <c r="F181" s="10" t="n"/>
@@ -14989,71 +15495,147 @@
       <c r="AJ181" s="10" t="n"/>
       <c r="AK181" s="11" t="n"/>
     </row>
-    <row r="182" ht="54" customHeight="1">
+    <row r="182" ht="18" customHeight="1">
       <c r="C182" s="38" t="inlineStr">
         <is>
+          <t>`selected_columns` に含まれる列のみ更新する。未選択列は既存値を維持する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="108" customHeight="1">
+      <c r="C183" s="38" t="inlineStr">
+        <is>
+          <t>更新可能カラムは取込テンプレートの全項目（email / 住所 / 配達先 / 口座 / 単価・販売店 等を含む）。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。NOT NULL の FK・参照列は `COALESCE(:値, 既存値)` で既存値を維持する。`dokusya_id` はキーのため更新しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="C184" s="38" t="inlineStr">
+        <is>
+          <t>動的に SET 句を構築する（擬似コード）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="288" customHeight="1">
+      <c r="C185" s="42" t="inlineStr">
+        <is>
+          <t>-- 更新前データ取得（操作ログ用）
+SELECT * FROM t_dokusya
+WHERE ja_id = :ja_id
+  AND dokusya_id = :dokusya_id
+  AND deleted_at IS NULL
+-- 動的 UPDATE（selected_columns に含まれる項目のみ SET）
+UPDATE t_dokusya
+SET {dynamic_set_clause},
+    rireki_no = rireki_no + 1,
+    updated_at = NOW(),
+    updated_by = :user_account_id
+WHERE ja_id = :ja_id
+  AND dokusya_id = :dokusya_id
+  AND deleted_at IS NULL
+RETURNING *</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="n"/>
+      <c r="E185" s="10" t="n"/>
+      <c r="F185" s="10" t="n"/>
+      <c r="G185" s="10" t="n"/>
+      <c r="H185" s="10" t="n"/>
+      <c r="I185" s="10" t="n"/>
+      <c r="J185" s="10" t="n"/>
+      <c r="K185" s="10" t="n"/>
+      <c r="L185" s="10" t="n"/>
+      <c r="M185" s="10" t="n"/>
+      <c r="N185" s="10" t="n"/>
+      <c r="O185" s="10" t="n"/>
+      <c r="P185" s="10" t="n"/>
+      <c r="Q185" s="10" t="n"/>
+      <c r="R185" s="10" t="n"/>
+      <c r="S185" s="10" t="n"/>
+      <c r="T185" s="10" t="n"/>
+      <c r="U185" s="10" t="n"/>
+      <c r="V185" s="10" t="n"/>
+      <c r="W185" s="10" t="n"/>
+      <c r="X185" s="10" t="n"/>
+      <c r="Y185" s="10" t="n"/>
+      <c r="Z185" s="10" t="n"/>
+      <c r="AA185" s="10" t="n"/>
+      <c r="AB185" s="10" t="n"/>
+      <c r="AC185" s="10" t="n"/>
+      <c r="AD185" s="10" t="n"/>
+      <c r="AE185" s="10" t="n"/>
+      <c r="AF185" s="10" t="n"/>
+      <c r="AG185" s="10" t="n"/>
+      <c r="AH185" s="10" t="n"/>
+      <c r="AI185" s="10" t="n"/>
+      <c r="AJ185" s="10" t="n"/>
+      <c r="AK185" s="11" t="n"/>
+    </row>
+    <row r="186" ht="54" customHeight="1">
+      <c r="C186" s="38" t="inlineStr">
+        <is>
           <t>**本処理は廃止**。手続種類カラムを取込テンプレートから削除し、取込で解約は扱わない。NEW は `tetsuzuki_shurui=1`（新規）固定、UPDATE は手続種類を変更しない（既存値を維持）。</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="36" customHeight="1">
-      <c r="C183" s="38" t="inlineStr">
+    <row r="187" ht="36" customHeight="1">
+      <c r="C187" s="38" t="inlineStr">
         <is>
           <t>解約は SCR-011/013 の編集運用と同じく「解約予定日（購読中止日）」の登録のみとし、実際の解約処理（購読部数=0・解約状態）は日次バッチが担う（バッチ未実装）。</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="36" customHeight="1">
-      <c r="C184" s="38" t="inlineStr">
+    <row r="188" ht="36" customHeight="1">
+      <c r="C188" s="38" t="inlineStr">
         <is>
           <t>取込モードに関わらず、取り込んだデータ件数分のレコードを `t_dokusya_rireki` に追加する。</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="C185" s="38" t="inlineStr">
+    <row r="189" ht="18" customHeight="1">
+      <c r="C189" s="38" t="inlineStr">
         <is>
           <t>履歴No（`rireki_no`）は `t_dokusya.rireki_no` の値を引き継ぐ。</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="36" customHeight="1">
-      <c r="C186" s="38" t="inlineStr">
+    <row r="190" ht="36" customHeight="1">
+      <c r="C190" s="38" t="inlineStr">
         <is>
           <t>`saishin_data_flg` は新規追加レコードのみ TRUE、既存履歴は FALSE に更新する。</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="90" customHeight="1">
-      <c r="C187" s="38" t="inlineStr">
+    <row r="191" ht="90" customHeight="1">
+      <c r="C191" s="38" t="inlineStr">
         <is>
           <t>**v1.3（顧客要件 2026-07）— UPDATE は1更新1レコード**: 販売店適用日を廃止し、適用日は `joho_henko_tekiyo_date` に統一。情報変更（購読部数/住所等）と販売店変更が同一行で同時に起きても履歴は **1件**にまとめる（UI編集 SCR-011/013・一括置換 SCR-015 と同一ロジック・共通実装）。旧 v1.2 の「適用日順に2件分割」は廃止。</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="36" customHeight="1">
-      <c r="D188" s="38" t="inlineStr">
+    <row r="192" ht="36" customHeight="1">
+      <c r="D192" s="38" t="inlineStr">
         <is>
           <t>追加レコード: `joho_henko_tekiyo_date`=読者情報変更適用日（販売店・支払方法を含む全変更の唯一の適用日。専用の販売店適用日列は持たない）。</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="36" customHeight="1">
-      <c r="D189" s="38" t="inlineStr">
+    <row r="193" ht="36" customHeight="1">
+      <c r="D193" s="38" t="inlineStr">
         <is>
           <t>`saishin_data_flg` は当日基準の再計算（recomputeMaster）で確定。`zenkai_*` / `zougen_hokoku_flg` は直前状態との差分で算出。</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="36" customHeight="1">
-      <c r="D190" s="38" t="inlineStr">
+    <row r="194" ht="36" customHeight="1">
+      <c r="D194" s="38" t="inlineStr">
         <is>
           <t>取込で解約は扱わないため `kaiyaku_flg` は常に FALSE。`shinki_flg` は NEW かつ手続種類=新規(1) のときのみ TRUE。</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="409" customHeight="1">
-      <c r="C191" s="42" t="inlineStr">
+    <row r="195" ht="409" customHeight="1">
+      <c r="C195" s="42" t="inlineStr">
         <is>
           <t>-- 既存履歴の saishin_data_flg を FALSE に更新
 UPDATE t_dokusya_rireki
@@ -15103,92 +15685,92 @@
 )</t>
         </is>
       </c>
-      <c r="D191" s="10" t="n"/>
-      <c r="E191" s="10" t="n"/>
-      <c r="F191" s="10" t="n"/>
-      <c r="G191" s="10" t="n"/>
-      <c r="H191" s="10" t="n"/>
-      <c r="I191" s="10" t="n"/>
-      <c r="J191" s="10" t="n"/>
-      <c r="K191" s="10" t="n"/>
-      <c r="L191" s="10" t="n"/>
-      <c r="M191" s="10" t="n"/>
-      <c r="N191" s="10" t="n"/>
-      <c r="O191" s="10" t="n"/>
-      <c r="P191" s="10" t="n"/>
-      <c r="Q191" s="10" t="n"/>
-      <c r="R191" s="10" t="n"/>
-      <c r="S191" s="10" t="n"/>
-      <c r="T191" s="10" t="n"/>
-      <c r="U191" s="10" t="n"/>
-      <c r="V191" s="10" t="n"/>
-      <c r="W191" s="10" t="n"/>
-      <c r="X191" s="10" t="n"/>
-      <c r="Y191" s="10" t="n"/>
-      <c r="Z191" s="10" t="n"/>
-      <c r="AA191" s="10" t="n"/>
-      <c r="AB191" s="10" t="n"/>
-      <c r="AC191" s="10" t="n"/>
-      <c r="AD191" s="10" t="n"/>
-      <c r="AE191" s="10" t="n"/>
-      <c r="AF191" s="10" t="n"/>
-      <c r="AG191" s="10" t="n"/>
-      <c r="AH191" s="10" t="n"/>
-      <c r="AI191" s="10" t="n"/>
-      <c r="AJ191" s="10" t="n"/>
-      <c r="AK191" s="11" t="n"/>
-    </row>
-    <row r="192" ht="18" customHeight="1">
-      <c r="C192" s="38" t="inlineStr">
+      <c r="D195" s="10" t="n"/>
+      <c r="E195" s="10" t="n"/>
+      <c r="F195" s="10" t="n"/>
+      <c r="G195" s="10" t="n"/>
+      <c r="H195" s="10" t="n"/>
+      <c r="I195" s="10" t="n"/>
+      <c r="J195" s="10" t="n"/>
+      <c r="K195" s="10" t="n"/>
+      <c r="L195" s="10" t="n"/>
+      <c r="M195" s="10" t="n"/>
+      <c r="N195" s="10" t="n"/>
+      <c r="O195" s="10" t="n"/>
+      <c r="P195" s="10" t="n"/>
+      <c r="Q195" s="10" t="n"/>
+      <c r="R195" s="10" t="n"/>
+      <c r="S195" s="10" t="n"/>
+      <c r="T195" s="10" t="n"/>
+      <c r="U195" s="10" t="n"/>
+      <c r="V195" s="10" t="n"/>
+      <c r="W195" s="10" t="n"/>
+      <c r="X195" s="10" t="n"/>
+      <c r="Y195" s="10" t="n"/>
+      <c r="Z195" s="10" t="n"/>
+      <c r="AA195" s="10" t="n"/>
+      <c r="AB195" s="10" t="n"/>
+      <c r="AC195" s="10" t="n"/>
+      <c r="AD195" s="10" t="n"/>
+      <c r="AE195" s="10" t="n"/>
+      <c r="AF195" s="10" t="n"/>
+      <c r="AG195" s="10" t="n"/>
+      <c r="AH195" s="10" t="n"/>
+      <c r="AI195" s="10" t="n"/>
+      <c r="AJ195" s="10" t="n"/>
+      <c r="AK195" s="11" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="C196" s="38" t="inlineStr">
         <is>
           <t>`shinki_flg`：新規購読 / 解約→再購読 の場合 TRUE</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="18" customHeight="1">
-      <c r="C193" s="38" t="inlineStr">
+    <row r="197" ht="18" customHeight="1">
+      <c r="C197" s="38" t="inlineStr">
         <is>
           <t>`kaiyaku_flg`：購読中→解約 の場合 TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="18" customHeight="1">
-      <c r="C194" s="38" t="inlineStr">
-        <is>
-          <t>`zougen_hokoku_flg`：購読部数や販売店等の増減報告対象項目が変化した場合 TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="36" customHeight="1">
-      <c r="C195" s="38" t="inlineStr">
-        <is>
-          <t>`zenkai_*` 項目：UPDATE系の場合、更新前の値を格納する（初回履歴・NEWモードは NULL）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="54" customHeight="1">
-      <c r="C196" s="38" t="inlineStr">
-        <is>
-          <t>実行中に DB 制約違反等が発生した場合：トランザクションを即時ロールバックし、HTTP 400 (`IMPORT_VALIDATION_ERROR`) または HTTP 500 (`INTERNAL_SERVER_ERROR`) を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="B197" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="C198" s="38" t="inlineStr">
         <is>
+          <t>`zougen_hokoku_flg`：購読部数や販売店等の増減報告対象項目が変化した場合 TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="36" customHeight="1">
+      <c r="C199" s="38" t="inlineStr">
+        <is>
+          <t>`zenkai_*` 項目：UPDATE系の場合、更新前の値を格納する（初回履歴・NEWモードは NULL）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="54" customHeight="1">
+      <c r="C200" s="38" t="inlineStr">
+        <is>
+          <t>実行中に DB 制約違反等が発生した場合：トランザクションを即時ロールバックし、HTTP 400 (`IMPORT_VALIDATION_ERROR`) または HTTP 500 (`INTERNAL_SERVER_ERROR`) を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="B201" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="C202" s="38" t="inlineStr">
+        <is>
           <t>全行の処理が完了した後、一括取込操作の操作ログを取込バッチ単位で1件記録する（行単位ではない）。</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="144" customHeight="1">
-      <c r="C199" s="42" t="inlineStr">
+    <row r="203" ht="144" customHeight="1">
+      <c r="C203" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -15200,106 +15782,106 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D199" s="10" t="n"/>
-      <c r="E199" s="10" t="n"/>
-      <c r="F199" s="10" t="n"/>
-      <c r="G199" s="10" t="n"/>
-      <c r="H199" s="10" t="n"/>
-      <c r="I199" s="10" t="n"/>
-      <c r="J199" s="10" t="n"/>
-      <c r="K199" s="10" t="n"/>
-      <c r="L199" s="10" t="n"/>
-      <c r="M199" s="10" t="n"/>
-      <c r="N199" s="10" t="n"/>
-      <c r="O199" s="10" t="n"/>
-      <c r="P199" s="10" t="n"/>
-      <c r="Q199" s="10" t="n"/>
-      <c r="R199" s="10" t="n"/>
-      <c r="S199" s="10" t="n"/>
-      <c r="T199" s="10" t="n"/>
-      <c r="U199" s="10" t="n"/>
-      <c r="V199" s="10" t="n"/>
-      <c r="W199" s="10" t="n"/>
-      <c r="X199" s="10" t="n"/>
-      <c r="Y199" s="10" t="n"/>
-      <c r="Z199" s="10" t="n"/>
-      <c r="AA199" s="10" t="n"/>
-      <c r="AB199" s="10" t="n"/>
-      <c r="AC199" s="10" t="n"/>
-      <c r="AD199" s="10" t="n"/>
-      <c r="AE199" s="10" t="n"/>
-      <c r="AF199" s="10" t="n"/>
-      <c r="AG199" s="10" t="n"/>
-      <c r="AH199" s="10" t="n"/>
-      <c r="AI199" s="10" t="n"/>
-      <c r="AJ199" s="10" t="n"/>
-      <c r="AK199" s="11" t="n"/>
-    </row>
-    <row r="200" ht="36" customHeight="1">
-      <c r="C200" s="38" t="inlineStr">
+      <c r="D203" s="10" t="n"/>
+      <c r="E203" s="10" t="n"/>
+      <c r="F203" s="10" t="n"/>
+      <c r="G203" s="10" t="n"/>
+      <c r="H203" s="10" t="n"/>
+      <c r="I203" s="10" t="n"/>
+      <c r="J203" s="10" t="n"/>
+      <c r="K203" s="10" t="n"/>
+      <c r="L203" s="10" t="n"/>
+      <c r="M203" s="10" t="n"/>
+      <c r="N203" s="10" t="n"/>
+      <c r="O203" s="10" t="n"/>
+      <c r="P203" s="10" t="n"/>
+      <c r="Q203" s="10" t="n"/>
+      <c r="R203" s="10" t="n"/>
+      <c r="S203" s="10" t="n"/>
+      <c r="T203" s="10" t="n"/>
+      <c r="U203" s="10" t="n"/>
+      <c r="V203" s="10" t="n"/>
+      <c r="W203" s="10" t="n"/>
+      <c r="X203" s="10" t="n"/>
+      <c r="Y203" s="10" t="n"/>
+      <c r="Z203" s="10" t="n"/>
+      <c r="AA203" s="10" t="n"/>
+      <c r="AB203" s="10" t="n"/>
+      <c r="AC203" s="10" t="n"/>
+      <c r="AD203" s="10" t="n"/>
+      <c r="AE203" s="10" t="n"/>
+      <c r="AF203" s="10" t="n"/>
+      <c r="AG203" s="10" t="n"/>
+      <c r="AH203" s="10" t="n"/>
+      <c r="AI203" s="10" t="n"/>
+      <c r="AJ203" s="10" t="n"/>
+      <c r="AK203" s="11" t="n"/>
+    </row>
+    <row r="204" ht="36" customHeight="1">
+      <c r="C204" s="38" t="inlineStr">
         <is>
           <t>`operation`：取込モード別の prefixed ラベル（販売店取込 SCR-019 と統一・bare-verb ルールの例外）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="18" customHeight="1">
-      <c r="D201" s="38" t="inlineStr">
-        <is>
-          <t>`NEW` → `'IMPORT_NEW'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="18" customHeight="1">
-      <c r="D202" s="38" t="inlineStr">
-        <is>
-          <t>`UPDATE_ALL` → `'IMPORT_UPDATE_ALL'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="D203" s="38" t="inlineStr">
-        <is>
-          <t>`UPDATE_PARTIAL` → `'IMPORT_UPDATE_PARTIAL'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="C204" s="38" t="inlineStr">
-        <is>
-          <t>`before_value`：</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="D205" s="38" t="inlineStr">
         <is>
-          <t>`NEW` モード：空文字列</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="54" customHeight="1">
+          <t>`NEW` → `'IMPORT_NEW'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
       <c r="D206" s="38" t="inlineStr">
         <is>
-          <t>`UPDATE_ALL` / `UPDATE_PARTIAL` / 一括中止：更新前データのサマリJSON `{ "rows": [{...}, ...] }`（各行の更新前状態を格納、最大100件まで）</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="72" customHeight="1">
-      <c r="C207" s="38" t="inlineStr">
-        <is>
-          <t>`after_value`：取込結果サマリJSON `{ "import_mode", "total_rows", "created_count", "updated_count", "cancelled_count", "created_ids": [...], "updated_ids": [...] }`</t>
+          <t>`UPDATE_ALL` → `'IMPORT_UPDATE_ALL'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="D207" s="38" t="inlineStr">
+        <is>
+          <t>`UPDATE_PARTIAL` → `'IMPORT_UPDATE_PARTIAL'`</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="C208" s="38" t="inlineStr">
         <is>
+          <t>`before_value`：</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="D209" s="38" t="inlineStr">
+        <is>
+          <t>`NEW` モード：空文字列</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="54" customHeight="1">
+      <c r="D210" s="38" t="inlineStr">
+        <is>
+          <t>`UPDATE_ALL` / `UPDATE_PARTIAL` / 一括中止：更新前データのサマリJSON `{ "rows": [{...}, ...] }`（各行の更新前状態を格納、最大100件まで）</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="72" customHeight="1">
+      <c r="C211" s="38" t="inlineStr">
+        <is>
+          <t>`after_value`：取込結果サマリJSON `{ "import_mode", "total_rows", "created_count", "updated_count", "cancelled_count", "created_ids": [...], "updated_ids": [...] }`</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="C212" s="38" t="inlineStr">
+        <is>
           <t>パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="180" customHeight="1">
-      <c r="C209" s="42" t="inlineStr">
+    <row r="213" ht="180" customHeight="1">
+      <c r="C213" s="42" t="inlineStr">
         <is>
           <t>{
   "import_mode": "NEW",
@@ -15313,99 +15895,99 @@
 }</t>
         </is>
       </c>
-      <c r="D209" s="10" t="n"/>
-      <c r="E209" s="10" t="n"/>
-      <c r="F209" s="10" t="n"/>
-      <c r="G209" s="10" t="n"/>
-      <c r="H209" s="10" t="n"/>
-      <c r="I209" s="10" t="n"/>
-      <c r="J209" s="10" t="n"/>
-      <c r="K209" s="10" t="n"/>
-      <c r="L209" s="10" t="n"/>
-      <c r="M209" s="10" t="n"/>
-      <c r="N209" s="10" t="n"/>
-      <c r="O209" s="10" t="n"/>
-      <c r="P209" s="10" t="n"/>
-      <c r="Q209" s="10" t="n"/>
-      <c r="R209" s="10" t="n"/>
-      <c r="S209" s="10" t="n"/>
-      <c r="T209" s="10" t="n"/>
-      <c r="U209" s="10" t="n"/>
-      <c r="V209" s="10" t="n"/>
-      <c r="W209" s="10" t="n"/>
-      <c r="X209" s="10" t="n"/>
-      <c r="Y209" s="10" t="n"/>
-      <c r="Z209" s="10" t="n"/>
-      <c r="AA209" s="10" t="n"/>
-      <c r="AB209" s="10" t="n"/>
-      <c r="AC209" s="10" t="n"/>
-      <c r="AD209" s="10" t="n"/>
-      <c r="AE209" s="10" t="n"/>
-      <c r="AF209" s="10" t="n"/>
-      <c r="AG209" s="10" t="n"/>
-      <c r="AH209" s="10" t="n"/>
-      <c r="AI209" s="10" t="n"/>
-      <c r="AJ209" s="10" t="n"/>
-      <c r="AK209" s="11" t="n"/>
-    </row>
-    <row r="210" ht="18" customHeight="1">
-      <c r="B210" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="18" customHeight="1">
-      <c r="C211" s="38" t="inlineStr">
-        <is>
-          <t>トランザクションをコミットする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="C212" s="38" t="inlineStr">
-        <is>
-          <t>取込結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="C213" s="38" t="inlineStr">
-        <is>
-          <t>`message`：`取り込みました。`（ACSMS-MSG-016-004）</t>
-        </is>
-      </c>
+      <c r="D213" s="10" t="n"/>
+      <c r="E213" s="10" t="n"/>
+      <c r="F213" s="10" t="n"/>
+      <c r="G213" s="10" t="n"/>
+      <c r="H213" s="10" t="n"/>
+      <c r="I213" s="10" t="n"/>
+      <c r="J213" s="10" t="n"/>
+      <c r="K213" s="10" t="n"/>
+      <c r="L213" s="10" t="n"/>
+      <c r="M213" s="10" t="n"/>
+      <c r="N213" s="10" t="n"/>
+      <c r="O213" s="10" t="n"/>
+      <c r="P213" s="10" t="n"/>
+      <c r="Q213" s="10" t="n"/>
+      <c r="R213" s="10" t="n"/>
+      <c r="S213" s="10" t="n"/>
+      <c r="T213" s="10" t="n"/>
+      <c r="U213" s="10" t="n"/>
+      <c r="V213" s="10" t="n"/>
+      <c r="W213" s="10" t="n"/>
+      <c r="X213" s="10" t="n"/>
+      <c r="Y213" s="10" t="n"/>
+      <c r="Z213" s="10" t="n"/>
+      <c r="AA213" s="10" t="n"/>
+      <c r="AB213" s="10" t="n"/>
+      <c r="AC213" s="10" t="n"/>
+      <c r="AD213" s="10" t="n"/>
+      <c r="AE213" s="10" t="n"/>
+      <c r="AF213" s="10" t="n"/>
+      <c r="AG213" s="10" t="n"/>
+      <c r="AH213" s="10" t="n"/>
+      <c r="AI213" s="10" t="n"/>
+      <c r="AJ213" s="10" t="n"/>
+      <c r="AK213" s="11" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="B214" s="27" t="inlineStr">
         <is>
-          <t>4.7 例外処理</t>
+          <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="C215" s="38" t="inlineStr">
         <is>
-          <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
+          <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="C216" s="38" t="inlineStr">
         <is>
+          <t>取込結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="C217" s="38" t="inlineStr">
+        <is>
+          <t>`message`：`取り込みました。`（ACSMS-MSG-016-004）</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="B218" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="C219" s="38" t="inlineStr">
+        <is>
+          <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="C220" s="38" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="36" customHeight="1">
-      <c r="C217" s="38" t="inlineStr">
+    <row r="221" ht="36" customHeight="1">
+      <c r="C221" s="38" t="inlineStr">
         <is>
           <t>エラー発生時もエラーログを記録する（`log_type = 3`）。**トランザクション外で別途記録する**。</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="144" customHeight="1">
-      <c r="C218" s="42" t="inlineStr">
+    <row r="222" ht="144" customHeight="1">
+      <c r="C222" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -15417,101 +15999,101 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D218" s="10" t="n"/>
-      <c r="E218" s="10" t="n"/>
-      <c r="F218" s="10" t="n"/>
-      <c r="G218" s="10" t="n"/>
-      <c r="H218" s="10" t="n"/>
-      <c r="I218" s="10" t="n"/>
-      <c r="J218" s="10" t="n"/>
-      <c r="K218" s="10" t="n"/>
-      <c r="L218" s="10" t="n"/>
-      <c r="M218" s="10" t="n"/>
-      <c r="N218" s="10" t="n"/>
-      <c r="O218" s="10" t="n"/>
-      <c r="P218" s="10" t="n"/>
-      <c r="Q218" s="10" t="n"/>
-      <c r="R218" s="10" t="n"/>
-      <c r="S218" s="10" t="n"/>
-      <c r="T218" s="10" t="n"/>
-      <c r="U218" s="10" t="n"/>
-      <c r="V218" s="10" t="n"/>
-      <c r="W218" s="10" t="n"/>
-      <c r="X218" s="10" t="n"/>
-      <c r="Y218" s="10" t="n"/>
-      <c r="Z218" s="10" t="n"/>
-      <c r="AA218" s="10" t="n"/>
-      <c r="AB218" s="10" t="n"/>
-      <c r="AC218" s="10" t="n"/>
-      <c r="AD218" s="10" t="n"/>
-      <c r="AE218" s="10" t="n"/>
-      <c r="AF218" s="10" t="n"/>
-      <c r="AG218" s="10" t="n"/>
-      <c r="AH218" s="10" t="n"/>
-      <c r="AI218" s="10" t="n"/>
-      <c r="AJ218" s="10" t="n"/>
-      <c r="AK218" s="11" t="n"/>
-    </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="B219" s="27" t="inlineStr">
+      <c r="D222" s="10" t="n"/>
+      <c r="E222" s="10" t="n"/>
+      <c r="F222" s="10" t="n"/>
+      <c r="G222" s="10" t="n"/>
+      <c r="H222" s="10" t="n"/>
+      <c r="I222" s="10" t="n"/>
+      <c r="J222" s="10" t="n"/>
+      <c r="K222" s="10" t="n"/>
+      <c r="L222" s="10" t="n"/>
+      <c r="M222" s="10" t="n"/>
+      <c r="N222" s="10" t="n"/>
+      <c r="O222" s="10" t="n"/>
+      <c r="P222" s="10" t="n"/>
+      <c r="Q222" s="10" t="n"/>
+      <c r="R222" s="10" t="n"/>
+      <c r="S222" s="10" t="n"/>
+      <c r="T222" s="10" t="n"/>
+      <c r="U222" s="10" t="n"/>
+      <c r="V222" s="10" t="n"/>
+      <c r="W222" s="10" t="n"/>
+      <c r="X222" s="10" t="n"/>
+      <c r="Y222" s="10" t="n"/>
+      <c r="Z222" s="10" t="n"/>
+      <c r="AA222" s="10" t="n"/>
+      <c r="AB222" s="10" t="n"/>
+      <c r="AC222" s="10" t="n"/>
+      <c r="AD222" s="10" t="n"/>
+      <c r="AE222" s="10" t="n"/>
+      <c r="AF222" s="10" t="n"/>
+      <c r="AG222" s="10" t="n"/>
+      <c r="AH222" s="10" t="n"/>
+      <c r="AI222" s="10" t="n"/>
+      <c r="AJ222" s="10" t="n"/>
+      <c r="AK222" s="11" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="B223" s="27" t="inlineStr">
         <is>
           <t>4.8 一括中止（`dokusya_chushi_date` 指定時・v1.6 顧客要件 2026-08）</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="36" customHeight="1">
-      <c r="C220" s="38" t="inlineStr">
+    <row r="224" ht="36" customHeight="1">
+      <c r="C224" s="38" t="inlineStr">
         <is>
           <t>対象は `dokusya_id`（無い行は `kumiaiin_code`）で特定し、行ロックのうえ**解約予約の履歴を1件 append** する。</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="36" customHeight="1">
-      <c r="C221" s="38" t="inlineStr">
+    <row r="225" ht="36" customHeight="1">
+      <c r="C225" s="38" t="inlineStr">
         <is>
           <t>**`selected_columns` に他の列が入っていても書き込まない**（画面も列グリッドをキー列へ縮退させるが、直接呼ばれても同じ）。</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="36" customHeight="1">
-      <c r="C222" s="38" t="inlineStr">
+    <row r="226" ht="36" customHeight="1">
+      <c r="C226" s="38" t="inlineStr">
         <is>
           <t>中止日は予約時点で `t_dokusya.dokusya_chushi_date` へ反映し、一覧（SCR-014）・詳細（SCR-011）に即時表示する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="610">
+  <mergeCells count="638">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="C174:AK174"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="D134:AK134"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y61:AB61"/>
+    <mergeCell ref="C189:AK189"/>
     <mergeCell ref="Y48:AB48"/>
+    <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
-    <mergeCell ref="D202:AK202"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="Y41:AB41"/>
+    <mergeCell ref="Q80:S80"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="Y56:AB56"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="Y43:AB43"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="AF91:AK91"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="M88:P88"/>
-    <mergeCell ref="M82:P82"/>
     <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="Q91:S91"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="C85:L85"/>
     <mergeCell ref="M90:P90"/>
     <mergeCell ref="AF86:AK86"/>
     <mergeCell ref="Q77:S77"/>
@@ -15519,11 +16101,13 @@
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y59:AB59"/>
     <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="D151:AK151"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M85:P85"/>
     <mergeCell ref="Y36:AB36"/>
     <mergeCell ref="AC58:AE58"/>
+    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="AC39:AE39"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="C220:AK220"/>
@@ -15532,7 +16116,7 @@
     <mergeCell ref="C195:AK195"/>
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="D129:AK129"/>
+    <mergeCell ref="C197:AK197"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="Q86:S86"/>
@@ -15542,6 +16126,7 @@
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y62:AB62"/>
     <mergeCell ref="AF81:AK81"/>
+    <mergeCell ref="C79:L79"/>
     <mergeCell ref="C73:L73"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D89:L89"/>
@@ -15550,43 +16135,46 @@
     <mergeCell ref="T76:X76"/>
     <mergeCell ref="Y64:AB64"/>
     <mergeCell ref="Y51:AB51"/>
-    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="T69:X69"/>
+    <mergeCell ref="D139:AK139"/>
     <mergeCell ref="C213:AK213"/>
-    <mergeCell ref="B197:AK197"/>
     <mergeCell ref="AC71:AE71"/>
     <mergeCell ref="C144:AK144"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="C208:AK208"/>
+    <mergeCell ref="C87:C94"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="M91:P91"/>
     <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AF92:AK92"/>
     <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C72:L72"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="M93:P93"/>
     <mergeCell ref="T87:X87"/>
+    <mergeCell ref="D152:AK152"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Y75:AB75"/>
+    <mergeCell ref="AF94:AK94"/>
     <mergeCell ref="AC60:AE60"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T59:X59"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="D83:L83"/>
     <mergeCell ref="T89:X89"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="B143:AK143"/>
     <mergeCell ref="Y39:AB39"/>
-    <mergeCell ref="D85:L85"/>
     <mergeCell ref="AF56:AK56"/>
     <mergeCell ref="C54:L54"/>
     <mergeCell ref="C163:AK163"/>
@@ -15596,83 +16184,83 @@
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="C56:L56"/>
+    <mergeCell ref="AC78:AE78"/>
     <mergeCell ref="C43:L43"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="C158:AK158"/>
     <mergeCell ref="Q64:S64"/>
+    <mergeCell ref="B97:I97"/>
+    <mergeCell ref="D209:AK209"/>
     <mergeCell ref="T77:X77"/>
-    <mergeCell ref="D147:AK147"/>
     <mergeCell ref="Y65:AB65"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B167:AK167"/>
     <mergeCell ref="Y57:AB57"/>
     <mergeCell ref="M24:P24"/>
+    <mergeCell ref="AC79:AE79"/>
     <mergeCell ref="AC73:AE73"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="C216:AK216"/>
     <mergeCell ref="Y87:AE87"/>
+    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="AF75:AK75"/>
-    <mergeCell ref="C218:AK218"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="C211:AK211"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
-    <mergeCell ref="B108:I108"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="C65:L65"/>
-    <mergeCell ref="Y82:AE82"/>
+    <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C80:L80"/>
     <mergeCell ref="Y60:AB60"/>
     <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="B126:AK126"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="D84:L84"/>
     <mergeCell ref="T90:X90"/>
     <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="Y78:AB78"/>
+    <mergeCell ref="B218:AK218"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
+    <mergeCell ref="C95:L95"/>
     <mergeCell ref="C60:L60"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
     <mergeCell ref="C165:AK165"/>
-    <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC67:AE67"/>
-    <mergeCell ref="C91:L91"/>
+    <mergeCell ref="Y80:AB80"/>
     <mergeCell ref="AC69:AE69"/>
     <mergeCell ref="C179:AK179"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="B96:I96"/>
     <mergeCell ref="C57:L57"/>
     <mergeCell ref="C166:AK166"/>
     <mergeCell ref="C160:AK160"/>
+    <mergeCell ref="D192:AK192"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="C141:AK141"/>
-    <mergeCell ref="B111:I111"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
-    <mergeCell ref="D148:AK148"/>
+    <mergeCell ref="C86:L86"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="Y71:AB71"/>
-    <mergeCell ref="C143:AK143"/>
     <mergeCell ref="Y58:AB58"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Y73:AB73"/>
-    <mergeCell ref="B139:AK139"/>
-    <mergeCell ref="T84:X84"/>
+    <mergeCell ref="B201:AK201"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
     <mergeCell ref="C75:L75"/>
@@ -15680,20 +16268,23 @@
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T86:X86"/>
-    <mergeCell ref="Q83:S83"/>
+    <mergeCell ref="C219:AK219"/>
     <mergeCell ref="Y90:AE90"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="C39:L39"/>
+    <mergeCell ref="B109:I109"/>
     <mergeCell ref="C70:L70"/>
     <mergeCell ref="Q85:S85"/>
+    <mergeCell ref="B130:AK130"/>
     <mergeCell ref="D205:AK205"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="C154:AK154"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC42:AE42"/>
+    <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="C81:L81"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
@@ -15701,15 +16292,13 @@
     <mergeCell ref="AC44:AE44"/>
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="C168:AK168"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="C180:AK180"/>
-    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C167:AK167"/>
     <mergeCell ref="C63:L63"/>
-    <mergeCell ref="D131:AK131"/>
     <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
@@ -15720,10 +16309,8 @@
     <mergeCell ref="C169:AK169"/>
     <mergeCell ref="M65:P65"/>
     <mergeCell ref="J20:M20"/>
-    <mergeCell ref="D189:AK189"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
-    <mergeCell ref="B114:I114"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="Y49:AB49"/>
@@ -15731,22 +16318,26 @@
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
     <mergeCell ref="Y76:AB76"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="Q84:S84"/>
-    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="C78:L78"/>
     <mergeCell ref="C187:AK187"/>
     <mergeCell ref="Y91:AE91"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="M83:P83"/>
     <mergeCell ref="C162:AK162"/>
+    <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="Y93:AE93"/>
+    <mergeCell ref="C226:AK226"/>
     <mergeCell ref="C164:AK164"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="AC52:AE52"/>
-    <mergeCell ref="D190:AK190"/>
+    <mergeCell ref="B112:I112"/>
     <mergeCell ref="Y54:AB54"/>
     <mergeCell ref="T41:X41"/>
+    <mergeCell ref="M78:P78"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
@@ -15754,53 +16345,57 @@
     <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="AC81:AE81"/>
     <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="T36:X36"/>
+    <mergeCell ref="C190:AK190"/>
     <mergeCell ref="AC76:AE76"/>
     <mergeCell ref="AF63:AK63"/>
+    <mergeCell ref="Q79:S79"/>
+    <mergeCell ref="D137:AK137"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="C66:L66"/>
     <mergeCell ref="Q81:S81"/>
     <mergeCell ref="C175:AK175"/>
-    <mergeCell ref="D130:AK130"/>
     <mergeCell ref="C53:L53"/>
     <mergeCell ref="AC63:AE63"/>
-    <mergeCell ref="D201:AK201"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AC50:AE50"/>
     <mergeCell ref="C185:AK185"/>
     <mergeCell ref="AF76:AK76"/>
-    <mergeCell ref="D188:AK188"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="C68:L68"/>
     <mergeCell ref="T62:X62"/>
+    <mergeCell ref="D132:AK132"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="Y44:AB44"/>
+    <mergeCell ref="C188:AK188"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="M84:P84"/>
-    <mergeCell ref="C138:AK138"/>
-    <mergeCell ref="C132:AK132"/>
+    <mergeCell ref="C203:AK203"/>
+    <mergeCell ref="Q92:S92"/>
     <mergeCell ref="M86:P86"/>
     <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M80:P80"/>
+    <mergeCell ref="D210:AK210"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="AF87:AK87"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="Q94:S94"/>
     <mergeCell ref="T33:X33"/>
-    <mergeCell ref="T82:X82"/>
     <mergeCell ref="Y70:AB70"/>
     <mergeCell ref="AF89:AK89"/>
     <mergeCell ref="AC55:AE55"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="D193:AK193"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
     <mergeCell ref="J12:AK12"/>
@@ -15809,18 +16404,18 @@
     <mergeCell ref="Y47:AB47"/>
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C112:AK112"/>
+    <mergeCell ref="A83:AK83"/>
     <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="C183:AK183"/>
+    <mergeCell ref="D138:AK138"/>
     <mergeCell ref="M70:P70"/>
-    <mergeCell ref="C127:AK127"/>
-    <mergeCell ref="C193:AK193"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="C176:AK176"/>
+    <mergeCell ref="D140:AK140"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
+    <mergeCell ref="B154:AK154"/>
     <mergeCell ref="Y50:AB50"/>
     <mergeCell ref="C178:AK178"/>
     <mergeCell ref="N20:AK20"/>
@@ -15834,21 +16429,20 @@
     <mergeCell ref="AC77:AE77"/>
     <mergeCell ref="AC74:AE74"/>
     <mergeCell ref="D135:AK135"/>
-    <mergeCell ref="C209:AK209"/>
     <mergeCell ref="AC68:AE68"/>
     <mergeCell ref="D206:AK206"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="AC43:AE43"/>
     <mergeCell ref="Y45:AB45"/>
-    <mergeCell ref="C140:AK140"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AC72:AE72"/>
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C204:AK204"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C83:C90"/>
+    <mergeCell ref="AF95:AK95"/>
+    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y42:AB42"/>
@@ -15857,9 +16451,9 @@
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
+    <mergeCell ref="Q95:S95"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="T83:X83"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF90:AK90"/>
     <mergeCell ref="Q32:S32"/>
@@ -15874,19 +16468,23 @@
     <mergeCell ref="AC62:AE62"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C159:AK159"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="C153:AK153"/>
+    <mergeCell ref="C224:AK224"/>
     <mergeCell ref="C199:AK199"/>
     <mergeCell ref="M36:P36"/>
+    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="C186:AK186"/>
     <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="C161:AK161"/>
     <mergeCell ref="C217:AK217"/>
     <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="B93:I93"/>
     <mergeCell ref="C37:L37"/>
+    <mergeCell ref="T78:X78"/>
     <mergeCell ref="Y66:AB66"/>
     <mergeCell ref="T65:X65"/>
     <mergeCell ref="Q27:S27"/>
@@ -15894,32 +16492,42 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Y53:AB53"/>
     <mergeCell ref="T44:X44"/>
+    <mergeCell ref="D207:AK207"/>
+    <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="Y68:AB68"/>
+    <mergeCell ref="D92:L92"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="Y55:AB55"/>
+    <mergeCell ref="T79:X79"/>
     <mergeCell ref="C212:AK212"/>
+    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="Y83:AE83"/>
+    <mergeCell ref="D94:L94"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
-    <mergeCell ref="C207:AK207"/>
+    <mergeCell ref="Y79:AB79"/>
     <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="B125:AK125"/>
+    <mergeCell ref="M95:P95"/>
     <mergeCell ref="M89:P89"/>
     <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="Y81:AB81"/>
     <mergeCell ref="Y37:AB37"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="C76:L76"/>
+    <mergeCell ref="B106:I106"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
+    <mergeCell ref="AF93:AK93"/>
     <mergeCell ref="AC64:AE64"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="D87:L87"/>
+    <mergeCell ref="C225:AK225"/>
+    <mergeCell ref="B171:AK171"/>
     <mergeCell ref="AC65:AE65"/>
     <mergeCell ref="C200:AK200"/>
     <mergeCell ref="J14:M14"/>
@@ -15929,9 +16537,9 @@
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="Y74:AB74"/>
     <mergeCell ref="C177:AK177"/>
+    <mergeCell ref="C202:AK202"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
-    <mergeCell ref="B99:I99"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="C47:L47"/>
@@ -15946,10 +16554,10 @@
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="Y69:AB69"/>
     <mergeCell ref="C51:L51"/>
+    <mergeCell ref="D150:AK150"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="C71:L71"/>
     <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="Y84:AE84"/>
     <mergeCell ref="C155:AK155"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
@@ -15957,22 +16565,20 @@
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="C157:AK157"/>
-    <mergeCell ref="C151:AK151"/>
-    <mergeCell ref="B105:I105"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="C77:L77"/>
-    <mergeCell ref="B120:I120"/>
     <mergeCell ref="C215:AK215"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
+    <mergeCell ref="T92:X92"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C152:AK152"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="D88:L88"/>
+    <mergeCell ref="T94:X94"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
@@ -15982,20 +16588,22 @@
     <mergeCell ref="D90:L90"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="C59:L59"/>
-    <mergeCell ref="C106:AK106"/>
+    <mergeCell ref="T95:X95"/>
+    <mergeCell ref="A128:AK128"/>
     <mergeCell ref="C46:L46"/>
-    <mergeCell ref="Y81:AE81"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
+    <mergeCell ref="B100:I100"/>
     <mergeCell ref="C61:L61"/>
     <mergeCell ref="C170:AK170"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="Y77:AB77"/>
+    <mergeCell ref="B115:I115"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
-    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="AF51:AK51"/>
@@ -16003,79 +16611,83 @@
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="C221:AK221"/>
     <mergeCell ref="C196:AK196"/>
+    <mergeCell ref="AC80:AE80"/>
     <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="M79:P79"/>
+    <mergeCell ref="Y92:AE92"/>
     <mergeCell ref="M73:P73"/>
-    <mergeCell ref="D203:AK203"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="C198:AK198"/>
     <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="Y94:AE94"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="AF82:AK82"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
-    <mergeCell ref="Q82:S82"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="B223:AK223"/>
+    <mergeCell ref="Q93:S93"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="C67:L67"/>
     <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="D91:L91"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="C191:AK191"/>
     <mergeCell ref="M50:P50"/>
+    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="C69:L69"/>
     <mergeCell ref="C172:AK172"/>
+    <mergeCell ref="D93:L93"/>
     <mergeCell ref="D133:AK133"/>
     <mergeCell ref="M68:P68"/>
     <mergeCell ref="C184:AK184"/>
+    <mergeCell ref="M92:P92"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="C62:L62"/>
-    <mergeCell ref="C171:AK171"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="AC59:AE59"/>
-    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="AF72:AK72"/>
+    <mergeCell ref="B103:I103"/>
     <mergeCell ref="C64:L64"/>
     <mergeCell ref="Q75:S75"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="C173:AK173"/>
-    <mergeCell ref="D128:AK128"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="AC61:AE61"/>
-    <mergeCell ref="A124:AK124"/>
+    <mergeCell ref="B118:I118"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="Y40:AB40"/>
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="D194:AK194"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B219:AK219"/>
     <mergeCell ref="Q88:S88"/>
     <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="B121:I121"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="B210:AK210"/>
-    <mergeCell ref="D146:AK146"/>
+    <mergeCell ref="Y95:AE95"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
-    <mergeCell ref="AF83:AK83"/>
+    <mergeCell ref="T93:X93"/>
     <mergeCell ref="AC54:AE54"/>
     <mergeCell ref="Q90:S90"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="AC56:AE56"/>
     <mergeCell ref="AF60:AK60"/>
@@ -16083,14 +16695,12 @@
     <mergeCell ref="AC49:AE49"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
-    <mergeCell ref="C192:AK192"/>
-    <mergeCell ref="A79:AK79"/>
+    <mergeCell ref="M94:P94"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C194:AK194"/>
+    <mergeCell ref="B124:I124"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="C181:AK181"/>
-    <mergeCell ref="D136:AK136"/>
     <mergeCell ref="M77:P77"/>
-    <mergeCell ref="B150:AK150"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1917,13 +1917,65 @@
       <c r="AF9" s="10" t="n"/>
       <c r="AG9" s="11" t="n"/>
     </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>記載不整合の是正：テンプレート列数の記述が「46列」のまま残っていた（ACSMS-API-016-001 の §概要・§出力仕様・§4.x）。#56405（購読者層分類の従属4項目追加）で列一覧自体は 50 列へ更新済みだったが、本文の数値だけが v1.6 時点のままで一覧と矛盾していた。3箇所を 50 列へ修正。テンプレートの実装・列順は変更なし（統合テスト `dokusya-import.integration.spec.ts` が 50 列を検証している）</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="11" t="n"/>
+      <c r="W10" s="17" t="inlineStr"/>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="17" t="inlineStr"/>
+      <c r="AC10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="70">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="W10:AA10"/>
     <mergeCell ref="R5:V5"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB9:AG9"/>
@@ -1933,8 +1985,10 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="R10:V10"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K10:Q10"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="R7:V7"/>
@@ -1942,6 +1996,7 @@
     <mergeCell ref="K6:Q6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="R6:V6"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
@@ -1955,6 +2010,7 @@
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="AB10:AG10"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
@@ -1970,9 +2026,11 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="W9:AA9"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H10:J10"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
@@ -2154,7 +2212,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2670,7 +2728,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3291,7 +3349,7 @@
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="19" t="inlineStr">
         <is>
-          <t>ファイルの行数が上限（30000行）を超えているため、取込みできません。</t>
+          <t>ファイルの行数が上限（5000行）を超えているため、取込みできません。</t>
         </is>
       </c>
       <c r="W15" s="10" t="n"/>
@@ -3542,7 +3600,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3687,7 +3745,7 @@
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータ取込用のテンプレートファイル（46列固定）を生成しダウンロードする。</t>
+          <t>購読者Excelデータ取込用のテンプレートファイル（50列固定）を生成しダウンロードする。</t>
         </is>
       </c>
       <c r="T6" s="10" t="n"/>
@@ -3977,7 +4035,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4101,7 +4159,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>購読者Excelデータ取込用のテンプレートファイル（46列固定）を生成しダウンロードする。</t>
+          <t>購読者Excelデータ取込用のテンプレートファイル（50列固定）を生成しダウンロードする。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -8344,7 +8402,7 @@
     <row r="113" ht="36" customHeight="1">
       <c r="C113" s="38" t="inlineStr">
         <is>
-          <t>1行目に46列のヘッダー文字列を以下の順序で書き込む（購読種別・読者情報変更適用日・購読中止日は画面で指定する単一ソースのため列に含めない）。</t>
+          <t>1行目に50列のヘッダー文字列を以下の順序で書き込む（購読種別・読者情報変更適用日・購読中止日は画面で指定する単一ソースのため列に含めない）。</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9095,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10158,13 +10216,13 @@
       <c r="AA30" s="10" t="n"/>
       <c r="AB30" s="11" t="n"/>
       <c r="AC30" s="17" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>取込データ行の配列。30000件を超える場合は `ROW_LIMIT_EXCEEDED` を返却する。</t>
+          <t>取込データ行の配列。5000件を超える場合は `ROW_LIMIT_EXCEEDED` を返却する。</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -14459,7 +14517,7 @@
         <is>
           <t>{
   "error_code": "ROW_LIMIT_EXCEEDED",
-  "message": "ファイルの行数が上限（30000行）を超えているため、取込みできません。"
+  "message": "ファイルの行数が上限（5000行）を超えているため、取込みできません。"
 }</t>
         </is>
       </c>
@@ -14836,7 +14894,7 @@
     <row r="134" ht="18" customHeight="1">
       <c r="D134" s="38" t="inlineStr">
         <is>
-          <t>`rows`：必須、配列、1件以上、30000件以下</t>
+          <t>`rows`：必須、配列、1件以上、5000件以下</t>
         </is>
       </c>
     </row>

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者Excelデータ取込画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1968,78 +1968,658 @@
       <c r="AF10" s="10" t="n"/>
       <c r="AG10" s="11" t="n"/>
     </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：電子版は実在の販売店へ配達しないため、部数(`dokusya_busu`)・販売店コード(`hanbaiten_code`)とも行の入力値に関わらず常に単一の固定値（1 / ダミー販売店コード9999999999）へ強制上書きするよう変更。両列は `NEW` モードの必須列からも除外（画面上もチェックボックス無しのグレー表示に変更）。当該JAにダミー販売店（`hanbaiten_code=9999999999`）が未整備の場合、電子版取込は行ループの前に一括で `VALIDATION_ERROR` を返すバリデーションを新設（ACSMS-SCR-011登録/編集・dokusya-syncバッチと同一のダミー販売店運用に統一）。</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="W11" s="17" t="inlineStr"/>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="10" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="17" t="inlineStr"/>
+      <c r="AC11" s="10" t="n"/>
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AF11" s="10" t="n"/>
+      <c r="AG11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="11" t="n"/>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：住所変更と販売店の移動が同一適用日に別々の更新として積み重なると増減連絡票（ACSMS-SCR-028）の同日集計が意図しない出力になるため、**紙版の`UPDATE`モード（joho_henko_tekiyo_dateが未来日）は同一適用日への変更を1回までに制限**（§4.3.5新設）。対象dokusya_idに既にアクティブな履歴行がある場合 `IMPORT_VALIDATION_ERROR`(field=joho_henko_tekiyo_date) を返す。同日にまとめて変更したいときはACSMS-SCR-013で該当履歴を取消してから1回で取込む。当日変更・電子版は対象外。ACSMS-SCR-011・SCR-015にも同一制限を適用（3経路共通ロジック）。</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="11" t="n"/>
+      <c r="W12" s="17" t="inlineStr"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="17" t="inlineStr"/>
+      <c r="AC12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正：`NEW`モードの`dokusya_kaishi_date`（購読開始日）が紙版・電子版とも一律「未来日のみ」で検証されており、**電子版で本日の日付を入力しても誤って拒否される**バグを修正。ACSMS-SCR-011登録画面（ラジオボタン「今日から/翌月1日から」）と同じ制約に揃え、**電子版のNEWは購読開始日=本日または翌月1日のみ許可**するよう変更（それ以外はエラー「電子版の購読開始日は本日または翌月1日を指定してください。」）。紙版は「未来日のみ」のまま変更なし。判定ロジックは共通モジュール`dokusya-shubetsu.rules.ts`に追加し、将来ACSMS-SCR-011のBE側にも同一制約を敷けるよう再利用可能にした。</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="W13" s="17" t="inlineStr"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="17" t="inlineStr"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="11" t="n"/>
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：電子版(2)は配達先情報エリアが画面上非活性化される（v1.9の`dokusya_busu`/`hanbaiten_code`と同種の制約）が、配達先情報12項目（`haitatsu_same_flg`＋住所5＋連絡先2＋氏名4）にはこれまでゲートが無く、`selected_columns`に含めて値を送れば電子版でも保存できてしまっていた。`dokusya_busu`/`hanbaiten_code`と同方式（BEが行ごと固定値へ強制上書き）で、電子版は12項目を常に`haitatsu_same_flg=true`・残り11項目=空文字へ強制するよう修正（BE: `buildHaitatsuPayload`。ACSMS-SCR-011登録/編集画面と同一のゲート）。取込列パネル（画面）も電子版選択時はこの12項目をグレー表示＋チェック解除するよう修正。</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="11" t="n"/>
+      <c r="W14" s="17" t="inlineStr"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="17" t="inlineStr"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="11" t="n"/>
+      <c r="R15" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：`UPDATE`モード（一括中止含む）で、`selected_columns`に含まれない列の値が行検証で誤って弾かれるバグを修正。一括中止（`dokusya_id`のみ選択）で取込んだ際、Excelシートに残っていた無関係セル（メールアドレス・メールマガジン・生年等）の値が`selected_columns`対象外にも関わらず`@IsEmail`/`@IsNumber`等の形式チェックへ届き、`IMPORT_VALIDATION_ERROR`で全体が拒否されていた。§4.1にドキュメント済みの「各行の検証はselected_columns対象列のみ」を実装で徹底し、`UPDATE`時は`selected_columns`（＋キー列`dokusya_id`）に無い列をDTO検証前にサーバ側で除去する`stripUnselectedColumns`をBEに追加。FE（`DokusyaImportView.vue`）も送信前に選択解除中の列を行データから除外するよう修正（従来は電子版固定列のみ個別除外していたのを、選択状態(`selected[col]`)に基づく一貫した除外へ統一）。`NEW`モードは対象外（必須列は既定で全選択）。</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="11" t="n"/>
+      <c r="W15" s="17" t="inlineStr"/>
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="11" t="n"/>
+      <c r="AB15" s="17" t="inlineStr"/>
+      <c r="AC15" s="10" t="n"/>
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="11" t="n"/>
+      <c r="R16" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：v1.13の`stripUnselectedColumns`（selected_columns対象外の列を除去）を**`NEW`モードにも拡張**。従来はUPDATEのみ対象だったため、新規登録でチェックを外した任意項目（例: メールアドレス・備考）にExcelセルの値が残っていると、選択解除＝未入力のつもりが誤って検証・登録されていた。除去された列はINSERT時にNULL/空文字（列のNOT NULL制約に従う既定値）になる。あわせて**取込列パネルの「ID」を新規登録モードでは常にグレー表示＋チェック不可**にする（自動採番のため新規登録では無意味な項目のため。dokusya_busu/hanbaiten_code(電子版)と同じ「チェックボックス無し」方式）。</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="11" t="n"/>
+      <c r="W16" s="17" t="inlineStr"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="11" t="n"/>
+      <c r="AB16" s="17" t="inlineStr"/>
+      <c r="AC16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AF16" s="10" t="n"/>
+      <c r="AG16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+      <c r="R17" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：①**組合員コードが同一JA内で重複している場合、`dokusya_id`未指定でのUPDATE/一括中止を拒否**するよう明記（`classifyImportRow`の`isAmbiguousKumiaiinKey`は既存実装だが未文書化だった。§4.1に追記）。②上記ガードの前提として、`kumiaiin_code`は`dokusya_id`と同様UPDATE時の突合フォールバックキーのため`stripUnselectedColumns`が`selected_columns`に無くても常に保持するよう修正（v1.13実装時の回帰 — 保持していなかったため、一括中止で組合員コードのみを指定すると常に「指定された購読者が見つかりません」で失敗していた）。③氏名かな4項目（`shimei_kana_sei`/`shimei_kana_mei`/`haitatsu_shimei_kana_sei`/`haitatsu_shimei_kana_mei`）に全角ひらがなのみ許容するバリデーションを追加（半角カナ・カタカナ・漢字・英数字を拒否。従来は最大100文字チェックのみで書式チェックが無かった）。氏名（漢字）4項目の最大50文字は既存仕様のまま変更なし。</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="11" t="n"/>
+      <c r="W17" s="17" t="inlineStr"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="11" t="n"/>
+      <c r="AB17" s="17" t="inlineStr"/>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n"/>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="10" t="n"/>
+      <c r="AG17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="11" t="n"/>
+      <c r="R18" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：電子版は`joho_henko_tekiyo_date`（読者情報変更適用日）省略を許容し、省略時は書込み側（`DokusyaImportService`）が当日を補って書き込むが、行検証（`validateImportRowTekiyoDates`）の「適用日は購読開始日以降」チェック（`collectTekiyoDateViolations`）は省略値=nullのままこの相対チェックをスキップしていた。購読開始日（`dokusya_kaishi_date`）が翌月1日等まだ到来していない電子版購読者を、適用日欄を空欄にしたままUPDATE取込（再取込含む）すると検証をすり抜け、共通履歴ライタ（`applyChange`の`findBefore`）が「当日時点で有効な直前の履歴行」を見つけられず、直前行なし（`before=null`）起点の不完全な履歴行が余分に作られてしまうバグを修正。行検証も書込み側と同じ既定値（電子版は当日）を用いて相対チェックを行うよう修正し、この組み合わせは`IMPORT_VALIDATION_ERROR`（field=joho_henko_tekiyo_date、§4.1参照）で拒否されるようにした（UI編集SCR-011は元々`assertUpdateDateConsistency`で同じ組み合わせを拒否しており、本画面のみ抜けていた）。</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="11" t="n"/>
+      <c r="W18" s="17" t="inlineStr"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="11" t="n"/>
+      <c r="AB18" s="17" t="inlineStr"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08（重大・誤更新）：`UPDATE`モード（一括中止含む）の更新対象解決（`resolveImportTargetId`）が`WHERE dokusya_id = :id OR kumiaiin_code = :code`という**OR条件**になっており、「dokusya_id優先・無ければkumiaiin_codeで代替」という設計意図（v1.15の重複防止ガードもこの前提）に反していた。`kumiaiin_code`はUNIQUE制約が無く同一JA内で重複しうるため、同一バッチ内に同じ`kumiaiin_code`を持つ行が2件以上あると、各行が明示的に異なる`dokusya_id`を指定していても、OR条件のもう一方（`kumiaiin_code`一致）で他方の購読者にヒットしうる。実測では`LIMIT 1`（ORDER BY無し）が常に物理的に先頭の行を返すため、**2行の更新が両方とも1人の購読者に誤って適用され、もう一方の購読者は一切更新されないまま**だった（ユーザー報告「Excel再取込で作られた履歴行のデータが一致しない」の実体）。`dokusya_id`が指定されている行は`kumiaiin_code`を一切参照せず`dokusya_id`のみで検索するよう2クエリに分離して修正（§4.3.4参照）。</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="11" t="n"/>
+      <c r="W19" s="17" t="inlineStr"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="11" t="n"/>
+      <c r="AB19" s="17" t="inlineStr"/>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="11" t="n"/>
+      <c r="R20" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：廃店(`m_hanbaiten.haiten_flg=true`)の販売店・失効(`m_tanka.active_flg=false`)の単価を取込で選択できてしまう不具合を修正。修正前は取込自体が成功し、購読者詳細画面（ACSMS-SCR-011）にも廃店・失効の旨を示す表示が無いため運用が事後に気付けなかった。§4.3.1/§4.3.2のFK解決クエリに`active_flg`/`haiten_flg`を追加し、存在するが廃店/失効している場合は`IMPORT_VALIDATION_ERROR`（field='tanka_code'/'hanbaiten_code', message='指定された新聞単価コードは失効しています。'/'指定された販売店コードは廃店のため選択できません。'）で拒否する。廃店/失効後もレコード自体は過去購読者の履歴参照のため削除されないため、「存在しない」エラーとは区別する。NEW/UPDATE（新規選択・変更時）両方が対象。UI編集画面(SCR-011)にはこの相当チェックが元々無く、本画面で新設した業務ルール（UI側は別途要検討・本対応の範囲外）。</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="11" t="n"/>
+      <c r="W20" s="17" t="inlineStr"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="10" t="n"/>
+      <c r="Z20" s="10" t="n"/>
+      <c r="AA20" s="11" t="n"/>
+      <c r="AB20" s="17" t="inlineStr"/>
+      <c r="AC20" s="10" t="n"/>
+      <c r="AD20" s="10" t="n"/>
+      <c r="AE20" s="10" t="n"/>
+      <c r="AF20" s="10" t="n"/>
+      <c r="AG20" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="R1:V1"/>
+  <mergeCells count="140">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R10:V10"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="W5:AA5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R16:V16"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="AB17:AG17"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AB10:AG10"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="AB19:AG19"/>
+    <mergeCell ref="W16:AA16"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="AB5:AG5"/>
+    <mergeCell ref="AB20:AG20"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="AB14:AG14"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="R14:V14"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="K16:Q16"/>
+    <mergeCell ref="AB13:AG13"/>
+    <mergeCell ref="AB8:AG8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="W12:AA12"/>
+    <mergeCell ref="AB18:AG18"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="R9:V9"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="H6:J6"/>
     <mergeCell ref="W10:AA10"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="AB9:AG9"/>
-    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R11:V11"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="W5:AA5"/>
-    <mergeCell ref="R4:V4"/>
-    <mergeCell ref="R10:V10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="R7:V7"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R13:V13"/>
+    <mergeCell ref="AB12:AG12"/>
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="W4:AA4"/>
-    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="R15:V15"/>
+    <mergeCell ref="K18:Q18"/>
     <mergeCell ref="W3:AA3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C9:G9"/>
-    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="AB7:AG7"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="AB10:AG10"/>
-    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H8:J8"/>
-    <mergeCell ref="R3:V3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="K20:Q20"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="W9:AA9"/>
-    <mergeCell ref="C7:G7"/>
     <mergeCell ref="H10:J10"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="AB5:AG5"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="W14:AA14"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="W13:AA13"/>
+    <mergeCell ref="AB16:AG16"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="K14:Q14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
+    <mergeCell ref="W15:AA15"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="K13:Q13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="AB11:AG11"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K15:Q15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="R12:V12"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="AB15:AG15"/>
+    <mergeCell ref="W17:AA17"/>
+    <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="R18:V18"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="R9:V9"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2212,7 +2792,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2728,7 +3308,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3600,7 +4180,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4035,7 +4615,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8934,7 +9514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK226"/>
+  <dimension ref="A1:AK240"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9095,7 +9675,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10883,7 +11463,7 @@
       <c r="AJ40" s="10" t="n"/>
       <c r="AK40" s="11" t="n"/>
     </row>
-    <row r="41" ht="36" customHeight="1">
+    <row r="41" ht="54" customHeight="1">
       <c r="B41" s="31" t="n">
         <v>14</v>
       </c>
@@ -10942,7 +11522,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>購読部数。`NEW`：&gt; 0、解約時：= 0。**電子版(2)は 1 固定**（v1.4・UI/一括置換と統一）。</t>
+          <t>購読部数。`NEW`：&gt; 0、解約時：= 0。**電子版(2)は行の値に関わらず常に 1 へ強制上書き**され、`NEW` モードの必須列からも除外される（v1.9・顧客要件 2026-08 — 電子版は実在の販売店へ配達しないため部数は常に単一固定値）。</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -12435,7 +13015,7 @@
       <c r="AJ64" s="10" t="n"/>
       <c r="AK64" s="11" t="n"/>
     </row>
-    <row r="65" ht="36" customHeight="1">
+    <row r="65" ht="162" customHeight="1">
       <c r="B65" s="31" t="n">
         <v>38</v>
       </c>
@@ -12490,7 +13070,7 @@
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>販売店コード（m_hanbaiten の hanbaiten_code で解決）。`NEW` モードは必須。</t>
+          <t>販売店コード（m_hanbaiten の hanbaiten_code で解決）。`NEW` モードは必須（紙版のみ）。**電子版(2)は行の値に関わらず常にダミー販売店コード `9999999999`（`HANBAITEN_DUMMY_CODE`）へ強制上書き**され、`NEW` モードの必須列からも除外される（v1.9・顧客要件 2026-08 — 電子版は実在の販売店へ配達しないため受け皿として自JAのダミー販売店に紐づける。ACSMS-SCR-011 登録/編集・dokusya-sync バッチと同一の運用）。当該 JA にダミー販売店（`hanbaiten_code=9999999999`）が未整備の場合、電子版取込は行ループに入る前に `VALIDATION_ERROR`（field=hanbaiten_code）で一括して弾かれる（下記エラー例参照）。</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -14450,22 +15030,18 @@
     <row r="106" ht="19.5" customHeight="1">
       <c r="B106" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Bad Request (Import Validation Error — 行別エラー)）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="198" customHeight="1">
+          <t>レスポンス（失敗 400 Bad Request (Validation Error — 電子版のダミー販売店未整備・v1.9)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="126" customHeight="1">
       <c r="C107" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "IMPORT_VALIDATION_ERROR",
-  "message": "Excel取込データにエラーがあります。詳細はerrorsフィールドを確認してください。",
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
   "errors": [
-    { "row": 2, "field": "dokusya_shubetsu", "message": "選択した購読種別と異なる購読者が含まれています。" },
-    { "row": 3, "field": "shiharai_hoho", "message": "電子版かつクレジットカード決済の組み合わせは取込みできません。" },
-    { "row": 5, "field": "tanka_code", "message": "指定された新聞単価コードが見つかりません。" },
-    { "row": 7, "field": "dokusya_busu", "message": "新規登録の場合、購読部数は0より大きい値を指定してください。" },
-    { "row": 9, "field": "kumiaiin_code", "message": "指定された組合員コードが見つかりません。" }
+    { "field": "hanbaiten_code", "message": "電子版の取込にはダミー販売店（販売店コード:9999999999）の事前登録が必要です。販売店マスタで作成してから再度お試しください。" }
   ]
 }</t>
         </is>
@@ -14508,16 +15084,23 @@
     <row r="109" ht="19.5" customHeight="1">
       <c r="B109" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Bad Request (Row Limit Exceeded)）</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="72" customHeight="1">
+          <t>レスポンス（失敗 400 Bad Request (Import Validation Error — 行別エラー)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="198" customHeight="1">
       <c r="C110" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "ROW_LIMIT_EXCEEDED",
-  "message": "ファイルの行数が上限（5000行）を超えているため、取込みできません。"
+  "error_code": "IMPORT_VALIDATION_ERROR",
+  "message": "Excel取込データにエラーがあります。詳細はerrorsフィールドを確認してください。",
+  "errors": [
+    { "row": 2, "field": "dokusya_shubetsu", "message": "選択した購読種別と異なる購読者が含まれています。" },
+    { "row": 3, "field": "shiharai_hoho", "message": "電子版かつクレジットカード決済の組み合わせは取込みできません。" },
+    { "row": 5, "field": "tanka_code", "message": "指定された新聞単価コードが見つかりません。" },
+    { "row": 7, "field": "dokusya_busu", "message": "新規登録の場合、購読部数は0より大きい値を指定してください。" },
+    { "row": 9, "field": "kumiaiin_code", "message": "指定された組合員コードが見つかりません。" }
+  ]
 }</t>
         </is>
       </c>
@@ -14559,7 +15142,7 @@
     <row r="112" ht="19.5" customHeight="1">
       <c r="B112" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Bad Request (File Format Error)）</t>
+          <t>レスポンス（失敗 400 Bad Request (Row Limit Exceeded)）</t>
         </is>
       </c>
     </row>
@@ -14567,8 +15150,8 @@
       <c r="C113" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FILE_FORMAT_ERROR",
-  "message": "Excelファイルの取り込みに失敗しました。ファイル形式を確認してください。"
+  "error_code": "ROW_LIMIT_EXCEEDED",
+  "message": "ファイルの行数が上限（5000行）を超えているため、取込みできません。"
 }</t>
         </is>
       </c>
@@ -14610,7 +15193,7 @@
     <row r="115" ht="19.5" customHeight="1">
       <c r="B115" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
+          <t>レスポンス（失敗 400 Bad Request (File Format Error)）</t>
         </is>
       </c>
     </row>
@@ -14618,8 +15201,8 @@
       <c r="C116" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください。"
+  "error_code": "FILE_FORMAT_ERROR",
+  "message": "Excelファイルの取り込みに失敗しました。ファイル形式を確認してください。"
 }</t>
         </is>
       </c>
@@ -14661,7 +15244,7 @@
     <row r="118" ht="19.5" customHeight="1">
       <c r="B118" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -14669,8 +15252,8 @@
       <c r="C119" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません。"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -14712,7 +15295,7 @@
     <row r="121" ht="19.5" customHeight="1">
       <c r="B121" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden (DataScope Violation)）</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -14720,8 +15303,8 @@
       <c r="C122" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "DATA_SCOPE_VIOLATION",
-  "message": "このデータへのアクセス権限がありません。"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -14763,7 +15346,7 @@
     <row r="124" ht="19.5" customHeight="1">
       <c r="B124" s="37" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 403 Forbidden (DataScope Violation)）</t>
         </is>
       </c>
     </row>
@@ -14771,8 +15354,8 @@
       <c r="C125" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+  "error_code": "DATA_SCOPE_VIOLATION",
+  "message": "このデータへのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -14811,251 +15394,330 @@
       <c r="AJ125" s="10" t="n"/>
       <c r="AK125" s="11" t="n"/>
     </row>
-    <row r="127" ht="19.5" customHeight="1"/>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="27" t="inlineStr">
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="B127" s="37" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="72" customHeight="1">
+      <c r="C128" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+}</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="10" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="10" t="n"/>
+      <c r="I128" s="10" t="n"/>
+      <c r="J128" s="10" t="n"/>
+      <c r="K128" s="10" t="n"/>
+      <c r="L128" s="10" t="n"/>
+      <c r="M128" s="10" t="n"/>
+      <c r="N128" s="10" t="n"/>
+      <c r="O128" s="10" t="n"/>
+      <c r="P128" s="10" t="n"/>
+      <c r="Q128" s="10" t="n"/>
+      <c r="R128" s="10" t="n"/>
+      <c r="S128" s="10" t="n"/>
+      <c r="T128" s="10" t="n"/>
+      <c r="U128" s="10" t="n"/>
+      <c r="V128" s="10" t="n"/>
+      <c r="W128" s="10" t="n"/>
+      <c r="X128" s="10" t="n"/>
+      <c r="Y128" s="10" t="n"/>
+      <c r="Z128" s="10" t="n"/>
+      <c r="AA128" s="10" t="n"/>
+      <c r="AB128" s="10" t="n"/>
+      <c r="AC128" s="10" t="n"/>
+      <c r="AD128" s="10" t="n"/>
+      <c r="AE128" s="10" t="n"/>
+      <c r="AF128" s="10" t="n"/>
+      <c r="AG128" s="10" t="n"/>
+      <c r="AH128" s="10" t="n"/>
+      <c r="AI128" s="10" t="n"/>
+      <c r="AJ128" s="10" t="n"/>
+      <c r="AK128" s="11" t="n"/>
+    </row>
+    <row r="130" ht="19.5" customHeight="1"/>
+    <row r="131" ht="19.5" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="54" customHeight="1">
-      <c r="B129" s="42" t="inlineStr">
+    <row r="132" ht="54" customHeight="1">
+      <c r="B132" s="42" t="inlineStr">
         <is>
           <t>※ 4.4 データ取込実行 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C129" s="10" t="n"/>
-      <c r="D129" s="10" t="n"/>
-      <c r="E129" s="10" t="n"/>
-      <c r="F129" s="10" t="n"/>
-      <c r="G129" s="10" t="n"/>
-      <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="n"/>
-      <c r="J129" s="10" t="n"/>
-      <c r="K129" s="10" t="n"/>
-      <c r="L129" s="10" t="n"/>
-      <c r="M129" s="10" t="n"/>
-      <c r="N129" s="10" t="n"/>
-      <c r="O129" s="10" t="n"/>
-      <c r="P129" s="10" t="n"/>
-      <c r="Q129" s="10" t="n"/>
-      <c r="R129" s="10" t="n"/>
-      <c r="S129" s="10" t="n"/>
-      <c r="T129" s="10" t="n"/>
-      <c r="U129" s="10" t="n"/>
-      <c r="V129" s="10" t="n"/>
-      <c r="W129" s="10" t="n"/>
-      <c r="X129" s="10" t="n"/>
-      <c r="Y129" s="10" t="n"/>
-      <c r="Z129" s="10" t="n"/>
-      <c r="AA129" s="10" t="n"/>
-      <c r="AB129" s="10" t="n"/>
-      <c r="AC129" s="10" t="n"/>
-      <c r="AD129" s="10" t="n"/>
-      <c r="AE129" s="10" t="n"/>
-      <c r="AF129" s="10" t="n"/>
-      <c r="AG129" s="10" t="n"/>
-      <c r="AH129" s="10" t="n"/>
-      <c r="AI129" s="10" t="n"/>
-      <c r="AJ129" s="10" t="n"/>
-      <c r="AK129" s="11" t="n"/>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="B130" s="27" t="inlineStr">
+      <c r="C132" s="10" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="10" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="10" t="n"/>
+      <c r="J132" s="10" t="n"/>
+      <c r="K132" s="10" t="n"/>
+      <c r="L132" s="10" t="n"/>
+      <c r="M132" s="10" t="n"/>
+      <c r="N132" s="10" t="n"/>
+      <c r="O132" s="10" t="n"/>
+      <c r="P132" s="10" t="n"/>
+      <c r="Q132" s="10" t="n"/>
+      <c r="R132" s="10" t="n"/>
+      <c r="S132" s="10" t="n"/>
+      <c r="T132" s="10" t="n"/>
+      <c r="U132" s="10" t="n"/>
+      <c r="V132" s="10" t="n"/>
+      <c r="W132" s="10" t="n"/>
+      <c r="X132" s="10" t="n"/>
+      <c r="Y132" s="10" t="n"/>
+      <c r="Z132" s="10" t="n"/>
+      <c r="AA132" s="10" t="n"/>
+      <c r="AB132" s="10" t="n"/>
+      <c r="AC132" s="10" t="n"/>
+      <c r="AD132" s="10" t="n"/>
+      <c r="AE132" s="10" t="n"/>
+      <c r="AF132" s="10" t="n"/>
+      <c r="AG132" s="10" t="n"/>
+      <c r="AH132" s="10" t="n"/>
+      <c r="AI132" s="10" t="n"/>
+      <c r="AJ132" s="10" t="n"/>
+      <c r="AK132" s="11" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="B133" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="C131" s="38" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="C134" s="38" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="36" customHeight="1">
-      <c r="D132" s="38" t="inlineStr">
+    <row r="135" ht="36" customHeight="1">
+      <c r="D135" s="38" t="inlineStr">
         <is>
           <t>`import_mode`：必須、`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL` のいずれか</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="D133" s="38" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="D136" s="38" t="inlineStr">
         <is>
           <t>`selected_columns`：必須、配列、1件以上</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="D134" s="38" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="D137" s="38" t="inlineStr">
         <is>
           <t>`rows`：必須、配列、1件以上、5000件以下</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="D135" s="38" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="D138" s="38" t="inlineStr">
         <is>
           <t>各行 `rows[i]` の検証（`selected_columns` 対象列のみ）：</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="36" customHeight="1">
-      <c r="C136" s="38" t="inlineStr">
+    <row r="139" ht="36" customHeight="1">
+      <c r="C139" s="38" t="inlineStr">
         <is>
           <t>業務ルールチェック（v1.4 — 共通モジュール `dokusya-shubetsu.rules.ts` に集約し UI/取込/一括置換で統一）：</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="36" customHeight="1">
-      <c r="D137" s="38" t="inlineStr">
+    <row r="140" ht="36" customHeight="1">
+      <c r="D140" s="38" t="inlineStr">
         <is>
           <t>併読（`dokusya_shubetsu`=3）は取込不可 → エラー「購読種別が3:併読のためExcel取込みできません。」（第3システム同期のため読取専用）</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="36" customHeight="1">
-      <c r="D138" s="38" t="inlineStr">
+    <row r="141" ht="36" customHeight="1">
+      <c r="D141" s="38" t="inlineStr">
         <is>
           <t>電子版（`dokusya_shubetsu`=2）かつクレジットカード決済（`shiharai_hoho`=6）の組み合わせは取込不可 → エラー（理由：電子版かつクレカ決済取込不可のため。読取専用）</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="D139" s="38" t="inlineStr">
+    <row r="142" ht="18" customHeight="1">
+      <c r="D142" s="38" t="inlineStr">
         <is>
           <t>電子版の購読部数=1（上記 `dokusya_busu` 参照）</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="D140" s="38" t="inlineStr">
+    <row r="143" ht="18" customHeight="1">
+      <c r="D143" s="38" t="inlineStr">
         <is>
           <t>種別依存の適用日ルール（上記 `joho_henko_tekiyo_date` 参照）</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="36" customHeight="1">
-      <c r="C141" s="38" t="inlineStr">
+    <row r="144" ht="144" customHeight="1">
+      <c r="D144" s="38" t="inlineStr">
+        <is>
+          <t>**電子版の販売店コード自動解決**（v1.9・顧客要件 2026-08）：電子版は実在の販売店へ配達しないため、行の `hanbaiten_code` に何が入っていても常にログインユーザーの JA が保有するダミー販売店（`hanbaiten_code=9999999999`・`HANBAITEN_DUMMY_CODE`）へ強制解決する。当該 JA にダミー販売店が未整備の場合、行ループへ入る前に一括で `VALIDATION_ERROR`（field=hanbaiten_code, message=「電子版の取込にはダミー販売店（販売店コード:9999999999）の事前登録が必要です。販売店マスタで作成してから再度お試しください。」）を返す（§4.3.2 も参照）。ダミー販売店の運用は ACSMS-SCR-011 登録/編集・dokusya-sync バッチと同一。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="252" customHeight="1">
+      <c r="D145" s="38" t="inlineStr">
+        <is>
+          <t>**電子版の配達先情報12項目を強制空欄化**（v1.12・不具合修正 2026-08）：電子版(2)は配達先情報エリアが画面上非活性化される（ACSMS-SCR-011 §7.5）ため配達先情報を一切持てない。`haitatsu_same_flg` / `haitatsu_yubin_no` / `haitatsu_todofuken_code` / `haitatsu_shikuchoson` / `haitatsu_chome_banchi` / `haitatsu_tatemono_mei` / `haitatsu_renrakusaki_1` / `haitatsu_renrakusaki_2` / `haitatsu_shimei_sei` / `haitatsu_shimei_mei` / `haitatsu_shimei_kana_sei` / `haitatsu_shimei_kana_mei` の12項目は、`selected_columns` の指定や行セルの値に関わらずサーバ側で `haitatsu_same_flg=true`・残り11項目=空文字へ強制する（BE: `dokusya.mapper.ts` の `buildHaitatsuPayload`。ACSMS-SCR-011 登録/編集画面と同一のゲート）。エラーにはせず値を落とすのみ（`dokusya_busu`/`hanbaiten_code` の強制上書きと同方式）。取込列パネル（画面）も電子版選択時はこの12項目をグレー表示＋チェック解除する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="216" customHeight="1">
+      <c r="D146" s="38" t="inlineStr">
+        <is>
+          <t>**組合員コード重複時は一括誤更新／誤解約を防止**（v1.15・不具合修正 2026-08）：`UPDATE`モード（一括中止含む）で `dokusya_id` を指定しない行は `kumiaiin_code` が突合フォールバックキーになるが、同コードが同一 JA 内で2件以上ヒットする場合はどちらの読者を更新／解約したいのか一意に決まらない。この場合、行ループへ入る前に一括で `IMPORT_VALIDATION_ERROR`（field=kumiaiin_code, message=「組合員コードが重複しているため、IDを指定してください。」）を返し、DB へは一切書き込まない（`classifyImportRow`の`isAmbiguousKumiaiinKey`）。一括中止（`selected_columns`が`dokusya_id`のみ）でも同様に適用される。※`kumiaiin_code`は`dokusya_id`と同じくUPDATE時の突合キーのため、`selected_columns`に含まれていなくてもサーバ側で常に保持する（`stripUnselectedColumns`。含めないと組合員コードのみでの一括中止が常に「指定された購読者が見つかりません」で失敗する）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="216" customHeight="1">
+      <c r="D147" s="38" t="inlineStr">
+        <is>
+          <t>**`dokusya_id`指定行の更新対象解決から`kumiaiin_code`の巻き込みを排除**（v1.17・不具合修正 2026-08）：上記ガードは`dokusya_id`未指定の行だけを対象にしていたが、実際の更新対象解決（`resolveImportTargetId`）は`WHERE dokusya_id = :id OR kumiaiin_code = :code`という**OR条件を1クエリにまとめた実装**になっており、これは「dokusya_id優先・無ければkumiaiin_codeで代替」ではなく「どちらか一致すればヒット」という別の意味になっていた。同一バッチ内で複数行が同じ`kumiaiin_code`を共有し、各行がそれぞれ異なる`dokusya_id`を明示していても、`LIMIT 1`（ORDER BY無し）は常に物理的に先頭の行を返すため、**2行とも同じ1人の購読者へ誤って書き込まれ、もう一方の購読者は一切更新されないまま**だった（`t_dokusya_rireki`に本来別々の購読者に入るはずの変更が1人分にまとめて積み上がり、データが一致しない不具合の実体）。`dokusya_id`が指定されている行は`kumiaiin_code`を一切参照せず`dokusya_id`のみで検索するよう修正（2クエリに分離）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="36" customHeight="1">
+      <c r="C148" s="38" t="inlineStr">
         <is>
           <t>トップレベルのバリデーションエラー：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="36" customHeight="1">
-      <c r="C142" s="38" t="inlineStr">
-        <is>
-          <t>行レベルのバリデーションエラー：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（row番号含む。最大10件まで返却）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="B143" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="C144" s="38" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="C145" s="38" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="C146" s="38" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.import`</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="36" customHeight="1">
-      <c r="C147" s="38" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="C148" s="38" t="inlineStr">
-        <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="C149" s="38" t="inlineStr">
         <is>
-          <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
+          <t>行レベルのバリデーションエラー：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（row番号含む。最大10件まで返却）</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="D150" s="38" t="inlineStr">
-        <is>
-          <t>中央会：自中央会管轄JAのみ取込可能。</t>
+      <c r="B150" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="D151" s="38" t="inlineStr">
-        <is>
-          <t>JA本店：自JAのみ取込可能。</t>
+      <c r="C151" s="38" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="D152" s="38" t="inlineStr">
-        <is>
-          <t>JA管理支店：自管理支店配下のみ取込可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="36" customHeight="1">
+      <c r="C152" s="38" t="inlineStr">
+        <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
       <c r="C153" s="38" t="inlineStr">
         <is>
-          <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="B154" s="27" t="inlineStr">
-        <is>
-          <t>4.3 事前チェック（参照整合性・重複）</t>
+          <t>必要権限: `dokusya.import`</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="36" customHeight="1">
+      <c r="C154" s="38" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）/ JA_HONTEN（JA本店）/ JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="C155" s="38" t="inlineStr">
         <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="36" customHeight="1">
+      <c r="C156" s="38" t="inlineStr">
+        <is>
+          <t>DataScope: ログインユーザーの `ja_id`（および JA_KANRI_SHITEN の場合は `kanri_shiten_id`）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="D157" s="38" t="inlineStr">
+        <is>
+          <t>中央会：自中央会管轄JAのみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="D158" s="38" t="inlineStr">
+        <is>
+          <t>JA本店：自JAのみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="D159" s="38" t="inlineStr">
+        <is>
+          <t>JA管理支店：自管理支店配下のみ取込可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="36" customHeight="1">
+      <c r="C160" s="38" t="inlineStr">
+        <is>
+          <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="B161" s="27" t="inlineStr">
+        <is>
+          <t>4.3 事前チェック（参照整合性・重複）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="C162" s="38" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する（`ja_id` / `kanri_shiten_id`）。</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="C156" s="38" t="inlineStr">
+    <row r="163" ht="18" customHeight="1">
+      <c r="C163" s="38" t="inlineStr">
         <is>
           <t>DBとの整合性チェックをバッチで実行する。</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="108" customHeight="1">
-      <c r="C157" s="42" t="inlineStr">
-        <is>
-          <t>SELECT tanka_id, tanka_code
+    <row r="164" ht="108" customHeight="1">
+      <c r="C164" s="42" t="inlineStr">
+        <is>
+          <t>SELECT tanka_id, tanka_code, active_flg
 FROM m_tanka
 WHERE ja_id = :ja_id
   AND tanka_code = ANY(:tanka_codes)
@@ -15063,102 +15725,123 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D157" s="10" t="n"/>
-      <c r="E157" s="10" t="n"/>
-      <c r="F157" s="10" t="n"/>
-      <c r="G157" s="10" t="n"/>
-      <c r="H157" s="10" t="n"/>
-      <c r="I157" s="10" t="n"/>
-      <c r="J157" s="10" t="n"/>
-      <c r="K157" s="10" t="n"/>
-      <c r="L157" s="10" t="n"/>
-      <c r="M157" s="10" t="n"/>
-      <c r="N157" s="10" t="n"/>
-      <c r="O157" s="10" t="n"/>
-      <c r="P157" s="10" t="n"/>
-      <c r="Q157" s="10" t="n"/>
-      <c r="R157" s="10" t="n"/>
-      <c r="S157" s="10" t="n"/>
-      <c r="T157" s="10" t="n"/>
-      <c r="U157" s="10" t="n"/>
-      <c r="V157" s="10" t="n"/>
-      <c r="W157" s="10" t="n"/>
-      <c r="X157" s="10" t="n"/>
-      <c r="Y157" s="10" t="n"/>
-      <c r="Z157" s="10" t="n"/>
-      <c r="AA157" s="10" t="n"/>
-      <c r="AB157" s="10" t="n"/>
-      <c r="AC157" s="10" t="n"/>
-      <c r="AD157" s="10" t="n"/>
-      <c r="AE157" s="10" t="n"/>
-      <c r="AF157" s="10" t="n"/>
-      <c r="AG157" s="10" t="n"/>
-      <c r="AH157" s="10" t="n"/>
-      <c r="AI157" s="10" t="n"/>
-      <c r="AJ157" s="10" t="n"/>
-      <c r="AK157" s="11" t="n"/>
-    </row>
-    <row r="158" ht="36" customHeight="1">
-      <c r="C158" s="38" t="inlineStr">
-        <is>
-          <t>未ヒットの `tanka_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='tanka_code'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="90" customHeight="1">
-      <c r="C159" s="42" t="inlineStr">
-        <is>
-          <t>SELECT hanbaiten_id, hanbaiten_code
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="10" t="n"/>
+      <c r="F164" s="10" t="n"/>
+      <c r="G164" s="10" t="n"/>
+      <c r="H164" s="10" t="n"/>
+      <c r="I164" s="10" t="n"/>
+      <c r="J164" s="10" t="n"/>
+      <c r="K164" s="10" t="n"/>
+      <c r="L164" s="10" t="n"/>
+      <c r="M164" s="10" t="n"/>
+      <c r="N164" s="10" t="n"/>
+      <c r="O164" s="10" t="n"/>
+      <c r="P164" s="10" t="n"/>
+      <c r="Q164" s="10" t="n"/>
+      <c r="R164" s="10" t="n"/>
+      <c r="S164" s="10" t="n"/>
+      <c r="T164" s="10" t="n"/>
+      <c r="U164" s="10" t="n"/>
+      <c r="V164" s="10" t="n"/>
+      <c r="W164" s="10" t="n"/>
+      <c r="X164" s="10" t="n"/>
+      <c r="Y164" s="10" t="n"/>
+      <c r="Z164" s="10" t="n"/>
+      <c r="AA164" s="10" t="n"/>
+      <c r="AB164" s="10" t="n"/>
+      <c r="AC164" s="10" t="n"/>
+      <c r="AD164" s="10" t="n"/>
+      <c r="AE164" s="10" t="n"/>
+      <c r="AF164" s="10" t="n"/>
+      <c r="AG164" s="10" t="n"/>
+      <c r="AH164" s="10" t="n"/>
+      <c r="AI164" s="10" t="n"/>
+      <c r="AJ164" s="10" t="n"/>
+      <c r="AK164" s="11" t="n"/>
+    </row>
+    <row r="165" ht="54" customHeight="1">
+      <c r="C165" s="38" t="inlineStr">
+        <is>
+          <t>未ヒットの `tanka_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='tanka_code', message='指定された新聞単価コードが見つかりません。'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="126" customHeight="1">
+      <c r="C166" s="38" t="inlineStr">
+        <is>
+          <t>**`active_flg=false`（失効）の `tanka_code` は選択不可**（v1.18・不具合修正 2026-08）：`IMPORT_VALIDATION_ERROR` + errors（row, field='tanka_code', message='指定された新聞単価コードは失効しています。'）。失効単価行は参照整合性のため削除されない（過去購読者の履歴・帳票が単価名を引ける必要がある）ので存在チェック自体は通るが、新規選択・単価変更（selected_columnsに`tanka_code`を含む行）だけを弾く。NEW/UPDATE両方が対象。UI編集(SCR-011)には元々このチェックが無く、本画面で新設した業務ルール。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="90" customHeight="1">
+      <c r="C167" s="42" t="inlineStr">
+        <is>
+          <t>SELECT hanbaiten_id, hanbaiten_code, haiten_flg
 FROM m_hanbaiten
 WHERE ja_id = :ja_id
   AND hanbaiten_code = ANY(:hanbaiten_codes)
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D159" s="10" t="n"/>
-      <c r="E159" s="10" t="n"/>
-      <c r="F159" s="10" t="n"/>
-      <c r="G159" s="10" t="n"/>
-      <c r="H159" s="10" t="n"/>
-      <c r="I159" s="10" t="n"/>
-      <c r="J159" s="10" t="n"/>
-      <c r="K159" s="10" t="n"/>
-      <c r="L159" s="10" t="n"/>
-      <c r="M159" s="10" t="n"/>
-      <c r="N159" s="10" t="n"/>
-      <c r="O159" s="10" t="n"/>
-      <c r="P159" s="10" t="n"/>
-      <c r="Q159" s="10" t="n"/>
-      <c r="R159" s="10" t="n"/>
-      <c r="S159" s="10" t="n"/>
-      <c r="T159" s="10" t="n"/>
-      <c r="U159" s="10" t="n"/>
-      <c r="V159" s="10" t="n"/>
-      <c r="W159" s="10" t="n"/>
-      <c r="X159" s="10" t="n"/>
-      <c r="Y159" s="10" t="n"/>
-      <c r="Z159" s="10" t="n"/>
-      <c r="AA159" s="10" t="n"/>
-      <c r="AB159" s="10" t="n"/>
-      <c r="AC159" s="10" t="n"/>
-      <c r="AD159" s="10" t="n"/>
-      <c r="AE159" s="10" t="n"/>
-      <c r="AF159" s="10" t="n"/>
-      <c r="AG159" s="10" t="n"/>
-      <c r="AH159" s="10" t="n"/>
-      <c r="AI159" s="10" t="n"/>
-      <c r="AJ159" s="10" t="n"/>
-      <c r="AK159" s="11" t="n"/>
-    </row>
-    <row r="160" ht="36" customHeight="1">
-      <c r="C160" s="38" t="inlineStr">
-        <is>
-          <t>未ヒットの `hanbaiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='hanbaiten_code'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="198" customHeight="1">
-      <c r="C161" s="42" t="inlineStr">
+      <c r="D167" s="10" t="n"/>
+      <c r="E167" s="10" t="n"/>
+      <c r="F167" s="10" t="n"/>
+      <c r="G167" s="10" t="n"/>
+      <c r="H167" s="10" t="n"/>
+      <c r="I167" s="10" t="n"/>
+      <c r="J167" s="10" t="n"/>
+      <c r="K167" s="10" t="n"/>
+      <c r="L167" s="10" t="n"/>
+      <c r="M167" s="10" t="n"/>
+      <c r="N167" s="10" t="n"/>
+      <c r="O167" s="10" t="n"/>
+      <c r="P167" s="10" t="n"/>
+      <c r="Q167" s="10" t="n"/>
+      <c r="R167" s="10" t="n"/>
+      <c r="S167" s="10" t="n"/>
+      <c r="T167" s="10" t="n"/>
+      <c r="U167" s="10" t="n"/>
+      <c r="V167" s="10" t="n"/>
+      <c r="W167" s="10" t="n"/>
+      <c r="X167" s="10" t="n"/>
+      <c r="Y167" s="10" t="n"/>
+      <c r="Z167" s="10" t="n"/>
+      <c r="AA167" s="10" t="n"/>
+      <c r="AB167" s="10" t="n"/>
+      <c r="AC167" s="10" t="n"/>
+      <c r="AD167" s="10" t="n"/>
+      <c r="AE167" s="10" t="n"/>
+      <c r="AF167" s="10" t="n"/>
+      <c r="AG167" s="10" t="n"/>
+      <c r="AH167" s="10" t="n"/>
+      <c r="AI167" s="10" t="n"/>
+      <c r="AJ167" s="10" t="n"/>
+      <c r="AK167" s="11" t="n"/>
+    </row>
+    <row r="168" ht="54" customHeight="1">
+      <c r="C168" s="38" t="inlineStr">
+        <is>
+          <t>未ヒットの `hanbaiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='hanbaiten_code', message='指定された販売店コードが見つかりません。'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="90" customHeight="1">
+      <c r="C169" s="38" t="inlineStr">
+        <is>
+          <t>**電子版(`dokusya_shubetsu`=2)は行ループの前処理でこの検索対象コードが常に `9999999999`（ダミー販売店）へ差し替わる**（v1.9・顧客要件 2026-08）。当該 JA にこのコードの `m_hanbaiten` 行が存在しない場合、上記クエリより前の §4.1 で `VALIDATION_ERROR` として一括検出し、行ごとの「販売店コードが見つかりません」連発は発生させない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="126" customHeight="1">
+      <c r="C170" s="38" t="inlineStr">
+        <is>
+          <t>**`haiten_flg=true`（廃店）の `hanbaiten_code` は選択不可**（v1.18・不具合修正 2026-08）：`IMPORT_VALIDATION_ERROR` + errors（row, field='hanbaiten_code', message='指定された販売店コードは廃店のため選択できません。'）。廃店後も過去購読者の履歴参照のため行は削除されないので存在チェックは通るが、新規選択・販売店変更だけを弾く（tanka_codeの失効チェックと同じ設計）。修正前は取込が成功してしまい、購読者詳細画面（ACSMS-SCR-011）にも廃店・失効の旨を示す表示が無いため運用が事後に気付けなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="198" customHeight="1">
+      <c r="C171" s="42" t="inlineStr">
         <is>
           <t>SELECT kanri_shiten_id, kanri_shiten_code
 FROM m_kanri_shiten
@@ -15172,71 +15855,71 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D161" s="10" t="n"/>
-      <c r="E161" s="10" t="n"/>
-      <c r="F161" s="10" t="n"/>
-      <c r="G161" s="10" t="n"/>
-      <c r="H161" s="10" t="n"/>
-      <c r="I161" s="10" t="n"/>
-      <c r="J161" s="10" t="n"/>
-      <c r="K161" s="10" t="n"/>
-      <c r="L161" s="10" t="n"/>
-      <c r="M161" s="10" t="n"/>
-      <c r="N161" s="10" t="n"/>
-      <c r="O161" s="10" t="n"/>
-      <c r="P161" s="10" t="n"/>
-      <c r="Q161" s="10" t="n"/>
-      <c r="R161" s="10" t="n"/>
-      <c r="S161" s="10" t="n"/>
-      <c r="T161" s="10" t="n"/>
-      <c r="U161" s="10" t="n"/>
-      <c r="V161" s="10" t="n"/>
-      <c r="W161" s="10" t="n"/>
-      <c r="X161" s="10" t="n"/>
-      <c r="Y161" s="10" t="n"/>
-      <c r="Z161" s="10" t="n"/>
-      <c r="AA161" s="10" t="n"/>
-      <c r="AB161" s="10" t="n"/>
-      <c r="AC161" s="10" t="n"/>
-      <c r="AD161" s="10" t="n"/>
-      <c r="AE161" s="10" t="n"/>
-      <c r="AF161" s="10" t="n"/>
-      <c r="AG161" s="10" t="n"/>
-      <c r="AH161" s="10" t="n"/>
-      <c r="AI161" s="10" t="n"/>
-      <c r="AJ161" s="10" t="n"/>
-      <c r="AK161" s="11" t="n"/>
-    </row>
-    <row r="162" ht="36" customHeight="1">
-      <c r="C162" s="38" t="inlineStr">
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="10" t="n"/>
+      <c r="F171" s="10" t="n"/>
+      <c r="G171" s="10" t="n"/>
+      <c r="H171" s="10" t="n"/>
+      <c r="I171" s="10" t="n"/>
+      <c r="J171" s="10" t="n"/>
+      <c r="K171" s="10" t="n"/>
+      <c r="L171" s="10" t="n"/>
+      <c r="M171" s="10" t="n"/>
+      <c r="N171" s="10" t="n"/>
+      <c r="O171" s="10" t="n"/>
+      <c r="P171" s="10" t="n"/>
+      <c r="Q171" s="10" t="n"/>
+      <c r="R171" s="10" t="n"/>
+      <c r="S171" s="10" t="n"/>
+      <c r="T171" s="10" t="n"/>
+      <c r="U171" s="10" t="n"/>
+      <c r="V171" s="10" t="n"/>
+      <c r="W171" s="10" t="n"/>
+      <c r="X171" s="10" t="n"/>
+      <c r="Y171" s="10" t="n"/>
+      <c r="Z171" s="10" t="n"/>
+      <c r="AA171" s="10" t="n"/>
+      <c r="AB171" s="10" t="n"/>
+      <c r="AC171" s="10" t="n"/>
+      <c r="AD171" s="10" t="n"/>
+      <c r="AE171" s="10" t="n"/>
+      <c r="AF171" s="10" t="n"/>
+      <c r="AG171" s="10" t="n"/>
+      <c r="AH171" s="10" t="n"/>
+      <c r="AI171" s="10" t="n"/>
+      <c r="AJ171" s="10" t="n"/>
+      <c r="AK171" s="11" t="n"/>
+    </row>
+    <row r="172" ht="36" customHeight="1">
+      <c r="C172" s="38" t="inlineStr">
         <is>
           <t>未ヒットの `kanri_shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='kanri_shiten_code'）</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="36" customHeight="1">
-      <c r="C163" s="38" t="inlineStr">
+    <row r="173" ht="36" customHeight="1">
+      <c r="C173" s="38" t="inlineStr">
         <is>
           <t>未ヒットの `shiten_code`：`IMPORT_VALIDATION_ERROR` + errors（row, field='shiten_code'）</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="36" customHeight="1">
-      <c r="C164" s="38" t="inlineStr">
+    <row r="174" ht="36" customHeight="1">
+      <c r="C174" s="38" t="inlineStr">
         <is>
           <t>未ヒット：`IMPORT_VALIDATION_ERROR` + errors（row, field）</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="36" customHeight="1">
-      <c r="C165" s="38" t="inlineStr">
+    <row r="175" ht="36" customHeight="1">
+      <c r="C175" s="38" t="inlineStr">
         <is>
           <t>JA_KANRI_SHITEN の場合、自管理支店 ID と一致しない `kanri_shiten_id` も DataScope 違反とする。</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="162" customHeight="1">
-      <c r="C166" s="42" t="inlineStr">
+    <row r="176" ht="162" customHeight="1">
+      <c r="C176" s="42" t="inlineStr">
         <is>
           <t>-- UPDATE_ALL / UPDATE_PARTIAL モード（dokusya_id をキー、または kumiaiin_code をキー）
 SELECT dokusya_id, kumiaiin_code, ja_id, kanri_shiten_id
@@ -15249,99 +15932,166 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n"/>
-      <c r="E166" s="10" t="n"/>
-      <c r="F166" s="10" t="n"/>
-      <c r="G166" s="10" t="n"/>
-      <c r="H166" s="10" t="n"/>
-      <c r="I166" s="10" t="n"/>
-      <c r="J166" s="10" t="n"/>
-      <c r="K166" s="10" t="n"/>
-      <c r="L166" s="10" t="n"/>
-      <c r="M166" s="10" t="n"/>
-      <c r="N166" s="10" t="n"/>
-      <c r="O166" s="10" t="n"/>
-      <c r="P166" s="10" t="n"/>
-      <c r="Q166" s="10" t="n"/>
-      <c r="R166" s="10" t="n"/>
-      <c r="S166" s="10" t="n"/>
-      <c r="T166" s="10" t="n"/>
-      <c r="U166" s="10" t="n"/>
-      <c r="V166" s="10" t="n"/>
-      <c r="W166" s="10" t="n"/>
-      <c r="X166" s="10" t="n"/>
-      <c r="Y166" s="10" t="n"/>
-      <c r="Z166" s="10" t="n"/>
-      <c r="AA166" s="10" t="n"/>
-      <c r="AB166" s="10" t="n"/>
-      <c r="AC166" s="10" t="n"/>
-      <c r="AD166" s="10" t="n"/>
-      <c r="AE166" s="10" t="n"/>
-      <c r="AF166" s="10" t="n"/>
-      <c r="AG166" s="10" t="n"/>
-      <c r="AH166" s="10" t="n"/>
-      <c r="AI166" s="10" t="n"/>
-      <c r="AJ166" s="10" t="n"/>
-      <c r="AK166" s="11" t="n"/>
-    </row>
-    <row r="167" ht="54" customHeight="1">
-      <c r="C167" s="38" t="inlineStr">
+      <c r="D176" s="10" t="n"/>
+      <c r="E176" s="10" t="n"/>
+      <c r="F176" s="10" t="n"/>
+      <c r="G176" s="10" t="n"/>
+      <c r="H176" s="10" t="n"/>
+      <c r="I176" s="10" t="n"/>
+      <c r="J176" s="10" t="n"/>
+      <c r="K176" s="10" t="n"/>
+      <c r="L176" s="10" t="n"/>
+      <c r="M176" s="10" t="n"/>
+      <c r="N176" s="10" t="n"/>
+      <c r="O176" s="10" t="n"/>
+      <c r="P176" s="10" t="n"/>
+      <c r="Q176" s="10" t="n"/>
+      <c r="R176" s="10" t="n"/>
+      <c r="S176" s="10" t="n"/>
+      <c r="T176" s="10" t="n"/>
+      <c r="U176" s="10" t="n"/>
+      <c r="V176" s="10" t="n"/>
+      <c r="W176" s="10" t="n"/>
+      <c r="X176" s="10" t="n"/>
+      <c r="Y176" s="10" t="n"/>
+      <c r="Z176" s="10" t="n"/>
+      <c r="AA176" s="10" t="n"/>
+      <c r="AB176" s="10" t="n"/>
+      <c r="AC176" s="10" t="n"/>
+      <c r="AD176" s="10" t="n"/>
+      <c r="AE176" s="10" t="n"/>
+      <c r="AF176" s="10" t="n"/>
+      <c r="AG176" s="10" t="n"/>
+      <c r="AH176" s="10" t="n"/>
+      <c r="AI176" s="10" t="n"/>
+      <c r="AJ176" s="10" t="n"/>
+      <c r="AK176" s="11" t="n"/>
+    </row>
+    <row r="177" ht="54" customHeight="1">
+      <c r="C177" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_ALL` / `UPDATE_PARTIAL` モード：未ヒットの行は「存在しない」エラー → `IMPORT_VALIDATION_ERROR` + errors（row, field='dokusya_id' または 'kumiaiin_code'）</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="36" customHeight="1">
-      <c r="C168" s="38" t="inlineStr">
+    <row r="178" ht="36" customHeight="1">
+      <c r="C178" s="38" t="inlineStr">
         <is>
           <t>一括中止（`tetsuzuki_shurui`=0）：`kumiaiin_code` をキーに既存購読者を取得する。未ヒットはエラーとする。</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="54" customHeight="1">
-      <c r="C169" s="38" t="inlineStr">
+    <row r="179" ht="54" customHeight="1">
+      <c r="C179" s="38" t="inlineStr">
         <is>
           <t>取得した既存購読者の `kanri_shiten_id` が JA_KANRI_SHITEN の自管理支店と一致しない場合：DataScope 違反 → HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="36" customHeight="1">
-      <c r="C170" s="38" t="inlineStr">
+    <row r="180" ht="108" customHeight="1">
+      <c r="C180" s="42" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT dokusya_id
+FROM t_dokusya_rireki
+WHERE dokusya_id = ANY(:dokusya_ids)
+  AND joho_henko_tekiyo_date = :joho_henko_tekiyo_date
+  AND torikeshi_flg = false
+  AND shinki_flg = false</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n"/>
+      <c r="E180" s="10" t="n"/>
+      <c r="F180" s="10" t="n"/>
+      <c r="G180" s="10" t="n"/>
+      <c r="H180" s="10" t="n"/>
+      <c r="I180" s="10" t="n"/>
+      <c r="J180" s="10" t="n"/>
+      <c r="K180" s="10" t="n"/>
+      <c r="L180" s="10" t="n"/>
+      <c r="M180" s="10" t="n"/>
+      <c r="N180" s="10" t="n"/>
+      <c r="O180" s="10" t="n"/>
+      <c r="P180" s="10" t="n"/>
+      <c r="Q180" s="10" t="n"/>
+      <c r="R180" s="10" t="n"/>
+      <c r="S180" s="10" t="n"/>
+      <c r="T180" s="10" t="n"/>
+      <c r="U180" s="10" t="n"/>
+      <c r="V180" s="10" t="n"/>
+      <c r="W180" s="10" t="n"/>
+      <c r="X180" s="10" t="n"/>
+      <c r="Y180" s="10" t="n"/>
+      <c r="Z180" s="10" t="n"/>
+      <c r="AA180" s="10" t="n"/>
+      <c r="AB180" s="10" t="n"/>
+      <c r="AC180" s="10" t="n"/>
+      <c r="AD180" s="10" t="n"/>
+      <c r="AE180" s="10" t="n"/>
+      <c r="AF180" s="10" t="n"/>
+      <c r="AG180" s="10" t="n"/>
+      <c r="AH180" s="10" t="n"/>
+      <c r="AI180" s="10" t="n"/>
+      <c r="AJ180" s="10" t="n"/>
+      <c r="AK180" s="11" t="n"/>
+    </row>
+    <row r="181" ht="72" customHeight="1">
+      <c r="C181" s="38" t="inlineStr">
+        <is>
+          <t>該当した `dokusya_id` を含む行：`IMPORT_VALIDATION_ERROR` + errors（row, field='joho_henko_tekiyo_date', message='この適用日には既に変更履歴が登録されています。購読者履歴情報画面から該当の変更を取消してから、まとめて更新してください。'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="36" customHeight="1">
+      <c r="C182" s="38" t="inlineStr">
+        <is>
+          <t>同日に複数項目をまとめて変更したいときは、ACSMS-SCR-013（購読者履歴情報画面）から該当の変更履歴を取消してから、1回の取込でまとめて反映する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="36" customHeight="1">
+      <c r="C183" s="38" t="inlineStr">
+        <is>
+          <t>ACSMS-SCR-011（画面更新）・ACSMS-SCR-015（販売店一括置換）にも同一制限を適用（3経路共通の `dokusya-shubetsu.rules.ts` に集約）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="36" customHeight="1">
+      <c r="C184" s="38" t="inlineStr">
         <is>
           <t>事前チェックエラーが存在する場合：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（最大10件）を返却し、以降の処理を中断する。</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="B171" s="27" t="inlineStr">
+    <row r="185" ht="18" customHeight="1">
+      <c r="B185" s="27" t="inlineStr">
         <is>
           <t>4.4 データ取込実行（トランザクション）</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="18" customHeight="1">
-      <c r="C172" s="38" t="inlineStr">
+    <row r="186" ht="18" customHeight="1">
+      <c r="C186" s="38" t="inlineStr">
         <is>
           <t>DBトランザクションを開始する。</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="C173" s="38" t="inlineStr">
+    <row r="187" ht="18" customHeight="1">
+      <c r="C187" s="38" t="inlineStr">
         <is>
           <t>取込モードに応じて以下の SQL を行ごとに実行する。</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="C174" s="38" t="inlineStr">
+    <row r="188" ht="18" customHeight="1">
+      <c r="C188" s="38" t="inlineStr">
         <is>
           <t>1件でもエラーが発生した場合はトランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="409" customHeight="1">
-      <c r="C175" s="42" t="inlineStr">
+    <row r="189" ht="409" customHeight="1">
+      <c r="C189" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya (
   ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -15380,78 +16130,78 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D175" s="10" t="n"/>
-      <c r="E175" s="10" t="n"/>
-      <c r="F175" s="10" t="n"/>
-      <c r="G175" s="10" t="n"/>
-      <c r="H175" s="10" t="n"/>
-      <c r="I175" s="10" t="n"/>
-      <c r="J175" s="10" t="n"/>
-      <c r="K175" s="10" t="n"/>
-      <c r="L175" s="10" t="n"/>
-      <c r="M175" s="10" t="n"/>
-      <c r="N175" s="10" t="n"/>
-      <c r="O175" s="10" t="n"/>
-      <c r="P175" s="10" t="n"/>
-      <c r="Q175" s="10" t="n"/>
-      <c r="R175" s="10" t="n"/>
-      <c r="S175" s="10" t="n"/>
-      <c r="T175" s="10" t="n"/>
-      <c r="U175" s="10" t="n"/>
-      <c r="V175" s="10" t="n"/>
-      <c r="W175" s="10" t="n"/>
-      <c r="X175" s="10" t="n"/>
-      <c r="Y175" s="10" t="n"/>
-      <c r="Z175" s="10" t="n"/>
-      <c r="AA175" s="10" t="n"/>
-      <c r="AB175" s="10" t="n"/>
-      <c r="AC175" s="10" t="n"/>
-      <c r="AD175" s="10" t="n"/>
-      <c r="AE175" s="10" t="n"/>
-      <c r="AF175" s="10" t="n"/>
-      <c r="AG175" s="10" t="n"/>
-      <c r="AH175" s="10" t="n"/>
-      <c r="AI175" s="10" t="n"/>
-      <c r="AJ175" s="10" t="n"/>
-      <c r="AK175" s="11" t="n"/>
-    </row>
-    <row r="176" ht="36" customHeight="1">
-      <c r="C176" s="38" t="inlineStr">
+      <c r="D189" s="10" t="n"/>
+      <c r="E189" s="10" t="n"/>
+      <c r="F189" s="10" t="n"/>
+      <c r="G189" s="10" t="n"/>
+      <c r="H189" s="10" t="n"/>
+      <c r="I189" s="10" t="n"/>
+      <c r="J189" s="10" t="n"/>
+      <c r="K189" s="10" t="n"/>
+      <c r="L189" s="10" t="n"/>
+      <c r="M189" s="10" t="n"/>
+      <c r="N189" s="10" t="n"/>
+      <c r="O189" s="10" t="n"/>
+      <c r="P189" s="10" t="n"/>
+      <c r="Q189" s="10" t="n"/>
+      <c r="R189" s="10" t="n"/>
+      <c r="S189" s="10" t="n"/>
+      <c r="T189" s="10" t="n"/>
+      <c r="U189" s="10" t="n"/>
+      <c r="V189" s="10" t="n"/>
+      <c r="W189" s="10" t="n"/>
+      <c r="X189" s="10" t="n"/>
+      <c r="Y189" s="10" t="n"/>
+      <c r="Z189" s="10" t="n"/>
+      <c r="AA189" s="10" t="n"/>
+      <c r="AB189" s="10" t="n"/>
+      <c r="AC189" s="10" t="n"/>
+      <c r="AD189" s="10" t="n"/>
+      <c r="AE189" s="10" t="n"/>
+      <c r="AF189" s="10" t="n"/>
+      <c r="AG189" s="10" t="n"/>
+      <c r="AH189" s="10" t="n"/>
+      <c r="AI189" s="10" t="n"/>
+      <c r="AJ189" s="10" t="n"/>
+      <c r="AK189" s="11" t="n"/>
+    </row>
+    <row r="190" ht="36" customHeight="1">
+      <c r="C190" s="38" t="inlineStr">
         <is>
           <t>`selected_columns` に含まれない列はデフォルト値（空文字 / NULL / 0 / false）を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="36" customHeight="1">
-      <c r="C177" s="38" t="inlineStr">
+    <row r="191" ht="36" customHeight="1">
+      <c r="C191" s="38" t="inlineStr">
         <is>
           <t>`shoki_dokusya_kaishi_date` には `dokusya_kaishi_date` と同じ値を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="72" customHeight="1">
-      <c r="C178" s="38" t="inlineStr">
+    <row r="192" ht="72" customHeight="1">
+      <c r="C192" s="38" t="inlineStr">
         <is>
           <t>`haitatsu_same_flg`（v1.2 顧客要件 2026-06）：**取込列「購読者情報と同じ」で明示指定された値を採用する**（BE は推論しない）。TRUE のとき配達先項目は未入力でよく、配達先住所は購読者住所を使用する。列が未指定（空欄）の行のみ、従来どおり「配達先項目が全て未入力→TRUE / いずれか入力あり→FALSE」で導出する。</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="54" customHeight="1">
-      <c r="C179" s="38" t="inlineStr">
+    <row r="193" ht="54" customHeight="1">
+      <c r="C193" s="38" t="inlineStr">
         <is>
           <t>既存購読者を `dokusya_id` または `kumiaiin_code` で検索し、`selected_columns` 対象外の項目も含めて全項目を更新する（未選択列は NULL / 空文字 / 0 で上書き）。</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="162" customHeight="1">
-      <c r="C180" s="38" t="inlineStr">
+    <row r="194" ht="162" customHeight="1">
+      <c r="C194" s="38" t="inlineStr">
         <is>
           <t>ただし NOT NULL の FK・参照列（kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id / dokusya_shubetsu / tetsuzuki_shurui / shiharai_hoho）は空欄上書きで制約違反になるため `COALESCE(:値, 既存値)` で既存値を維持する（UPDATE モードでは FK コードは任意入力＝存在時のみ検証）。`dokusya_kaishi_date` も空欄時は既存値を維持。`shoki_dokusya_kaishi_date`（初回購読開始日）は不変のため SET から除外する。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="409" customHeight="1">
-      <c r="C181" s="42" t="inlineStr">
+    <row r="195" ht="409" customHeight="1">
+      <c r="C195" s="42" t="inlineStr">
         <is>
           <t>-- 更新前データ取得（操作ログ用）
 SELECT * FROM t_dokusya
@@ -15518,64 +16268,64 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D181" s="10" t="n"/>
-      <c r="E181" s="10" t="n"/>
-      <c r="F181" s="10" t="n"/>
-      <c r="G181" s="10" t="n"/>
-      <c r="H181" s="10" t="n"/>
-      <c r="I181" s="10" t="n"/>
-      <c r="J181" s="10" t="n"/>
-      <c r="K181" s="10" t="n"/>
-      <c r="L181" s="10" t="n"/>
-      <c r="M181" s="10" t="n"/>
-      <c r="N181" s="10" t="n"/>
-      <c r="O181" s="10" t="n"/>
-      <c r="P181" s="10" t="n"/>
-      <c r="Q181" s="10" t="n"/>
-      <c r="R181" s="10" t="n"/>
-      <c r="S181" s="10" t="n"/>
-      <c r="T181" s="10" t="n"/>
-      <c r="U181" s="10" t="n"/>
-      <c r="V181" s="10" t="n"/>
-      <c r="W181" s="10" t="n"/>
-      <c r="X181" s="10" t="n"/>
-      <c r="Y181" s="10" t="n"/>
-      <c r="Z181" s="10" t="n"/>
-      <c r="AA181" s="10" t="n"/>
-      <c r="AB181" s="10" t="n"/>
-      <c r="AC181" s="10" t="n"/>
-      <c r="AD181" s="10" t="n"/>
-      <c r="AE181" s="10" t="n"/>
-      <c r="AF181" s="10" t="n"/>
-      <c r="AG181" s="10" t="n"/>
-      <c r="AH181" s="10" t="n"/>
-      <c r="AI181" s="10" t="n"/>
-      <c r="AJ181" s="10" t="n"/>
-      <c r="AK181" s="11" t="n"/>
-    </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="C182" s="38" t="inlineStr">
+      <c r="D195" s="10" t="n"/>
+      <c r="E195" s="10" t="n"/>
+      <c r="F195" s="10" t="n"/>
+      <c r="G195" s="10" t="n"/>
+      <c r="H195" s="10" t="n"/>
+      <c r="I195" s="10" t="n"/>
+      <c r="J195" s="10" t="n"/>
+      <c r="K195" s="10" t="n"/>
+      <c r="L195" s="10" t="n"/>
+      <c r="M195" s="10" t="n"/>
+      <c r="N195" s="10" t="n"/>
+      <c r="O195" s="10" t="n"/>
+      <c r="P195" s="10" t="n"/>
+      <c r="Q195" s="10" t="n"/>
+      <c r="R195" s="10" t="n"/>
+      <c r="S195" s="10" t="n"/>
+      <c r="T195" s="10" t="n"/>
+      <c r="U195" s="10" t="n"/>
+      <c r="V195" s="10" t="n"/>
+      <c r="W195" s="10" t="n"/>
+      <c r="X195" s="10" t="n"/>
+      <c r="Y195" s="10" t="n"/>
+      <c r="Z195" s="10" t="n"/>
+      <c r="AA195" s="10" t="n"/>
+      <c r="AB195" s="10" t="n"/>
+      <c r="AC195" s="10" t="n"/>
+      <c r="AD195" s="10" t="n"/>
+      <c r="AE195" s="10" t="n"/>
+      <c r="AF195" s="10" t="n"/>
+      <c r="AG195" s="10" t="n"/>
+      <c r="AH195" s="10" t="n"/>
+      <c r="AI195" s="10" t="n"/>
+      <c r="AJ195" s="10" t="n"/>
+      <c r="AK195" s="11" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="C196" s="38" t="inlineStr">
         <is>
           <t>`selected_columns` に含まれる列のみ更新する。未選択列は既存値を維持する。</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="108" customHeight="1">
-      <c r="C183" s="38" t="inlineStr">
+    <row r="197" ht="108" customHeight="1">
+      <c r="C197" s="38" t="inlineStr">
         <is>
           <t>更新可能カラムは取込テンプレートの全項目（email / 住所 / 配達先 / 口座 / 単価・販売店 等を含む）。FK コード列（kanri_shiten_code / shiten_code / hanbaiten_code / tanka_code）は物理カラム kanri_shiten_id / shiten_id / hanbaiten_id / tanka_id へ解決して書く。NOT NULL の FK・参照列は `COALESCE(:値, 既存値)` で既存値を維持する。`dokusya_id` はキーのため更新しない。</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="C184" s="38" t="inlineStr">
+    <row r="198" ht="18" customHeight="1">
+      <c r="C198" s="38" t="inlineStr">
         <is>
           <t>動的に SET 句を構築する（擬似コード）。</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="288" customHeight="1">
-      <c r="C185" s="42" t="inlineStr">
+    <row r="199" ht="288" customHeight="1">
+      <c r="C199" s="42" t="inlineStr">
         <is>
           <t>-- 更新前データ取得（操作ログ用）
 SELECT * FROM t_dokusya
@@ -15594,106 +16344,106 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D185" s="10" t="n"/>
-      <c r="E185" s="10" t="n"/>
-      <c r="F185" s="10" t="n"/>
-      <c r="G185" s="10" t="n"/>
-      <c r="H185" s="10" t="n"/>
-      <c r="I185" s="10" t="n"/>
-      <c r="J185" s="10" t="n"/>
-      <c r="K185" s="10" t="n"/>
-      <c r="L185" s="10" t="n"/>
-      <c r="M185" s="10" t="n"/>
-      <c r="N185" s="10" t="n"/>
-      <c r="O185" s="10" t="n"/>
-      <c r="P185" s="10" t="n"/>
-      <c r="Q185" s="10" t="n"/>
-      <c r="R185" s="10" t="n"/>
-      <c r="S185" s="10" t="n"/>
-      <c r="T185" s="10" t="n"/>
-      <c r="U185" s="10" t="n"/>
-      <c r="V185" s="10" t="n"/>
-      <c r="W185" s="10" t="n"/>
-      <c r="X185" s="10" t="n"/>
-      <c r="Y185" s="10" t="n"/>
-      <c r="Z185" s="10" t="n"/>
-      <c r="AA185" s="10" t="n"/>
-      <c r="AB185" s="10" t="n"/>
-      <c r="AC185" s="10" t="n"/>
-      <c r="AD185" s="10" t="n"/>
-      <c r="AE185" s="10" t="n"/>
-      <c r="AF185" s="10" t="n"/>
-      <c r="AG185" s="10" t="n"/>
-      <c r="AH185" s="10" t="n"/>
-      <c r="AI185" s="10" t="n"/>
-      <c r="AJ185" s="10" t="n"/>
-      <c r="AK185" s="11" t="n"/>
-    </row>
-    <row r="186" ht="54" customHeight="1">
-      <c r="C186" s="38" t="inlineStr">
+      <c r="D199" s="10" t="n"/>
+      <c r="E199" s="10" t="n"/>
+      <c r="F199" s="10" t="n"/>
+      <c r="G199" s="10" t="n"/>
+      <c r="H199" s="10" t="n"/>
+      <c r="I199" s="10" t="n"/>
+      <c r="J199" s="10" t="n"/>
+      <c r="K199" s="10" t="n"/>
+      <c r="L199" s="10" t="n"/>
+      <c r="M199" s="10" t="n"/>
+      <c r="N199" s="10" t="n"/>
+      <c r="O199" s="10" t="n"/>
+      <c r="P199" s="10" t="n"/>
+      <c r="Q199" s="10" t="n"/>
+      <c r="R199" s="10" t="n"/>
+      <c r="S199" s="10" t="n"/>
+      <c r="T199" s="10" t="n"/>
+      <c r="U199" s="10" t="n"/>
+      <c r="V199" s="10" t="n"/>
+      <c r="W199" s="10" t="n"/>
+      <c r="X199" s="10" t="n"/>
+      <c r="Y199" s="10" t="n"/>
+      <c r="Z199" s="10" t="n"/>
+      <c r="AA199" s="10" t="n"/>
+      <c r="AB199" s="10" t="n"/>
+      <c r="AC199" s="10" t="n"/>
+      <c r="AD199" s="10" t="n"/>
+      <c r="AE199" s="10" t="n"/>
+      <c r="AF199" s="10" t="n"/>
+      <c r="AG199" s="10" t="n"/>
+      <c r="AH199" s="10" t="n"/>
+      <c r="AI199" s="10" t="n"/>
+      <c r="AJ199" s="10" t="n"/>
+      <c r="AK199" s="11" t="n"/>
+    </row>
+    <row r="200" ht="54" customHeight="1">
+      <c r="C200" s="38" t="inlineStr">
         <is>
           <t>**本処理は廃止**。手続種類カラムを取込テンプレートから削除し、取込で解約は扱わない。NEW は `tetsuzuki_shurui=1`（新規）固定、UPDATE は手続種類を変更しない（既存値を維持）。</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="36" customHeight="1">
-      <c r="C187" s="38" t="inlineStr">
+    <row r="201" ht="36" customHeight="1">
+      <c r="C201" s="38" t="inlineStr">
         <is>
           <t>解約は SCR-011/013 の編集運用と同じく「解約予定日（購読中止日）」の登録のみとし、実際の解約処理（購読部数=0・解約状態）は日次バッチが担う（バッチ未実装）。</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="36" customHeight="1">
-      <c r="C188" s="38" t="inlineStr">
+    <row r="202" ht="36" customHeight="1">
+      <c r="C202" s="38" t="inlineStr">
         <is>
           <t>取込モードに関わらず、取り込んだデータ件数分のレコードを `t_dokusya_rireki` に追加する。</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="C189" s="38" t="inlineStr">
+    <row r="203" ht="18" customHeight="1">
+      <c r="C203" s="38" t="inlineStr">
         <is>
           <t>履歴No（`rireki_no`）は `t_dokusya.rireki_no` の値を引き継ぐ。</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="36" customHeight="1">
-      <c r="C190" s="38" t="inlineStr">
+    <row r="204" ht="36" customHeight="1">
+      <c r="C204" s="38" t="inlineStr">
         <is>
           <t>`saishin_data_flg` は新規追加レコードのみ TRUE、既存履歴は FALSE に更新する。</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="90" customHeight="1">
-      <c r="C191" s="38" t="inlineStr">
+    <row r="205" ht="90" customHeight="1">
+      <c r="C205" s="38" t="inlineStr">
         <is>
           <t>**v1.3（顧客要件 2026-07）— UPDATE は1更新1レコード**: 販売店適用日を廃止し、適用日は `joho_henko_tekiyo_date` に統一。情報変更（購読部数/住所等）と販売店変更が同一行で同時に起きても履歴は **1件**にまとめる（UI編集 SCR-011/013・一括置換 SCR-015 と同一ロジック・共通実装）。旧 v1.2 の「適用日順に2件分割」は廃止。</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="36" customHeight="1">
-      <c r="D192" s="38" t="inlineStr">
+    <row r="206" ht="36" customHeight="1">
+      <c r="D206" s="38" t="inlineStr">
         <is>
           <t>追加レコード: `joho_henko_tekiyo_date`=読者情報変更適用日（販売店・支払方法を含む全変更の唯一の適用日。専用の販売店適用日列は持たない）。</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="36" customHeight="1">
-      <c r="D193" s="38" t="inlineStr">
+    <row r="207" ht="36" customHeight="1">
+      <c r="D207" s="38" t="inlineStr">
         <is>
           <t>`saishin_data_flg` は当日基準の再計算（recomputeMaster）で確定。`zenkai_*` / `zougen_hokoku_flg` は直前状態との差分で算出。</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="36" customHeight="1">
-      <c r="D194" s="38" t="inlineStr">
+    <row r="208" ht="36" customHeight="1">
+      <c r="D208" s="38" t="inlineStr">
         <is>
           <t>取込で解約は扱わないため `kaiyaku_flg` は常に FALSE。`shinki_flg` は NEW かつ手続種類=新規(1) のときのみ TRUE。</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="409" customHeight="1">
-      <c r="C195" s="42" t="inlineStr">
+    <row r="209" ht="409" customHeight="1">
+      <c r="C209" s="42" t="inlineStr">
         <is>
           <t>-- 既存履歴の saishin_data_flg を FALSE に更新
 UPDATE t_dokusya_rireki
@@ -15743,92 +16493,92 @@
 )</t>
         </is>
       </c>
-      <c r="D195" s="10" t="n"/>
-      <c r="E195" s="10" t="n"/>
-      <c r="F195" s="10" t="n"/>
-      <c r="G195" s="10" t="n"/>
-      <c r="H195" s="10" t="n"/>
-      <c r="I195" s="10" t="n"/>
-      <c r="J195" s="10" t="n"/>
-      <c r="K195" s="10" t="n"/>
-      <c r="L195" s="10" t="n"/>
-      <c r="M195" s="10" t="n"/>
-      <c r="N195" s="10" t="n"/>
-      <c r="O195" s="10" t="n"/>
-      <c r="P195" s="10" t="n"/>
-      <c r="Q195" s="10" t="n"/>
-      <c r="R195" s="10" t="n"/>
-      <c r="S195" s="10" t="n"/>
-      <c r="T195" s="10" t="n"/>
-      <c r="U195" s="10" t="n"/>
-      <c r="V195" s="10" t="n"/>
-      <c r="W195" s="10" t="n"/>
-      <c r="X195" s="10" t="n"/>
-      <c r="Y195" s="10" t="n"/>
-      <c r="Z195" s="10" t="n"/>
-      <c r="AA195" s="10" t="n"/>
-      <c r="AB195" s="10" t="n"/>
-      <c r="AC195" s="10" t="n"/>
-      <c r="AD195" s="10" t="n"/>
-      <c r="AE195" s="10" t="n"/>
-      <c r="AF195" s="10" t="n"/>
-      <c r="AG195" s="10" t="n"/>
-      <c r="AH195" s="10" t="n"/>
-      <c r="AI195" s="10" t="n"/>
-      <c r="AJ195" s="10" t="n"/>
-      <c r="AK195" s="11" t="n"/>
-    </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="C196" s="38" t="inlineStr">
+      <c r="D209" s="10" t="n"/>
+      <c r="E209" s="10" t="n"/>
+      <c r="F209" s="10" t="n"/>
+      <c r="G209" s="10" t="n"/>
+      <c r="H209" s="10" t="n"/>
+      <c r="I209" s="10" t="n"/>
+      <c r="J209" s="10" t="n"/>
+      <c r="K209" s="10" t="n"/>
+      <c r="L209" s="10" t="n"/>
+      <c r="M209" s="10" t="n"/>
+      <c r="N209" s="10" t="n"/>
+      <c r="O209" s="10" t="n"/>
+      <c r="P209" s="10" t="n"/>
+      <c r="Q209" s="10" t="n"/>
+      <c r="R209" s="10" t="n"/>
+      <c r="S209" s="10" t="n"/>
+      <c r="T209" s="10" t="n"/>
+      <c r="U209" s="10" t="n"/>
+      <c r="V209" s="10" t="n"/>
+      <c r="W209" s="10" t="n"/>
+      <c r="X209" s="10" t="n"/>
+      <c r="Y209" s="10" t="n"/>
+      <c r="Z209" s="10" t="n"/>
+      <c r="AA209" s="10" t="n"/>
+      <c r="AB209" s="10" t="n"/>
+      <c r="AC209" s="10" t="n"/>
+      <c r="AD209" s="10" t="n"/>
+      <c r="AE209" s="10" t="n"/>
+      <c r="AF209" s="10" t="n"/>
+      <c r="AG209" s="10" t="n"/>
+      <c r="AH209" s="10" t="n"/>
+      <c r="AI209" s="10" t="n"/>
+      <c r="AJ209" s="10" t="n"/>
+      <c r="AK209" s="11" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="C210" s="38" t="inlineStr">
         <is>
           <t>`shinki_flg`：新規購読 / 解約→再購読 の場合 TRUE</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="C197" s="38" t="inlineStr">
+    <row r="211" ht="18" customHeight="1">
+      <c r="C211" s="38" t="inlineStr">
         <is>
           <t>`kaiyaku_flg`：購読中→解約 の場合 TRUE</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="C198" s="38" t="inlineStr">
+    <row r="212" ht="18" customHeight="1">
+      <c r="C212" s="38" t="inlineStr">
         <is>
           <t>`zougen_hokoku_flg`：購読部数や販売店等の増減報告対象項目が変化した場合 TRUE</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="36" customHeight="1">
-      <c r="C199" s="38" t="inlineStr">
+    <row r="213" ht="36" customHeight="1">
+      <c r="C213" s="38" t="inlineStr">
         <is>
           <t>`zenkai_*` 項目：UPDATE系の場合、更新前の値を格納する（初回履歴・NEWモードは NULL）。</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="54" customHeight="1">
-      <c r="C200" s="38" t="inlineStr">
+    <row r="214" ht="54" customHeight="1">
+      <c r="C214" s="38" t="inlineStr">
         <is>
           <t>実行中に DB 制約違反等が発生した場合：トランザクションを即時ロールバックし、HTTP 400 (`IMPORT_VALIDATION_ERROR`) または HTTP 500 (`INTERNAL_SERVER_ERROR`) を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="18" customHeight="1">
-      <c r="B201" s="27" t="inlineStr">
+    <row r="215" ht="18" customHeight="1">
+      <c r="B215" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="18" customHeight="1">
-      <c r="C202" s="38" t="inlineStr">
+    <row r="216" ht="18" customHeight="1">
+      <c r="C216" s="38" t="inlineStr">
         <is>
           <t>全行の処理が完了した後、一括取込操作の操作ログを取込バッチ単位で1件記録する（行単位ではない）。</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="144" customHeight="1">
-      <c r="C203" s="42" t="inlineStr">
+    <row r="217" ht="144" customHeight="1">
+      <c r="C217" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -15840,106 +16590,106 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D203" s="10" t="n"/>
-      <c r="E203" s="10" t="n"/>
-      <c r="F203" s="10" t="n"/>
-      <c r="G203" s="10" t="n"/>
-      <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
-      <c r="J203" s="10" t="n"/>
-      <c r="K203" s="10" t="n"/>
-      <c r="L203" s="10" t="n"/>
-      <c r="M203" s="10" t="n"/>
-      <c r="N203" s="10" t="n"/>
-      <c r="O203" s="10" t="n"/>
-      <c r="P203" s="10" t="n"/>
-      <c r="Q203" s="10" t="n"/>
-      <c r="R203" s="10" t="n"/>
-      <c r="S203" s="10" t="n"/>
-      <c r="T203" s="10" t="n"/>
-      <c r="U203" s="10" t="n"/>
-      <c r="V203" s="10" t="n"/>
-      <c r="W203" s="10" t="n"/>
-      <c r="X203" s="10" t="n"/>
-      <c r="Y203" s="10" t="n"/>
-      <c r="Z203" s="10" t="n"/>
-      <c r="AA203" s="10" t="n"/>
-      <c r="AB203" s="10" t="n"/>
-      <c r="AC203" s="10" t="n"/>
-      <c r="AD203" s="10" t="n"/>
-      <c r="AE203" s="10" t="n"/>
-      <c r="AF203" s="10" t="n"/>
-      <c r="AG203" s="10" t="n"/>
-      <c r="AH203" s="10" t="n"/>
-      <c r="AI203" s="10" t="n"/>
-      <c r="AJ203" s="10" t="n"/>
-      <c r="AK203" s="11" t="n"/>
-    </row>
-    <row r="204" ht="36" customHeight="1">
-      <c r="C204" s="38" t="inlineStr">
+      <c r="D217" s="10" t="n"/>
+      <c r="E217" s="10" t="n"/>
+      <c r="F217" s="10" t="n"/>
+      <c r="G217" s="10" t="n"/>
+      <c r="H217" s="10" t="n"/>
+      <c r="I217" s="10" t="n"/>
+      <c r="J217" s="10" t="n"/>
+      <c r="K217" s="10" t="n"/>
+      <c r="L217" s="10" t="n"/>
+      <c r="M217" s="10" t="n"/>
+      <c r="N217" s="10" t="n"/>
+      <c r="O217" s="10" t="n"/>
+      <c r="P217" s="10" t="n"/>
+      <c r="Q217" s="10" t="n"/>
+      <c r="R217" s="10" t="n"/>
+      <c r="S217" s="10" t="n"/>
+      <c r="T217" s="10" t="n"/>
+      <c r="U217" s="10" t="n"/>
+      <c r="V217" s="10" t="n"/>
+      <c r="W217" s="10" t="n"/>
+      <c r="X217" s="10" t="n"/>
+      <c r="Y217" s="10" t="n"/>
+      <c r="Z217" s="10" t="n"/>
+      <c r="AA217" s="10" t="n"/>
+      <c r="AB217" s="10" t="n"/>
+      <c r="AC217" s="10" t="n"/>
+      <c r="AD217" s="10" t="n"/>
+      <c r="AE217" s="10" t="n"/>
+      <c r="AF217" s="10" t="n"/>
+      <c r="AG217" s="10" t="n"/>
+      <c r="AH217" s="10" t="n"/>
+      <c r="AI217" s="10" t="n"/>
+      <c r="AJ217" s="10" t="n"/>
+      <c r="AK217" s="11" t="n"/>
+    </row>
+    <row r="218" ht="36" customHeight="1">
+      <c r="C218" s="38" t="inlineStr">
         <is>
           <t>`operation`：取込モード別の prefixed ラベル（販売店取込 SCR-019 と統一・bare-verb ルールの例外）。</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="18" customHeight="1">
-      <c r="D205" s="38" t="inlineStr">
+    <row r="219" ht="18" customHeight="1">
+      <c r="D219" s="38" t="inlineStr">
         <is>
           <t>`NEW` → `'IMPORT_NEW'`</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="D206" s="38" t="inlineStr">
+    <row r="220" ht="18" customHeight="1">
+      <c r="D220" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_ALL` → `'IMPORT_UPDATE_ALL'`</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="18" customHeight="1">
-      <c r="D207" s="38" t="inlineStr">
+    <row r="221" ht="18" customHeight="1">
+      <c r="D221" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_PARTIAL` → `'IMPORT_UPDATE_PARTIAL'`</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="18" customHeight="1">
-      <c r="C208" s="38" t="inlineStr">
+    <row r="222" ht="18" customHeight="1">
+      <c r="C222" s="38" t="inlineStr">
         <is>
           <t>`before_value`：</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="D209" s="38" t="inlineStr">
+    <row r="223" ht="18" customHeight="1">
+      <c r="D223" s="38" t="inlineStr">
         <is>
           <t>`NEW` モード：空文字列</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="54" customHeight="1">
-      <c r="D210" s="38" t="inlineStr">
+    <row r="224" ht="54" customHeight="1">
+      <c r="D224" s="38" t="inlineStr">
         <is>
           <t>`UPDATE_ALL` / `UPDATE_PARTIAL` / 一括中止：更新前データのサマリJSON `{ "rows": [{...}, ...] }`（各行の更新前状態を格納、最大100件まで）</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="72" customHeight="1">
-      <c r="C211" s="38" t="inlineStr">
+    <row r="225" ht="72" customHeight="1">
+      <c r="C225" s="38" t="inlineStr">
         <is>
           <t>`after_value`：取込結果サマリJSON `{ "import_mode", "total_rows", "created_count", "updated_count", "cancelled_count", "created_ids": [...], "updated_ids": [...] }`</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="C212" s="38" t="inlineStr">
+    <row r="226" ht="18" customHeight="1">
+      <c r="C226" s="38" t="inlineStr">
         <is>
           <t>パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="180" customHeight="1">
-      <c r="C213" s="42" t="inlineStr">
+    <row r="227" ht="180" customHeight="1">
+      <c r="C227" s="42" t="inlineStr">
         <is>
           <t>{
   "import_mode": "NEW",
@@ -15953,99 +16703,99 @@
 }</t>
         </is>
       </c>
-      <c r="D213" s="10" t="n"/>
-      <c r="E213" s="10" t="n"/>
-      <c r="F213" s="10" t="n"/>
-      <c r="G213" s="10" t="n"/>
-      <c r="H213" s="10" t="n"/>
-      <c r="I213" s="10" t="n"/>
-      <c r="J213" s="10" t="n"/>
-      <c r="K213" s="10" t="n"/>
-      <c r="L213" s="10" t="n"/>
-      <c r="M213" s="10" t="n"/>
-      <c r="N213" s="10" t="n"/>
-      <c r="O213" s="10" t="n"/>
-      <c r="P213" s="10" t="n"/>
-      <c r="Q213" s="10" t="n"/>
-      <c r="R213" s="10" t="n"/>
-      <c r="S213" s="10" t="n"/>
-      <c r="T213" s="10" t="n"/>
-      <c r="U213" s="10" t="n"/>
-      <c r="V213" s="10" t="n"/>
-      <c r="W213" s="10" t="n"/>
-      <c r="X213" s="10" t="n"/>
-      <c r="Y213" s="10" t="n"/>
-      <c r="Z213" s="10" t="n"/>
-      <c r="AA213" s="10" t="n"/>
-      <c r="AB213" s="10" t="n"/>
-      <c r="AC213" s="10" t="n"/>
-      <c r="AD213" s="10" t="n"/>
-      <c r="AE213" s="10" t="n"/>
-      <c r="AF213" s="10" t="n"/>
-      <c r="AG213" s="10" t="n"/>
-      <c r="AH213" s="10" t="n"/>
-      <c r="AI213" s="10" t="n"/>
-      <c r="AJ213" s="10" t="n"/>
-      <c r="AK213" s="11" t="n"/>
-    </row>
-    <row r="214" ht="18" customHeight="1">
-      <c r="B214" s="27" t="inlineStr">
+      <c r="D227" s="10" t="n"/>
+      <c r="E227" s="10" t="n"/>
+      <c r="F227" s="10" t="n"/>
+      <c r="G227" s="10" t="n"/>
+      <c r="H227" s="10" t="n"/>
+      <c r="I227" s="10" t="n"/>
+      <c r="J227" s="10" t="n"/>
+      <c r="K227" s="10" t="n"/>
+      <c r="L227" s="10" t="n"/>
+      <c r="M227" s="10" t="n"/>
+      <c r="N227" s="10" t="n"/>
+      <c r="O227" s="10" t="n"/>
+      <c r="P227" s="10" t="n"/>
+      <c r="Q227" s="10" t="n"/>
+      <c r="R227" s="10" t="n"/>
+      <c r="S227" s="10" t="n"/>
+      <c r="T227" s="10" t="n"/>
+      <c r="U227" s="10" t="n"/>
+      <c r="V227" s="10" t="n"/>
+      <c r="W227" s="10" t="n"/>
+      <c r="X227" s="10" t="n"/>
+      <c r="Y227" s="10" t="n"/>
+      <c r="Z227" s="10" t="n"/>
+      <c r="AA227" s="10" t="n"/>
+      <c r="AB227" s="10" t="n"/>
+      <c r="AC227" s="10" t="n"/>
+      <c r="AD227" s="10" t="n"/>
+      <c r="AE227" s="10" t="n"/>
+      <c r="AF227" s="10" t="n"/>
+      <c r="AG227" s="10" t="n"/>
+      <c r="AH227" s="10" t="n"/>
+      <c r="AI227" s="10" t="n"/>
+      <c r="AJ227" s="10" t="n"/>
+      <c r="AK227" s="11" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="B228" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="18" customHeight="1">
-      <c r="C215" s="38" t="inlineStr">
+    <row r="229" ht="18" customHeight="1">
+      <c r="C229" s="38" t="inlineStr">
         <is>
           <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="18" customHeight="1">
-      <c r="C216" s="38" t="inlineStr">
+    <row r="230" ht="18" customHeight="1">
+      <c r="C230" s="38" t="inlineStr">
         <is>
           <t>取込結果サマリを `data` オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="18" customHeight="1">
-      <c r="C217" s="38" t="inlineStr">
+    <row r="231" ht="18" customHeight="1">
+      <c r="C231" s="38" t="inlineStr">
         <is>
           <t>`message`：`取り込みました。`（ACSMS-MSG-016-004）</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="18" customHeight="1">
-      <c r="B218" s="27" t="inlineStr">
+    <row r="232" ht="18" customHeight="1">
+      <c r="B232" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="C219" s="38" t="inlineStr">
+    <row r="233" ht="18" customHeight="1">
+      <c r="C233" s="38" t="inlineStr">
         <is>
           <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="18" customHeight="1">
-      <c r="C220" s="38" t="inlineStr">
+    <row r="234" ht="18" customHeight="1">
+      <c r="C234" s="38" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="36" customHeight="1">
-      <c r="C221" s="38" t="inlineStr">
+    <row r="235" ht="36" customHeight="1">
+      <c r="C235" s="38" t="inlineStr">
         <is>
           <t>エラー発生時もエラーログを記録する（`log_type = 3`）。**トランザクション外で別途記録する**。</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="144" customHeight="1">
-      <c r="C222" s="42" t="inlineStr">
+    <row r="236" ht="144" customHeight="1">
+      <c r="C236" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -16057,75 +16807,75 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D222" s="10" t="n"/>
-      <c r="E222" s="10" t="n"/>
-      <c r="F222" s="10" t="n"/>
-      <c r="G222" s="10" t="n"/>
-      <c r="H222" s="10" t="n"/>
-      <c r="I222" s="10" t="n"/>
-      <c r="J222" s="10" t="n"/>
-      <c r="K222" s="10" t="n"/>
-      <c r="L222" s="10" t="n"/>
-      <c r="M222" s="10" t="n"/>
-      <c r="N222" s="10" t="n"/>
-      <c r="O222" s="10" t="n"/>
-      <c r="P222" s="10" t="n"/>
-      <c r="Q222" s="10" t="n"/>
-      <c r="R222" s="10" t="n"/>
-      <c r="S222" s="10" t="n"/>
-      <c r="T222" s="10" t="n"/>
-      <c r="U222" s="10" t="n"/>
-      <c r="V222" s="10" t="n"/>
-      <c r="W222" s="10" t="n"/>
-      <c r="X222" s="10" t="n"/>
-      <c r="Y222" s="10" t="n"/>
-      <c r="Z222" s="10" t="n"/>
-      <c r="AA222" s="10" t="n"/>
-      <c r="AB222" s="10" t="n"/>
-      <c r="AC222" s="10" t="n"/>
-      <c r="AD222" s="10" t="n"/>
-      <c r="AE222" s="10" t="n"/>
-      <c r="AF222" s="10" t="n"/>
-      <c r="AG222" s="10" t="n"/>
-      <c r="AH222" s="10" t="n"/>
-      <c r="AI222" s="10" t="n"/>
-      <c r="AJ222" s="10" t="n"/>
-      <c r="AK222" s="11" t="n"/>
-    </row>
-    <row r="223" ht="18" customHeight="1">
-      <c r="B223" s="27" t="inlineStr">
+      <c r="D236" s="10" t="n"/>
+      <c r="E236" s="10" t="n"/>
+      <c r="F236" s="10" t="n"/>
+      <c r="G236" s="10" t="n"/>
+      <c r="H236" s="10" t="n"/>
+      <c r="I236" s="10" t="n"/>
+      <c r="J236" s="10" t="n"/>
+      <c r="K236" s="10" t="n"/>
+      <c r="L236" s="10" t="n"/>
+      <c r="M236" s="10" t="n"/>
+      <c r="N236" s="10" t="n"/>
+      <c r="O236" s="10" t="n"/>
+      <c r="P236" s="10" t="n"/>
+      <c r="Q236" s="10" t="n"/>
+      <c r="R236" s="10" t="n"/>
+      <c r="S236" s="10" t="n"/>
+      <c r="T236" s="10" t="n"/>
+      <c r="U236" s="10" t="n"/>
+      <c r="V236" s="10" t="n"/>
+      <c r="W236" s="10" t="n"/>
+      <c r="X236" s="10" t="n"/>
+      <c r="Y236" s="10" t="n"/>
+      <c r="Z236" s="10" t="n"/>
+      <c r="AA236" s="10" t="n"/>
+      <c r="AB236" s="10" t="n"/>
+      <c r="AC236" s="10" t="n"/>
+      <c r="AD236" s="10" t="n"/>
+      <c r="AE236" s="10" t="n"/>
+      <c r="AF236" s="10" t="n"/>
+      <c r="AG236" s="10" t="n"/>
+      <c r="AH236" s="10" t="n"/>
+      <c r="AI236" s="10" t="n"/>
+      <c r="AJ236" s="10" t="n"/>
+      <c r="AK236" s="11" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="B237" s="27" t="inlineStr">
         <is>
           <t>4.8 一括中止（`dokusya_chushi_date` 指定時・v1.6 顧客要件 2026-08）</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="36" customHeight="1">
-      <c r="C224" s="38" t="inlineStr">
+    <row r="238" ht="36" customHeight="1">
+      <c r="C238" s="38" t="inlineStr">
         <is>
           <t>対象は `dokusya_id`（無い行は `kumiaiin_code`）で特定し、行ロックのうえ**解約予約の履歴を1件 append** する。</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="36" customHeight="1">
-      <c r="C225" s="38" t="inlineStr">
+    <row r="239" ht="36" customHeight="1">
+      <c r="C239" s="38" t="inlineStr">
         <is>
           <t>**`selected_columns` に他の列が入っていても書き込まない**（画面も列グリッドをキー列へ縮退させるが、直接呼ばれても同じ）。</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="36" customHeight="1">
-      <c r="C226" s="38" t="inlineStr">
+    <row r="240" ht="36" customHeight="1">
+      <c r="C240" s="38" t="inlineStr">
         <is>
           <t>中止日は予約時点で `t_dokusya.dokusya_chushi_date` へ反映し、一覧（SCR-014）・詳細（SCR-011）に即時表示する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="638">
+  <mergeCells count="651">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="C174:AK174"/>
+    <mergeCell ref="B215:AK215"/>
     <mergeCell ref="AF65:AK65"/>
-    <mergeCell ref="D134:AK134"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y61:AB61"/>
     <mergeCell ref="C189:AK189"/>
@@ -16137,6 +16887,7 @@
     <mergeCell ref="Q80:S80"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="Y56:AB56"/>
+    <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="Y43:AB43"/>
@@ -16145,8 +16896,8 @@
     <mergeCell ref="AF91:AK91"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C205:AK205"/>
     <mergeCell ref="M88:P88"/>
-    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Q91:S91"/>
     <mergeCell ref="Q25:S25"/>
@@ -16159,16 +16910,13 @@
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y59:AB59"/>
     <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="D151:AK151"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M85:P85"/>
     <mergeCell ref="Y36:AB36"/>
     <mergeCell ref="AC58:AE58"/>
-    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="AC39:AE39"/>
     <mergeCell ref="T38:X38"/>
-    <mergeCell ref="C220:AK220"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="C195:AK195"/>
@@ -16194,17 +16942,14 @@
     <mergeCell ref="Y64:AB64"/>
     <mergeCell ref="Y51:AB51"/>
     <mergeCell ref="T69:X69"/>
-    <mergeCell ref="D139:AK139"/>
     <mergeCell ref="C213:AK213"/>
     <mergeCell ref="AC71:AE71"/>
-    <mergeCell ref="C144:AK144"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="C208:AK208"/>
     <mergeCell ref="C87:C94"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="M91:P91"/>
-    <mergeCell ref="C145:AK145"/>
+    <mergeCell ref="D221:AK221"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF92:AK92"/>
@@ -16213,10 +16958,11 @@
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C72:L72"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C210:AK210"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="M93:P93"/>
     <mergeCell ref="T87:X87"/>
-    <mergeCell ref="D152:AK152"/>
+    <mergeCell ref="D223:AK223"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Y75:AB75"/>
@@ -16228,11 +16974,12 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T89:X89"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B143:AK143"/>
     <mergeCell ref="Y39:AB39"/>
+    <mergeCell ref="C236:AK236"/>
     <mergeCell ref="AF56:AK56"/>
     <mergeCell ref="C54:L54"/>
     <mergeCell ref="C163:AK163"/>
@@ -16244,18 +16991,19 @@
     <mergeCell ref="Q62:S62"/>
     <mergeCell ref="C119:AK119"/>
     <mergeCell ref="C56:L56"/>
+    <mergeCell ref="D145:AK145"/>
     <mergeCell ref="AC78:AE78"/>
     <mergeCell ref="C43:L43"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="C158:AK158"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="B97:I97"/>
-    <mergeCell ref="D209:AK209"/>
     <mergeCell ref="T77:X77"/>
+    <mergeCell ref="D147:AK147"/>
     <mergeCell ref="Y65:AB65"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B161:AK161"/>
     <mergeCell ref="Y57:AB57"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="AC79:AE79"/>
@@ -16265,8 +17013,8 @@
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="C216:AK216"/>
     <mergeCell ref="Y87:AE87"/>
-    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="AF75:AK75"/>
+    <mergeCell ref="C218:AK218"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="C211:AK211"/>
@@ -16274,6 +17022,7 @@
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="C65:L65"/>
+    <mergeCell ref="D158:AK158"/>
     <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
@@ -16286,7 +17035,6 @@
     <mergeCell ref="T90:X90"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Y78:AB78"/>
-    <mergeCell ref="B218:AK218"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="C95:L95"/>
@@ -16297,17 +17045,16 @@
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC67:AE67"/>
     <mergeCell ref="Y80:AB80"/>
+    <mergeCell ref="C229:AK229"/>
     <mergeCell ref="AC69:AE69"/>
     <mergeCell ref="C179:AK179"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="C57:L57"/>
     <mergeCell ref="C166:AK166"/>
     <mergeCell ref="C160:AK160"/>
-    <mergeCell ref="D192:AK192"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
-    <mergeCell ref="C141:AK141"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
@@ -16318,7 +17065,6 @@
     <mergeCell ref="Y58:AB58"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Y73:AB73"/>
-    <mergeCell ref="B201:AK201"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
     <mergeCell ref="C75:L75"/>
@@ -16326,7 +17072,6 @@
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T86:X86"/>
-    <mergeCell ref="C219:AK219"/>
     <mergeCell ref="Y90:AE90"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
@@ -16335,10 +17080,9 @@
     <mergeCell ref="B109:I109"/>
     <mergeCell ref="C70:L70"/>
     <mergeCell ref="Q85:S85"/>
-    <mergeCell ref="B130:AK130"/>
-    <mergeCell ref="D205:AK205"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="C154:AK154"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC42:AE42"/>
@@ -16346,16 +17090,19 @@
     <mergeCell ref="C81:L81"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B132:AK132"/>
     <mergeCell ref="C156:AK156"/>
     <mergeCell ref="AC44:AE44"/>
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="C230:AK230"/>
     <mergeCell ref="C168:AK168"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="C180:AK180"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="C167:AK167"/>
+    <mergeCell ref="C238:AK238"/>
     <mergeCell ref="C63:L63"/>
     <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
@@ -16365,14 +17112,15 @@
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
     <mergeCell ref="C169:AK169"/>
+    <mergeCell ref="B237:AK237"/>
     <mergeCell ref="M65:P65"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
+    <mergeCell ref="C233:AK233"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="Y49:AB49"/>
-    <mergeCell ref="B214:AK214"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
     <mergeCell ref="Y76:AB76"/>
@@ -16382,12 +17130,14 @@
     <mergeCell ref="C78:L78"/>
     <mergeCell ref="C187:AK187"/>
     <mergeCell ref="Y91:AE91"/>
+    <mergeCell ref="D142:AK142"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="C162:AK162"/>
     <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="Y93:AE93"/>
+    <mergeCell ref="D144:AK144"/>
     <mergeCell ref="C226:AK226"/>
     <mergeCell ref="C164:AK164"/>
     <mergeCell ref="Y30:AB30"/>
@@ -16397,42 +17147,49 @@
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="M78:P78"/>
     <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="B133:AK133"/>
     <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="D208:AK208"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="C222:AK222"/>
-    <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="AC81:AE81"/>
+    <mergeCell ref="D219:AK219"/>
     <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="T36:X36"/>
+    <mergeCell ref="C240:AK240"/>
     <mergeCell ref="C190:AK190"/>
     <mergeCell ref="AC76:AE76"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
+    <mergeCell ref="B228:AK228"/>
     <mergeCell ref="D137:AK137"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="C66:L66"/>
     <mergeCell ref="Q81:S81"/>
     <mergeCell ref="C175:AK175"/>
+    <mergeCell ref="C235:AK235"/>
     <mergeCell ref="C53:L53"/>
     <mergeCell ref="AC63:AE63"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AC50:AE50"/>
-    <mergeCell ref="C185:AK185"/>
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="C68:L68"/>
     <mergeCell ref="T62:X62"/>
-    <mergeCell ref="D132:AK132"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="Y44:AB44"/>
+    <mergeCell ref="C201:AK201"/>
+    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="C188:AK188"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C203:AK203"/>
@@ -16440,7 +17197,6 @@
     <mergeCell ref="M86:P86"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="M80:P80"/>
-    <mergeCell ref="D210:AK210"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="AF87:AK87"/>
     <mergeCell ref="J11:AK11"/>
@@ -16453,9 +17209,10 @@
     <mergeCell ref="AF89:AK89"/>
     <mergeCell ref="AC55:AE55"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="D193:AK193"/>
+    <mergeCell ref="D224:AK224"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="A131:AK131"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="AC46:AE46"/>
     <mergeCell ref="Q89:S89"/>
@@ -16467,13 +17224,13 @@
     <mergeCell ref="C183:AK183"/>
     <mergeCell ref="D138:AK138"/>
     <mergeCell ref="M70:P70"/>
+    <mergeCell ref="C193:AK193"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="C176:AK176"/>
     <mergeCell ref="D140:AK140"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
-    <mergeCell ref="B154:AK154"/>
     <mergeCell ref="Y50:AB50"/>
     <mergeCell ref="C178:AK178"/>
     <mergeCell ref="N20:AK20"/>
@@ -16485,8 +17242,10 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y52:AB52"/>
     <mergeCell ref="AC77:AE77"/>
+    <mergeCell ref="D141:AK141"/>
     <mergeCell ref="AC74:AE74"/>
     <mergeCell ref="D135:AK135"/>
+    <mergeCell ref="C209:AK209"/>
     <mergeCell ref="AC68:AE68"/>
     <mergeCell ref="D206:AK206"/>
     <mergeCell ref="T30:X30"/>
@@ -16506,6 +17265,7 @@
     <mergeCell ref="Y42:AB42"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="AF88:AK88"/>
+    <mergeCell ref="C231:AK231"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -16525,22 +17285,19 @@
     <mergeCell ref="C55:L55"/>
     <mergeCell ref="AC62:AE62"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C159:AK159"/>
     <mergeCell ref="C122:AK122"/>
     <mergeCell ref="C153:AK153"/>
-    <mergeCell ref="C224:AK224"/>
     <mergeCell ref="C199:AK199"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="C125:AK125"/>
     <mergeCell ref="C186:AK186"/>
     <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
-    <mergeCell ref="C161:AK161"/>
     <mergeCell ref="C217:AK217"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="D143:AK143"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T78:X78"/>
     <mergeCell ref="Y66:AB66"/>
@@ -16559,15 +17316,17 @@
     <mergeCell ref="Y55:AB55"/>
     <mergeCell ref="T79:X79"/>
     <mergeCell ref="C212:AK212"/>
-    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="D159:AK159"/>
     <mergeCell ref="D94:L94"/>
+    <mergeCell ref="C214:AK214"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
     <mergeCell ref="Y79:AB79"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="M95:P95"/>
+    <mergeCell ref="B185:AK185"/>
     <mergeCell ref="M89:P89"/>
     <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
@@ -16583,13 +17342,15 @@
     <mergeCell ref="AC64:AE64"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="D220:AK220"/>
     <mergeCell ref="D87:L87"/>
+    <mergeCell ref="D157:AK157"/>
     <mergeCell ref="C225:AK225"/>
-    <mergeCell ref="B171:AK171"/>
     <mergeCell ref="AC65:AE65"/>
     <mergeCell ref="C200:AK200"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="Y63:AB63"/>
+    <mergeCell ref="C227:AK227"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="C45:L45"/>
@@ -16612,7 +17373,6 @@
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="Y69:AB69"/>
     <mergeCell ref="C51:L51"/>
-    <mergeCell ref="D150:AK150"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="C71:L71"/>
     <mergeCell ref="Q72:S72"/>
@@ -16622,17 +17382,17 @@
     <mergeCell ref="Y86:AE86"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C157:AK157"/>
+    <mergeCell ref="C151:AK151"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="C77:L77"/>
-    <mergeCell ref="C215:AK215"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="T92:X92"/>
     <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="C152:AK152"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="D88:L88"/>
@@ -16647,7 +17407,6 @@
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="C59:L59"/>
     <mergeCell ref="T95:X95"/>
-    <mergeCell ref="A128:AK128"/>
     <mergeCell ref="C46:L46"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
@@ -16667,7 +17426,6 @@
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="Y72:AB72"/>
     <mergeCell ref="M44:P44"/>
-    <mergeCell ref="C221:AK221"/>
     <mergeCell ref="C196:AK196"/>
     <mergeCell ref="AC80:AE80"/>
     <mergeCell ref="AC51:AE51"/>
@@ -16684,14 +17442,12 @@
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="B223:AK223"/>
     <mergeCell ref="Q93:S93"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="C67:L67"/>
@@ -16705,14 +17461,15 @@
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="C107:AK107"/>
     <mergeCell ref="C69:L69"/>
+    <mergeCell ref="C234:AK234"/>
     <mergeCell ref="C172:AK172"/>
     <mergeCell ref="D93:L93"/>
-    <mergeCell ref="D133:AK133"/>
     <mergeCell ref="M68:P68"/>
     <mergeCell ref="C184:AK184"/>
     <mergeCell ref="M92:P92"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="C62:L62"/>
+    <mergeCell ref="C171:AK171"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="AC59:AE59"/>
     <mergeCell ref="M48:P48"/>
@@ -16730,7 +17487,6 @@
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="D194:AK194"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
@@ -16739,8 +17495,10 @@
     <mergeCell ref="B121:I121"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="Y95:AE95"/>
+    <mergeCell ref="D146:AK146"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
+    <mergeCell ref="C239:AK239"/>
     <mergeCell ref="T93:X93"/>
     <mergeCell ref="AC54:AE54"/>
     <mergeCell ref="Q90:S90"/>
@@ -16753,12 +17511,17 @@
     <mergeCell ref="AC49:AE49"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
+    <mergeCell ref="C192:AK192"/>
     <mergeCell ref="M94:P94"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="B124:I124"/>
+    <mergeCell ref="C194:AK194"/>
     <mergeCell ref="C110:AK110"/>
     <mergeCell ref="C181:AK181"/>
+    <mergeCell ref="D136:AK136"/>
     <mergeCell ref="M77:P77"/>
+    <mergeCell ref="B232:AK232"/>
+    <mergeCell ref="B150:AK150"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
